--- a/ingredient_asset_tracker.xlsx
+++ b/ingredient_asset_tracker.xlsx
@@ -85,7 +85,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Draft text for the books. It hints at target and strength in prose, never as a tag.</t>
+          <t xml:space="preserve">Draft text for the books. It hints at target and strength through a situation, never as a tag, and never names a hidden keyword (the words the player fills into the blanks).</t>
         </r>
       </text>
     </comment>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9842" uniqueCount="2330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9842" uniqueCount="2335">
   <si>
     <t xml:space="preserve">Image Asset Tracker</t>
   </si>
@@ -4177,7 +4177,7 @@
     <t xml:space="preserve">Gentle</t>
   </si>
   <si>
-    <t xml:space="preserve">Draws the mind inward, soft as moonlight. For dreams and for letting go.</t>
+    <t xml:space="preserve">Drink it by the window before bed. It loosens what the day left behind and carries you somewhere far.</t>
   </si>
   <si>
     <t xml:space="preserve">calm,dreams,intuition,release</t>
@@ -4189,7 +4189,7 @@
     <t xml:space="preserve">Strong</t>
   </si>
   <si>
-    <t xml:space="preserve">Bright and bold. Pours courage straight into the heart.</t>
+    <t xml:space="preserve">Bright and bold. Pours nerve straight into the heart.</t>
   </si>
   <si>
     <t xml:space="preserve">confidence,courage,energy,joy,success</t>
@@ -4234,7 +4234,7 @@
     <t xml:space="preserve">love, beauty, self-love, confidence</t>
   </si>
   <si>
-    <t xml:space="preserve">Softens the heart, toward others and toward yourself.</t>
+    <t xml:space="preserve">A splash on the face before the mirror, to be kinder to whoever looks back.</t>
   </si>
   <si>
     <t xml:space="preserve">beauty,confidence,love,self-love</t>
@@ -4243,7 +4243,7 @@
     <t xml:space="preserve">beginnings, intuition, growth</t>
   </si>
   <si>
-    <t xml:space="preserve">For quiet beginnings planted in the dark.</t>
+    <t xml:space="preserve">For a plan you haven't told anyone about yet.</t>
   </si>
   <si>
     <t xml:space="preserve">beginnings,growth,intuition</t>
@@ -4330,7 +4330,7 @@
     <t xml:space="preserve">calm, sleep, comfort, healing</t>
   </si>
   <si>
-    <t xml:space="preserve">Settles a busy mind toward sleep. Mild enough for children.</t>
+    <t xml:space="preserve">For the child who lies awake worrying. Mild as warm milk.</t>
   </si>
   <si>
     <t xml:space="preserve">calm,comfort,healing,sleep</t>
@@ -4363,7 +4363,7 @@
     <t xml:space="preserve">calm, intuition</t>
   </si>
   <si>
-    <t xml:space="preserve">Clears the mind's eye softly, like a blue sky.</t>
+    <t xml:space="preserve">Clears the mind's eye like a blue sky after a muddle.</t>
   </si>
   <si>
     <t xml:space="preserve">calm,intuition</t>
@@ -4372,7 +4372,7 @@
     <t xml:space="preserve">joy, friendship, beginnings</t>
   </si>
   <si>
-    <t xml:space="preserve">Simple cheer, for friendships and fresh starts.</t>
+    <t xml:space="preserve">A chain of them for a new classmate on the first day of school.</t>
   </si>
   <si>
     <t xml:space="preserve">beginnings,friendship,joy</t>
@@ -4381,7 +4381,7 @@
     <t xml:space="preserve">wonder, joy, beginnings</t>
   </si>
   <si>
-    <t xml:space="preserve">Blow it and make a wish. Childlike wonder.</t>
+    <t xml:space="preserve">Blow it and make a wish. Childlike amazement.</t>
   </si>
   <si>
     <t xml:space="preserve">beginnings,joy,wonder</t>
@@ -4402,7 +4402,7 @@
     <t xml:space="preserve">joy, wonder</t>
   </si>
   <si>
-    <t xml:space="preserve">Light, sparkling joy, like a summer cordial.</t>
+    <t xml:space="preserve">Light and sparkling, like cordial at a garden party.</t>
   </si>
   <si>
     <t xml:space="preserve">joy,wonder</t>
@@ -4435,7 +4435,7 @@
     <t xml:space="preserve">cleansing, truth, protection</t>
   </si>
   <si>
-    <t xml:space="preserve">Smoke that clears a room and leaves only the truth in it.</t>
+    <t xml:space="preserve">Smoke that clears a room and leaves no space for lies.</t>
   </si>
   <si>
     <t xml:space="preserve">cleansing,protection,truth</t>
@@ -4462,7 +4462,7 @@
     <t xml:space="preserve">dreams, beauty, intuition</t>
   </si>
   <si>
-    <t xml:space="preserve">Night-blooming. Sweet dreams and soft intuition.</t>
+    <t xml:space="preserve">Opens at night. Sweetens the hours between lying down and drifting off.</t>
   </si>
   <si>
     <t xml:space="preserve">beauty,dreams,intuition</t>
@@ -4471,7 +4471,7 @@
     <t xml:space="preserve">calm, sleep, cleansing, love, joy</t>
   </si>
   <si>
-    <t xml:space="preserve">The great soother. Calms, cleans and sweetens.</t>
+    <t xml:space="preserve">The great soother. For an evening that won't settle, a pillow, a drawer, a note to a sweetheart.</t>
   </si>
   <si>
     <t xml:space="preserve">calm,cleansing,joy,love,sleep</t>
@@ -4480,7 +4480,7 @@
     <t xml:space="preserve">calm, healing, communication</t>
   </si>
   <si>
-    <t xml:space="preserve">Calms the nerves and the tongue alike. Soothes worry.</t>
+    <t xml:space="preserve">For the nervous stammer, and the worry underneath it.</t>
   </si>
   <si>
     <t xml:space="preserve">calm,communication,healing</t>
@@ -4507,7 +4507,7 @@
     <t xml:space="preserve">memory, beauty, comfort</t>
   </si>
   <si>
-    <t xml:space="preserve">Nostalgic. Brings back sweet memories.</t>
+    <t xml:space="preserve">Smells like a grandmother's garden. Brings back the good years.</t>
   </si>
   <si>
     <t xml:space="preserve">beauty,comfort,memory</t>
@@ -4555,7 +4555,7 @@
     <t xml:space="preserve">joy, beauty</t>
   </si>
   <si>
-    <t xml:space="preserve">Bridal sweetness. Light, happy beauty.</t>
+    <t xml:space="preserve">Worn by brides. Happiness that glows.</t>
   </si>
   <si>
     <t xml:space="preserve">beauty,joy</t>
@@ -4591,7 +4591,7 @@
     <t xml:space="preserve">love, self-love, comfort, joy</t>
   </si>
   <si>
-    <t xml:space="preserve">Tender love, especially the kind you give yourself.</t>
+    <t xml:space="preserve">Scattered in a bath you run for yourself, for once.</t>
   </si>
   <si>
     <t xml:space="preserve">comfort,joy,love,self-love</t>
@@ -4600,7 +4600,7 @@
     <t xml:space="preserve">patience, growth, love</t>
   </si>
   <si>
-    <t xml:space="preserve">Love that hasn't opened yet. For patience.</t>
+    <t xml:space="preserve">For a romance that isn't ready yet. Wait for it.</t>
   </si>
   <si>
     <t xml:space="preserve">growth,love,patience</t>
@@ -4618,7 +4618,7 @@
     <t xml:space="preserve">protection, memory, cleansing, focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Sharpens memory and guards the mind.</t>
+    <t xml:space="preserve">Sharpens the mind. Students sip it before exams so nothing slips away.</t>
   </si>
   <si>
     <t xml:space="preserve">cleansing,focus,memory,protection</t>
@@ -4627,7 +4627,7 @@
     <t xml:space="preserve">protection, banishing, boundaries</t>
   </si>
   <si>
-    <t xml:space="preserve">The bitter herb of banishing. Shuts the door hard.</t>
+    <t xml:space="preserve">The bitter herb. Shuts the door hard on what isn't welcome.</t>
   </si>
   <si>
     <t xml:space="preserve">banishing,boundaries,protection</t>
@@ -4645,7 +4645,7 @@
     <t xml:space="preserve">joy, confidence</t>
   </si>
   <si>
-    <t xml:space="preserve">Turns your face toward the sun. Easy cheer.</t>
+    <t xml:space="preserve">For the shy child on stage. Turns their face toward the light.</t>
   </si>
   <si>
     <t xml:space="preserve">confidence,joy</t>
@@ -4654,7 +4654,7 @@
     <t xml:space="preserve">friendship</t>
   </si>
   <si>
-    <t xml:space="preserve">The thank-you flower. Kind to friendships.</t>
+    <t xml:space="preserve">The thank-you flower. Kind to the people you'd hate to lose.</t>
   </si>
   <si>
     <t xml:space="preserve">courage, confidence</t>
@@ -4672,7 +4672,7 @@
     <t xml:space="preserve">dreams, creativity, wonder</t>
   </si>
   <si>
-    <t xml:space="preserve">Shy dreams and quiet creativity.</t>
+    <t xml:space="preserve">For the shy artist who only draws at night.</t>
   </si>
   <si>
     <t xml:space="preserve">creativity,dreams,wonder</t>
@@ -4681,7 +4681,7 @@
     <t xml:space="preserve">beauty, calm, truth</t>
   </si>
   <si>
-    <t xml:space="preserve">Pure and still. Honesty and calm.</t>
+    <t xml:space="preserve">Still and white. For an honest answer, given quietly.</t>
   </si>
   <si>
     <t xml:space="preserve">beauty,calm,truth</t>
@@ -4717,7 +4717,7 @@
     <t xml:space="preserve">gratitude, connection, memory</t>
   </si>
   <si>
-    <t xml:space="preserve">Kept memories of loved ones. Thankful remembrance.</t>
+    <t xml:space="preserve">Pressed in a book for someone who's gone. Thank them, and feel them near.</t>
   </si>
   <si>
     <t xml:space="preserve">connection,gratitude,memory</t>
@@ -4735,7 +4735,7 @@
     <t xml:space="preserve">protection, cleansing, home</t>
   </si>
   <si>
-    <t xml:space="preserve">Guards a home's corners. Clean, stern wood.</t>
+    <t xml:space="preserve">Guards a house's corners. Clean, stern wood.</t>
   </si>
   <si>
     <t xml:space="preserve">cleansing,home,protection</t>
@@ -4744,13 +4744,13 @@
     <t xml:space="preserve">home</t>
   </si>
   <si>
-    <t xml:space="preserve">Scattered in drawers and cupboards. Makes a house a home.</t>
+    <t xml:space="preserve">Scattered in drawers and cupboards until the place smells like yours.</t>
   </si>
   <si>
     <t xml:space="preserve">endings, comfort, release</t>
   </si>
   <si>
-    <t xml:space="preserve">The mourning tree. Comforts at endings.</t>
+    <t xml:space="preserve">The mourning tree. Planted at gravesides for the ones left behind.</t>
   </si>
   <si>
     <t xml:space="preserve">comfort,endings,release</t>
@@ -4789,7 +4789,7 @@
     <t xml:space="preserve">transformation, gratitude</t>
   </si>
   <si>
-    <t xml:space="preserve">Change that comes gently, with thanks.</t>
+    <t xml:space="preserve">Let it fall. Change that comes softly, with thanks for what was.</t>
   </si>
   <si>
     <t xml:space="preserve">gratitude,transformation</t>
@@ -4798,13 +4798,13 @@
     <t xml:space="preserve">love</t>
   </si>
   <si>
-    <t xml:space="preserve">The plain, honest fruit of love.</t>
+    <t xml:space="preserve">Shared between two people, bite for bite. Plain, honest affection.</t>
   </si>
   <si>
     <t xml:space="preserve">love, home</t>
   </si>
   <si>
-    <t xml:space="preserve">Love kept in the home. A family's sweetness.</t>
+    <t xml:space="preserve">A family's sweetness, peeled in one long curl at the kitchen table.</t>
   </si>
   <si>
     <t xml:space="preserve">home,love</t>
@@ -4813,7 +4813,7 @@
     <t xml:space="preserve">play, wonder</t>
   </si>
   <si>
-    <t xml:space="preserve">Playful and a little cheeky.</t>
+    <t xml:space="preserve">Tie the stalk in a knot with your tongue. Mischief and small amazements.</t>
   </si>
   <si>
     <t xml:space="preserve">play,wonder</t>
@@ -4822,7 +4822,7 @@
     <t xml:space="preserve">joy, success</t>
   </si>
   <si>
-    <t xml:space="preserve">Abundant clusters. Success shared at a feast.</t>
+    <t xml:space="preserve">Abundant clusters. A feast for a job well done.</t>
   </si>
   <si>
     <t xml:space="preserve">joy,success</t>
@@ -4846,7 +4846,7 @@
     <t xml:space="preserve">cleansing, banishing, release</t>
   </si>
   <si>
-    <t xml:space="preserve">Cuts ties sharply. Banishing zest.</t>
+    <t xml:space="preserve">Cuts ties sharply. Sour zest that sends things packing.</t>
   </si>
   <si>
     <t xml:space="preserve">banishing,cleansing,release</t>
@@ -4855,7 +4855,7 @@
     <t xml:space="preserve">joy, abundance</t>
   </si>
   <si>
-    <t xml:space="preserve">Round, sunny cheer.</t>
+    <t xml:space="preserve">A whole orange in the toe of a stocking. Cheer, and the feeling there's enough.</t>
   </si>
   <si>
     <t xml:space="preserve">abundance,joy</t>
@@ -4888,7 +4888,7 @@
     <t xml:space="preserve">healing, love, comfort</t>
   </si>
   <si>
-    <t xml:space="preserve">Winter fruit for colds and for comfort.</t>
+    <t xml:space="preserve">Winter fruit for colds, and for being looked after.</t>
   </si>
   <si>
     <t xml:space="preserve">comfort,healing,love</t>
@@ -4897,7 +4897,7 @@
     <t xml:space="preserve">love, play, joy</t>
   </si>
   <si>
-    <t xml:space="preserve">Sweet, flirtatious love.</t>
+    <t xml:space="preserve">For a first date, or a flirt across the market stall.</t>
   </si>
   <si>
     <t xml:space="preserve">joy,love,play</t>
@@ -4906,13 +4906,13 @@
     <t xml:space="preserve">joy</t>
   </si>
   <si>
-    <t xml:space="preserve">Small, chewy happiness.</t>
+    <t xml:space="preserve">In a child's lunch tin. Small, chewy happiness.</t>
   </si>
   <si>
     <t xml:space="preserve">passion</t>
   </si>
   <si>
-    <t xml:space="preserve">Colours lips and cheeks. Flushed passion.</t>
+    <t xml:space="preserve">Colours lips and cheeks. A hot, flushed blush.</t>
   </si>
   <si>
     <t xml:space="preserve">luck, abundance, energy</t>
@@ -4927,19 +4927,19 @@
     <t xml:space="preserve">calm</t>
   </si>
   <si>
-    <t xml:space="preserve">Floral calm for frayed nerves.</t>
+    <t xml:space="preserve">For frayed nerves at tea-time.</t>
   </si>
   <si>
     <t xml:space="preserve">courage</t>
   </si>
   <si>
-    <t xml:space="preserve">Heat in the belly. Courage you can feel.</t>
+    <t xml:space="preserve">Heat in the belly. Nerve you can feel.</t>
   </si>
   <si>
     <t xml:space="preserve">love, passion, joy</t>
   </si>
   <si>
-    <t xml:space="preserve">The fragrant warmth of affection.</t>
+    <t xml:space="preserve">In the pastries you bake for someone special.</t>
   </si>
   <si>
     <t xml:space="preserve">Could be Strong (passion). Gentle chosen to separate it from Chili and Garnet.</t>
@@ -4966,7 +4966,7 @@
     <t xml:space="preserve">abundance,comfort,energy,passion,success</t>
   </si>
   <si>
-    <t xml:space="preserve">The warm spice of welcome. The feeling of coming home.</t>
+    <t xml:space="preserve">Simmered on the stove so a house smells like welcome.</t>
   </si>
   <si>
     <t xml:space="preserve">protection, abundance, home</t>
@@ -4981,7 +4981,7 @@
     <t xml:space="preserve">gratitude</t>
   </si>
   <si>
-    <t xml:space="preserve">Thankfulness after a good meal.</t>
+    <t xml:space="preserve">Chewed after a good meal, to thank the cook.</t>
   </si>
   <si>
     <t xml:space="preserve">energy, courage, success</t>
@@ -4996,7 +4996,7 @@
     <t xml:space="preserve">luck, comfort</t>
   </si>
   <si>
-    <t xml:space="preserve">Slow luck and comfort, a grated pinch at a time.</t>
+    <t xml:space="preserve">Slow fortune, a grated pinch at a time, warm as a pudding.</t>
   </si>
   <si>
     <t xml:space="preserve">comfort,luck</t>
@@ -5005,7 +5005,7 @@
     <t xml:space="preserve">luck, dreams</t>
   </si>
   <si>
-    <t xml:space="preserve">Drowsy dreams and small fortunes.</t>
+    <t xml:space="preserve">For drowsy nights that end in good news.</t>
   </si>
   <si>
     <t xml:space="preserve">dreams,luck</t>
@@ -5014,7 +5014,7 @@
     <t xml:space="preserve">success, joy, creativity</t>
   </si>
   <si>
-    <t xml:space="preserve">Precious golden threads of genius and joy.</t>
+    <t xml:space="preserve">Precious golden threads. For the masterpiece, and the delight of finishing it.</t>
   </si>
   <si>
     <t xml:space="preserve">creativity,joy,success</t>
@@ -5068,7 +5068,7 @@
     <t xml:space="preserve">joy, play</t>
   </si>
   <si>
-    <t xml:space="preserve">Joy in treat-sized pieces.</t>
+    <t xml:space="preserve">Stirred into cookies on a rainy afternoon with nothing to do.</t>
   </si>
   <si>
     <t xml:space="preserve">joy,play</t>
@@ -5077,7 +5077,7 @@
     <t xml:space="preserve">comfort, joy</t>
   </si>
   <si>
-    <t xml:space="preserve">A warm mug of comfort.</t>
+    <t xml:space="preserve">A warm mug after coming in from the cold.</t>
   </si>
   <si>
     <t xml:space="preserve">comfort,joy</t>
@@ -5104,13 +5104,13 @@
     <t xml:space="preserve">success, joy</t>
   </si>
   <si>
-    <t xml:space="preserve">A small win, sprinkled on top.</t>
+    <t xml:space="preserve">On a cake for passing a test. A small win, sprinkled on top.</t>
   </si>
   <si>
     <t xml:space="preserve">love, comfort, joy, friendship, communication</t>
   </si>
   <si>
-    <t xml:space="preserve">Sweetens words, hearts and friendships.</t>
+    <t xml:space="preserve">A spoonful sweetens anything: a word, a tea, a grudge.</t>
   </si>
   <si>
     <t xml:space="preserve">comfort,communication,friendship,joy,love</t>
@@ -5128,7 +5128,7 @@
     <t xml:space="preserve">comfort, rest, self-love</t>
   </si>
   <si>
-    <t xml:space="preserve">Nursery comfort. Tenderness toward yourself.</t>
+    <t xml:space="preserve">Nursery comfort for grown-ups who need tucking in.</t>
   </si>
   <si>
     <t xml:space="preserve">comfort,rest,self-love</t>
@@ -5137,7 +5137,7 @@
     <t xml:space="preserve">self-love, love</t>
   </si>
   <si>
-    <t xml:space="preserve">A pink bath. Self-love the body can feel.</t>
+    <t xml:space="preserve">A pink bath. Tenderness the body can feel.</t>
   </si>
   <si>
     <t xml:space="preserve">love,self-love</t>
@@ -5146,7 +5146,7 @@
     <t xml:space="preserve">love, play</t>
   </si>
   <si>
-    <t xml:space="preserve">A playful crush.</t>
+    <t xml:space="preserve">On a cupcake for a crush.</t>
   </si>
   <si>
     <t xml:space="preserve">love,play</t>
@@ -5155,7 +5155,7 @@
     <t xml:space="preserve">luck, joy</t>
   </si>
   <si>
-    <t xml:space="preserve">Birthday luck.</t>
+    <t xml:space="preserve">Birthday-cake luck for whoever blows out the candles.</t>
   </si>
   <si>
     <t xml:space="preserve">joy,luck</t>
@@ -5191,7 +5191,7 @@
     <t xml:space="preserve">grounding, growth</t>
   </si>
   <si>
-    <t xml:space="preserve">Bare feet on earth. Grounding and growth.</t>
+    <t xml:space="preserve">Bare feet on earth. Roots, and green things coming up.</t>
   </si>
   <si>
     <t xml:space="preserve">grounding,growth</t>
@@ -5200,7 +5200,7 @@
     <t xml:space="preserve">protection, home, endings</t>
   </si>
   <si>
-    <t xml:space="preserve">From the home fire. Protects, and closes what is finished.</t>
+    <t xml:space="preserve">From the household fire. Guards, and closes what is finished.</t>
   </si>
   <si>
     <t xml:space="preserve">endings,home,protection</t>
@@ -5221,7 +5221,7 @@
     <t xml:space="preserve">success, confidence, joy</t>
   </si>
   <si>
-    <t xml:space="preserve">Shimmer on the skin. Confidence people can see.</t>
+    <t xml:space="preserve">Shimmer on the skin that makes people look twice.</t>
   </si>
   <si>
     <t xml:space="preserve">confidence,joy,success</t>
@@ -5230,7 +5230,7 @@
     <t xml:space="preserve">intuition, wonder, dreams</t>
   </si>
   <si>
-    <t xml:space="preserve">Moonlit shimmer for dreamers.</t>
+    <t xml:space="preserve">Brushed on the eyelids of people who see things in their sleep.</t>
   </si>
   <si>
     <t xml:space="preserve">dreams,intuition,wonder</t>
@@ -5239,7 +5239,7 @@
     <t xml:space="preserve">wonder, dreams, play</t>
   </si>
   <si>
-    <t xml:space="preserve">Starry play.</t>
+    <t xml:space="preserve">Shaken over a child's bedroom on a starless night.</t>
   </si>
   <si>
     <t xml:space="preserve">dreams,play,wonder</t>
@@ -5248,7 +5248,7 @@
     <t xml:space="preserve">play, self-love</t>
   </si>
   <si>
-    <t xml:space="preserve">Sparkly self-love.</t>
+    <t xml:space="preserve">Sparkle for anyone who's been told to tone it down.</t>
   </si>
   <si>
     <t xml:space="preserve">play,self-love</t>
@@ -5257,7 +5257,7 @@
     <t xml:space="preserve">play, creativity</t>
   </si>
   <si>
-    <t xml:space="preserve">Messy, playful creativity.</t>
+    <t xml:space="preserve">Gets everywhere, like a good idea.</t>
   </si>
   <si>
     <t xml:space="preserve">creativity,play</t>
@@ -5266,7 +5266,7 @@
     <t xml:space="preserve">comfort, calm, joy</t>
   </si>
   <si>
-    <t xml:space="preserve">Warm, golden calm.</t>
+    <t xml:space="preserve">Golden and warm, like sitting by the fire with an old dog.</t>
   </si>
   <si>
     <t xml:space="preserve">calm,comfort,joy</t>
@@ -5293,7 +5293,7 @@
     <t xml:space="preserve">release, protection, healing, intuition</t>
   </si>
   <si>
-    <t xml:space="preserve">Bitter resin for deep healing and release.</t>
+    <t xml:space="preserve">Bitter resin for deep mending and letting go.</t>
   </si>
   <si>
     <t xml:space="preserve">healing,intuition,protection,release</t>
@@ -5302,7 +5302,7 @@
     <t xml:space="preserve">grounding, attraction</t>
   </si>
   <si>
-    <t xml:space="preserve">Earthy, heady musk. Attraction you can smell.</t>
+    <t xml:space="preserve">Earthy, heady musk. People drift closer and don't know why.</t>
   </si>
   <si>
     <t xml:space="preserve">attraction,grounding</t>
@@ -5311,7 +5311,7 @@
     <t xml:space="preserve">calm, intuition, rest</t>
   </si>
   <si>
-    <t xml:space="preserve">Meditative calm.</t>
+    <t xml:space="preserve">Burned before meditation, for sitting still.</t>
   </si>
   <si>
     <t xml:space="preserve">calm,intuition,rest</t>
@@ -5320,7 +5320,7 @@
     <t xml:space="preserve">communication, friendship, calm</t>
   </si>
   <si>
-    <t xml:space="preserve">Calm words between friends.</t>
+    <t xml:space="preserve">For making up with a friend over tea.</t>
   </si>
   <si>
     <t xml:space="preserve">calm,communication,friendship</t>
@@ -5329,7 +5329,7 @@
     <t xml:space="preserve">intuition, dreams, calm</t>
   </si>
   <si>
-    <t xml:space="preserve">Calm sleep and true dreams.</t>
+    <t xml:space="preserve">Under the pillow of a restless sleeper who sees riddles in the night.</t>
   </si>
   <si>
     <t xml:space="preserve">calm,dreams,intuition</t>
@@ -5338,7 +5338,7 @@
     <t xml:space="preserve">calm, communication, release</t>
   </si>
   <si>
-    <t xml:space="preserve">Sea-calm courage to speak.</t>
+    <t xml:space="preserve">For saying the thing you've swallowed for years, then letting it go out with the tide.</t>
   </si>
   <si>
     <t xml:space="preserve">calm,communication,release</t>
@@ -5359,7 +5359,7 @@
     <t xml:space="preserve">calm, communication, comfort</t>
   </si>
   <si>
-    <t xml:space="preserve">Soft-spoken comfort.</t>
+    <t xml:space="preserve">For the quiet one who needs to be heard, softly.</t>
   </si>
   <si>
     <t xml:space="preserve">calm,comfort,communication</t>
@@ -5377,7 +5377,7 @@
     <t xml:space="preserve">abundance, joy, success, luck</t>
   </si>
   <si>
-    <t xml:space="preserve">The merchant's stone. Draws money and success.</t>
+    <t xml:space="preserve">The merchant's stone. Draws money to the till.</t>
   </si>
   <si>
     <t xml:space="preserve">abundance,joy,luck,success</t>
@@ -5395,7 +5395,7 @@
     <t xml:space="preserve">focus, creativity</t>
   </si>
   <si>
-    <t xml:space="preserve">An orderly mind.</t>
+    <t xml:space="preserve">For a child's messy homework. Puts thoughts in neat rows.</t>
   </si>
   <si>
     <t xml:space="preserve">creativity,focus</t>
@@ -5431,7 +5431,7 @@
     <t xml:space="preserve">calm, patience</t>
   </si>
   <si>
-    <t xml:space="preserve">Patience and calm.</t>
+    <t xml:space="preserve">For the long wait by the telephone.</t>
   </si>
   <si>
     <t xml:space="preserve">calm,patience</t>
@@ -5440,7 +5440,7 @@
     <t xml:space="preserve">abundance, harmony, friendship</t>
   </si>
   <si>
-    <t xml:space="preserve">Harmony in the household and among friends.</t>
+    <t xml:space="preserve">Keeps a household and its friends getting along.</t>
   </si>
   <si>
     <t xml:space="preserve">abundance,friendship,harmony</t>
@@ -5467,7 +5467,7 @@
     <t xml:space="preserve">transformation, protection, travel</t>
   </si>
   <si>
-    <t xml:space="preserve">Protects travellers through great change.</t>
+    <t xml:space="preserve">Guards those on long roads through great change.</t>
   </si>
   <si>
     <t xml:space="preserve">protection,transformation,travel</t>
@@ -5476,7 +5476,7 @@
     <t xml:space="preserve">intuition, dreams, beginnings, self-love</t>
   </si>
   <si>
-    <t xml:space="preserve">New beginnings, intuition, softness toward yourself.</t>
+    <t xml:space="preserve">For a new chapter, and for trusting yourself in it.</t>
   </si>
   <si>
     <t xml:space="preserve">beginnings,dreams,intuition,self-love</t>
@@ -5485,13 +5485,13 @@
     <t xml:space="preserve">growth, connection</t>
   </si>
   <si>
-    <t xml:space="preserve">Patient inner growth. Roots for the heart.</t>
+    <t xml:space="preserve">For a slow friendship or a garden just planted. It takes its time.</t>
   </si>
   <si>
     <t xml:space="preserve">protection, release, truth</t>
   </si>
   <si>
-    <t xml:space="preserve">Black glass that shows the truth.</t>
+    <t xml:space="preserve">Black glass that shows things as they are.</t>
   </si>
   <si>
     <t xml:space="preserve">protection,release,truth</t>
@@ -5500,7 +5500,7 @@
     <t xml:space="preserve">beauty, self-love, calm</t>
   </si>
   <si>
-    <t xml:space="preserve">Lustrous, calm beauty.</t>
+    <t xml:space="preserve">Lustrous and still. Beauty that doesn't need to try.</t>
   </si>
   <si>
     <t xml:space="preserve">beauty,calm,self-love</t>
@@ -5509,7 +5509,7 @@
     <t xml:space="preserve">growth, joy</t>
   </si>
   <si>
-    <t xml:space="preserve">Fresh green growth and joy.</t>
+    <t xml:space="preserve">For the first good week after a hard winter.</t>
   </si>
   <si>
     <t xml:space="preserve">growth,joy</t>
@@ -5518,7 +5518,7 @@
     <t xml:space="preserve">abundance, success, confidence</t>
   </si>
   <si>
-    <t xml:space="preserve">Fool's gold. Plenty and success.</t>
+    <t xml:space="preserve">Fool's gold. Plenty, and the nerve to ask for more.</t>
   </si>
   <si>
     <t xml:space="preserve">abundance,confidence,success</t>
@@ -5536,7 +5536,7 @@
     <t xml:space="preserve">self-love, love, comfort</t>
   </si>
   <si>
-    <t xml:space="preserve">Love's gentlest stone.</t>
+    <t xml:space="preserve">Hold it after a cruel word, whether someone else said it or you did.</t>
   </si>
   <si>
     <t xml:space="preserve">comfort,love,self-love</t>
@@ -5569,7 +5569,7 @@
     <t xml:space="preserve">courage, confidence, success</t>
   </si>
   <si>
-    <t xml:space="preserve">Courage and confidence.</t>
+    <t xml:space="preserve">A striped stone for walking into the room first.</t>
   </si>
   <si>
     <t xml:space="preserve">confidence,courage,success</t>
@@ -5578,7 +5578,7 @@
     <t xml:space="preserve">grounding, patience, calm</t>
   </si>
   <si>
-    <t xml:space="preserve">The patience of water-worn stone.</t>
+    <t xml:space="preserve">Pocketed by people who rush. It slows the step.</t>
   </si>
   <si>
     <t xml:space="preserve">calm,grounding,patience</t>
@@ -5596,7 +5596,7 @@
     <t xml:space="preserve">love, calm, friendship</t>
   </si>
   <si>
-    <t xml:space="preserve">Peace and gentle love.</t>
+    <t xml:space="preserve">Tucked into a letter to make peace after a quarrel.</t>
   </si>
   <si>
     <t xml:space="preserve">calm,friendship,love</t>
@@ -5611,7 +5611,7 @@
     <t xml:space="preserve">abundance, home, friendship</t>
   </si>
   <si>
-    <t xml:space="preserve">Hive plenty for the home.</t>
+    <t xml:space="preserve">Hive plenty for a busy, crowded kitchen.</t>
   </si>
   <si>
     <t xml:space="preserve">abundance,friendship,home</t>
@@ -5665,7 +5665,7 @@
     <t xml:space="preserve">calm, beauty, communication</t>
   </si>
   <si>
-    <t xml:space="preserve">The soft voice of the sea.</t>
+    <t xml:space="preserve">Hold it to your ear before a hard conversation, and let the sea speak first.</t>
   </si>
   <si>
     <t xml:space="preserve">beauty,calm,communication</t>
@@ -5701,7 +5701,7 @@
     <t xml:space="preserve">beauty, love</t>
   </si>
   <si>
-    <t xml:space="preserve">Soft grace and love.</t>
+    <t xml:space="preserve">Soft grace, and two necks bent into a heart.</t>
   </si>
   <si>
     <t xml:space="preserve">beauty,love</t>
@@ -5710,7 +5710,7 @@
     <t xml:space="preserve">wonder, calm</t>
   </si>
   <si>
-    <t xml:space="preserve">A small sign of comfort.</t>
+    <t xml:space="preserve">Found on the path after a bad day, as if someone left it there for you.</t>
   </si>
   <si>
     <t xml:space="preserve">calm,wonder</t>
@@ -5719,13 +5719,13 @@
     <t xml:space="preserve">home, abundance, comfort</t>
   </si>
   <si>
-    <t xml:space="preserve">The feeling of a safe, warm nest.</t>
+    <t xml:space="preserve">For the first night in a new room, when nowhere feels like yours yet.</t>
   </si>
   <si>
     <t xml:space="preserve">focus, success, protection</t>
   </si>
   <si>
-    <t xml:space="preserve">Polished duty. Focus and protection.</t>
+    <t xml:space="preserve">Polished duty. A uniform's button that stands guard.</t>
   </si>
   <si>
     <t xml:space="preserve">focus,protection,success</t>
@@ -5734,7 +5734,7 @@
     <t xml:space="preserve">play, joy, creativity</t>
   </si>
   <si>
-    <t xml:space="preserve">Childlike play.</t>
+    <t xml:space="preserve">Off a child's coat. Sewn on, they make grown-ups silly again.</t>
   </si>
   <si>
     <t xml:space="preserve">creativity,joy,play</t>
@@ -5752,25 +5752,25 @@
     <t xml:space="preserve">love, self-love</t>
   </si>
   <si>
-    <t xml:space="preserve">A love token.</t>
+    <t xml:space="preserve">Sewn inside a sleeve, over the pulse, where only the wearer knows.</t>
   </si>
   <si>
     <t xml:space="preserve">creativity, self-love</t>
   </si>
   <si>
-    <t xml:space="preserve">The odd one out, loved anyway.</t>
+    <t xml:space="preserve">For the one who never quite matches, and is better for it.</t>
   </si>
   <si>
     <t xml:space="preserve">creativity,self-love</t>
   </si>
   <si>
-    <t xml:space="preserve">A quiet keepsake of fond friendship.</t>
+    <t xml:space="preserve">Off an old friend's cardigan. Keeps two people fond across the years.</t>
   </si>
   <si>
     <t xml:space="preserve">play, luck</t>
   </si>
   <si>
-    <t xml:space="preserve">A game piece's luck.</t>
+    <t xml:space="preserve">Lost from a board game and found again. Good for games of chance.</t>
   </si>
   <si>
     <t xml:space="preserve">luck,play</t>
@@ -5779,7 +5779,7 @@
     <t xml:space="preserve">wonder, luck, joy</t>
   </si>
   <si>
-    <t xml:space="preserve">Wish upon it.</t>
+    <t xml:space="preserve">Every child's first wish was made on one of these.</t>
   </si>
   <si>
     <t xml:space="preserve">joy,luck,wonder</t>
@@ -5788,7 +5788,7 @@
     <t xml:space="preserve">beauty, creativity</t>
   </si>
   <si>
-    <t xml:space="preserve">Old-fashioned charm and craft.</t>
+    <t xml:space="preserve">From a grandmother's tin. Makes an old dress feel new.</t>
   </si>
   <si>
     <t xml:space="preserve">beauty,creativity</t>
@@ -5797,7 +5797,7 @@
     <t xml:space="preserve">banishing, protection, endings</t>
   </si>
   <si>
-    <t xml:space="preserve">Binds and banishes.</t>
+    <t xml:space="preserve">Wound tight round what must not come back.</t>
   </si>
   <si>
     <t xml:space="preserve">Same meaning as Black ink. The spell type decides which medium.</t>
@@ -5809,7 +5809,7 @@
     <t xml:space="preserve">truth, memory, calm</t>
   </si>
   <si>
-    <t xml:space="preserve">Truth and calm memory.</t>
+    <t xml:space="preserve">Stitched into a diary's spine so it stays honest.</t>
   </si>
   <si>
     <t xml:space="preserve">calm,memory,truth</t>
@@ -5830,7 +5830,7 @@
     <t xml:space="preserve">luck, abundance, growth</t>
   </si>
   <si>
-    <t xml:space="preserve">Growth and luck.</t>
+    <t xml:space="preserve">Tied round a seed packet or a purse. Things come up.</t>
   </si>
   <si>
     <t xml:space="preserve">abundance,growth,luck</t>
@@ -5839,7 +5839,7 @@
     <t xml:space="preserve">balance, release, endings</t>
   </si>
   <si>
-    <t xml:space="preserve">Balance and quiet endings.</t>
+    <t xml:space="preserve">For closing a chapter without slamming the book.</t>
   </si>
   <si>
     <t xml:space="preserve">balance,endings,release</t>
@@ -5848,7 +5848,7 @@
     <t xml:space="preserve">creativity, energy, joy</t>
   </si>
   <si>
-    <t xml:space="preserve">Creative energy.</t>
+    <t xml:space="preserve">A bright creative spark, stitched in.</t>
   </si>
   <si>
     <t xml:space="preserve">creativity,energy,joy</t>
@@ -5857,7 +5857,7 @@
     <t xml:space="preserve">self-love, love, friendship</t>
   </si>
   <si>
-    <t xml:space="preserve">Love and friendship.</t>
+    <t xml:space="preserve">For bracelets swapped between friends, and kind notes to yourself.</t>
   </si>
   <si>
     <t xml:space="preserve">friendship,love,self-love</t>
@@ -5866,7 +5866,7 @@
     <t xml:space="preserve">intuition, transformation, wonder</t>
   </si>
   <si>
-    <t xml:space="preserve">Intuition and change.</t>
+    <t xml:space="preserve">Braided into a witch's ladder for a life about to change.</t>
   </si>
   <si>
     <t xml:space="preserve">Same meaning as Violet ink. The spell type decides which medium.</t>
@@ -5878,7 +5878,7 @@
     <t xml:space="preserve">play, creativity, friendship</t>
   </si>
   <si>
-    <t xml:space="preserve">Friendship-bracelet play.</t>
+    <t xml:space="preserve">Bracelet threads swapped at summer camp.</t>
   </si>
   <si>
     <t xml:space="preserve">creativity,friendship,play</t>
@@ -5887,7 +5887,7 @@
     <t xml:space="preserve">passion, courage, energy, love</t>
   </si>
   <si>
-    <t xml:space="preserve">Passion and nerve.</t>
+    <t xml:space="preserve">Tied round the wrist before a dare.</t>
   </si>
   <si>
     <t xml:space="preserve">Same meaning as Red ink, Red paint. The spell type decides which medium.</t>
@@ -5899,7 +5899,7 @@
     <t xml:space="preserve">intuition, dreams, connection, calm</t>
   </si>
   <si>
-    <t xml:space="preserve">Dreams and quiet connection.</t>
+    <t xml:space="preserve">Stitch a dream into a pillowcase so it comes back.</t>
   </si>
   <si>
     <t xml:space="preserve">Same meaning as Silver ink. The spell type decides which medium.</t>
@@ -5911,7 +5911,7 @@
     <t xml:space="preserve">cleansing, protection, calm, beginnings</t>
   </si>
   <si>
-    <t xml:space="preserve">Purity and protection.</t>
+    <t xml:space="preserve">Clean and plain. Tied round a newborn's cot.</t>
   </si>
   <si>
     <t xml:space="preserve">beginnings,calm,cleansing,protection</t>
@@ -5920,7 +5920,7 @@
     <t xml:space="preserve">joy, communication, focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Cheerful words.</t>
+    <t xml:space="preserve">Sewn into a speaker's collar. Bright, clear words.</t>
   </si>
   <si>
     <t xml:space="preserve">communication,focus,joy</t>
@@ -5929,7 +5929,7 @@
     <t xml:space="preserve">beauty, joy, attraction</t>
   </si>
   <si>
-    <t xml:space="preserve">Pretty, easy attraction.</t>
+    <t xml:space="preserve">Pretty bows that catch the eye.</t>
   </si>
   <si>
     <t xml:space="preserve">attraction,beauty,joy</t>
@@ -5947,7 +5947,7 @@
     <t xml:space="preserve">creativity, connection, patience</t>
   </si>
   <si>
-    <t xml:space="preserve">Patient connections.</t>
+    <t xml:space="preserve">Ties people together, one slow stitch at a time.</t>
   </si>
   <si>
     <t xml:space="preserve">connection,creativity,patience</t>
@@ -5962,7 +5962,7 @@
     <t xml:space="preserve">play, creativity, joy</t>
   </si>
   <si>
-    <t xml:space="preserve">Pieces sewn together. Creative joy for a home.</t>
+    <t xml:space="preserve">Pieces sewn together into something cheerful for a home.</t>
   </si>
   <si>
     <t xml:space="preserve">intuition</t>
@@ -5983,19 +5983,19 @@
     <t xml:space="preserve">beginnings</t>
   </si>
   <si>
-    <t xml:space="preserve">Wand wood of fresh starts.</t>
+    <t xml:space="preserve">Wand wood for someone starting over.</t>
   </si>
   <si>
     <t xml:space="preserve">Same meaning as Birch wood. The spell type decides which medium.</t>
   </si>
   <si>
-    <t xml:space="preserve">Carving wood of fresh starts.</t>
+    <t xml:space="preserve">Carving wood for someone starting over.</t>
   </si>
   <si>
     <t xml:space="preserve">Same meaning as Birch branch. The spell type decides which medium.</t>
   </si>
   <si>
-    <t xml:space="preserve">A thorny staff. Courage to stand your ground.</t>
+    <t xml:space="preserve">A thorny staff. Nerve to stand your ground.</t>
   </si>
   <si>
     <t xml:space="preserve">memory, creativity, intuition</t>
@@ -6010,7 +6010,7 @@
     <t xml:space="preserve">courage, grounding, protection</t>
   </si>
   <si>
-    <t xml:space="preserve">Steadfast, rooted protection.</t>
+    <t xml:space="preserve">Steadfast and rooted. The wood that stands guard.</t>
   </si>
   <si>
     <t xml:space="preserve">courage,grounding,protection</t>
@@ -6028,13 +6028,13 @@
     <t xml:space="preserve">opportunity,play,travel</t>
   </si>
   <si>
-    <t xml:space="preserve">Bends and listens. Gentle intuition.</t>
+    <t xml:space="preserve">Wand wood that bends and listens.</t>
   </si>
   <si>
     <t xml:space="preserve">release</t>
   </si>
   <si>
-    <t xml:space="preserve">Bends and lets go.</t>
+    <t xml:space="preserve">Carving wood that bends and lets go.</t>
   </si>
   <si>
     <t xml:space="preserve">Base for Talisman.</t>
@@ -6043,7 +6043,7 @@
     <t xml:space="preserve">luck</t>
   </si>
   <si>
-    <t xml:space="preserve">A little luck that grows.</t>
+    <t xml:space="preserve">A little fortune that grows.</t>
   </si>
   <si>
     <t xml:space="preserve">Base for Hand Mirror.</t>
@@ -6073,7 +6073,7 @@
     <t xml:space="preserve">protection, grounding</t>
   </si>
   <si>
-    <t xml:space="preserve">Grounding iron.</t>
+    <t xml:space="preserve">Heavy iron dust that keeps feet on the floor.</t>
   </si>
   <si>
     <t xml:space="preserve">grounding,protection</t>
@@ -6088,13 +6088,13 @@
     <t xml:space="preserve">boundaries</t>
   </si>
   <si>
-    <t xml:space="preserve">Firm personal boundaries.</t>
+    <t xml:space="preserve">Pinned to a collar. Thus far, and no further.</t>
   </si>
   <si>
     <t xml:space="preserve">memory, self-love</t>
   </si>
   <si>
-    <t xml:space="preserve">A kept memory.</t>
+    <t xml:space="preserve">Keeps a face close, and reminds you that you were loved.</t>
   </si>
   <si>
     <t xml:space="preserve">memory,self-love</t>
@@ -6103,16 +6103,16 @@
     <t xml:space="preserve">creativity</t>
   </si>
   <si>
-    <t xml:space="preserve">Creativity in the hand.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Words and ideas.</t>
+    <t xml:space="preserve">Makes the hand eager to make things.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For the writer stuck on the first line.</t>
   </si>
   <si>
     <t xml:space="preserve">intuition, calm, communication</t>
   </si>
   <si>
-    <t xml:space="preserve">Quiet intuition and gentle words.</t>
+    <t xml:space="preserve">Strung on a bracelet, it nudges you to listen before you speak.</t>
   </si>
   <si>
     <t xml:space="preserve">calm,communication,intuition</t>
@@ -6130,7 +6130,7 @@
     <t xml:space="preserve">comfort, calm, travel</t>
   </si>
   <si>
-    <t xml:space="preserve">Cosy calm, even far from home.</t>
+    <t xml:space="preserve">For someone far from home. Tastes like their own kitchen.</t>
   </si>
   <si>
     <t xml:space="preserve">calm,comfort,travel</t>
@@ -6139,7 +6139,7 @@
     <t xml:space="preserve">joy, beginnings</t>
   </si>
   <si>
-    <t xml:space="preserve">Rings in beginnings.</t>
+    <t xml:space="preserve">Rings in the first day of anything.</t>
   </si>
   <si>
     <t xml:space="preserve">beginnings,joy</t>
@@ -6160,6 +6160,9 @@
     <t xml:space="preserve">A roll of chance. Bold luck.</t>
   </si>
   <si>
+    <t xml:space="preserve">Write a name in it, then burn the page.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Same meaning as Black thread. The spell type decides which medium.</t>
   </si>
   <si>
@@ -6169,12 +6172,21 @@
     <t xml:space="preserve">Same meaning as Gold thread, Gold paint. The spell type decides which medium.</t>
   </si>
   <si>
+    <t xml:space="preserve">For a letter that means every word and burns a little.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Same meaning as Red thread, Red paint. The spell type decides which medium.</t>
   </si>
   <si>
+    <t xml:space="preserve">Write a dream down in it before it fades.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Same meaning as Silver thread. The spell type decides which medium.</t>
   </si>
   <si>
+    <t xml:space="preserve">For a letter to the person you're becoming.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Same meaning as Purple thread. The spell type decides which medium.</t>
   </si>
   <si>
@@ -6182,6 +6194,9 @@
   </si>
   <si>
     <t xml:space="preserve">Same meaning as Gold thread, Gold ink. The spell type decides which medium.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bold strokes on a door or a drum.</t>
   </si>
   <si>
     <t xml:space="preserve">Same meaning as Red thread, Red ink. The spell type decides which medium.</t>
@@ -7966,10 +7981,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>2234</v>
+        <v>2239</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>2235</v>
+        <v>2240</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>1041</v>
@@ -7990,13 +8005,13 @@
         <v>10</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>2236</v>
+        <v>2241</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>2237</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8008,13 +8023,13 @@
         <v>8</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>2238</v>
+        <v>2243</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>2237</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8026,13 +8041,13 @@
         <v>9</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>2239</v>
+        <v>2244</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>2237</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8044,13 +8059,13 @@
         <v>7</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>2240</v>
+        <v>2245</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>2237</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8062,13 +8077,13 @@
         <v>13</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>2241</v>
+        <v>2246</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>2237</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8080,13 +8095,13 @@
         <v>8</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>2242</v>
+        <v>2247</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>2237</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8098,13 +8113,13 @@
         <v>11</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>2243</v>
+        <v>2248</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>2237</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8116,13 +8131,13 @@
         <v>10</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>2244</v>
+        <v>2249</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>2237</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8134,13 +8149,13 @@
         <v>11</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>2245</v>
+        <v>2250</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>2237</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8152,13 +8167,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>2246</v>
+        <v>2251</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>2237</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8170,13 +8185,13 @@
         <v>6</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>2247</v>
+        <v>2252</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>2237</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8188,13 +8203,13 @@
         <v>12</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>2248</v>
+        <v>2253</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>2237</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8206,13 +8221,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>2249</v>
+        <v>2254</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>2237</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8224,13 +8239,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>2250</v>
+        <v>2255</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>2237</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8242,13 +8257,13 @@
         <v>12</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>2251</v>
+        <v>2256</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>2237</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8260,13 +8275,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>2252</v>
+        <v>2257</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>2237</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8278,13 +8293,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>2253</v>
+        <v>2258</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>2237</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8296,13 +8311,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>2254</v>
+        <v>2259</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>2237</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8314,13 +8329,13 @@
         <v>10</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>2255</v>
+        <v>2260</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>2237</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8332,13 +8347,13 @@
         <v>12</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>2256</v>
+        <v>2261</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>2237</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8350,13 +8365,13 @@
         <v>7</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>2257</v>
+        <v>2262</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>2237</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8368,13 +8383,13 @@
         <v>9</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>2258</v>
+        <v>2263</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>2237</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8386,13 +8401,13 @@
         <v>9</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>2259</v>
+        <v>2264</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>2237</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8404,13 +8419,13 @@
         <v>8</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>2260</v>
+        <v>2265</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>2237</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8422,13 +8437,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>2261</v>
+        <v>2266</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>2237</v>
+        <v>2242</v>
       </c>
     </row>
   </sheetData>
@@ -8467,10 +8482,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>2262</v>
+        <v>2267</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>2263</v>
+        <v>2268</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>1041</v>
@@ -8484,13 +8499,13 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>2264</v>
+        <v>2269</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>2265</v>
+        <v>2270</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>2266</v>
+        <v>2271</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>6</v>
@@ -8499,13 +8514,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>2267</v>
+        <v>2272</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>2265</v>
+        <v>2270</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>2268</v>
+        <v>2273</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>6</v>
@@ -8514,13 +8529,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>2269</v>
+        <v>2274</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>2265</v>
+        <v>2270</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>2270</v>
+        <v>2275</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>6</v>
@@ -8529,13 +8544,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>2271</v>
+        <v>2276</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2265</v>
+        <v>2270</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>2272</v>
+        <v>2277</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>6</v>
@@ -8544,13 +8559,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>2273</v>
+        <v>2278</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2265</v>
+        <v>2270</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>2274</v>
+        <v>2279</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>6</v>
@@ -8559,13 +8574,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>2275</v>
+        <v>2280</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>2265</v>
+        <v>2270</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>2276</v>
+        <v>2281</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>6</v>
@@ -8574,13 +8589,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>2277</v>
+        <v>2282</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>2265</v>
+        <v>2270</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>2278</v>
+        <v>2283</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>6</v>
@@ -8589,13 +8604,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>2279</v>
+        <v>2284</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2265</v>
+        <v>2270</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>2280</v>
+        <v>2285</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>6</v>
@@ -8604,13 +8619,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>2281</v>
+        <v>2286</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>1058</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>2282</v>
+        <v>2287</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>6</v>
@@ -8619,13 +8634,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>2283</v>
+        <v>2288</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>1058</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>2284</v>
+        <v>2289</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>6</v>
@@ -8634,13 +8649,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>2285</v>
+        <v>2290</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>1058</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>2286</v>
+        <v>2291</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>6</v>
@@ -8649,13 +8664,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>2287</v>
+        <v>2292</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>1058</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>2288</v>
+        <v>2293</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>6</v>
@@ -8664,13 +8679,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>2289</v>
+        <v>2294</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>1058</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>2290</v>
+        <v>2295</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>6</v>
@@ -8679,13 +8694,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>2291</v>
+        <v>2296</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>1058</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>2292</v>
+        <v>2297</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>6</v>
@@ -8694,13 +8709,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>2293</v>
+        <v>2298</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>1058</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>2294</v>
+        <v>2299</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>6</v>
@@ -8709,13 +8724,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>2295</v>
+        <v>2300</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>1058</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>2296</v>
+        <v>2301</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>6</v>
@@ -8724,13 +8739,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>2297</v>
+        <v>2302</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>1067</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>2298</v>
+        <v>2303</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>6</v>
@@ -8739,13 +8754,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>2299</v>
+        <v>2304</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>1045</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>2300</v>
+        <v>2305</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>6</v>
@@ -8754,13 +8769,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>2301</v>
+        <v>2306</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>1045</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>2302</v>
+        <v>2307</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>6</v>
@@ -8769,13 +8784,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>2303</v>
+        <v>2308</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>2304</v>
+        <v>2309</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>2305</v>
+        <v>2310</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>6</v>
@@ -8784,13 +8799,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>2306</v>
+        <v>2311</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>2304</v>
+        <v>2309</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>2307</v>
+        <v>2312</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>6</v>
@@ -8799,13 +8814,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>2308</v>
+        <v>2313</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>2304</v>
+        <v>2309</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>2309</v>
+        <v>2314</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>6</v>
@@ -8814,13 +8829,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>2310</v>
+        <v>2315</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>2304</v>
+        <v>2309</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>2311</v>
+        <v>2316</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>6</v>
@@ -8829,13 +8844,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>2312</v>
+        <v>2317</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>2304</v>
+        <v>2309</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>2313</v>
+        <v>2318</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>6</v>
@@ -8844,13 +8859,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
-        <v>2314</v>
+        <v>2319</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>2304</v>
+        <v>2309</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>2315</v>
+        <v>2320</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>6</v>
@@ -8859,13 +8874,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>2316</v>
+        <v>2321</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>2277</v>
+        <v>2282</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>2317</v>
+        <v>2322</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>6</v>
@@ -8874,13 +8889,13 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
-        <v>2318</v>
+        <v>2323</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>2277</v>
+        <v>2282</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>2319</v>
+        <v>2324</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>6</v>
@@ -8889,13 +8904,13 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>2320</v>
+        <v>2325</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>2277</v>
+        <v>2282</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>2321</v>
+        <v>2326</v>
       </c>
       <c r="D29" s="11" t="s">
         <v>6</v>
@@ -8904,13 +8919,13 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>2322</v>
+        <v>2327</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>2277</v>
+        <v>2282</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>2323</v>
+        <v>2328</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>6</v>
@@ -8919,13 +8934,13 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>2324</v>
+        <v>2329</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>2277</v>
+        <v>2282</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>2325</v>
+        <v>2330</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>6</v>
@@ -8934,13 +8949,13 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
-        <v>2326</v>
+        <v>2331</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>2277</v>
+        <v>2282</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>2327</v>
+        <v>2332</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>6</v>
@@ -8949,13 +8964,13 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>2328</v>
+        <v>2333</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>2277</v>
+        <v>2282</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>2329</v>
+        <v>2334</v>
       </c>
       <c r="D33" s="11" t="s">
         <v>6</v>
@@ -48526,7 +48541,7 @@
         <v>1340</v>
       </c>
       <c r="F252" s="13" t="s">
-        <v>1877</v>
+        <v>1998</v>
       </c>
       <c r="G252" s="12" t="n">
         <f aca="false">IF(OR(D252="—",D252="",K252=""),"",COUNTIF($J$2:$J$259,J252)-1)</f>
@@ -48534,7 +48549,7 @@
       </c>
       <c r="H252" s="14"/>
       <c r="I252" s="13" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="J252" s="5" t="str">
         <f aca="false">K252&amp;"|"&amp;D252&amp;"|"&amp;E252</f>
@@ -48565,7 +48580,7 @@
         <v>1340</v>
       </c>
       <c r="F253" s="13" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="G253" s="12" t="n">
         <f aca="false">IF(OR(D253="—",D253="",K253=""),"",COUNTIF($J$2:$J$259,J253)-1)</f>
@@ -48573,7 +48588,7 @@
       </c>
       <c r="H253" s="14"/>
       <c r="I253" s="13" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="J253" s="5" t="str">
         <f aca="false">K253&amp;"|"&amp;D253&amp;"|"&amp;E253</f>
@@ -48637,7 +48652,7 @@
         <v>1340</v>
       </c>
       <c r="F255" s="13" t="s">
-        <v>1907</v>
+        <v>2002</v>
       </c>
       <c r="G255" s="12" t="n">
         <f aca="false">IF(OR(D255="—",D255="",K255=""),"",COUNTIF($J$2:$J$259,J255)-1)</f>
@@ -48645,7 +48660,7 @@
       </c>
       <c r="H255" s="14"/>
       <c r="I255" s="13" t="s">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="J255" s="5" t="str">
         <f aca="false">K255&amp;"|"&amp;D255&amp;"|"&amp;E255</f>
@@ -48676,7 +48691,7 @@
         <v>1336</v>
       </c>
       <c r="F256" s="13" t="s">
-        <v>1911</v>
+        <v>2004</v>
       </c>
       <c r="G256" s="12" t="n">
         <f aca="false">IF(OR(D256="—",D256="",K256=""),"",COUNTIF($J$2:$J$259,J256)-1)</f>
@@ -48684,7 +48699,7 @@
       </c>
       <c r="H256" s="14"/>
       <c r="I256" s="13" t="s">
-        <v>2002</v>
+        <v>2005</v>
       </c>
       <c r="J256" s="5" t="str">
         <f aca="false">K256&amp;"|"&amp;D256&amp;"|"&amp;E256</f>
@@ -48715,7 +48730,7 @@
         <v>1340</v>
       </c>
       <c r="F257" s="13" t="s">
-        <v>1900</v>
+        <v>2006</v>
       </c>
       <c r="G257" s="12" t="n">
         <f aca="false">IF(OR(D257="—",D257="",K257=""),"",COUNTIF($J$2:$J$259,J257)-1)</f>
@@ -48723,7 +48738,7 @@
       </c>
       <c r="H257" s="14"/>
       <c r="I257" s="13" t="s">
-        <v>2003</v>
+        <v>2007</v>
       </c>
       <c r="J257" s="5" t="str">
         <f aca="false">K257&amp;"|"&amp;D257&amp;"|"&amp;E257</f>
@@ -48754,7 +48769,7 @@
         <v>1340</v>
       </c>
       <c r="F258" s="13" t="s">
-        <v>2004</v>
+        <v>2008</v>
       </c>
       <c r="G258" s="12" t="n">
         <f aca="false">IF(OR(D258="—",D258="",K258=""),"",COUNTIF($J$2:$J$259,J258)-1)</f>
@@ -48762,7 +48777,7 @@
       </c>
       <c r="H258" s="14"/>
       <c r="I258" s="13" t="s">
-        <v>2005</v>
+        <v>2009</v>
       </c>
       <c r="J258" s="5" t="str">
         <f aca="false">K258&amp;"|"&amp;D258&amp;"|"&amp;E258</f>
@@ -48793,7 +48808,7 @@
         <v>1340</v>
       </c>
       <c r="F259" s="13" t="s">
-        <v>1907</v>
+        <v>2010</v>
       </c>
       <c r="G259" s="12" t="n">
         <f aca="false">IF(OR(D259="—",D259="",K259=""),"",COUNTIF($J$2:$J$259,J259)-1)</f>
@@ -48801,7 +48816,7 @@
       </c>
       <c r="H259" s="14"/>
       <c r="I259" s="13" t="s">
-        <v>2006</v>
+        <v>2011</v>
       </c>
       <c r="J259" s="5" t="str">
         <f aca="false">K259&amp;"|"&amp;D259&amp;"|"&amp;E259</f>
@@ -48870,19 +48885,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>2007</v>
+        <v>2012</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>2008</v>
+        <v>2013</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>2009</v>
+        <v>2014</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>2010</v>
+        <v>2015</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>2011</v>
+        <v>2016</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>1326</v>
@@ -48891,22 +48906,22 @@
         <v>939</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>2012</v>
+        <v>2017</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>2017</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -48914,10 +48929,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="D2" s="14" t="s">
         <v>1066</v>
@@ -48935,7 +48950,7 @@
         <v>129</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="J2" s="16" t="n">
         <f aca="false">COUNTIFS('Ingredient Feel'!$L$2:$L$259,"*, "&amp;E2&amp;", *",'Ingredient Feel'!$B$2:$B$259,D2,'Ingredient Feel'!$D$2:$D$259,F2,'Ingredient Feel'!$E$2:$E$259,G2)</f>
@@ -48950,7 +48965,7 @@
         <v>8</v>
       </c>
       <c r="M2" s="13" t="s">
-        <v>2021</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -48958,16 +48973,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>2022</v>
+        <v>2027</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>2023</v>
+        <v>2028</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>1066</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>2024</v>
+        <v>2029</v>
       </c>
       <c r="F3" s="14" t="s">
         <v>1344</v>
@@ -48979,7 +48994,7 @@
         <v>604</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>2025</v>
+        <v>2030</v>
       </c>
       <c r="J3" s="16" t="n">
         <f aca="false">COUNTIFS('Ingredient Feel'!$L$2:$L$259,"*, "&amp;E3&amp;", *",'Ingredient Feel'!$B$2:$B$259,D3,'Ingredient Feel'!$D$2:$D$259,F3,'Ingredient Feel'!$E$2:$E$259,G3)</f>
@@ -48994,7 +49009,7 @@
         <v>3</v>
       </c>
       <c r="M3" s="13" t="s">
-        <v>2026</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -49002,16 +49017,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>2027</v>
+        <v>2032</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>2028</v>
+        <v>2033</v>
       </c>
       <c r="D4" s="14" t="s">
         <v>1066</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>2029</v>
+        <v>2034</v>
       </c>
       <c r="F4" s="14" t="s">
         <v>1344</v>
@@ -49023,7 +49038,7 @@
         <v>718</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>2030</v>
+        <v>2035</v>
       </c>
       <c r="J4" s="16" t="n">
         <f aca="false">COUNTIFS('Ingredient Feel'!$L$2:$L$259,"*, "&amp;E4&amp;", *",'Ingredient Feel'!$B$2:$B$259,D4,'Ingredient Feel'!$D$2:$D$259,F4,'Ingredient Feel'!$E$2:$E$259,G4)</f>
@@ -49038,7 +49053,7 @@
         <v>3</v>
       </c>
       <c r="M4" s="13" t="s">
-        <v>2031</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -49046,16 +49061,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>2032</v>
+        <v>2037</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>2033</v>
+        <v>2038</v>
       </c>
       <c r="D5" s="14" t="s">
         <v>1066</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>2029</v>
+        <v>2034</v>
       </c>
       <c r="F5" s="14" t="s">
         <v>1335</v>
@@ -49067,7 +49082,7 @@
         <v>467</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>2034</v>
+        <v>2039</v>
       </c>
       <c r="J5" s="16" t="n">
         <f aca="false">COUNTIFS('Ingredient Feel'!$L$2:$L$259,"*, "&amp;E5&amp;", *",'Ingredient Feel'!$B$2:$B$259,D5,'Ingredient Feel'!$D$2:$D$259,F5,'Ingredient Feel'!$E$2:$E$259,G5)</f>
@@ -49082,7 +49097,7 @@
         <v>3</v>
       </c>
       <c r="M5" s="13" t="s">
-        <v>2035</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -49090,10 +49105,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>2027</v>
+        <v>2032</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>2036</v>
+        <v>2041</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>1066</v>
@@ -49111,7 +49126,7 @@
         <v>624</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>2037</v>
+        <v>2042</v>
       </c>
       <c r="J6" s="16" t="n">
         <f aca="false">COUNTIFS('Ingredient Feel'!$L$2:$L$259,"*, "&amp;E6&amp;", *",'Ingredient Feel'!$B$2:$B$259,D6,'Ingredient Feel'!$D$2:$D$259,F6,'Ingredient Feel'!$E$2:$E$259,G6)</f>
@@ -49126,7 +49141,7 @@
         <v>8</v>
       </c>
       <c r="M6" s="13" t="s">
-        <v>2038</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -49134,10 +49149,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>2027</v>
+        <v>2032</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>2039</v>
+        <v>2044</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>1066</v>
@@ -49155,7 +49170,7 @@
         <v>115</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>2040</v>
+        <v>2045</v>
       </c>
       <c r="J7" s="16" t="n">
         <f aca="false">COUNTIFS('Ingredient Feel'!$L$2:$L$259,"*, "&amp;E7&amp;", *",'Ingredient Feel'!$B$2:$B$259,D7,'Ingredient Feel'!$D$2:$D$259,F7,'Ingredient Feel'!$E$2:$E$259,G7)</f>
@@ -49170,7 +49185,7 @@
         <v>7</v>
       </c>
       <c r="M7" s="13" t="s">
-        <v>2041</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -49178,10 +49193,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>2027</v>
+        <v>2032</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>2042</v>
+        <v>2047</v>
       </c>
       <c r="D8" s="14" t="s">
         <v>1066</v>
@@ -49199,7 +49214,7 @@
         <v>596</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>2043</v>
+        <v>2048</v>
       </c>
       <c r="J8" s="16" t="n">
         <f aca="false">COUNTIFS('Ingredient Feel'!$L$2:$L$259,"*, "&amp;E8&amp;", *",'Ingredient Feel'!$B$2:$B$259,D8,'Ingredient Feel'!$D$2:$D$259,F8,'Ingredient Feel'!$E$2:$E$259,G8)</f>
@@ -49214,7 +49229,7 @@
         <v>7</v>
       </c>
       <c r="M8" s="13" t="s">
-        <v>2044</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -49222,16 +49237,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>2046</v>
+        <v>2051</v>
       </c>
       <c r="D9" s="14" t="s">
         <v>1066</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>2047</v>
+        <v>2052</v>
       </c>
       <c r="F9" s="14" t="s">
         <v>1335</v>
@@ -49243,7 +49258,7 @@
         <v>184</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>2048</v>
+        <v>2053</v>
       </c>
       <c r="J9" s="16" t="n">
         <f aca="false">COUNTIFS('Ingredient Feel'!$L$2:$L$259,"*, "&amp;E9&amp;", *",'Ingredient Feel'!$B$2:$B$259,D9,'Ingredient Feel'!$D$2:$D$259,F9,'Ingredient Feel'!$E$2:$E$259,G9)</f>
@@ -49258,7 +49273,7 @@
         <v>2</v>
       </c>
       <c r="M9" s="13" t="s">
-        <v>2049</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -49266,10 +49281,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>2050</v>
+        <v>2055</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>2051</v>
+        <v>2056</v>
       </c>
       <c r="D10" s="14" t="s">
         <v>1066</v>
@@ -49287,7 +49302,7 @@
         <v>99</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>2052</v>
+        <v>2057</v>
       </c>
       <c r="J10" s="16" t="n">
         <f aca="false">COUNTIFS('Ingredient Feel'!$L$2:$L$259,"*, "&amp;E10&amp;", *",'Ingredient Feel'!$B$2:$B$259,D10,'Ingredient Feel'!$D$2:$D$259,F10,'Ingredient Feel'!$E$2:$E$259,G10)</f>
@@ -49302,7 +49317,7 @@
         <v>4</v>
       </c>
       <c r="M10" s="13" t="s">
-        <v>2053</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -49310,10 +49325,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>2050</v>
+        <v>2055</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>2054</v>
+        <v>2059</v>
       </c>
       <c r="D11" s="14" t="s">
         <v>1066</v>
@@ -49331,7 +49346,7 @@
         <v>71</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>2055</v>
+        <v>2060</v>
       </c>
       <c r="J11" s="16" t="n">
         <f aca="false">COUNTIFS('Ingredient Feel'!$L$2:$L$259,"*, "&amp;E11&amp;", *",'Ingredient Feel'!$B$2:$B$259,D11,'Ingredient Feel'!$D$2:$D$259,F11,'Ingredient Feel'!$E$2:$E$259,G11)</f>
@@ -49346,7 +49361,7 @@
         <v>4</v>
       </c>
       <c r="M11" s="13" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -49354,10 +49369,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>2027</v>
+        <v>2032</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>2057</v>
+        <v>2062</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>1066</v>
@@ -49375,7 +49390,7 @@
         <v>227</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>2058</v>
+        <v>2063</v>
       </c>
       <c r="J12" s="16" t="n">
         <f aca="false">COUNTIFS('Ingredient Feel'!$L$2:$L$259,"*, "&amp;E12&amp;", *",'Ingredient Feel'!$B$2:$B$259,D12,'Ingredient Feel'!$D$2:$D$259,F12,'Ingredient Feel'!$E$2:$E$259,G12)</f>
@@ -49390,7 +49405,7 @@
         <v>8</v>
       </c>
       <c r="M12" s="13" t="s">
-        <v>2059</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -49398,10 +49413,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>2027</v>
+        <v>2032</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>2060</v>
+        <v>2065</v>
       </c>
       <c r="D13" s="14" t="s">
         <v>1066</v>
@@ -49419,7 +49434,7 @@
         <v>500</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>2061</v>
+        <v>2066</v>
       </c>
       <c r="J13" s="16" t="n">
         <f aca="false">COUNTIFS('Ingredient Feel'!$L$2:$L$259,"*, "&amp;E13&amp;", *",'Ingredient Feel'!$B$2:$B$259,D13,'Ingredient Feel'!$D$2:$D$259,F13,'Ingredient Feel'!$E$2:$E$259,G13)</f>
@@ -49434,7 +49449,7 @@
         <v>8</v>
       </c>
       <c r="M13" s="13" t="s">
-        <v>2062</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -49442,10 +49457,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>2027</v>
+        <v>2032</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>2063</v>
+        <v>2068</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>1066</v>
@@ -49463,7 +49478,7 @@
         <v>480</v>
       </c>
       <c r="I14" s="15" t="s">
-        <v>2064</v>
+        <v>2069</v>
       </c>
       <c r="J14" s="16" t="n">
         <f aca="false">COUNTIFS('Ingredient Feel'!$L$2:$L$259,"*, "&amp;E14&amp;", *",'Ingredient Feel'!$B$2:$B$259,D14,'Ingredient Feel'!$D$2:$D$259,F14,'Ingredient Feel'!$E$2:$E$259,G14)</f>
@@ -49478,7 +49493,7 @@
         <v>2</v>
       </c>
       <c r="M14" s="13" t="s">
-        <v>2065</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -49486,10 +49501,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>2027</v>
+        <v>2032</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>2066</v>
+        <v>2071</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>1066</v>
@@ -49507,7 +49522,7 @@
         <v>355</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>2067</v>
+        <v>2072</v>
       </c>
       <c r="J15" s="16" t="n">
         <f aca="false">COUNTIFS('Ingredient Feel'!$L$2:$L$259,"*, "&amp;E15&amp;", *",'Ingredient Feel'!$B$2:$B$259,D15,'Ingredient Feel'!$D$2:$D$259,F15,'Ingredient Feel'!$E$2:$E$259,G15)</f>
@@ -49522,7 +49537,7 @@
         <v>2</v>
       </c>
       <c r="M15" s="13" t="s">
-        <v>2068</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -49530,10 +49545,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>2027</v>
+        <v>2032</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>2069</v>
+        <v>2074</v>
       </c>
       <c r="D16" s="14" t="s">
         <v>1066</v>
@@ -49551,7 +49566,7 @@
         <v>243</v>
       </c>
       <c r="I16" s="15" t="s">
-        <v>2070</v>
+        <v>2075</v>
       </c>
       <c r="J16" s="16" t="n">
         <f aca="false">COUNTIFS('Ingredient Feel'!$L$2:$L$259,"*, "&amp;E16&amp;", *",'Ingredient Feel'!$B$2:$B$259,D16,'Ingredient Feel'!$D$2:$D$259,F16,'Ingredient Feel'!$E$2:$E$259,G16)</f>
@@ -49566,7 +49581,7 @@
         <v>2</v>
       </c>
       <c r="M16" s="13" t="s">
-        <v>2071</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -49574,16 +49589,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>2072</v>
+        <v>2077</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>2073</v>
+        <v>2078</v>
       </c>
       <c r="D17" s="14" t="s">
         <v>1066</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>2074</v>
+        <v>2079</v>
       </c>
       <c r="F17" s="14" t="s">
         <v>1335</v>
@@ -49595,7 +49610,7 @@
         <v>229</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>2075</v>
+        <v>2080</v>
       </c>
       <c r="J17" s="16" t="n">
         <f aca="false">COUNTIFS('Ingredient Feel'!$L$2:$L$259,"*, "&amp;E17&amp;", *",'Ingredient Feel'!$B$2:$B$259,D17,'Ingredient Feel'!$D$2:$D$259,F17,'Ingredient Feel'!$E$2:$E$259,G17)</f>
@@ -49610,7 +49625,7 @@
         <v>2</v>
       </c>
       <c r="M17" s="13" t="s">
-        <v>2076</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -49618,16 +49633,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>2022</v>
+        <v>2027</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>2077</v>
+        <v>2082</v>
       </c>
       <c r="D18" s="14" t="s">
         <v>1066</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>2078</v>
+        <v>2083</v>
       </c>
       <c r="F18" s="14" t="s">
         <v>1335</v>
@@ -49639,7 +49654,7 @@
         <v>459</v>
       </c>
       <c r="I18" s="15" t="s">
-        <v>2079</v>
+        <v>2084</v>
       </c>
       <c r="J18" s="16" t="n">
         <f aca="false">COUNTIFS('Ingredient Feel'!$L$2:$L$259,"*, "&amp;E18&amp;", *",'Ingredient Feel'!$B$2:$B$259,D18,'Ingredient Feel'!$D$2:$D$259,F18,'Ingredient Feel'!$E$2:$E$259,G18)</f>
@@ -49654,7 +49669,7 @@
         <v>3</v>
       </c>
       <c r="M18" s="13" t="s">
-        <v>2080</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -49662,16 +49677,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>2027</v>
+        <v>2032</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>2081</v>
+        <v>2086</v>
       </c>
       <c r="D19" s="14" t="s">
         <v>1066</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>2082</v>
+        <v>2087</v>
       </c>
       <c r="F19" s="14" t="s">
         <v>1335</v>
@@ -49683,7 +49698,7 @@
         <v>468</v>
       </c>
       <c r="I19" s="15" t="s">
-        <v>2083</v>
+        <v>2088</v>
       </c>
       <c r="J19" s="16" t="n">
         <f aca="false">COUNTIFS('Ingredient Feel'!$L$2:$L$259,"*, "&amp;E19&amp;", *",'Ingredient Feel'!$B$2:$B$259,D19,'Ingredient Feel'!$D$2:$D$259,F19,'Ingredient Feel'!$E$2:$E$259,G19)</f>
@@ -49698,7 +49713,7 @@
         <v>3</v>
       </c>
       <c r="M19" s="13" t="s">
-        <v>2084</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -49706,10 +49721,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>2085</v>
+        <v>2090</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>2086</v>
+        <v>2091</v>
       </c>
       <c r="D20" s="14" t="s">
         <v>1196</v>
@@ -49727,7 +49742,7 @@
         <v>337</v>
       </c>
       <c r="I20" s="15" t="s">
-        <v>2087</v>
+        <v>2092</v>
       </c>
       <c r="J20" s="16" t="n">
         <f aca="false">COUNTIFS('Ingredient Feel'!$L$2:$L$259,"*, "&amp;E20&amp;", *",'Ingredient Feel'!$B$2:$B$259,D20,'Ingredient Feel'!$D$2:$D$259,F20,'Ingredient Feel'!$E$2:$E$259,G20)</f>
@@ -49742,7 +49757,7 @@
         <v>2</v>
       </c>
       <c r="M20" s="13" t="s">
-        <v>2088</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -49750,16 +49765,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>2027</v>
+        <v>2032</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>2089</v>
+        <v>2094</v>
       </c>
       <c r="D21" s="14" t="s">
         <v>1196</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>2090</v>
+        <v>2095</v>
       </c>
       <c r="F21" s="14" t="s">
         <v>1344</v>
@@ -49771,7 +49786,7 @@
         <v>213</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>2091</v>
+        <v>2096</v>
       </c>
       <c r="J21" s="16" t="n">
         <f aca="false">COUNTIFS('Ingredient Feel'!$L$2:$L$259,"*, "&amp;E21&amp;", *",'Ingredient Feel'!$B$2:$B$259,D21,'Ingredient Feel'!$D$2:$D$259,F21,'Ingredient Feel'!$E$2:$E$259,G21)</f>
@@ -49786,7 +49801,7 @@
         <v>2</v>
       </c>
       <c r="M21" s="13" t="s">
-        <v>2092</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -49794,16 +49809,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>2027</v>
+        <v>2032</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>2093</v>
+        <v>2098</v>
       </c>
       <c r="D22" s="14" t="s">
         <v>1196</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>2090</v>
+        <v>2095</v>
       </c>
       <c r="F22" s="14" t="s">
         <v>1335</v>
@@ -49815,7 +49830,7 @@
         <v>614</v>
       </c>
       <c r="I22" s="15" t="s">
-        <v>2094</v>
+        <v>2099</v>
       </c>
       <c r="J22" s="16" t="n">
         <f aca="false">COUNTIFS('Ingredient Feel'!$L$2:$L$259,"*, "&amp;E22&amp;", *",'Ingredient Feel'!$B$2:$B$259,D22,'Ingredient Feel'!$D$2:$D$259,F22,'Ingredient Feel'!$E$2:$E$259,G22)</f>
@@ -49830,7 +49845,7 @@
         <v>2</v>
       </c>
       <c r="M22" s="13" t="s">
-        <v>2095</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -49838,16 +49853,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>2096</v>
+        <v>2101</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>2097</v>
+        <v>2102</v>
       </c>
       <c r="D23" s="14" t="s">
         <v>1196</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>2098</v>
+        <v>2103</v>
       </c>
       <c r="F23" s="14" t="s">
         <v>1344</v>
@@ -49859,7 +49874,7 @@
         <v>88</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>2099</v>
+        <v>2104</v>
       </c>
       <c r="J23" s="16" t="n">
         <f aca="false">COUNTIFS('Ingredient Feel'!$L$2:$L$259,"*, "&amp;E23&amp;", *",'Ingredient Feel'!$B$2:$B$259,D23,'Ingredient Feel'!$D$2:$D$259,F23,'Ingredient Feel'!$E$2:$E$259,G23)</f>
@@ -49874,7 +49889,7 @@
         <v>3</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>2100</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -49882,16 +49897,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>2027</v>
+        <v>2032</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>2101</v>
+        <v>2106</v>
       </c>
       <c r="D24" s="14" t="s">
         <v>1196</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>2098</v>
+        <v>2103</v>
       </c>
       <c r="F24" s="14" t="s">
         <v>1335</v>
@@ -49903,7 +49918,7 @@
         <v>131</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>2102</v>
+        <v>2107</v>
       </c>
       <c r="J24" s="16" t="n">
         <f aca="false">COUNTIFS('Ingredient Feel'!$L$2:$L$259,"*, "&amp;E24&amp;", *",'Ingredient Feel'!$B$2:$B$259,D24,'Ingredient Feel'!$D$2:$D$259,F24,'Ingredient Feel'!$E$2:$E$259,G24)</f>
@@ -49918,7 +49933,7 @@
         <v>3</v>
       </c>
       <c r="M24" s="13" t="s">
-        <v>2103</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -49926,16 +49941,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>2027</v>
+        <v>2032</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>2104</v>
+        <v>2109</v>
       </c>
       <c r="D25" s="14" t="s">
         <v>1196</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>2082</v>
+        <v>2087</v>
       </c>
       <c r="F25" s="14" t="s">
         <v>1335</v>
@@ -49947,7 +49962,7 @@
         <v>586</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>2105</v>
+        <v>2110</v>
       </c>
       <c r="J25" s="16" t="n">
         <f aca="false">COUNTIFS('Ingredient Feel'!$L$2:$L$259,"*, "&amp;E25&amp;", *",'Ingredient Feel'!$B$2:$B$259,D25,'Ingredient Feel'!$D$2:$D$259,F25,'Ingredient Feel'!$E$2:$E$259,G25)</f>
@@ -49962,7 +49977,7 @@
         <v>3</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>2106</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -49970,10 +49985,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>2027</v>
+        <v>2032</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>2107</v>
+        <v>2112</v>
       </c>
       <c r="D26" s="14" t="s">
         <v>1196</v>
@@ -49991,7 +50006,7 @@
         <v>290</v>
       </c>
       <c r="I26" s="15" t="s">
-        <v>2108</v>
+        <v>2113</v>
       </c>
       <c r="J26" s="16" t="n">
         <f aca="false">COUNTIFS('Ingredient Feel'!$L$2:$L$259,"*, "&amp;E26&amp;", *",'Ingredient Feel'!$B$2:$B$259,D26,'Ingredient Feel'!$D$2:$D$259,F26,'Ingredient Feel'!$E$2:$E$259,G26)</f>
@@ -50006,7 +50021,7 @@
         <v>7</v>
       </c>
       <c r="M26" s="13" t="s">
-        <v>2109</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -50014,10 +50029,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>2027</v>
+        <v>2032</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>2110</v>
+        <v>2115</v>
       </c>
       <c r="D27" s="14" t="s">
         <v>1196</v>
@@ -50035,7 +50050,7 @@
         <v>262</v>
       </c>
       <c r="I27" s="15" t="s">
-        <v>2111</v>
+        <v>2116</v>
       </c>
       <c r="J27" s="16" t="n">
         <f aca="false">COUNTIFS('Ingredient Feel'!$L$2:$L$259,"*, "&amp;E27&amp;", *",'Ingredient Feel'!$B$2:$B$259,D27,'Ingredient Feel'!$D$2:$D$259,F27,'Ingredient Feel'!$E$2:$E$259,G27)</f>
@@ -50050,7 +50065,7 @@
         <v>3</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>2112</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -50058,16 +50073,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>2022</v>
+        <v>2027</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>2113</v>
+        <v>2118</v>
       </c>
       <c r="D28" s="14" t="s">
         <v>1196</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>2114</v>
+        <v>2119</v>
       </c>
       <c r="F28" s="14" t="s">
         <v>1335</v>
@@ -50079,7 +50094,7 @@
         <v>446</v>
       </c>
       <c r="I28" s="15" t="s">
-        <v>2115</v>
+        <v>2120</v>
       </c>
       <c r="J28" s="16" t="n">
         <f aca="false">COUNTIFS('Ingredient Feel'!$L$2:$L$259,"*, "&amp;E28&amp;", *",'Ingredient Feel'!$B$2:$B$259,D28,'Ingredient Feel'!$D$2:$D$259,F28,'Ingredient Feel'!$E$2:$E$259,G28)</f>
@@ -50094,7 +50109,7 @@
         <v>2</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>2116</v>
+        <v>2121</v>
       </c>
     </row>
   </sheetData>
@@ -50152,7 +50167,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>2117</v>
+        <v>2122</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>1040</v>
@@ -50176,7 +50191,7 @@
         <v>15</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>6</v>
@@ -50192,7 +50207,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>2119</v>
+        <v>2124</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>6</v>
@@ -50208,7 +50223,7 @@
         <v>14</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>2120</v>
+        <v>2125</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>6</v>
@@ -50224,7 +50239,7 @@
         <v>18</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>2121</v>
+        <v>2126</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>6</v>
@@ -50240,7 +50255,7 @@
         <v>9</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>2122</v>
+        <v>2127</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>6</v>
@@ -50256,7 +50271,7 @@
         <v>10</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>2123</v>
+        <v>2128</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>6</v>
@@ -50272,7 +50287,7 @@
         <v>14</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>2124</v>
+        <v>2129</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>6</v>
@@ -50288,7 +50303,7 @@
         <v>12</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>2125</v>
+        <v>2130</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>6</v>
@@ -50304,7 +50319,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>2126</v>
+        <v>2131</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>6</v>
@@ -50320,7 +50335,7 @@
         <v>13</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>2127</v>
+        <v>2132</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>6</v>
@@ -50336,7 +50351,7 @@
         <v>17</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>2128</v>
+        <v>2133</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>6</v>
@@ -50352,7 +50367,7 @@
         <v>9</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>2129</v>
+        <v>2134</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>6</v>
@@ -50368,7 +50383,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>2130</v>
+        <v>2135</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>6</v>
@@ -50384,7 +50399,7 @@
         <v>9</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>2131</v>
+        <v>2136</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>6</v>
@@ -50400,7 +50415,7 @@
         <v>10</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>2132</v>
+        <v>2137</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>6</v>
@@ -50443,7 +50458,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>2133</v>
+        <v>2138</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>1040</v>
@@ -50467,7 +50482,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>2134</v>
+        <v>2139</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>6</v>
@@ -50483,7 +50498,7 @@
         <v>9</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>2135</v>
+        <v>2140</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>6</v>
@@ -50499,7 +50514,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>2136</v>
+        <v>2141</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>6</v>
@@ -50515,7 +50530,7 @@
         <v>10</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>2137</v>
+        <v>2142</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>6</v>
@@ -50531,7 +50546,7 @@
         <v>8</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>2138</v>
+        <v>2143</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>6</v>
@@ -50547,7 +50562,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>2139</v>
+        <v>2144</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>6</v>
@@ -50563,7 +50578,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>2140</v>
+        <v>2145</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>6</v>
@@ -50579,7 +50594,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>2141</v>
+        <v>2146</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>6</v>
@@ -50595,7 +50610,7 @@
         <v>10</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>2142</v>
+        <v>2147</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>6</v>
@@ -50611,7 +50626,7 @@
         <v>8</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>2143</v>
+        <v>2148</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>6</v>
@@ -50627,7 +50642,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>2144</v>
+        <v>2149</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>6</v>
@@ -50643,7 +50658,7 @@
         <v>5</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>2145</v>
+        <v>2150</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>6</v>
@@ -50659,7 +50674,7 @@
         <v>6</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>2146</v>
+        <v>2151</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>6</v>
@@ -50675,7 +50690,7 @@
         <v>6</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>2147</v>
+        <v>2152</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>6</v>
@@ -50691,7 +50706,7 @@
         <v>7</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>2148</v>
+        <v>2153</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>6</v>
@@ -50707,7 +50722,7 @@
         <v>6</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>2149</v>
+        <v>2154</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>6</v>
@@ -50723,7 +50738,7 @@
         <v>5</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>2150</v>
+        <v>2155</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>6</v>
@@ -50739,7 +50754,7 @@
         <v>9</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>2151</v>
+        <v>2156</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>6</v>
@@ -50755,7 +50770,7 @@
         <v>6</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>2152</v>
+        <v>2157</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>6</v>
@@ -50771,7 +50786,7 @@
         <v>11</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>2153</v>
+        <v>2158</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>6</v>
@@ -50787,7 +50802,7 @@
         <v>8</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>2154</v>
+        <v>2159</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>6</v>
@@ -50803,7 +50818,7 @@
         <v>6</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>2155</v>
+        <v>2160</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>6</v>
@@ -50846,10 +50861,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>2156</v>
+        <v>2161</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>2157</v>
+        <v>2162</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>1041</v>
@@ -50863,13 +50878,13 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>2158</v>
+        <v>2163</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>2159</v>
+        <v>2164</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>2160</v>
+        <v>2165</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>6</v>
@@ -50881,10 +50896,10 @@
         <v>994</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>2159</v>
+        <v>2164</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>2161</v>
+        <v>2166</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>6</v>
@@ -50896,10 +50911,10 @@
         <v>970</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>2159</v>
+        <v>2164</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>2162</v>
+        <v>2167</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>6</v>
@@ -50908,13 +50923,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>2163</v>
+        <v>2168</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2159</v>
+        <v>2164</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>2164</v>
+        <v>2169</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>6</v>
@@ -50926,10 +50941,10 @@
         <v>999</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2159</v>
+        <v>2164</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>2165</v>
+        <v>2170</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>6</v>
@@ -50941,10 +50956,10 @@
         <v>884</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>2159</v>
+        <v>2164</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>2166</v>
+        <v>2171</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>6</v>
@@ -50956,10 +50971,10 @@
         <v>996</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>2159</v>
+        <v>2164</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>2167</v>
+        <v>2172</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>6</v>
@@ -50968,13 +50983,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>2168</v>
+        <v>2173</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2159</v>
+        <v>2164</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>2169</v>
+        <v>2174</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>6</v>
@@ -50986,10 +51001,10 @@
         <v>1000</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2159</v>
+        <v>2164</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>2170</v>
+        <v>2175</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>6</v>
@@ -50998,13 +51013,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>2171</v>
+        <v>2176</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>2172</v>
+        <v>2177</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>2173</v>
+        <v>2178</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>6</v>
@@ -51013,13 +51028,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>2174</v>
+        <v>2179</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>2172</v>
+        <v>2177</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>2175</v>
+        <v>2180</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>6</v>
@@ -51028,13 +51043,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>2176</v>
+        <v>2181</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>2172</v>
+        <v>2177</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>2177</v>
+        <v>2182</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>6</v>
@@ -51043,13 +51058,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>2178</v>
+        <v>2183</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>2172</v>
+        <v>2177</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>2179</v>
+        <v>2184</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>6</v>
@@ -51058,13 +51073,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>2180</v>
+        <v>2185</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>2172</v>
+        <v>2177</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>2181</v>
+        <v>2186</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>6</v>
@@ -51076,10 +51091,10 @@
         <v>133</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>2172</v>
+        <v>2177</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>2182</v>
+        <v>2187</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>6</v>
@@ -51088,13 +51103,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>2183</v>
+        <v>2188</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>2172</v>
+        <v>2177</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>2184</v>
+        <v>2189</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>6</v>
@@ -51103,13 +51118,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>2185</v>
+        <v>2190</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>2172</v>
+        <v>2177</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>2186</v>
+        <v>2191</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>6</v>
@@ -51118,13 +51133,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>2187</v>
+        <v>2192</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>2172</v>
+        <v>2177</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>2188</v>
+        <v>2193</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>6</v>
@@ -51133,13 +51148,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>2189</v>
+        <v>2194</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>2172</v>
+        <v>2177</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>2190</v>
+        <v>2195</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>6</v>
@@ -51148,13 +51163,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>2191</v>
+        <v>2196</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>2172</v>
+        <v>2177</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>2192</v>
+        <v>2197</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>6</v>
@@ -51163,13 +51178,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>2193</v>
+        <v>2198</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>2172</v>
+        <v>2177</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>2194</v>
+        <v>2199</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>6</v>
@@ -51178,13 +51193,13 @@
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>2195</v>
+        <v>2200</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>2172</v>
+        <v>2177</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>2196</v>
+        <v>2201</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>6</v>
@@ -51193,13 +51208,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>2197</v>
+        <v>2202</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>2172</v>
+        <v>2177</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>2198</v>
+        <v>2203</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>6</v>
@@ -51211,10 +51226,10 @@
         <v>977</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>2199</v>
+        <v>2204</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>2200</v>
+        <v>2205</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>6</v>
@@ -51226,10 +51241,10 @@
         <v>903</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>2199</v>
+        <v>2204</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>2201</v>
+        <v>2206</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>6</v>
@@ -51241,10 +51256,10 @@
         <v>957</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>2199</v>
+        <v>2204</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>2202</v>
+        <v>2207</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>6</v>
@@ -51256,10 +51271,10 @@
         <v>922</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>2199</v>
+        <v>2204</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>2203</v>
+        <v>2208</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>6</v>
@@ -51271,10 +51286,10 @@
         <v>878</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>2199</v>
+        <v>2204</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>2204</v>
+        <v>2209</v>
       </c>
       <c r="D29" s="11" t="s">
         <v>6</v>
@@ -51286,10 +51301,10 @@
         <v>933</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>2199</v>
+        <v>2204</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>2205</v>
+        <v>2210</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>6</v>
@@ -51301,10 +51316,10 @@
         <v>986</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>2199</v>
+        <v>2204</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>2206</v>
+        <v>2211</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>6</v>
@@ -51316,10 +51331,10 @@
         <v>1001</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>2207</v>
+        <v>2212</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>2208</v>
+        <v>2213</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>6</v>
@@ -51328,13 +51343,13 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>2209</v>
+        <v>2214</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>2207</v>
+        <v>2212</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>2210</v>
+        <v>2215</v>
       </c>
       <c r="D33" s="11" t="s">
         <v>6</v>
@@ -51346,10 +51361,10 @@
         <v>978</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>2207</v>
+        <v>2212</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>2211</v>
+        <v>2216</v>
       </c>
       <c r="D34" s="11" t="s">
         <v>6</v>
@@ -51361,10 +51376,10 @@
         <v>983</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>2207</v>
+        <v>2212</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>2212</v>
+        <v>2217</v>
       </c>
       <c r="D35" s="11" t="s">
         <v>6</v>
@@ -51376,10 +51391,10 @@
         <v>1015</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>2213</v>
+        <v>2218</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>2214</v>
+        <v>2219</v>
       </c>
       <c r="D36" s="11" t="s">
         <v>6</v>
@@ -51388,13 +51403,13 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>2215</v>
+        <v>2220</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>2213</v>
+        <v>2218</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>2216</v>
+        <v>2221</v>
       </c>
       <c r="D37" s="11" t="s">
         <v>6</v>
@@ -51406,10 +51421,10 @@
         <v>1017</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>2213</v>
+        <v>2218</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>2217</v>
+        <v>2222</v>
       </c>
       <c r="D38" s="11" t="s">
         <v>6</v>
@@ -51421,10 +51436,10 @@
         <v>971</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>2213</v>
+        <v>2218</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>2218</v>
+        <v>2223</v>
       </c>
       <c r="D39" s="11" t="s">
         <v>6</v>
@@ -51436,10 +51451,10 @@
         <v>1028</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>2213</v>
+        <v>2218</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>2219</v>
+        <v>2224</v>
       </c>
       <c r="D40" s="11" t="s">
         <v>6</v>
@@ -51451,10 +51466,10 @@
         <v>930</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>2213</v>
+        <v>2218</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>2220</v>
+        <v>2225</v>
       </c>
       <c r="D41" s="11" t="s">
         <v>6</v>
@@ -51466,10 +51481,10 @@
         <v>1023</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>2213</v>
+        <v>2218</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="D42" s="11" t="s">
         <v>6</v>
@@ -51481,10 +51496,10 @@
         <v>998</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>2213</v>
+        <v>2218</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>2222</v>
+        <v>2227</v>
       </c>
       <c r="D43" s="11" t="s">
         <v>6</v>
@@ -51496,10 +51511,10 @@
         <v>1021</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>2213</v>
+        <v>2218</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>2223</v>
+        <v>2228</v>
       </c>
       <c r="D44" s="11" t="s">
         <v>6</v>
@@ -51511,10 +51526,10 @@
         <v>1037</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>2213</v>
+        <v>2218</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>2224</v>
+        <v>2229</v>
       </c>
       <c r="D45" s="11" t="s">
         <v>6</v>
@@ -51526,10 +51541,10 @@
         <v>991</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>2225</v>
+        <v>2230</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>2226</v>
+        <v>2231</v>
       </c>
       <c r="D46" s="11" t="s">
         <v>6</v>
@@ -51541,10 +51556,10 @@
         <v>960</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>2225</v>
+        <v>2230</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>2227</v>
+        <v>2232</v>
       </c>
       <c r="D47" s="11" t="s">
         <v>6</v>
@@ -51556,10 +51571,10 @@
         <v>918</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>2225</v>
+        <v>2230</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>2228</v>
+        <v>2233</v>
       </c>
       <c r="D48" s="11" t="s">
         <v>6</v>
@@ -51571,10 +51586,10 @@
         <v>955</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>2225</v>
+        <v>2230</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>2229</v>
+        <v>2234</v>
       </c>
       <c r="D49" s="11" t="s">
         <v>6</v>
@@ -51586,10 +51601,10 @@
         <v>892</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>2225</v>
+        <v>2230</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>2230</v>
+        <v>2235</v>
       </c>
       <c r="D50" s="11" t="s">
         <v>6</v>
@@ -51601,10 +51616,10 @@
         <v>967</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>2225</v>
+        <v>2230</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>2231</v>
+        <v>2236</v>
       </c>
       <c r="D51" s="11" t="s">
         <v>6</v>
@@ -51616,10 +51631,10 @@
         <v>937</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>2225</v>
+        <v>2230</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>2232</v>
+        <v>2237</v>
       </c>
       <c r="D52" s="11" t="s">
         <v>6</v>
@@ -51631,10 +51646,10 @@
         <v>964</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>2225</v>
+        <v>2230</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>2233</v>
+        <v>2238</v>
       </c>
       <c r="D53" s="11" t="s">
         <v>6</v>

--- a/ingredient_asset_tracker.xlsx
+++ b/ingredient_asset_tracker.xlsx
@@ -247,7 +247,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11428" uniqueCount="2566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11429" uniqueCount="2567">
   <si>
     <t xml:space="preserve">Image Asset Tracker</t>
   </si>
@@ -6678,7 +6678,7 @@
     <t xml:space="preserve">Week one (fixed)</t>
   </si>
   <si>
-    <t xml:space="preserve">Nettle, Rose hips</t>
+    <t xml:space="preserve">Milk powder, Nettle</t>
   </si>
   <si>
     <t xml:space="preserve">Honey, Rose petals</t>
@@ -6858,18 +6858,12 @@
     <t xml:space="preserve">Pearl, Rosewater, Selenite, White lily, Temperance, Snow</t>
   </si>
   <si>
-    <t xml:space="preserve">Rose quartz, The Star, Waning Gibbous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Goldie #7, Morwenna #145</t>
+    <t xml:space="preserve">Hops, Moss agate, Silver candle</t>
   </si>
   <si>
     <t xml:space="preserve">February</t>
   </si>
   <si>
-    <t xml:space="preserve">Hops, Imbolc</t>
-  </si>
-  <si>
     <t xml:space="preserve">Birch wood, Black pepper, Red paint</t>
   </si>
   <si>
@@ -6879,7 +6873,10 @@
     <t xml:space="preserve">Goldie #7</t>
   </si>
   <si>
-    <t xml:space="preserve">Moss agate, Silver candle</t>
+    <t xml:space="preserve">Nest twig, Rose quartz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basil, Citrine, Paintbrush bristle</t>
   </si>
   <si>
     <t xml:space="preserve">Coconut milk powder, Jasmine, Pyrite, Seashell, The Devil, Waxing Crescent</t>
@@ -6888,7 +6885,7 @@
     <t xml:space="preserve">Goldie #219, Goldie #7</t>
   </si>
   <si>
-    <t xml:space="preserve">Fluorite, Paintbrush bristle, Peacock feather, Violet, The Hanged Man</t>
+    <t xml:space="preserve">Fluorite, Peacock feather, Violet, The Hanged Man</t>
   </si>
   <si>
     <t xml:space="preserve">Ivy #218</t>
@@ -6906,21 +6903,27 @@
     <t xml:space="preserve">Cornflower, Poppy seeds</t>
   </si>
   <si>
+    <t xml:space="preserve">Rose hips, The Star</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edmund #69</t>
+  </si>
+  <si>
     <t xml:space="preserve">March</t>
   </si>
   <si>
     <t xml:space="preserve">Sam #221</t>
   </si>
   <si>
+    <t xml:space="preserve">Acorn, Coin, Magpie feather</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cypress, Myrrh, Waning Crescent</t>
   </si>
   <si>
     <t xml:space="preserve">Edmund #208</t>
   </si>
   <si>
-    <t xml:space="preserve">Acorn, Glass bead, Magpie feather</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ivy #20</t>
   </si>
   <si>
@@ -6978,6 +6981,9 @@
     <t xml:space="preserve">Flower Moon</t>
   </si>
   <si>
+    <t xml:space="preserve">Pink glitter, Seaweed</t>
+  </si>
+  <si>
     <t xml:space="preserve">June</t>
   </si>
   <si>
@@ -7024,9 +7030,6 @@
   </si>
   <si>
     <t xml:space="preserve">September</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dottie #42</t>
   </si>
   <si>
     <t xml:space="preserve">Edmund #71</t>
@@ -8793,7 +8796,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>2381</v>
+        <v>2382</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>1041</v>
@@ -8817,7 +8820,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>2382</v>
+        <v>2383</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>6</v>
@@ -8833,7 +8836,7 @@
         <v>9</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>2383</v>
+        <v>2384</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>6</v>
@@ -8849,7 +8852,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>2384</v>
+        <v>2385</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>6</v>
@@ -8865,7 +8868,7 @@
         <v>10</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>2385</v>
+        <v>2386</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>6</v>
@@ -8881,7 +8884,7 @@
         <v>8</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>2386</v>
+        <v>2387</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>6</v>
@@ -8897,7 +8900,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>2387</v>
+        <v>2388</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>6</v>
@@ -8913,7 +8916,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>2388</v>
+        <v>2389</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>6</v>
@@ -8929,7 +8932,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>2389</v>
+        <v>2390</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>6</v>
@@ -8945,7 +8948,7 @@
         <v>10</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>2390</v>
+        <v>2391</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>6</v>
@@ -8961,7 +8964,7 @@
         <v>8</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>2391</v>
+        <v>2392</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>6</v>
@@ -8977,7 +8980,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>2392</v>
+        <v>2393</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>6</v>
@@ -8993,7 +8996,7 @@
         <v>5</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>2393</v>
+        <v>2394</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>6</v>
@@ -9009,7 +9012,7 @@
         <v>6</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>2394</v>
+        <v>2395</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>6</v>
@@ -9025,7 +9028,7 @@
         <v>6</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>2395</v>
+        <v>2396</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>6</v>
@@ -9041,7 +9044,7 @@
         <v>7</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>2396</v>
+        <v>2397</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>6</v>
@@ -9057,7 +9060,7 @@
         <v>6</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>2397</v>
+        <v>2398</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>6</v>
@@ -9073,7 +9076,7 @@
         <v>5</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>2398</v>
+        <v>2399</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>6</v>
@@ -9089,7 +9092,7 @@
         <v>9</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>2399</v>
+        <v>2400</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>6</v>
@@ -9105,7 +9108,7 @@
         <v>6</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>2400</v>
+        <v>2401</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>6</v>
@@ -9121,7 +9124,7 @@
         <v>11</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>2401</v>
+        <v>2402</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>6</v>
@@ -9137,7 +9140,7 @@
         <v>8</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>2402</v>
+        <v>2403</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>6</v>
@@ -9153,7 +9156,7 @@
         <v>6</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>2403</v>
+        <v>2404</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>6</v>
@@ -9196,10 +9199,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>2404</v>
+        <v>2405</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>2405</v>
+        <v>2406</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>1042</v>
@@ -9213,13 +9216,13 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>2406</v>
+        <v>2407</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>2408</v>
+        <v>2409</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>6</v>
@@ -9231,10 +9234,10 @@
         <v>995</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>2409</v>
+        <v>2410</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>6</v>
@@ -9246,10 +9249,10 @@
         <v>971</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>2410</v>
+        <v>2411</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>6</v>
@@ -9261,10 +9264,10 @@
         <v>2147</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>2411</v>
+        <v>2412</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>6</v>
@@ -9276,10 +9279,10 @@
         <v>1000</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>2412</v>
+        <v>2413</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>6</v>
@@ -9291,10 +9294,10 @@
         <v>885</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>2413</v>
+        <v>2414</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>6</v>
@@ -9306,10 +9309,10 @@
         <v>997</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>2414</v>
+        <v>2415</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>6</v>
@@ -9321,10 +9324,10 @@
         <v>2138</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>2415</v>
+        <v>2416</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>6</v>
@@ -9336,10 +9339,10 @@
         <v>1001</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>2416</v>
+        <v>2417</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>6</v>
@@ -9348,13 +9351,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>2417</v>
+        <v>2418</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>2419</v>
+        <v>2420</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>6</v>
@@ -9363,13 +9366,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>2420</v>
+        <v>2421</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>2421</v>
+        <v>2422</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>6</v>
@@ -9378,13 +9381,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>2229</v>
+        <v>2230</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>2422</v>
+        <v>2423</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>6</v>
@@ -9393,13 +9396,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>2237</v>
+        <v>2238</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>2423</v>
+        <v>2424</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>6</v>
@@ -9408,13 +9411,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>2242</v>
+        <v>2243</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>2424</v>
+        <v>2425</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>6</v>
@@ -9426,10 +9429,10 @@
         <v>134</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>2425</v>
+        <v>2426</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>6</v>
@@ -9438,13 +9441,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>2252</v>
+        <v>2254</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>2426</v>
+        <v>2427</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>6</v>
@@ -9453,13 +9456,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>2256</v>
+        <v>2258</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>2427</v>
+        <v>2428</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>6</v>
@@ -9468,13 +9471,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>2263</v>
+        <v>2264</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>2428</v>
+        <v>2429</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>6</v>
@@ -9483,13 +9486,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>2429</v>
+        <v>2430</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>6</v>
@@ -9498,13 +9501,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>2431</v>
+        <v>2432</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>6</v>
@@ -9513,13 +9516,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>2434</v>
+        <v>2435</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>6</v>
@@ -9528,13 +9531,13 @@
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>2435</v>
+        <v>2436</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>2436</v>
+        <v>2437</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>6</v>
@@ -9543,13 +9546,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>2437</v>
+        <v>2438</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>2438</v>
+        <v>2439</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>6</v>
@@ -9564,7 +9567,7 @@
         <v>2123</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>2439</v>
+        <v>2440</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>6</v>
@@ -9579,7 +9582,7 @@
         <v>2123</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>6</v>
@@ -9594,7 +9597,7 @@
         <v>2123</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>2441</v>
+        <v>2442</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>6</v>
@@ -9609,7 +9612,7 @@
         <v>2123</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>2442</v>
+        <v>2443</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>6</v>
@@ -9624,7 +9627,7 @@
         <v>2123</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>2443</v>
+        <v>2444</v>
       </c>
       <c r="D29" s="11" t="s">
         <v>6</v>
@@ -9639,7 +9642,7 @@
         <v>2123</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>2444</v>
+        <v>2445</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>6</v>
@@ -9654,7 +9657,7 @@
         <v>2123</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>6</v>
@@ -9666,10 +9669,10 @@
         <v>1002</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>6</v>
@@ -9681,10 +9684,10 @@
         <v>2140</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="D33" s="11" t="s">
         <v>6</v>
@@ -9696,10 +9699,10 @@
         <v>979</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="D34" s="11" t="s">
         <v>6</v>
@@ -9711,10 +9714,10 @@
         <v>984</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="D35" s="11" t="s">
         <v>6</v>
@@ -9729,7 +9732,7 @@
         <v>2127</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="D36" s="11" t="s">
         <v>6</v>
@@ -9744,7 +9747,7 @@
         <v>2127</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>2452</v>
+        <v>2453</v>
       </c>
       <c r="D37" s="11" t="s">
         <v>6</v>
@@ -9759,7 +9762,7 @@
         <v>2127</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>2453</v>
+        <v>2454</v>
       </c>
       <c r="D38" s="11" t="s">
         <v>6</v>
@@ -9774,7 +9777,7 @@
         <v>2127</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>2454</v>
+        <v>2455</v>
       </c>
       <c r="D39" s="11" t="s">
         <v>6</v>
@@ -9789,7 +9792,7 @@
         <v>2127</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>2455</v>
+        <v>2456</v>
       </c>
       <c r="D40" s="11" t="s">
         <v>6</v>
@@ -9804,7 +9807,7 @@
         <v>2127</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>2456</v>
+        <v>2457</v>
       </c>
       <c r="D41" s="11" t="s">
         <v>6</v>
@@ -9819,7 +9822,7 @@
         <v>2127</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>2457</v>
+        <v>2458</v>
       </c>
       <c r="D42" s="11" t="s">
         <v>6</v>
@@ -9834,7 +9837,7 @@
         <v>2127</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>2458</v>
+        <v>2459</v>
       </c>
       <c r="D43" s="11" t="s">
         <v>6</v>
@@ -9849,7 +9852,7 @@
         <v>2127</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>2459</v>
+        <v>2460</v>
       </c>
       <c r="D44" s="11" t="s">
         <v>6</v>
@@ -9864,7 +9867,7 @@
         <v>2127</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>2460</v>
+        <v>2461</v>
       </c>
       <c r="D45" s="11" t="s">
         <v>6</v>
@@ -9876,10 +9879,10 @@
         <v>992</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>2461</v>
+        <v>2462</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>2462</v>
+        <v>2463</v>
       </c>
       <c r="D46" s="11" t="s">
         <v>6</v>
@@ -9891,10 +9894,10 @@
         <v>961</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>2461</v>
+        <v>2462</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>2463</v>
+        <v>2464</v>
       </c>
       <c r="D47" s="11" t="s">
         <v>6</v>
@@ -9906,10 +9909,10 @@
         <v>919</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>2461</v>
+        <v>2462</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>2464</v>
+        <v>2465</v>
       </c>
       <c r="D48" s="11" t="s">
         <v>6</v>
@@ -9921,10 +9924,10 @@
         <v>956</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>2461</v>
+        <v>2462</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>2465</v>
+        <v>2466</v>
       </c>
       <c r="D49" s="11" t="s">
         <v>6</v>
@@ -9936,10 +9939,10 @@
         <v>893</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>2461</v>
+        <v>2462</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>2466</v>
+        <v>2467</v>
       </c>
       <c r="D50" s="11" t="s">
         <v>6</v>
@@ -9951,10 +9954,10 @@
         <v>968</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>2461</v>
+        <v>2462</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>2467</v>
+        <v>2468</v>
       </c>
       <c r="D51" s="11" t="s">
         <v>6</v>
@@ -9966,10 +9969,10 @@
         <v>938</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>2461</v>
+        <v>2462</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>2468</v>
+        <v>2469</v>
       </c>
       <c r="D52" s="11" t="s">
         <v>6</v>
@@ -9981,10 +9984,10 @@
         <v>965</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>2461</v>
+        <v>2462</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>2469</v>
+        <v>2470</v>
       </c>
       <c r="D53" s="11" t="s">
         <v>6</v>
@@ -10027,10 +10030,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>2470</v>
+        <v>2471</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>2471</v>
+        <v>2472</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>1042</v>
@@ -10051,13 +10054,13 @@
         <v>10</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>2472</v>
+        <v>2473</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10069,13 +10072,13 @@
         <v>8</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>2474</v>
+        <v>2475</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10087,13 +10090,13 @@
         <v>9</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>2475</v>
+        <v>2476</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10105,13 +10108,13 @@
         <v>7</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>2476</v>
+        <v>2477</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10123,13 +10126,13 @@
         <v>13</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>2477</v>
+        <v>2478</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10141,13 +10144,13 @@
         <v>8</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>2478</v>
+        <v>2479</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10159,13 +10162,13 @@
         <v>11</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>2479</v>
+        <v>2480</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10177,13 +10180,13 @@
         <v>10</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>2480</v>
+        <v>2481</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10195,13 +10198,13 @@
         <v>11</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>2481</v>
+        <v>2482</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10213,13 +10216,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>2482</v>
+        <v>2483</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10231,13 +10234,13 @@
         <v>6</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>2483</v>
+        <v>2484</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10249,13 +10252,13 @@
         <v>12</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>2484</v>
+        <v>2485</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10267,13 +10270,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>2485</v>
+        <v>2486</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10285,13 +10288,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>2486</v>
+        <v>2487</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10303,13 +10306,13 @@
         <v>12</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>2487</v>
+        <v>2488</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10321,13 +10324,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>2488</v>
+        <v>2489</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10339,13 +10342,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>2489</v>
+        <v>2490</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10357,13 +10360,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>2490</v>
+        <v>2491</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10375,13 +10378,13 @@
         <v>10</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>2491</v>
+        <v>2492</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10393,13 +10396,13 @@
         <v>12</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10411,13 +10414,13 @@
         <v>7</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10429,13 +10432,13 @@
         <v>9</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10447,13 +10450,13 @@
         <v>9</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10465,13 +10468,13 @@
         <v>8</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10483,13 +10486,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
     </row>
   </sheetData>
@@ -10528,10 +10531,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>1042</v>
@@ -10545,13 +10548,13 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>2501</v>
+        <v>2502</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>6</v>
@@ -10560,13 +10563,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>2501</v>
+        <v>2502</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>6</v>
@@ -10575,13 +10578,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>2501</v>
+        <v>2502</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>6</v>
@@ -10590,13 +10593,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>2507</v>
+        <v>2508</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2501</v>
+        <v>2502</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>2508</v>
+        <v>2509</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>6</v>
@@ -10605,13 +10608,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>2509</v>
+        <v>2510</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>2501</v>
+        <v>2502</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>2510</v>
+        <v>2511</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>6</v>
@@ -10620,13 +10623,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>2511</v>
+        <v>2512</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>2501</v>
+        <v>2502</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>2512</v>
+        <v>2513</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>6</v>
@@ -10635,13 +10638,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>2513</v>
+        <v>2514</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>2501</v>
+        <v>2502</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>2514</v>
+        <v>2515</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>6</v>
@@ -10650,13 +10653,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>2515</v>
+        <v>2516</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>2501</v>
+        <v>2502</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>2516</v>
+        <v>2517</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>6</v>
@@ -10665,13 +10668,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>2517</v>
+        <v>2518</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>1059</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>2518</v>
+        <v>2519</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>6</v>
@@ -10680,13 +10683,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>2519</v>
+        <v>2520</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>1059</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>2520</v>
+        <v>2521</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>6</v>
@@ -10695,13 +10698,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>2521</v>
+        <v>2522</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>1059</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>2522</v>
+        <v>2523</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>6</v>
@@ -10710,13 +10713,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>2523</v>
+        <v>2524</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>1059</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>2524</v>
+        <v>2525</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>6</v>
@@ -10725,13 +10728,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>2525</v>
+        <v>2526</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>1059</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>2526</v>
+        <v>2527</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>6</v>
@@ -10740,13 +10743,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>2527</v>
+        <v>2528</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>1059</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>2528</v>
+        <v>2529</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>6</v>
@@ -10755,13 +10758,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>2529</v>
+        <v>2530</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>1059</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>2530</v>
+        <v>2531</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>6</v>
@@ -10770,13 +10773,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>2531</v>
+        <v>2532</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>1059</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>2532</v>
+        <v>2533</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>6</v>
@@ -10785,13 +10788,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>2533</v>
+        <v>2534</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>1068</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>2534</v>
+        <v>2535</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>6</v>
@@ -10800,13 +10803,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>2535</v>
+        <v>2536</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>1046</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>2536</v>
+        <v>2537</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>6</v>
@@ -10815,13 +10818,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>2537</v>
+        <v>2538</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>1046</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>2538</v>
+        <v>2539</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>6</v>
@@ -10830,13 +10833,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>2539</v>
+        <v>2540</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>2540</v>
+        <v>2541</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>2541</v>
+        <v>2542</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>6</v>
@@ -10845,13 +10848,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>2542</v>
+        <v>2543</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>2540</v>
+        <v>2541</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>2543</v>
+        <v>2544</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>6</v>
@@ -10860,13 +10863,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>2544</v>
+        <v>2545</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>2540</v>
+        <v>2541</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>2545</v>
+        <v>2546</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>6</v>
@@ -10875,13 +10878,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>2546</v>
+        <v>2547</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>2540</v>
+        <v>2541</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>2547</v>
+        <v>2548</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>6</v>
@@ -10890,13 +10893,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>2548</v>
+        <v>2549</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>2540</v>
+        <v>2541</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>2549</v>
+        <v>2550</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>6</v>
@@ -10905,13 +10908,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
-        <v>2550</v>
+        <v>2551</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>2540</v>
+        <v>2541</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>2551</v>
+        <v>2552</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>6</v>
@@ -10920,13 +10923,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>2552</v>
+        <v>2553</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>2513</v>
+        <v>2514</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>2553</v>
+        <v>2554</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>6</v>
@@ -10935,13 +10938,13 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
-        <v>2554</v>
+        <v>2555</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>2513</v>
+        <v>2514</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>2555</v>
+        <v>2556</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>6</v>
@@ -10950,13 +10953,13 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>2556</v>
+        <v>2557</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>2513</v>
+        <v>2514</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>2557</v>
+        <v>2558</v>
       </c>
       <c r="D29" s="11" t="s">
         <v>6</v>
@@ -10965,13 +10968,13 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>2558</v>
+        <v>2559</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>2513</v>
+        <v>2514</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>2559</v>
+        <v>2560</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>6</v>
@@ -10980,13 +10983,13 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>2560</v>
+        <v>2561</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>2513</v>
+        <v>2514</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>2561</v>
+        <v>2562</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>6</v>
@@ -10995,13 +10998,13 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
-        <v>2562</v>
+        <v>2563</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>2513</v>
+        <v>2514</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>2563</v>
+        <v>2564</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>6</v>
@@ -11010,13 +11013,13 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>2564</v>
+        <v>2565</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>2513</v>
+        <v>2514</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>2565</v>
+        <v>2566</v>
       </c>
       <c r="D33" s="11" t="s">
         <v>6</v>
@@ -27082,10 +27085,10 @@
         <v>106</v>
       </c>
       <c r="D943" s="5" t="s">
-        <v>107</v>
+        <v>761</v>
       </c>
       <c r="E943" s="5" t="s">
-        <v>108</v>
+        <v>762</v>
       </c>
     </row>
     <row r="944" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -37524,7 +37527,7 @@
       </c>
       <c r="D88" s="10" t="n">
         <f aca="false">COUNTIF('Recipe Usage'!$D$2:$D$1114,A88)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E88" s="10" t="s">
         <v>1138</v>
@@ -38184,7 +38187,7 @@
       </c>
       <c r="D118" s="10" t="n">
         <f aca="false">COUNTIF('Recipe Usage'!$D$2:$D$1114,A118)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E118" s="10" t="s">
         <v>1171</v>
@@ -54201,16 +54204,16 @@
       </c>
       <c r="G43" s="12"/>
       <c r="H43" s="12" t="n">
-        <v>195</v>
+        <v>174</v>
       </c>
       <c r="I43" s="13" t="s">
-        <v>793</v>
+        <v>756</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>125</v>
+        <v>279</v>
       </c>
       <c r="K43" s="13" t="s">
-        <v>997</v>
+        <v>1024</v>
       </c>
       <c r="L43" s="16" t="n">
         <f aca="false">IF(M43="",0,LEN(M43)-LEN(SUBSTITUTE(M43,",",""))+1)</f>
@@ -54222,9 +54225,7 @@
       <c r="N43" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="O43" s="13" t="s">
-        <v>2204</v>
-      </c>
+      <c r="O43" s="13"/>
       <c r="P43" s="13"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54232,7 +54233,7 @@
         <v>25</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="C44" s="12" t="s">
         <v>904</v>
@@ -54261,13 +54262,13 @@
       </c>
       <c r="L44" s="16" t="n">
         <f aca="false">IF(M44="",0,LEN(M44)-LEN(SUBSTITUTE(M44,",",""))+1)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M44" s="13" t="s">
-        <v>2206</v>
+        <v>919</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O44" s="13" t="s">
         <v>2192</v>
@@ -54279,7 +54280,7 @@
         <v>25</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="C45" s="12" t="s">
         <v>904</v>
@@ -54311,7 +54312,7 @@
         <v>3</v>
       </c>
       <c r="M45" s="13" t="s">
-        <v>2207</v>
+        <v>2205</v>
       </c>
       <c r="N45" s="12" t="n">
         <v>5</v>
@@ -54324,7 +54325,7 @@
         <v>26</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="C46" s="12" t="s">
         <v>958</v>
@@ -54356,13 +54357,13 @@
         <v>2</v>
       </c>
       <c r="M46" s="13" t="s">
-        <v>2208</v>
+        <v>2206</v>
       </c>
       <c r="N46" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O46" s="13" t="s">
-        <v>2209</v>
+        <v>2207</v>
       </c>
       <c r="P46" s="13"/>
     </row>
@@ -54371,7 +54372,7 @@
         <v>26</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="C47" s="12" t="s">
         <v>958</v>
@@ -54383,32 +54384,34 @@
         <v>1016</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>979</v>
+        <v>1002</v>
       </c>
       <c r="G47" s="12"/>
       <c r="H47" s="12" t="n">
-        <v>90</v>
+        <v>177</v>
       </c>
       <c r="I47" s="13" t="s">
-        <v>591</v>
+        <v>763</v>
       </c>
       <c r="J47" s="12" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="K47" s="13" t="s">
-        <v>979</v>
+        <v>943</v>
       </c>
       <c r="L47" s="16" t="n">
         <f aca="false">IF(M47="",0,LEN(M47)-LEN(SUBSTITUTE(M47,",",""))+1)</f>
+        <v>2</v>
+      </c>
+      <c r="M47" s="13" t="s">
+        <v>2208</v>
+      </c>
+      <c r="N47" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="M47" s="13" t="s">
-        <v>593</v>
-      </c>
-      <c r="N47" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="O47" s="13"/>
+      <c r="O47" s="13" t="s">
+        <v>2207</v>
+      </c>
       <c r="P47" s="13"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54416,7 +54419,7 @@
         <v>27</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="C48" s="12" t="s">
         <v>923</v>
@@ -54428,30 +54431,30 @@
         <v>1024</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>1002</v>
+        <v>984</v>
       </c>
       <c r="G48" s="12"/>
       <c r="H48" s="12" t="n">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="I48" s="13" t="s">
-        <v>756</v>
+        <v>558</v>
       </c>
       <c r="J48" s="12" t="s">
-        <v>279</v>
+        <v>210</v>
       </c>
       <c r="K48" s="13" t="s">
-        <v>1024</v>
+        <v>973</v>
       </c>
       <c r="L48" s="16" t="n">
         <f aca="false">IF(M48="",0,LEN(M48)-LEN(SUBSTITUTE(M48,",",""))+1)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M48" s="13" t="s">
-        <v>2210</v>
+        <v>559</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O48" s="13"/>
       <c r="P48" s="13"/>
@@ -54461,7 +54464,7 @@
         <v>27</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="C49" s="12" t="s">
         <v>923</v>
@@ -54473,30 +54476,30 @@
         <v>1024</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>984</v>
+        <v>1002</v>
       </c>
       <c r="G49" s="12"/>
       <c r="H49" s="12" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I49" s="13" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="J49" s="12" t="s">
-        <v>210</v>
+        <v>51</v>
       </c>
       <c r="K49" s="13" t="s">
-        <v>973</v>
+        <v>923</v>
       </c>
       <c r="L49" s="16" t="n">
         <f aca="false">IF(M49="",0,LEN(M49)-LEN(SUBSTITUTE(M49,",",""))+1)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M49" s="13" t="s">
-        <v>559</v>
+        <v>2209</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O49" s="13"/>
       <c r="P49" s="13"/>
@@ -54506,7 +54509,7 @@
         <v>28</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="C50" s="12" t="s">
         <v>879</v>
@@ -54538,13 +54541,13 @@
         <v>6</v>
       </c>
       <c r="M50" s="13" t="s">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="N50" s="12" t="n">
         <v>4</v>
       </c>
       <c r="O50" s="13" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
       <c r="P50" s="13"/>
     </row>
@@ -54553,7 +54556,7 @@
         <v>28</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="C51" s="12" t="s">
         <v>879</v>
@@ -54582,16 +54585,16 @@
       </c>
       <c r="L51" s="16" t="n">
         <f aca="false">IF(M51="",0,LEN(M51)-LEN(SUBSTITUTE(M51,",",""))+1)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M51" s="13" t="s">
+        <v>2212</v>
+      </c>
+      <c r="N51" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="O51" s="13" t="s">
         <v>2213</v>
-      </c>
-      <c r="N51" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="O51" s="13" t="s">
-        <v>2214</v>
       </c>
       <c r="P51" s="13"/>
     </row>
@@ -54600,7 +54603,7 @@
         <v>29</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="C52" s="12" t="s">
         <v>934</v>
@@ -54612,30 +54615,30 @@
         <v>1024</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>1002</v>
-      </c>
-      <c r="G52" s="12" t="s">
-        <v>2158</v>
-      </c>
+        <v>979</v>
+      </c>
+      <c r="G52" s="12"/>
       <c r="H52" s="12" t="n">
-        <v>169</v>
+        <v>90</v>
       </c>
       <c r="I52" s="13" t="s">
-        <v>751</v>
+        <v>591</v>
       </c>
       <c r="J52" s="12" t="s">
-        <v>84</v>
+        <v>135</v>
       </c>
       <c r="K52" s="13" t="s">
-        <v>1002</v>
+        <v>979</v>
       </c>
       <c r="L52" s="16" t="n">
         <f aca="false">IF(M52="",0,LEN(M52)-LEN(SUBSTITUTE(M52,",",""))+1)</f>
-        <v>0</v>
-      </c>
-      <c r="M52" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="M52" s="13" t="s">
+        <v>593</v>
+      </c>
       <c r="N52" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O52" s="13"/>
       <c r="P52" s="13"/>
@@ -54645,7 +54648,7 @@
         <v>29</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="C53" s="12" t="s">
         <v>934</v>
@@ -54657,28 +54660,28 @@
         <v>1024</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>2140</v>
-      </c>
-      <c r="G53" s="12"/>
+        <v>1002</v>
+      </c>
+      <c r="G53" s="12" t="s">
+        <v>2158</v>
+      </c>
       <c r="H53" s="12" t="n">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="I53" s="13" t="s">
-        <v>776</v>
+        <v>751</v>
       </c>
       <c r="J53" s="12" t="s">
-        <v>171</v>
+        <v>84</v>
       </c>
       <c r="K53" s="13" t="s">
-        <v>934</v>
+        <v>1002</v>
       </c>
       <c r="L53" s="16" t="n">
         <f aca="false">IF(M53="",0,LEN(M53)-LEN(SUBSTITUTE(M53,",",""))+1)</f>
-        <v>1</v>
-      </c>
-      <c r="M53" s="13" t="s">
-        <v>777</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M53" s="13"/>
       <c r="N53" s="12" t="n">
         <v>4</v>
       </c>
@@ -54690,7 +54693,7 @@
         <v>30</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="C54" s="12" t="s">
         <v>987</v>
@@ -54722,7 +54725,7 @@
         <v>2</v>
       </c>
       <c r="M54" s="13" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="N54" s="12" t="n">
         <v>3</v>
@@ -54735,7 +54738,7 @@
         <v>30</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="C55" s="12" t="s">
         <v>987</v>
@@ -54780,13 +54783,13 @@
         <v>31</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="C56" s="12" t="s">
         <v>978</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>2216</v>
+        <v>2215</v>
       </c>
       <c r="E56" s="12" t="s">
         <v>1016</v>
@@ -54812,7 +54815,7 @@
         <v>2</v>
       </c>
       <c r="M56" s="13" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="N56" s="12" t="n">
         <v>5</v>
@@ -54827,13 +54830,13 @@
         <v>31</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="C57" s="12" t="s">
         <v>978</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>2216</v>
+        <v>2215</v>
       </c>
       <c r="E57" s="12" t="s">
         <v>1016</v>
@@ -54859,7 +54862,7 @@
         <v>2</v>
       </c>
       <c r="M57" s="13" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
       <c r="N57" s="12" t="n">
         <v>7</v>
@@ -54872,7 +54875,7 @@
         <v>32</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="C58" s="12" t="s">
         <v>904</v>
@@ -54884,40 +54887,42 @@
         <v>1016</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>984</v>
+        <v>1002</v>
       </c>
       <c r="G58" s="12"/>
       <c r="H58" s="12" t="n">
-        <v>131</v>
+        <v>195</v>
       </c>
       <c r="I58" s="13" t="s">
-        <v>677</v>
+        <v>793</v>
       </c>
       <c r="J58" s="12" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="K58" s="13" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="L58" s="16" t="n">
         <f aca="false">IF(M58="",0,LEN(M58)-LEN(SUBSTITUTE(M58,",",""))+1)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M58" s="13" t="s">
-        <v>176</v>
+        <v>2218</v>
       </c>
       <c r="N58" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="O58" s="13"/>
+        <v>4</v>
+      </c>
+      <c r="O58" s="13" t="s">
+        <v>2219</v>
+      </c>
       <c r="P58" s="13"/>
     </row>
-    <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="12" t="n">
         <v>32</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="C59" s="12" t="s">
         <v>904</v>
@@ -54929,28 +54934,30 @@
         <v>1016</v>
       </c>
       <c r="F59" s="12" t="s">
-        <v>1002</v>
+        <v>984</v>
       </c>
       <c r="G59" s="12"/>
       <c r="H59" s="12" t="n">
+        <v>131</v>
+      </c>
+      <c r="I59" s="13" t="s">
+        <v>677</v>
+      </c>
+      <c r="J59" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="I59" s="13" t="s">
-        <v>713</v>
-      </c>
-      <c r="J59" s="12" t="s">
-        <v>181</v>
-      </c>
       <c r="K59" s="13" t="s">
-        <v>1012</v>
+        <v>999</v>
       </c>
       <c r="L59" s="16" t="n">
         <f aca="false">IF(M59="",0,LEN(M59)-LEN(SUBSTITUTE(M59,",",""))+1)</f>
-        <v>0</v>
-      </c>
-      <c r="M59" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="M59" s="13" t="s">
+        <v>176</v>
+      </c>
       <c r="N59" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O59" s="13"/>
       <c r="P59" s="13"/>
@@ -54960,7 +54967,7 @@
         <v>33</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="C60" s="12" t="s">
         <v>958</v>
@@ -54998,7 +55005,7 @@
         <v>5</v>
       </c>
       <c r="O60" s="13" t="s">
-        <v>2220</v>
+        <v>2221</v>
       </c>
       <c r="P60" s="13"/>
     </row>
@@ -55007,7 +55014,7 @@
         <v>33</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="C61" s="12" t="s">
         <v>958</v>
@@ -55023,26 +55030,26 @@
       </c>
       <c r="G61" s="12"/>
       <c r="H61" s="12" t="n">
-        <v>152</v>
+        <v>39</v>
       </c>
       <c r="I61" s="13" t="s">
-        <v>721</v>
+        <v>368</v>
       </c>
       <c r="J61" s="12" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="K61" s="13" t="s">
-        <v>958</v>
+        <v>931</v>
       </c>
       <c r="L61" s="16" t="n">
         <f aca="false">IF(M61="",0,LEN(M61)-LEN(SUBSTITUTE(M61,",",""))+1)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M61" s="13" t="s">
-        <v>722</v>
+        <v>2222</v>
       </c>
       <c r="N61" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O61" s="13"/>
       <c r="P61" s="13"/>
@@ -55052,7 +55059,7 @@
         <v>34</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="C62" s="12" t="s">
         <v>923</v>
@@ -55084,13 +55091,13 @@
         <v>3</v>
       </c>
       <c r="M62" s="13" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="N62" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O62" s="13" t="s">
-        <v>2222</v>
+        <v>2224</v>
       </c>
       <c r="P62" s="13"/>
     </row>
@@ -55099,7 +55106,7 @@
         <v>34</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="C63" s="12" t="s">
         <v>923</v>
@@ -55128,16 +55135,16 @@
       </c>
       <c r="L63" s="16" t="n">
         <f aca="false">IF(M63="",0,LEN(M63)-LEN(SUBSTITUTE(M63,",",""))+1)</f>
+        <v>1</v>
+      </c>
+      <c r="M63" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="N63" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="M63" s="13" t="s">
-        <v>2223</v>
-      </c>
-      <c r="N63" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="O63" s="13" t="s">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="P63" s="13"/>
     </row>
@@ -55146,7 +55153,7 @@
         <v>35</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="C64" s="12" t="s">
         <v>879</v>
@@ -55178,13 +55185,13 @@
         <v>3</v>
       </c>
       <c r="M64" s="13" t="s">
-        <v>2225</v>
+        <v>2226</v>
       </c>
       <c r="N64" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O64" s="13" t="s">
-        <v>2226</v>
+        <v>2227</v>
       </c>
       <c r="P64" s="13"/>
     </row>
@@ -55193,7 +55200,7 @@
         <v>35</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="C65" s="12" t="s">
         <v>879</v>
@@ -55240,7 +55247,7 @@
         <v>36</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="C66" s="12" t="s">
         <v>934</v>
@@ -55285,7 +55292,7 @@
         <v>36</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="C67" s="12" t="s">
         <v>934</v>
@@ -55317,7 +55324,7 @@
         <v>3</v>
       </c>
       <c r="M67" s="13" t="s">
-        <v>2227</v>
+        <v>2228</v>
       </c>
       <c r="N67" s="12" t="n">
         <v>6</v>
@@ -55330,7 +55337,7 @@
         <v>37</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="C68" s="12" t="s">
         <v>987</v>
@@ -55377,7 +55384,7 @@
         <v>37</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="C69" s="12" t="s">
         <v>987</v>
@@ -55406,13 +55413,11 @@
       </c>
       <c r="L69" s="16" t="n">
         <f aca="false">IF(M69="",0,LEN(M69)-LEN(SUBSTITUTE(M69,",",""))+1)</f>
-        <v>1</v>
-      </c>
-      <c r="M69" s="13" t="s">
-        <v>331</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M69" s="13"/>
       <c r="N69" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O69" s="13"/>
       <c r="P69" s="13"/>
@@ -55422,7 +55427,7 @@
         <v>38</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="C70" s="12" t="s">
         <v>978</v>
@@ -55467,7 +55472,7 @@
         <v>38</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="C71" s="12" t="s">
         <v>978</v>
@@ -55512,13 +55517,13 @@
         <v>39</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="C72" s="12" t="s">
         <v>904</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>2228</v>
+        <v>2229</v>
       </c>
       <c r="E72" s="12" t="s">
         <v>931</v>
@@ -55544,7 +55549,7 @@
         <v>1</v>
       </c>
       <c r="M72" s="13" t="s">
-        <v>2229</v>
+        <v>2230</v>
       </c>
       <c r="N72" s="12" t="n">
         <v>3</v>
@@ -55559,13 +55564,13 @@
         <v>39</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="C73" s="12" t="s">
         <v>904</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>2228</v>
+        <v>2229</v>
       </c>
       <c r="E73" s="12" t="s">
         <v>931</v>
@@ -55591,7 +55596,7 @@
         <v>3</v>
       </c>
       <c r="M73" s="13" t="s">
-        <v>2230</v>
+        <v>2231</v>
       </c>
       <c r="N73" s="12" t="n">
         <v>7</v>
@@ -55604,7 +55609,7 @@
         <v>40</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="C74" s="12" t="s">
         <v>958</v>
@@ -55647,7 +55652,7 @@
         <v>40</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="C75" s="12" t="s">
         <v>958</v>
@@ -55692,7 +55697,7 @@
         <v>41</v>
       </c>
       <c r="B76" s="12" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="C76" s="12" t="s">
         <v>923</v>
@@ -55724,7 +55729,7 @@
         <v>2</v>
       </c>
       <c r="M76" s="13" t="s">
-        <v>2232</v>
+        <v>2233</v>
       </c>
       <c r="N76" s="12" t="n">
         <v>3</v>
@@ -55737,7 +55742,7 @@
         <v>41</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="C77" s="12" t="s">
         <v>923</v>
@@ -55780,7 +55785,7 @@
         <v>42</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="C78" s="12" t="s">
         <v>879</v>
@@ -55825,7 +55830,7 @@
         <v>42</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="C79" s="12" t="s">
         <v>879</v>
@@ -55868,7 +55873,7 @@
         <v>43</v>
       </c>
       <c r="B80" s="12" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="C80" s="12" t="s">
         <v>934</v>
@@ -55913,7 +55918,7 @@
         <v>44</v>
       </c>
       <c r="B81" s="12" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="C81" s="12" t="s">
         <v>987</v>
@@ -55945,13 +55950,13 @@
         <v>2</v>
       </c>
       <c r="M81" s="13" t="s">
-        <v>2233</v>
+        <v>2234</v>
       </c>
       <c r="N81" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O81" s="13" t="s">
-        <v>2234</v>
+        <v>2235</v>
       </c>
       <c r="P81" s="13"/>
     </row>
@@ -55960,7 +55965,7 @@
         <v>45</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="C82" s="12" t="s">
         <v>978</v>
@@ -56000,7 +56005,7 @@
         <v>5</v>
       </c>
       <c r="O82" s="13" t="s">
-        <v>2235</v>
+        <v>2236</v>
       </c>
       <c r="P82" s="13"/>
     </row>
@@ -56009,7 +56014,7 @@
         <v>45</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="C83" s="12" t="s">
         <v>978</v>
@@ -56054,7 +56059,7 @@
         <v>46</v>
       </c>
       <c r="B84" s="12" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="C84" s="12" t="s">
         <v>904</v>
@@ -56097,13 +56102,13 @@
         <v>47</v>
       </c>
       <c r="B85" s="12" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="C85" s="12" t="s">
         <v>958</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
       <c r="E85" s="12" t="s">
         <v>931</v>
@@ -56129,7 +56134,7 @@
         <v>1</v>
       </c>
       <c r="M85" s="13" t="s">
-        <v>2237</v>
+        <v>2238</v>
       </c>
       <c r="N85" s="12" t="n">
         <v>8</v>
@@ -56139,12 +56144,12 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="12" t="n">
         <v>48</v>
       </c>
       <c r="B86" s="12" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="C86" s="12" t="s">
         <v>923</v>
@@ -56156,28 +56161,28 @@
         <v>1016</v>
       </c>
       <c r="F86" s="12" t="s">
-        <v>2140</v>
-      </c>
-      <c r="G86" s="12"/>
+        <v>1002</v>
+      </c>
+      <c r="G86" s="12" t="s">
+        <v>2158</v>
+      </c>
       <c r="H86" s="12" t="n">
-        <v>80</v>
+        <v>148</v>
       </c>
       <c r="I86" s="13" t="s">
-        <v>563</v>
+        <v>713</v>
       </c>
       <c r="J86" s="12" t="s">
-        <v>51</v>
+        <v>181</v>
       </c>
       <c r="K86" s="13" t="s">
-        <v>923</v>
+        <v>1012</v>
       </c>
       <c r="L86" s="16" t="n">
         <f aca="false">IF(M86="",0,LEN(M86)-LEN(SUBSTITUTE(M86,",",""))+1)</f>
-        <v>1</v>
-      </c>
-      <c r="M86" s="13" t="s">
-        <v>323</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M86" s="13"/>
       <c r="N86" s="12" t="n">
         <v>7</v>
       </c>
@@ -56189,7 +56194,7 @@
         <v>49</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
       <c r="C87" s="12" t="s">
         <v>879</v>
@@ -56221,13 +56226,13 @@
         <v>2</v>
       </c>
       <c r="M87" s="13" t="s">
-        <v>2239</v>
+        <v>2240</v>
       </c>
       <c r="N87" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O87" s="13" t="s">
-        <v>2235</v>
+        <v>2236</v>
       </c>
       <c r="P87" s="13"/>
     </row>
@@ -56236,7 +56241,7 @@
         <v>49</v>
       </c>
       <c r="B88" s="12" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
       <c r="C88" s="12" t="s">
         <v>879</v>
@@ -56279,7 +56284,7 @@
         <v>50</v>
       </c>
       <c r="B89" s="12" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
       <c r="C89" s="12" t="s">
         <v>934</v>
@@ -56311,7 +56316,7 @@
         <v>2</v>
       </c>
       <c r="M89" s="13" t="s">
-        <v>2240</v>
+        <v>2241</v>
       </c>
       <c r="N89" s="12" t="n">
         <v>10</v>
@@ -56324,7 +56329,7 @@
         <v>51</v>
       </c>
       <c r="B90" s="12" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
       <c r="C90" s="12" t="s">
         <v>987</v>
@@ -56367,7 +56372,7 @@
         <v>52</v>
       </c>
       <c r="B91" s="12" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
       <c r="C91" s="12" t="s">
         <v>978</v>
@@ -56414,7 +56419,7 @@
         <v>53</v>
       </c>
       <c r="B92" s="12" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
       <c r="C92" s="12" t="s">
         <v>904</v>
@@ -56459,7 +56464,7 @@
         <v>53</v>
       </c>
       <c r="B93" s="12" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
       <c r="C93" s="12" t="s">
         <v>904</v>
@@ -56502,7 +56507,7 @@
         <v>54</v>
       </c>
       <c r="B94" s="12" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
       <c r="C94" s="12" t="s">
         <v>958</v>
@@ -56547,13 +56552,13 @@
         <v>55</v>
       </c>
       <c r="B95" s="12" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
       <c r="C95" s="12" t="s">
         <v>923</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>2241</v>
+        <v>2242</v>
       </c>
       <c r="E95" s="12" t="s">
         <v>1016</v>
@@ -56579,7 +56584,7 @@
         <v>1</v>
       </c>
       <c r="M95" s="13" t="s">
-        <v>2242</v>
+        <v>2243</v>
       </c>
       <c r="N95" s="12" t="n">
         <v>3</v>
@@ -56594,7 +56599,7 @@
         <v>56</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
       <c r="C96" s="12" t="s">
         <v>879</v>
@@ -56610,24 +56615,26 @@
       </c>
       <c r="G96" s="12"/>
       <c r="H96" s="12" t="n">
-        <v>39</v>
+        <v>198</v>
       </c>
       <c r="I96" s="13" t="s">
-        <v>368</v>
+        <v>796</v>
       </c>
       <c r="J96" s="12" t="s">
-        <v>210</v>
+        <v>77</v>
       </c>
       <c r="K96" s="13" t="s">
-        <v>931</v>
+        <v>997</v>
       </c>
       <c r="L96" s="16" t="n">
         <f aca="false">IF(M96="",0,LEN(M96)-LEN(SUBSTITUTE(M96,",",""))+1)</f>
-        <v>0</v>
-      </c>
-      <c r="M96" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="M96" s="13" t="s">
+        <v>2244</v>
+      </c>
       <c r="N96" s="12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O96" s="13"/>
       <c r="P96" s="13"/>
@@ -56637,7 +56644,7 @@
         <v>57</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>2243</v>
+        <v>2245</v>
       </c>
       <c r="C97" s="12" t="s">
         <v>934</v>
@@ -56680,7 +56687,7 @@
         <v>57</v>
       </c>
       <c r="B98" s="12" t="s">
-        <v>2243</v>
+        <v>2245</v>
       </c>
       <c r="C98" s="12" t="s">
         <v>934</v>
@@ -56725,7 +56732,7 @@
         <v>58</v>
       </c>
       <c r="B99" s="12" t="s">
-        <v>2243</v>
+        <v>2245</v>
       </c>
       <c r="C99" s="12" t="s">
         <v>987</v>
@@ -56768,7 +56775,7 @@
         <v>59</v>
       </c>
       <c r="B100" s="12" t="s">
-        <v>2243</v>
+        <v>2245</v>
       </c>
       <c r="C100" s="12" t="s">
         <v>978</v>
@@ -56813,7 +56820,7 @@
         <v>60</v>
       </c>
       <c r="B101" s="12" t="s">
-        <v>2243</v>
+        <v>2245</v>
       </c>
       <c r="C101" s="12" t="s">
         <v>904</v>
@@ -56856,7 +56863,7 @@
         <v>61</v>
       </c>
       <c r="B102" s="12" t="s">
-        <v>2243</v>
+        <v>2245</v>
       </c>
       <c r="C102" s="12" t="s">
         <v>958</v>
@@ -56888,7 +56895,7 @@
         <v>3</v>
       </c>
       <c r="M102" s="13" t="s">
-        <v>2244</v>
+        <v>2246</v>
       </c>
       <c r="N102" s="12" t="n">
         <v>3</v>
@@ -56901,7 +56908,7 @@
         <v>61</v>
       </c>
       <c r="B103" s="12" t="s">
-        <v>2243</v>
+        <v>2245</v>
       </c>
       <c r="C103" s="12" t="s">
         <v>958</v>
@@ -56917,24 +56924,26 @@
       </c>
       <c r="G103" s="12"/>
       <c r="H103" s="12" t="n">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="I103" s="13" t="s">
-        <v>739</v>
+        <v>721</v>
       </c>
       <c r="J103" s="12" t="s">
-        <v>25</v>
+        <v>181</v>
       </c>
       <c r="K103" s="13" t="s">
-        <v>1020</v>
+        <v>958</v>
       </c>
       <c r="L103" s="16" t="n">
         <f aca="false">IF(M103="",0,LEN(M103)-LEN(SUBSTITUTE(M103,",",""))+1)</f>
-        <v>0</v>
-      </c>
-      <c r="M103" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="M103" s="13" t="s">
+        <v>722</v>
+      </c>
       <c r="N103" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O103" s="13"/>
       <c r="P103" s="13"/>
@@ -56944,7 +56953,7 @@
         <v>62</v>
       </c>
       <c r="B104" s="12" t="s">
-        <v>2243</v>
+        <v>2245</v>
       </c>
       <c r="C104" s="12" t="s">
         <v>923</v>
@@ -56989,7 +56998,7 @@
         <v>62</v>
       </c>
       <c r="B105" s="12" t="s">
-        <v>2243</v>
+        <v>2245</v>
       </c>
       <c r="C105" s="12" t="s">
         <v>923</v>
@@ -57036,13 +57045,13 @@
         <v>63</v>
       </c>
       <c r="B106" s="12" t="s">
-        <v>2243</v>
+        <v>2245</v>
       </c>
       <c r="C106" s="12" t="s">
         <v>879</v>
       </c>
       <c r="D106" s="12" t="s">
-        <v>2245</v>
+        <v>2247</v>
       </c>
       <c r="E106" s="12" t="s">
         <v>1016</v>
@@ -57074,7 +57083,7 @@
         <v>8</v>
       </c>
       <c r="O106" s="13" t="s">
-        <v>2246</v>
+        <v>2248</v>
       </c>
       <c r="P106" s="13" t="s">
         <v>2181</v>
@@ -57085,13 +57094,13 @@
         <v>63</v>
       </c>
       <c r="B107" s="12" t="s">
-        <v>2243</v>
+        <v>2245</v>
       </c>
       <c r="C107" s="12" t="s">
         <v>879</v>
       </c>
       <c r="D107" s="12" t="s">
-        <v>2245</v>
+        <v>2247</v>
       </c>
       <c r="E107" s="12" t="s">
         <v>1016</v>
@@ -57117,7 +57126,7 @@
         <v>2</v>
       </c>
       <c r="M107" s="13" t="s">
-        <v>2247</v>
+        <v>2249</v>
       </c>
       <c r="N107" s="12" t="n">
         <v>6</v>
@@ -57132,13 +57141,13 @@
         <v>63</v>
       </c>
       <c r="B108" s="12" t="s">
-        <v>2243</v>
+        <v>2245</v>
       </c>
       <c r="C108" s="12" t="s">
         <v>879</v>
       </c>
       <c r="D108" s="12" t="s">
-        <v>2245</v>
+        <v>2247</v>
       </c>
       <c r="E108" s="12" t="s">
         <v>1016</v>
@@ -57179,7 +57188,7 @@
         <v>64</v>
       </c>
       <c r="B109" s="12" t="s">
-        <v>2243</v>
+        <v>2245</v>
       </c>
       <c r="C109" s="12" t="s">
         <v>934</v>
@@ -57224,7 +57233,7 @@
         <v>64</v>
       </c>
       <c r="B110" s="12" t="s">
-        <v>2243</v>
+        <v>2245</v>
       </c>
       <c r="C110" s="12" t="s">
         <v>934</v>
@@ -57269,7 +57278,7 @@
         <v>64</v>
       </c>
       <c r="B111" s="12" t="s">
-        <v>2243</v>
+        <v>2245</v>
       </c>
       <c r="C111" s="12" t="s">
         <v>934</v>
@@ -57316,7 +57325,7 @@
         <v>65</v>
       </c>
       <c r="B112" s="12" t="s">
-        <v>2248</v>
+        <v>2250</v>
       </c>
       <c r="C112" s="12" t="s">
         <v>987</v>
@@ -57359,7 +57368,7 @@
         <v>66</v>
       </c>
       <c r="B113" s="12" t="s">
-        <v>2248</v>
+        <v>2250</v>
       </c>
       <c r="C113" s="12" t="s">
         <v>978</v>
@@ -57402,7 +57411,7 @@
         <v>67</v>
       </c>
       <c r="B114" s="12" t="s">
-        <v>2248</v>
+        <v>2250</v>
       </c>
       <c r="C114" s="12" t="s">
         <v>904</v>
@@ -57445,7 +57454,7 @@
         <v>68</v>
       </c>
       <c r="B115" s="12" t="s">
-        <v>2248</v>
+        <v>2250</v>
       </c>
       <c r="C115" s="12" t="s">
         <v>958</v>
@@ -57461,16 +57470,16 @@
       </c>
       <c r="G115" s="12"/>
       <c r="H115" s="12" t="n">
-        <v>204</v>
+        <v>162</v>
       </c>
       <c r="I115" s="13" t="s">
-        <v>807</v>
+        <v>739</v>
       </c>
       <c r="J115" s="12" t="s">
-        <v>148</v>
+        <v>25</v>
       </c>
       <c r="K115" s="13" t="s">
-        <v>958</v>
+        <v>1020</v>
       </c>
       <c r="L115" s="16" t="n">
         <f aca="false">IF(M115="",0,LEN(M115)-LEN(SUBSTITUTE(M115,",",""))+1)</f>
@@ -57478,7 +57487,7 @@
       </c>
       <c r="M115" s="13"/>
       <c r="N115" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O115" s="13"/>
       <c r="P115" s="13"/>
@@ -57488,7 +57497,7 @@
         <v>69</v>
       </c>
       <c r="B116" s="12" t="s">
-        <v>2248</v>
+        <v>2250</v>
       </c>
       <c r="C116" s="12" t="s">
         <v>923</v>
@@ -57520,13 +57529,13 @@
         <v>2</v>
       </c>
       <c r="M116" s="13" t="s">
-        <v>2249</v>
+        <v>2251</v>
       </c>
       <c r="N116" s="12" t="n">
         <v>7</v>
       </c>
       <c r="O116" s="13" t="s">
-        <v>2250</v>
+        <v>2252</v>
       </c>
       <c r="P116" s="13"/>
     </row>
@@ -57535,7 +57544,7 @@
         <v>70</v>
       </c>
       <c r="B117" s="12" t="s">
-        <v>2248</v>
+        <v>2250</v>
       </c>
       <c r="C117" s="12" t="s">
         <v>879</v>
@@ -57580,13 +57589,13 @@
         <v>71</v>
       </c>
       <c r="B118" s="12" t="s">
-        <v>2248</v>
+        <v>2250</v>
       </c>
       <c r="C118" s="12" t="s">
         <v>934</v>
       </c>
       <c r="D118" s="12" t="s">
-        <v>2251</v>
+        <v>2253</v>
       </c>
       <c r="E118" s="12" t="s">
         <v>1016</v>
@@ -57625,13 +57634,13 @@
         <v>71</v>
       </c>
       <c r="B119" s="12" t="s">
-        <v>2248</v>
+        <v>2250</v>
       </c>
       <c r="C119" s="12" t="s">
         <v>934</v>
       </c>
       <c r="D119" s="12" t="s">
-        <v>2251</v>
+        <v>2253</v>
       </c>
       <c r="E119" s="12" t="s">
         <v>1016</v>
@@ -57657,7 +57666,7 @@
         <v>1</v>
       </c>
       <c r="M119" s="13" t="s">
-        <v>2252</v>
+        <v>2254</v>
       </c>
       <c r="N119" s="12" t="n">
         <v>6</v>
@@ -57672,7 +57681,7 @@
         <v>72</v>
       </c>
       <c r="B120" s="12" t="s">
-        <v>2248</v>
+        <v>2250</v>
       </c>
       <c r="C120" s="12" t="s">
         <v>987</v>
@@ -57688,26 +57697,24 @@
       </c>
       <c r="G120" s="12"/>
       <c r="H120" s="12" t="n">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="I120" s="13" t="s">
-        <v>796</v>
+        <v>845</v>
       </c>
       <c r="J120" s="12" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="K120" s="13" t="s">
-        <v>997</v>
+        <v>943</v>
       </c>
       <c r="L120" s="16" t="n">
         <f aca="false">IF(M120="",0,LEN(M120)-LEN(SUBSTITUTE(M120,",",""))+1)</f>
-        <v>1</v>
-      </c>
-      <c r="M120" s="13" t="s">
-        <v>667</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M120" s="13"/>
       <c r="N120" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O120" s="13"/>
       <c r="P120" s="13"/>
@@ -57717,7 +57724,7 @@
         <v>73</v>
       </c>
       <c r="B121" s="12" t="s">
-        <v>2253</v>
+        <v>2255</v>
       </c>
       <c r="C121" s="12" t="s">
         <v>978</v>
@@ -57760,7 +57767,7 @@
         <v>74</v>
       </c>
       <c r="B122" s="12" t="s">
-        <v>2253</v>
+        <v>2255</v>
       </c>
       <c r="C122" s="12" t="s">
         <v>904</v>
@@ -57803,7 +57810,7 @@
         <v>75</v>
       </c>
       <c r="B123" s="12" t="s">
-        <v>2253</v>
+        <v>2255</v>
       </c>
       <c r="C123" s="12" t="s">
         <v>958</v>
@@ -57835,7 +57842,7 @@
         <v>2</v>
       </c>
       <c r="M123" s="13" t="s">
-        <v>2254</v>
+        <v>2256</v>
       </c>
       <c r="N123" s="12" t="n">
         <v>2</v>
@@ -57848,7 +57855,7 @@
         <v>76</v>
       </c>
       <c r="B124" s="12" t="s">
-        <v>2253</v>
+        <v>2255</v>
       </c>
       <c r="C124" s="12" t="s">
         <v>923</v>
@@ -57893,7 +57900,7 @@
         <v>77</v>
       </c>
       <c r="B125" s="12" t="s">
-        <v>2253</v>
+        <v>2255</v>
       </c>
       <c r="C125" s="12" t="s">
         <v>879</v>
@@ -57909,13 +57916,13 @@
       </c>
       <c r="G125" s="12"/>
       <c r="H125" s="12" t="n">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="I125" s="13" t="s">
-        <v>845</v>
+        <v>854</v>
       </c>
       <c r="J125" s="12" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="K125" s="13" t="s">
         <v>943</v>
@@ -57936,7 +57943,7 @@
         <v>78</v>
       </c>
       <c r="B126" s="12" t="s">
-        <v>2253</v>
+        <v>2255</v>
       </c>
       <c r="C126" s="12" t="s">
         <v>934</v>
@@ -57952,24 +57959,26 @@
       </c>
       <c r="G126" s="12"/>
       <c r="H126" s="12" t="n">
-        <v>233</v>
+        <v>186</v>
       </c>
       <c r="I126" s="13" t="s">
-        <v>854</v>
+        <v>776</v>
       </c>
       <c r="J126" s="12" t="s">
-        <v>84</v>
+        <v>171</v>
       </c>
       <c r="K126" s="13" t="s">
-        <v>943</v>
+        <v>934</v>
       </c>
       <c r="L126" s="16" t="n">
         <f aca="false">IF(M126="",0,LEN(M126)-LEN(SUBSTITUTE(M126,",",""))+1)</f>
-        <v>0</v>
-      </c>
-      <c r="M126" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="M126" s="13" t="s">
+        <v>777</v>
+      </c>
       <c r="N126" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O126" s="13"/>
       <c r="P126" s="13"/>
@@ -57979,13 +57988,13 @@
         <v>79</v>
       </c>
       <c r="B127" s="12" t="s">
-        <v>2253</v>
+        <v>2255</v>
       </c>
       <c r="C127" s="12" t="s">
         <v>987</v>
       </c>
       <c r="D127" s="12" t="s">
-        <v>2255</v>
+        <v>2257</v>
       </c>
       <c r="E127" s="12" t="s">
         <v>1016</v>
@@ -58024,13 +58033,13 @@
         <v>79</v>
       </c>
       <c r="B128" s="12" t="s">
-        <v>2253</v>
+        <v>2255</v>
       </c>
       <c r="C128" s="12" t="s">
         <v>987</v>
       </c>
       <c r="D128" s="12" t="s">
-        <v>2255</v>
+        <v>2257</v>
       </c>
       <c r="E128" s="12" t="s">
         <v>1016</v>
@@ -58056,7 +58065,7 @@
         <v>1</v>
       </c>
       <c r="M128" s="13" t="s">
-        <v>2256</v>
+        <v>2258</v>
       </c>
       <c r="N128" s="12" t="n">
         <v>4</v>
@@ -58071,7 +58080,7 @@
         <v>80</v>
       </c>
       <c r="B129" s="12" t="s">
-        <v>2253</v>
+        <v>2255</v>
       </c>
       <c r="C129" s="12" t="s">
         <v>978</v>
@@ -58109,7 +58118,7 @@
         <v>3</v>
       </c>
       <c r="O129" s="13" t="s">
-        <v>2257</v>
+        <v>2259</v>
       </c>
       <c r="P129" s="13"/>
     </row>
@@ -58118,7 +58127,7 @@
         <v>81</v>
       </c>
       <c r="B130" s="12" t="s">
-        <v>2258</v>
+        <v>2260</v>
       </c>
       <c r="C130" s="12" t="s">
         <v>904</v>
@@ -58134,30 +58143,26 @@
       </c>
       <c r="G130" s="12"/>
       <c r="H130" s="12" t="n">
-        <v>177</v>
+        <v>237</v>
       </c>
       <c r="I130" s="13" t="s">
-        <v>763</v>
+        <v>860</v>
       </c>
       <c r="J130" s="12" t="s">
-        <v>148</v>
+        <v>210</v>
       </c>
       <c r="K130" s="13" t="s">
         <v>943</v>
       </c>
       <c r="L130" s="16" t="n">
         <f aca="false">IF(M130="",0,LEN(M130)-LEN(SUBSTITUTE(M130,",",""))+1)</f>
-        <v>1</v>
-      </c>
-      <c r="M130" s="13" t="s">
-        <v>390</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M130" s="13"/>
       <c r="N130" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="O130" s="13" t="s">
-        <v>2259</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="O130" s="13"/>
       <c r="P130" s="13"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58165,7 +58170,7 @@
         <v>82</v>
       </c>
       <c r="B131" s="12" t="s">
-        <v>2258</v>
+        <v>2260</v>
       </c>
       <c r="C131" s="12" t="s">
         <v>958</v>
@@ -58210,7 +58215,7 @@
         <v>83</v>
       </c>
       <c r="B132" s="12" t="s">
-        <v>2258</v>
+        <v>2260</v>
       </c>
       <c r="C132" s="12" t="s">
         <v>923</v>
@@ -58250,59 +58255,63 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="12" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B133" s="12" t="s">
-        <v>2258</v>
+        <v>2260</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>879</v>
+        <v>934</v>
       </c>
       <c r="D133" s="12" t="s">
-        <v>971</v>
+        <v>2147</v>
       </c>
       <c r="E133" s="12" t="s">
-        <v>931</v>
+        <v>1016</v>
       </c>
       <c r="F133" s="12" t="s">
         <v>1002</v>
       </c>
       <c r="G133" s="12"/>
       <c r="H133" s="12" t="n">
-        <v>237</v>
+        <v>101</v>
       </c>
       <c r="I133" s="13" t="s">
-        <v>860</v>
+        <v>621</v>
       </c>
       <c r="J133" s="12" t="s">
-        <v>210</v>
+        <v>25</v>
       </c>
       <c r="K133" s="13" t="s">
-        <v>943</v>
+        <v>965</v>
       </c>
       <c r="L133" s="16" t="n">
         <f aca="false">IF(M133="",0,LEN(M133)-LEN(SUBSTITUTE(M133,",",""))+1)</f>
-        <v>0</v>
-      </c>
-      <c r="M133" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="M133" s="13" t="s">
+        <v>965</v>
+      </c>
       <c r="N133" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="O133" s="13"/>
+        <v>8</v>
+      </c>
+      <c r="O133" s="13" t="s">
+        <v>2261</v>
+      </c>
       <c r="P133" s="13"/>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="12" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B134" s="12" t="s">
-        <v>2258</v>
+        <v>2260</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>934</v>
+        <v>978</v>
       </c>
       <c r="D134" s="12" t="s">
-        <v>2147</v>
+        <v>2262</v>
       </c>
       <c r="E134" s="12" t="s">
         <v>1016</v>
@@ -58312,44 +58321,44 @@
       </c>
       <c r="G134" s="12"/>
       <c r="H134" s="12" t="n">
-        <v>101</v>
+        <v>3</v>
       </c>
       <c r="I134" s="13" t="s">
-        <v>621</v>
+        <v>50</v>
       </c>
       <c r="J134" s="12" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="K134" s="13" t="s">
-        <v>965</v>
+        <v>875</v>
       </c>
       <c r="L134" s="16" t="n">
         <f aca="false">IF(M134="",0,LEN(M134)-LEN(SUBSTITUTE(M134,",",""))+1)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M134" s="13" t="s">
-        <v>965</v>
+        <v>2263</v>
       </c>
       <c r="N134" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="O134" s="13" t="s">
-        <v>2260</v>
-      </c>
-      <c r="P134" s="13"/>
-    </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>9</v>
+      </c>
+      <c r="O134" s="13"/>
+      <c r="P134" s="13" t="s">
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="12" t="n">
         <v>87</v>
       </c>
       <c r="B135" s="12" t="s">
-        <v>2258</v>
+        <v>2260</v>
       </c>
       <c r="C135" s="12" t="s">
         <v>978</v>
       </c>
       <c r="D135" s="12" t="s">
-        <v>2261</v>
+        <v>2262</v>
       </c>
       <c r="E135" s="12" t="s">
         <v>1016</v>
@@ -58359,44 +58368,44 @@
       </c>
       <c r="G135" s="12"/>
       <c r="H135" s="12" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="I135" s="13" t="s">
-        <v>50</v>
+        <v>377</v>
       </c>
       <c r="J135" s="12" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="K135" s="13" t="s">
-        <v>875</v>
+        <v>932</v>
       </c>
       <c r="L135" s="16" t="n">
         <f aca="false">IF(M135="",0,LEN(M135)-LEN(SUBSTITUTE(M135,",",""))+1)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M135" s="13" t="s">
-        <v>2262</v>
+        <v>2264</v>
       </c>
       <c r="N135" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O135" s="13"/>
       <c r="P135" s="13" t="s">
         <v>2181</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="12" t="n">
         <v>87</v>
       </c>
       <c r="B136" s="12" t="s">
-        <v>2258</v>
+        <v>2260</v>
       </c>
       <c r="C136" s="12" t="s">
         <v>978</v>
       </c>
       <c r="D136" s="12" t="s">
-        <v>2261</v>
+        <v>2262</v>
       </c>
       <c r="E136" s="12" t="s">
         <v>1016</v>
@@ -58406,23 +58415,23 @@
       </c>
       <c r="G136" s="12"/>
       <c r="H136" s="12" t="n">
-        <v>40</v>
+        <v>112</v>
       </c>
       <c r="I136" s="13" t="s">
-        <v>377</v>
+        <v>641</v>
       </c>
       <c r="J136" s="12" t="s">
-        <v>38</v>
+        <v>210</v>
       </c>
       <c r="K136" s="13" t="s">
-        <v>932</v>
+        <v>875</v>
       </c>
       <c r="L136" s="16" t="n">
         <f aca="false">IF(M136="",0,LEN(M136)-LEN(SUBSTITUTE(M136,",",""))+1)</f>
         <v>1</v>
       </c>
       <c r="M136" s="13" t="s">
-        <v>2263</v>
+        <v>644</v>
       </c>
       <c r="N136" s="12" t="n">
         <v>7</v>
@@ -58437,42 +58446,42 @@
         <v>87</v>
       </c>
       <c r="B137" s="12" t="s">
-        <v>2258</v>
+        <v>2260</v>
       </c>
       <c r="C137" s="12" t="s">
         <v>978</v>
       </c>
       <c r="D137" s="12" t="s">
-        <v>2261</v>
+        <v>2262</v>
       </c>
       <c r="E137" s="12" t="s">
         <v>1016</v>
       </c>
       <c r="F137" s="12" t="s">
-        <v>1002</v>
-      </c>
-      <c r="G137" s="12"/>
+        <v>984</v>
+      </c>
+      <c r="G137" s="12" t="s">
+        <v>2158</v>
+      </c>
       <c r="H137" s="12" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I137" s="13" t="s">
-        <v>641</v>
+        <v>651</v>
       </c>
       <c r="J137" s="12" t="s">
-        <v>210</v>
+        <v>51</v>
       </c>
       <c r="K137" s="13" t="s">
-        <v>875</v>
+        <v>993</v>
       </c>
       <c r="L137" s="16" t="n">
         <f aca="false">IF(M137="",0,LEN(M137)-LEN(SUBSTITUTE(M137,",",""))+1)</f>
-        <v>1</v>
-      </c>
-      <c r="M137" s="13" t="s">
-        <v>644</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M137" s="13"/>
       <c r="N137" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O137" s="13"/>
       <c r="P137" s="13" t="s">
@@ -58481,37 +58490,35 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="12" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B138" s="12" t="s">
-        <v>2258</v>
+        <v>2265</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>978</v>
+        <v>958</v>
       </c>
       <c r="D138" s="12" t="s">
-        <v>2261</v>
+        <v>2138</v>
       </c>
       <c r="E138" s="12" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="F138" s="12" t="s">
-        <v>984</v>
-      </c>
-      <c r="G138" s="12" t="s">
-        <v>2158</v>
-      </c>
+        <v>1002</v>
+      </c>
+      <c r="G138" s="12"/>
       <c r="H138" s="12" t="n">
-        <v>115</v>
+        <v>204</v>
       </c>
       <c r="I138" s="13" t="s">
-        <v>651</v>
+        <v>807</v>
       </c>
       <c r="J138" s="12" t="s">
-        <v>51</v>
+        <v>148</v>
       </c>
       <c r="K138" s="13" t="s">
-        <v>993</v>
+        <v>958</v>
       </c>
       <c r="L138" s="16" t="n">
         <f aca="false">IF(M138="",0,LEN(M138)-LEN(SUBSTITUTE(M138,",",""))+1)</f>
@@ -58519,44 +58526,44 @@
       </c>
       <c r="M138" s="13"/>
       <c r="N138" s="12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="O138" s="13"/>
-      <c r="P138" s="13" t="s">
-        <v>2181</v>
-      </c>
+      <c r="P138" s="13"/>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="12" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B139" s="12" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>958</v>
+        <v>879</v>
       </c>
       <c r="D139" s="12" t="s">
-        <v>2138</v>
+        <v>995</v>
       </c>
       <c r="E139" s="12" t="s">
         <v>1018</v>
       </c>
       <c r="F139" s="12" t="s">
-        <v>1002</v>
-      </c>
-      <c r="G139" s="12"/>
+        <v>984</v>
+      </c>
+      <c r="G139" s="12" t="s">
+        <v>2158</v>
+      </c>
       <c r="H139" s="12" t="n">
-        <v>213</v>
+        <v>120</v>
       </c>
       <c r="I139" s="13" t="s">
-        <v>818</v>
+        <v>660</v>
       </c>
       <c r="J139" s="12" t="s">
-        <v>210</v>
+        <v>148</v>
       </c>
       <c r="K139" s="13" t="s">
-        <v>958</v>
+        <v>989</v>
       </c>
       <c r="L139" s="16" t="n">
         <f aca="false">IF(M139="",0,LEN(M139)-LEN(SUBSTITUTE(M139,",",""))+1)</f>
@@ -58564,7 +58571,7 @@
       </c>
       <c r="M139" s="13"/>
       <c r="N139" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O139" s="13"/>
       <c r="P139" s="13"/>
@@ -58574,7 +58581,7 @@
         <v>91</v>
       </c>
       <c r="B140" s="12" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="C140" s="12" t="s">
         <v>879</v>
@@ -58586,22 +58593,20 @@
         <v>1018</v>
       </c>
       <c r="F140" s="12" t="s">
-        <v>984</v>
-      </c>
-      <c r="G140" s="12" t="s">
-        <v>2158</v>
-      </c>
+        <v>1002</v>
+      </c>
+      <c r="G140" s="12"/>
       <c r="H140" s="12" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I140" s="13" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="J140" s="12" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="K140" s="13" t="s">
-        <v>989</v>
+        <v>995</v>
       </c>
       <c r="L140" s="16" t="n">
         <f aca="false">IF(M140="",0,LEN(M140)-LEN(SUBSTITUTE(M140,",",""))+1)</f>
@@ -58619,7 +58624,7 @@
         <v>92</v>
       </c>
       <c r="B141" s="12" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="C141" s="12" t="s">
         <v>934</v>
@@ -58666,13 +58671,13 @@
         <v>95</v>
       </c>
       <c r="B142" s="12" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="C142" s="12" t="s">
         <v>904</v>
       </c>
       <c r="D142" s="12" t="s">
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="E142" s="12" t="s">
         <v>1016</v>
@@ -58713,13 +58718,13 @@
         <v>95</v>
       </c>
       <c r="B143" s="12" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="C143" s="12" t="s">
         <v>904</v>
       </c>
       <c r="D143" s="12" t="s">
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="E143" s="12" t="s">
         <v>1016</v>
@@ -58758,13 +58763,13 @@
         <v>95</v>
       </c>
       <c r="B144" s="12" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="C144" s="12" t="s">
         <v>904</v>
       </c>
       <c r="D144" s="12" t="s">
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="E144" s="12" t="s">
         <v>1016</v>
@@ -58805,13 +58810,13 @@
         <v>95</v>
       </c>
       <c r="B145" s="12" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="C145" s="12" t="s">
         <v>904</v>
       </c>
       <c r="D145" s="12" t="s">
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="E145" s="12" t="s">
         <v>1016</v>
@@ -58852,7 +58857,7 @@
         <v>96</v>
       </c>
       <c r="B146" s="12" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="C146" s="12" t="s">
         <v>958</v>
@@ -58868,13 +58873,13 @@
       </c>
       <c r="G146" s="12"/>
       <c r="H146" s="12" t="n">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="I146" s="13" t="s">
-        <v>838</v>
+        <v>818</v>
       </c>
       <c r="J146" s="12" t="s">
-        <v>106</v>
+        <v>210</v>
       </c>
       <c r="K146" s="13" t="s">
         <v>958</v>
@@ -58885,7 +58890,7 @@
       </c>
       <c r="M146" s="13"/>
       <c r="N146" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O146" s="13"/>
       <c r="P146" s="13" t="s">
@@ -58894,35 +58899,35 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="12" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B147" s="12" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="C147" s="12" t="s">
-        <v>923</v>
+        <v>958</v>
       </c>
       <c r="D147" s="12" t="s">
-        <v>2138</v>
+        <v>997</v>
       </c>
       <c r="E147" s="12" t="s">
-        <v>2139</v>
+        <v>1029</v>
       </c>
       <c r="F147" s="12" t="s">
         <v>2140</v>
       </c>
       <c r="G147" s="12"/>
       <c r="H147" s="12" t="n">
-        <v>117</v>
+        <v>226</v>
       </c>
       <c r="I147" s="13" t="s">
-        <v>656</v>
+        <v>838</v>
       </c>
       <c r="J147" s="12" t="s">
-        <v>519</v>
+        <v>106</v>
       </c>
       <c r="K147" s="13" t="s">
-        <v>985</v>
+        <v>958</v>
       </c>
       <c r="L147" s="16" t="n">
         <f aca="false">IF(M147="",0,LEN(M147)-LEN(SUBSTITUTE(M147,",",""))+1)</f>
@@ -58930,17 +58935,19 @@
       </c>
       <c r="M147" s="13"/>
       <c r="N147" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O147" s="13"/>
-      <c r="P147" s="13"/>
+      <c r="P147" s="13" t="s">
+        <v>2181</v>
+      </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="12" t="n">
         <v>97</v>
       </c>
       <c r="B148" s="12" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="C148" s="12" t="s">
         <v>923</v>
@@ -58956,16 +58963,16 @@
       </c>
       <c r="G148" s="12"/>
       <c r="H148" s="12" t="n">
-        <v>190</v>
+        <v>117</v>
       </c>
       <c r="I148" s="13" t="s">
-        <v>784</v>
+        <v>656</v>
       </c>
       <c r="J148" s="12" t="s">
-        <v>84</v>
+        <v>519</v>
       </c>
       <c r="K148" s="13" t="s">
-        <v>992</v>
+        <v>985</v>
       </c>
       <c r="L148" s="16" t="n">
         <f aca="false">IF(M148="",0,LEN(M148)-LEN(SUBSTITUTE(M148,",",""))+1)</f>
@@ -58973,23 +58980,23 @@
       </c>
       <c r="M148" s="13"/>
       <c r="N148" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O148" s="13"/>
       <c r="P148" s="13"/>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B149" s="12" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="C149" s="12" t="s">
-        <v>934</v>
+        <v>879</v>
       </c>
       <c r="D149" s="12" t="s">
-        <v>995</v>
+        <v>1001</v>
       </c>
       <c r="E149" s="12" t="s">
         <v>1016</v>
@@ -58999,16 +59006,16 @@
       </c>
       <c r="G149" s="12"/>
       <c r="H149" s="12" t="n">
-        <v>121</v>
+        <v>190</v>
       </c>
       <c r="I149" s="13" t="s">
-        <v>663</v>
+        <v>784</v>
       </c>
       <c r="J149" s="12" t="s">
-        <v>171</v>
+        <v>84</v>
       </c>
       <c r="K149" s="13" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="L149" s="16" t="n">
         <f aca="false">IF(M149="",0,LEN(M149)-LEN(SUBSTITUTE(M149,",",""))+1)</f>
@@ -59016,19 +59023,17 @@
       </c>
       <c r="M149" s="13"/>
       <c r="N149" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O149" s="13"/>
-      <c r="P149" s="13" t="s">
-        <v>2181</v>
-      </c>
+      <c r="P149" s="13"/>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="12" t="n">
         <v>99</v>
       </c>
       <c r="B150" s="12" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="C150" s="12" t="s">
         <v>934</v>
@@ -59105,25 +59110,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
       <c r="C1" s="17" t="s">
         <v>2130</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>2268</v>
+        <v>2269</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>2269</v>
+        <v>2270</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>2270</v>
+        <v>2271</v>
       </c>
       <c r="G1" s="17" t="s">
-        <v>2271</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59131,10 +59136,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>2272</v>
+        <v>2273</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>2273</v>
+        <v>2274</v>
       </c>
       <c r="D2" s="18" t="n">
         <v>3</v>
@@ -59159,7 +59164,7 @@
         <v>2051</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>2274</v>
+        <v>2275</v>
       </c>
       <c r="D3" s="18" t="n">
         <v>0</v>
@@ -59181,10 +59186,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
       <c r="D4" s="18" t="n">
         <v>0</v>
@@ -59206,10 +59211,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>2278</v>
+        <v>2279</v>
       </c>
       <c r="D5" s="18" t="n">
         <v>4</v>
@@ -59231,10 +59236,10 @@
         <v>12</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>2280</v>
+        <v>2281</v>
       </c>
       <c r="D6" s="18" t="n">
         <v>6</v>
@@ -59256,10 +59261,10 @@
         <v>9</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>2282</v>
+        <v>2283</v>
       </c>
       <c r="D7" s="18" t="n">
         <v>7</v>
@@ -59284,7 +59289,7 @@
         <v>2024</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>2283</v>
+        <v>2284</v>
       </c>
       <c r="D8" s="18" t="n">
         <v>2</v>
@@ -59306,10 +59311,10 @@
         <v>10</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>2284</v>
+        <v>2285</v>
       </c>
       <c r="D9" s="18" t="n">
         <v>2</v>
@@ -59334,7 +59339,7 @@
         <v>2102</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>2285</v>
+        <v>2286</v>
       </c>
       <c r="D10" s="18" t="n">
         <v>1</v>
@@ -59356,10 +59361,10 @@
         <v>13</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>2272</v>
+        <v>2273</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>2286</v>
+        <v>2287</v>
       </c>
       <c r="D11" s="18" t="n">
         <v>6</v>
@@ -59384,7 +59389,7 @@
         <v>2038</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>2287</v>
+        <v>2288</v>
       </c>
       <c r="D12" s="18" t="n">
         <v>2</v>
@@ -59406,10 +59411,10 @@
         <v>15</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>2288</v>
+        <v>2289</v>
       </c>
       <c r="D13" s="18" t="n">
         <v>5</v>
@@ -59431,10 +59436,10 @@
         <v>18</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="D14" s="18" t="n">
         <v>3</v>
@@ -59459,7 +59464,7 @@
         <v>2038</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>2290</v>
+        <v>2291</v>
       </c>
       <c r="D15" s="18" t="n">
         <v>3</v>
@@ -59481,10 +59486,10 @@
         <v>28</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>2291</v>
+        <v>2292</v>
       </c>
       <c r="D16" s="18" t="n">
         <v>6</v>
@@ -59509,7 +59514,7 @@
         <v>2024</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>2292</v>
+        <v>2293</v>
       </c>
       <c r="D17" s="18" t="n">
         <v>2</v>
@@ -59534,7 +59539,7 @@
         <v>2051</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="D18" s="18" t="n">
         <v>2</v>
@@ -59556,20 +59561,20 @@
         <v>24</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>2294</v>
+        <v>2295</v>
       </c>
       <c r="D19" s="18" t="n">
         <v>4</v>
       </c>
       <c r="E19" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F19" s="18" t="n">
         <f aca="false">D19-E19</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" s="18" t="str">
         <f aca="false">IF(E19&gt;=5,"Check","")</f>
@@ -59584,7 +59589,7 @@
         <v>2038</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>2295</v>
+        <v>2296</v>
       </c>
       <c r="D20" s="18" t="n">
         <v>0</v>
@@ -59609,7 +59614,7 @@
         <v>2078</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>2296</v>
+        <v>2297</v>
       </c>
       <c r="D21" s="18" t="n">
         <v>1</v>
@@ -59631,10 +59636,10 @@
         <v>25</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>2272</v>
+        <v>2273</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>2297</v>
+        <v>2298</v>
       </c>
       <c r="D22" s="18" t="n">
         <v>6</v>
@@ -59656,10 +59661,10 @@
         <v>26</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>2298</v>
+        <v>2299</v>
       </c>
       <c r="D23" s="18" t="n">
         <v>1</v>
@@ -59684,7 +59689,7 @@
         <v>2102</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>2299</v>
+        <v>2300</v>
       </c>
       <c r="D24" s="18" t="n">
         <v>4</v>
@@ -59706,10 +59711,10 @@
         <v>33</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>2300</v>
+        <v>2301</v>
       </c>
       <c r="D25" s="18" t="n">
         <v>2</v>
@@ -59731,10 +59736,10 @@
         <v>34</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>2301</v>
+        <v>2302</v>
       </c>
       <c r="D26" s="18" t="n">
         <v>4</v>
@@ -59756,10 +59761,10 @@
         <v>31</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>2302</v>
+        <v>2303</v>
       </c>
       <c r="D27" s="18" t="n">
         <v>5</v>
@@ -59784,17 +59789,17 @@
         <v>2051</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>2303</v>
+        <v>2304</v>
       </c>
       <c r="D28" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E28" s="18" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="18" t="n">
         <f aca="false">D28-E28</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="18" t="str">
         <f aca="false">IF(E28&gt;=5,"Check","")</f>
@@ -59806,10 +59811,10 @@
         <v>32</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>2304</v>
+        <v>2305</v>
       </c>
       <c r="D29" s="18" t="n">
         <v>1</v>
@@ -59834,7 +59839,7 @@
         <v>2038</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>2305</v>
+        <v>2306</v>
       </c>
       <c r="D30" s="18" t="n">
         <v>0</v>
@@ -59859,7 +59864,7 @@
         <v>2051</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>2306</v>
+        <v>2307</v>
       </c>
       <c r="D31" s="18" t="n">
         <v>5</v>
@@ -59884,7 +59889,7 @@
         <v>2078</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>2307</v>
+        <v>2308</v>
       </c>
       <c r="D32" s="18" t="n">
         <v>4</v>
@@ -59906,10 +59911,10 @@
         <v>36</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>2272</v>
+        <v>2273</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
       <c r="D33" s="18" t="n">
         <v>3</v>
@@ -59934,7 +59939,7 @@
         <v>2102</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="D34" s="18" t="n">
         <v>2</v>
@@ -59959,7 +59964,7 @@
         <v>2024</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>2310</v>
+        <v>2311</v>
       </c>
       <c r="D35" s="18" t="n">
         <v>2</v>
@@ -59981,10 +59986,10 @@
         <v>45</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>2311</v>
+        <v>2312</v>
       </c>
       <c r="D36" s="18" t="n">
         <v>2</v>
@@ -60006,10 +60011,10 @@
         <v>44</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>2312</v>
+        <v>2313</v>
       </c>
       <c r="D37" s="18" t="n">
         <v>0</v>
@@ -60034,7 +60039,7 @@
         <v>2038</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>2313</v>
+        <v>2314</v>
       </c>
       <c r="D38" s="18" t="n">
         <v>2</v>
@@ -60056,10 +60061,10 @@
         <v>43</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>2314</v>
+        <v>2315</v>
       </c>
       <c r="D39" s="18" t="n">
         <v>1</v>
@@ -60084,7 +60089,7 @@
         <v>2051</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="D40" s="18" t="n">
         <v>1</v>
@@ -60106,10 +60111,10 @@
         <v>47</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="D41" s="18" t="n">
         <v>2</v>
@@ -60131,10 +60136,10 @@
         <v>49</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
       <c r="D42" s="18" t="n">
         <v>1</v>
@@ -60156,10 +60161,10 @@
         <v>50</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>2272</v>
+        <v>2273</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
       <c r="D43" s="18" t="n">
         <v>4</v>
@@ -60184,7 +60189,7 @@
         <v>2024</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="D44" s="18" t="n">
         <v>2</v>
@@ -60206,20 +60211,20 @@
         <v>55</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>2320</v>
+        <v>2321</v>
       </c>
       <c r="D45" s="18" t="n">
         <v>3</v>
       </c>
       <c r="E45" s="18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" s="18" t="n">
         <f aca="false">D45-E45</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G45" s="18" t="str">
         <f aca="false">IF(E45&gt;=5,"Check","")</f>
@@ -60234,7 +60239,7 @@
         <v>2038</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>2321</v>
+        <v>2322</v>
       </c>
       <c r="D46" s="18" t="n">
         <v>3</v>
@@ -60259,7 +60264,7 @@
         <v>2078</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>2322</v>
+        <v>2323</v>
       </c>
       <c r="D47" s="18" t="n">
         <v>0</v>
@@ -60281,10 +60286,10 @@
         <v>55</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="D48" s="18" t="n">
         <v>0</v>
@@ -60306,10 +60311,10 @@
         <v>63</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
       <c r="D49" s="18" t="n">
         <v>2</v>
@@ -60334,7 +60339,7 @@
         <v>2102</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="D50" s="18" t="n">
         <v>2</v>
@@ -60356,10 +60361,10 @@
         <v>67</v>
       </c>
       <c r="B51" s="18" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>2326</v>
+        <v>2327</v>
       </c>
       <c r="D51" s="18" t="n">
         <v>1</v>
@@ -60384,7 +60389,7 @@
         <v>2078</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>2327</v>
+        <v>2328</v>
       </c>
       <c r="D52" s="18" t="n">
         <v>0</v>
@@ -60406,10 +60411,10 @@
         <v>63</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="D53" s="18" t="n">
         <v>2</v>
@@ -60431,10 +60436,10 @@
         <v>61</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>2329</v>
+        <v>2330</v>
       </c>
       <c r="D54" s="18" t="n">
         <v>3</v>
@@ -60456,10 +60461,10 @@
         <v>63</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>2272</v>
+        <v>2273</v>
       </c>
       <c r="C55" s="18" t="s">
-        <v>2330</v>
+        <v>2331</v>
       </c>
       <c r="D55" s="18" t="n">
         <v>3</v>
@@ -60481,10 +60486,10 @@
         <v>63</v>
       </c>
       <c r="B56" s="18" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>2331</v>
+        <v>2332</v>
       </c>
       <c r="D56" s="18" t="n">
         <v>5</v>
@@ -60506,10 +60511,10 @@
         <v>67</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>2332</v>
+        <v>2333</v>
       </c>
       <c r="D57" s="18" t="n">
         <v>3</v>
@@ -60534,7 +60539,7 @@
         <v>2038</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>2333</v>
+        <v>2334</v>
       </c>
       <c r="D58" s="18" t="n">
         <v>0</v>
@@ -60559,7 +60564,7 @@
         <v>2051</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>2334</v>
+        <v>2335</v>
       </c>
       <c r="D59" s="18" t="n">
         <v>0</v>
@@ -60584,7 +60589,7 @@
         <v>2102</v>
       </c>
       <c r="C60" s="18" t="s">
-        <v>2335</v>
+        <v>2336</v>
       </c>
       <c r="D60" s="18" t="n">
         <v>1</v>
@@ -60606,20 +60611,20 @@
         <v>68</v>
       </c>
       <c r="B61" s="18" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
       <c r="C61" s="18" t="s">
-        <v>2336</v>
+        <v>2337</v>
       </c>
       <c r="D61" s="18" t="n">
         <v>4</v>
       </c>
       <c r="E61" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F61" s="18" t="n">
         <f aca="false">D61-E61</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G61" s="18" t="str">
         <f aca="false">IF(E61&gt;=5,"Check","")</f>
@@ -60634,7 +60639,7 @@
         <v>2078</v>
       </c>
       <c r="C62" s="18" t="s">
-        <v>2337</v>
+        <v>2338</v>
       </c>
       <c r="D62" s="18" t="n">
         <v>1</v>
@@ -60656,10 +60661,10 @@
         <v>75</v>
       </c>
       <c r="B63" s="18" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
       <c r="C63" s="18" t="s">
-        <v>2338</v>
+        <v>2339</v>
       </c>
       <c r="D63" s="18" t="n">
         <v>0</v>
@@ -60681,10 +60686,10 @@
         <v>71</v>
       </c>
       <c r="B64" s="18" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
       <c r="C64" s="18" t="s">
-        <v>2339</v>
+        <v>2340</v>
       </c>
       <c r="D64" s="18" t="n">
         <v>0</v>
@@ -60709,13 +60714,13 @@
         <v>2024</v>
       </c>
       <c r="C65" s="18" t="s">
-        <v>2340</v>
+        <v>2341</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65" s="18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F65" s="18" t="n">
         <f aca="false">D65-E65</f>
@@ -60731,10 +60736,10 @@
         <v>73</v>
       </c>
       <c r="B66" s="18" t="s">
-        <v>2272</v>
+        <v>2273</v>
       </c>
       <c r="C66" s="18" t="s">
-        <v>2341</v>
+        <v>2342</v>
       </c>
       <c r="D66" s="18" t="n">
         <v>6</v>
@@ -60759,7 +60764,7 @@
         <v>2102</v>
       </c>
       <c r="C67" s="18" t="s">
-        <v>2342</v>
+        <v>2343</v>
       </c>
       <c r="D67" s="18" t="n">
         <v>1</v>
@@ -60781,10 +60786,10 @@
         <v>76</v>
       </c>
       <c r="B68" s="18" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="C68" s="18" t="s">
-        <v>2343</v>
+        <v>2344</v>
       </c>
       <c r="D68" s="18" t="n">
         <v>2</v>
@@ -60806,10 +60811,10 @@
         <v>84</v>
       </c>
       <c r="B69" s="18" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
       <c r="C69" s="18" t="s">
-        <v>2344</v>
+        <v>2345</v>
       </c>
       <c r="D69" s="18" t="n">
         <v>3</v>
@@ -60831,10 +60836,10 @@
         <v>79</v>
       </c>
       <c r="B70" s="18" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
       <c r="C70" s="18" t="s">
-        <v>2345</v>
+        <v>2346</v>
       </c>
       <c r="D70" s="18" t="n">
         <v>3</v>
@@ -60859,7 +60864,7 @@
         <v>2051</v>
       </c>
       <c r="C71" s="18" t="s">
-        <v>2346</v>
+        <v>2347</v>
       </c>
       <c r="D71" s="18" t="n">
         <v>3</v>
@@ -60884,7 +60889,7 @@
         <v>2102</v>
       </c>
       <c r="C72" s="18" t="s">
-        <v>2347</v>
+        <v>2348</v>
       </c>
       <c r="D72" s="18" t="n">
         <v>4</v>
@@ -60906,10 +60911,10 @@
         <v>80</v>
       </c>
       <c r="B73" s="18" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
       <c r="C73" s="18" t="s">
-        <v>2348</v>
+        <v>2349</v>
       </c>
       <c r="D73" s="18" t="n">
         <v>1</v>
@@ -60934,7 +60939,7 @@
         <v>2038</v>
       </c>
       <c r="C74" s="18" t="s">
-        <v>2349</v>
+        <v>2350</v>
       </c>
       <c r="D74" s="18" t="n">
         <v>0</v>
@@ -60956,10 +60961,10 @@
         <v>87</v>
       </c>
       <c r="B75" s="18" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
       <c r="C75" s="18" t="s">
-        <v>2350</v>
+        <v>2351</v>
       </c>
       <c r="D75" s="18" t="n">
         <v>3</v>
@@ -60984,7 +60989,7 @@
         <v>2078</v>
       </c>
       <c r="C76" s="18" t="s">
-        <v>2351</v>
+        <v>2352</v>
       </c>
       <c r="D76" s="18" t="n">
         <v>1</v>
@@ -61006,10 +61011,10 @@
         <v>85</v>
       </c>
       <c r="B77" s="18" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
       <c r="C77" s="18" t="s">
-        <v>2352</v>
+        <v>2353</v>
       </c>
       <c r="D77" s="18" t="n">
         <v>1</v>
@@ -61031,10 +61036,10 @@
         <v>86</v>
       </c>
       <c r="B78" s="18" t="s">
-        <v>2272</v>
+        <v>2273</v>
       </c>
       <c r="C78" s="18" t="s">
-        <v>2353</v>
+        <v>2354</v>
       </c>
       <c r="D78" s="18" t="n">
         <v>2</v>
@@ -61056,10 +61061,10 @@
         <v>87</v>
       </c>
       <c r="B79" s="18" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
       <c r="C79" s="18" t="s">
-        <v>2354</v>
+        <v>2355</v>
       </c>
       <c r="D79" s="18" t="n">
         <v>1</v>
@@ -61081,10 +61086,10 @@
         <v>93</v>
       </c>
       <c r="B80" s="18" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="C80" s="18" t="s">
-        <v>2355</v>
+        <v>2356</v>
       </c>
       <c r="D80" s="18" t="n">
         <v>0</v>
@@ -61109,7 +61114,7 @@
         <v>2024</v>
       </c>
       <c r="C81" s="18" t="s">
-        <v>2356</v>
+        <v>2357</v>
       </c>
       <c r="D81" s="18" t="n">
         <v>0</v>
@@ -61134,7 +61139,7 @@
         <v>2038</v>
       </c>
       <c r="C82" s="18" t="s">
-        <v>2357</v>
+        <v>2358</v>
       </c>
       <c r="D82" s="18" t="n">
         <v>0</v>
@@ -61159,7 +61164,7 @@
         <v>2051</v>
       </c>
       <c r="C83" s="18" t="s">
-        <v>2358</v>
+        <v>2359</v>
       </c>
       <c r="D83" s="18" t="n">
         <v>0</v>
@@ -61181,10 +61186,10 @@
         <v>94</v>
       </c>
       <c r="B84" s="18" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
       <c r="C84" s="18" t="s">
-        <v>2359</v>
+        <v>2360</v>
       </c>
       <c r="D84" s="18" t="n">
         <v>0</v>
@@ -61206,10 +61211,10 @@
         <v>95</v>
       </c>
       <c r="B85" s="18" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
       <c r="C85" s="18" t="s">
-        <v>2360</v>
+        <v>2361</v>
       </c>
       <c r="D85" s="18" t="n">
         <v>2</v>
@@ -61231,10 +61236,10 @@
         <v>98</v>
       </c>
       <c r="B86" s="18" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
       <c r="C86" s="18" t="s">
-        <v>2361</v>
+        <v>2362</v>
       </c>
       <c r="D86" s="18" t="n">
         <v>0</v>
@@ -61256,10 +61261,10 @@
         <v>97</v>
       </c>
       <c r="B87" s="18" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="C87" s="18" t="s">
-        <v>2362</v>
+        <v>2363</v>
       </c>
       <c r="D87" s="18" t="n">
         <v>0</v>
@@ -61281,10 +61286,10 @@
         <v>98</v>
       </c>
       <c r="B88" s="18" t="s">
-        <v>2272</v>
+        <v>2273</v>
       </c>
       <c r="C88" s="18" t="s">
-        <v>2363</v>
+        <v>2364</v>
       </c>
       <c r="D88" s="18" t="n">
         <v>1</v>
@@ -61303,7 +61308,7 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B90" s="19" t="s">
-        <v>2364</v>
+        <v>2365</v>
       </c>
       <c r="D90" s="18" t="n">
         <f aca="false">COUNTIF(D2:D88,"&gt;=5")</f>
@@ -61348,7 +61353,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>2365</v>
+        <v>2366</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>1041</v>
@@ -61372,7 +61377,7 @@
         <v>15</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>2366</v>
+        <v>2367</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>6</v>
@@ -61388,7 +61393,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>2367</v>
+        <v>2368</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>6</v>
@@ -61404,7 +61409,7 @@
         <v>14</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>2368</v>
+        <v>2369</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>6</v>
@@ -61420,7 +61425,7 @@
         <v>18</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>2369</v>
+        <v>2370</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>6</v>
@@ -61436,7 +61441,7 @@
         <v>9</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>2370</v>
+        <v>2371</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>6</v>
@@ -61452,7 +61457,7 @@
         <v>10</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>2371</v>
+        <v>2372</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>6</v>
@@ -61468,7 +61473,7 @@
         <v>14</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>2372</v>
+        <v>2373</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>6</v>
@@ -61484,7 +61489,7 @@
         <v>12</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>2373</v>
+        <v>2374</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>6</v>
@@ -61500,7 +61505,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>2374</v>
+        <v>2375</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>6</v>
@@ -61516,7 +61521,7 @@
         <v>13</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>2375</v>
+        <v>2376</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>6</v>
@@ -61532,7 +61537,7 @@
         <v>17</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>2376</v>
+        <v>2377</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>6</v>
@@ -61548,7 +61553,7 @@
         <v>9</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>2377</v>
+        <v>2378</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>6</v>
@@ -61564,7 +61569,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>2378</v>
+        <v>2379</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>6</v>
@@ -61580,7 +61585,7 @@
         <v>9</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>2379</v>
+        <v>2380</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>6</v>
@@ -61596,7 +61601,7 @@
         <v>10</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>2380</v>
+        <v>2381</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>6</v>

--- a/ingredient_asset_tracker.xlsx
+++ b/ingredient_asset_tracker.xlsx
@@ -5892,7 +5892,7 @@
     <t xml:space="preserve">banishing,endings,protection</t>
   </si>
   <si>
-    <t xml:space="preserve">truth, memory, calm</t>
+    <t xml:space="preserve">calm, truth, memory</t>
   </si>
   <si>
     <t xml:space="preserve">Stitched into a diary's spine so it stays honest.</t>
@@ -8095,7 +8095,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -8162,18 +8162,6 @@
     </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -48707,7 +48695,7 @@
       </c>
       <c r="L200" s="5" t="str">
         <f aca="false">", "&amp;C200&amp;", "</f>
-        <v>, truth, memory, calm, </v>
+        <v>, calm, truth, memory, </v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -52207,74 +52195,74 @@
   <dimension ref="A1:P150"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="22"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
         <v>2123</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="4" t="s">
         <v>2124</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="4" t="s">
         <v>2125</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="4" t="s">
         <v>2126</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="4" t="s">
         <v>2127</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="4" t="s">
         <v>2128</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="4" t="s">
         <v>2129</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="4" t="s">
         <v>2013</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="4" t="s">
         <v>2130</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J1" s="4" t="s">
         <v>2131</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K1" s="4" t="s">
         <v>868</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="L1" s="4" t="s">
         <v>2132</v>
       </c>
-      <c r="M1" s="17" t="s">
+      <c r="M1" s="4" t="s">
         <v>2133</v>
       </c>
-      <c r="N1" s="17" t="s">
+      <c r="N1" s="4" t="s">
         <v>2134</v>
       </c>
-      <c r="O1" s="17" t="s">
+      <c r="O1" s="4" t="s">
         <v>2135</v>
       </c>
-      <c r="P1" s="17" t="s">
+      <c r="P1" s="4" t="s">
         <v>2136</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="n">
         <v>1</v>
       </c>
@@ -52321,7 +52309,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="n">
         <v>1</v>
       </c>
@@ -52368,7 +52356,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="n">
         <v>2</v>
       </c>
@@ -52415,7 +52403,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="n">
         <v>3</v>
       </c>
@@ -52462,7 +52450,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="n">
         <v>4</v>
       </c>
@@ -52509,7 +52497,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="n">
         <v>5</v>
       </c>
@@ -52556,7 +52544,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="n">
         <v>6</v>
       </c>
@@ -52603,7 +52591,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="n">
         <v>7</v>
       </c>
@@ -52650,7 +52638,7 @@
         <v>2152</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="n">
         <v>8</v>
       </c>
@@ -52697,7 +52685,7 @@
       </c>
       <c r="P10" s="13"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="n">
         <v>8</v>
       </c>
@@ -52744,7 +52732,7 @@
       </c>
       <c r="P11" s="13"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="n">
         <v>9</v>
       </c>
@@ -52793,7 +52781,7 @@
       </c>
       <c r="P12" s="13"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="n">
         <v>9</v>
       </c>
@@ -52840,7 +52828,7 @@
       </c>
       <c r="P13" s="13"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="n">
         <v>10</v>
       </c>
@@ -52887,7 +52875,7 @@
       </c>
       <c r="P14" s="13"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="n">
         <v>10</v>
       </c>
@@ -52934,7 +52922,7 @@
       </c>
       <c r="P15" s="13"/>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="n">
         <v>11</v>
       </c>
@@ -52981,7 +52969,7 @@
       </c>
       <c r="P16" s="13"/>
     </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="n">
         <v>11</v>
       </c>
@@ -53028,7 +53016,7 @@
       </c>
       <c r="P17" s="13"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="n">
         <v>12</v>
       </c>
@@ -53075,7 +53063,7 @@
       </c>
       <c r="P18" s="13"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="n">
         <v>12</v>
       </c>
@@ -53122,7 +53110,7 @@
       </c>
       <c r="P19" s="13"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="n">
         <v>13</v>
       </c>
@@ -53169,7 +53157,7 @@
       </c>
       <c r="P20" s="13"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="n">
         <v>13</v>
       </c>
@@ -53214,7 +53202,7 @@
       <c r="O21" s="13"/>
       <c r="P21" s="13"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="n">
         <v>14</v>
       </c>
@@ -53261,7 +53249,7 @@
       </c>
       <c r="P22" s="13"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="n">
         <v>14</v>
       </c>
@@ -53308,7 +53296,7 @@
       </c>
       <c r="P23" s="13"/>
     </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="n">
         <v>15</v>
       </c>
@@ -53357,7 +53345,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="n">
         <v>15</v>
       </c>
@@ -53402,7 +53390,7 @@
       <c r="O25" s="13"/>
       <c r="P25" s="13"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="n">
         <v>16</v>
       </c>
@@ -53447,7 +53435,7 @@
       <c r="O26" s="13"/>
       <c r="P26" s="13"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="n">
         <v>16</v>
       </c>
@@ -53492,7 +53480,7 @@
       <c r="O27" s="13"/>
       <c r="P27" s="13"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="n">
         <v>17</v>
       </c>
@@ -53539,7 +53527,7 @@
       </c>
       <c r="P28" s="13"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="n">
         <v>17</v>
       </c>
@@ -53584,7 +53572,7 @@
       <c r="O29" s="13"/>
       <c r="P29" s="13"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="n">
         <v>18</v>
       </c>
@@ -53631,7 +53619,7 @@
       <c r="O30" s="13"/>
       <c r="P30" s="13"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="n">
         <v>18</v>
       </c>
@@ -53678,7 +53666,7 @@
       <c r="O31" s="13"/>
       <c r="P31" s="13"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="n">
         <v>19</v>
       </c>
@@ -53725,7 +53713,7 @@
       <c r="O32" s="13"/>
       <c r="P32" s="13"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="n">
         <v>19</v>
       </c>
@@ -53770,7 +53758,7 @@
       <c r="O33" s="13"/>
       <c r="P33" s="13"/>
     </row>
-    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="n">
         <v>20</v>
       </c>
@@ -53817,7 +53805,7 @@
       </c>
       <c r="P34" s="13"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="n">
         <v>20</v>
       </c>
@@ -53862,7 +53850,7 @@
       <c r="O35" s="13"/>
       <c r="P35" s="13"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="n">
         <v>21</v>
       </c>
@@ -53907,7 +53895,7 @@
       <c r="O36" s="13"/>
       <c r="P36" s="13"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="n">
         <v>21</v>
       </c>
@@ -53952,7 +53940,7 @@
       <c r="O37" s="13"/>
       <c r="P37" s="13"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="n">
         <v>22</v>
       </c>
@@ -53999,7 +53987,7 @@
       </c>
       <c r="P38" s="13"/>
     </row>
-    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="n">
         <v>22</v>
       </c>
@@ -54044,7 +54032,7 @@
       <c r="O39" s="13"/>
       <c r="P39" s="13"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="n">
         <v>23</v>
       </c>
@@ -54091,7 +54079,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="n">
         <v>23</v>
       </c>
@@ -54136,7 +54124,7 @@
       <c r="O41" s="13"/>
       <c r="P41" s="13"/>
     </row>
-    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="n">
         <v>24</v>
       </c>
@@ -54183,7 +54171,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="n">
         <v>24</v>
       </c>
@@ -54228,7 +54216,7 @@
       <c r="O43" s="13"/>
       <c r="P43" s="13"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="n">
         <v>25</v>
       </c>
@@ -54275,7 +54263,7 @@
       </c>
       <c r="P44" s="13"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="n">
         <v>25</v>
       </c>
@@ -54320,7 +54308,7 @@
       <c r="O45" s="13"/>
       <c r="P45" s="13"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="n">
         <v>26</v>
       </c>
@@ -54367,7 +54355,7 @@
       </c>
       <c r="P46" s="13"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="n">
         <v>26</v>
       </c>
@@ -54414,7 +54402,7 @@
       </c>
       <c r="P47" s="13"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="n">
         <v>27</v>
       </c>
@@ -54459,7 +54447,7 @@
       <c r="O48" s="13"/>
       <c r="P48" s="13"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="n">
         <v>27</v>
       </c>
@@ -54504,7 +54492,7 @@
       <c r="O49" s="13"/>
       <c r="P49" s="13"/>
     </row>
-    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="n">
         <v>28</v>
       </c>
@@ -54551,7 +54539,7 @@
       </c>
       <c r="P50" s="13"/>
     </row>
-    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="12" t="n">
         <v>28</v>
       </c>
@@ -54598,7 +54586,7 @@
       </c>
       <c r="P51" s="13"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="n">
         <v>29</v>
       </c>
@@ -54643,7 +54631,7 @@
       <c r="O52" s="13"/>
       <c r="P52" s="13"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="12" t="n">
         <v>29</v>
       </c>
@@ -54688,7 +54676,7 @@
       <c r="O53" s="13"/>
       <c r="P53" s="13"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="12" t="n">
         <v>30</v>
       </c>
@@ -54733,7 +54721,7 @@
       <c r="O54" s="13"/>
       <c r="P54" s="13"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="12" t="n">
         <v>30</v>
       </c>
@@ -54778,7 +54766,7 @@
       <c r="O55" s="13"/>
       <c r="P55" s="13"/>
     </row>
-    <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="12" t="n">
         <v>31</v>
       </c>
@@ -54825,7 +54813,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="12" t="n">
         <v>31</v>
       </c>
@@ -54870,7 +54858,7 @@
       <c r="O57" s="13"/>
       <c r="P57" s="13"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="12" t="n">
         <v>32</v>
       </c>
@@ -54917,7 +54905,7 @@
       </c>
       <c r="P58" s="13"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="12" t="n">
         <v>32</v>
       </c>
@@ -54962,7 +54950,7 @@
       <c r="O59" s="13"/>
       <c r="P59" s="13"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="n">
         <v>33</v>
       </c>
@@ -55009,7 +54997,7 @@
       </c>
       <c r="P60" s="13"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="12" t="n">
         <v>33</v>
       </c>
@@ -55054,7 +55042,7 @@
       <c r="O61" s="13"/>
       <c r="P61" s="13"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="12" t="n">
         <v>34</v>
       </c>
@@ -55101,7 +55089,7 @@
       </c>
       <c r="P62" s="13"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="12" t="n">
         <v>34</v>
       </c>
@@ -55148,7 +55136,7 @@
       </c>
       <c r="P63" s="13"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="12" t="n">
         <v>35</v>
       </c>
@@ -55195,7 +55183,7 @@
       </c>
       <c r="P64" s="13"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="12" t="n">
         <v>35</v>
       </c>
@@ -55242,7 +55230,7 @@
       <c r="O65" s="13"/>
       <c r="P65" s="13"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="12" t="n">
         <v>36</v>
       </c>
@@ -55287,7 +55275,7 @@
       <c r="O66" s="13"/>
       <c r="P66" s="13"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="12" t="n">
         <v>36</v>
       </c>
@@ -55332,7 +55320,7 @@
       <c r="O67" s="13"/>
       <c r="P67" s="13"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="12" t="n">
         <v>37</v>
       </c>
@@ -55379,7 +55367,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="12" t="n">
         <v>37</v>
       </c>
@@ -55422,7 +55410,7 @@
       <c r="O69" s="13"/>
       <c r="P69" s="13"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="12" t="n">
         <v>38</v>
       </c>
@@ -55467,7 +55455,7 @@
       <c r="O70" s="13"/>
       <c r="P70" s="13"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="12" t="n">
         <v>38</v>
       </c>
@@ -55512,7 +55500,7 @@
       <c r="O71" s="13"/>
       <c r="P71" s="13"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="12" t="n">
         <v>39</v>
       </c>
@@ -55559,7 +55547,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="12" t="n">
         <v>39</v>
       </c>
@@ -55604,7 +55592,7 @@
       <c r="O73" s="13"/>
       <c r="P73" s="13"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="12" t="n">
         <v>40</v>
       </c>
@@ -55647,7 +55635,7 @@
       <c r="O74" s="13"/>
       <c r="P74" s="13"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="12" t="n">
         <v>40</v>
       </c>
@@ -55692,7 +55680,7 @@
       <c r="O75" s="13"/>
       <c r="P75" s="13"/>
     </row>
-    <row r="76" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="12" t="n">
         <v>41</v>
       </c>
@@ -55737,7 +55725,7 @@
       <c r="O76" s="13"/>
       <c r="P76" s="13"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="12" t="n">
         <v>41</v>
       </c>
@@ -55780,7 +55768,7 @@
       <c r="O77" s="13"/>
       <c r="P77" s="13"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="12" t="n">
         <v>42</v>
       </c>
@@ -55825,7 +55813,7 @@
       <c r="O78" s="13"/>
       <c r="P78" s="13"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="12" t="n">
         <v>42</v>
       </c>
@@ -55868,7 +55856,7 @@
       <c r="O79" s="13"/>
       <c r="P79" s="13"/>
     </row>
-    <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="12" t="n">
         <v>43</v>
       </c>
@@ -55913,7 +55901,7 @@
       <c r="O80" s="13"/>
       <c r="P80" s="13"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="12" t="n">
         <v>44</v>
       </c>
@@ -55960,7 +55948,7 @@
       </c>
       <c r="P81" s="13"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="12" t="n">
         <v>45</v>
       </c>
@@ -56009,7 +55997,7 @@
       </c>
       <c r="P82" s="13"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="12" t="n">
         <v>45</v>
       </c>
@@ -56054,7 +56042,7 @@
       <c r="O83" s="13"/>
       <c r="P83" s="13"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="12" t="n">
         <v>46</v>
       </c>
@@ -56097,7 +56085,7 @@
       <c r="O84" s="13"/>
       <c r="P84" s="13"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="12" t="n">
         <v>47</v>
       </c>
@@ -56144,7 +56132,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="12" t="n">
         <v>48</v>
       </c>
@@ -56189,7 +56177,7 @@
       <c r="O86" s="13"/>
       <c r="P86" s="13"/>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="12" t="n">
         <v>49</v>
       </c>
@@ -56236,7 +56224,7 @@
       </c>
       <c r="P87" s="13"/>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="12" t="n">
         <v>49</v>
       </c>
@@ -56279,7 +56267,7 @@
       <c r="O88" s="13"/>
       <c r="P88" s="13"/>
     </row>
-    <row r="89" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="12" t="n">
         <v>50</v>
       </c>
@@ -56324,7 +56312,7 @@
       <c r="O89" s="13"/>
       <c r="P89" s="13"/>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="12" t="n">
         <v>51</v>
       </c>
@@ -56367,7 +56355,7 @@
       <c r="O90" s="13"/>
       <c r="P90" s="13"/>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="12" t="n">
         <v>52</v>
       </c>
@@ -56414,7 +56402,7 @@
       <c r="O91" s="13"/>
       <c r="P91" s="13"/>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="12" t="n">
         <v>53</v>
       </c>
@@ -56459,7 +56447,7 @@
       <c r="O92" s="13"/>
       <c r="P92" s="13"/>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="12" t="n">
         <v>53</v>
       </c>
@@ -56502,7 +56490,7 @@
       <c r="O93" s="13"/>
       <c r="P93" s="13"/>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="12" t="n">
         <v>54</v>
       </c>
@@ -56547,7 +56535,7 @@
       <c r="O94" s="13"/>
       <c r="P94" s="13"/>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="12" t="n">
         <v>55</v>
       </c>
@@ -56594,7 +56582,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="12" t="n">
         <v>56</v>
       </c>
@@ -56639,7 +56627,7 @@
       <c r="O96" s="13"/>
       <c r="P96" s="13"/>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="12" t="n">
         <v>57</v>
       </c>
@@ -56682,7 +56670,7 @@
       <c r="O97" s="13"/>
       <c r="P97" s="13"/>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="12" t="n">
         <v>57</v>
       </c>
@@ -56727,7 +56715,7 @@
       <c r="O98" s="13"/>
       <c r="P98" s="13"/>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="12" t="n">
         <v>58</v>
       </c>
@@ -56770,7 +56758,7 @@
       <c r="O99" s="13"/>
       <c r="P99" s="13"/>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="12" t="n">
         <v>59</v>
       </c>
@@ -56815,7 +56803,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="12" t="n">
         <v>60</v>
       </c>
@@ -56858,7 +56846,7 @@
       <c r="O101" s="13"/>
       <c r="P101" s="13"/>
     </row>
-    <row r="102" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="12" t="n">
         <v>61</v>
       </c>
@@ -56903,7 +56891,7 @@
       <c r="O102" s="13"/>
       <c r="P102" s="13"/>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="12" t="n">
         <v>61</v>
       </c>
@@ -56948,7 +56936,7 @@
       <c r="O103" s="13"/>
       <c r="P103" s="13"/>
     </row>
-    <row r="104" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="12" t="n">
         <v>62</v>
       </c>
@@ -56993,7 +56981,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="12" t="n">
         <v>62</v>
       </c>
@@ -57040,7 +57028,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="12" t="n">
         <v>63</v>
       </c>
@@ -57089,7 +57077,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="12" t="n">
         <v>63</v>
       </c>
@@ -57136,7 +57124,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="12" t="n">
         <v>63</v>
       </c>
@@ -57183,7 +57171,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="12" t="n">
         <v>64</v>
       </c>
@@ -57228,7 +57216,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="12" t="n">
         <v>64</v>
       </c>
@@ -57273,7 +57261,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="12" t="n">
         <v>64</v>
       </c>
@@ -57320,7 +57308,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="12" t="n">
         <v>65</v>
       </c>
@@ -57363,7 +57351,7 @@
       <c r="O112" s="13"/>
       <c r="P112" s="13"/>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="12" t="n">
         <v>66</v>
       </c>
@@ -57406,7 +57394,7 @@
       <c r="O113" s="13"/>
       <c r="P113" s="13"/>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="12" t="n">
         <v>67</v>
       </c>
@@ -57449,7 +57437,7 @@
       <c r="O114" s="13"/>
       <c r="P114" s="13"/>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="12" t="n">
         <v>68</v>
       </c>
@@ -57492,7 +57480,7 @@
       <c r="O115" s="13"/>
       <c r="P115" s="13"/>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="12" t="n">
         <v>69</v>
       </c>
@@ -57539,7 +57527,7 @@
       </c>
       <c r="P116" s="13"/>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="12" t="n">
         <v>70</v>
       </c>
@@ -57584,7 +57572,7 @@
       <c r="O117" s="13"/>
       <c r="P117" s="13"/>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="12" t="n">
         <v>71</v>
       </c>
@@ -57629,7 +57617,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="12" t="n">
         <v>71</v>
       </c>
@@ -57676,7 +57664,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="12" t="n">
         <v>72</v>
       </c>
@@ -57719,7 +57707,7 @@
       <c r="O120" s="13"/>
       <c r="P120" s="13"/>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="12" t="n">
         <v>73</v>
       </c>
@@ -57762,7 +57750,7 @@
       <c r="O121" s="13"/>
       <c r="P121" s="13"/>
     </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="12" t="n">
         <v>74</v>
       </c>
@@ -57805,7 +57793,7 @@
       <c r="O122" s="13"/>
       <c r="P122" s="13"/>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="12" t="n">
         <v>75</v>
       </c>
@@ -57850,7 +57838,7 @@
       <c r="O123" s="13"/>
       <c r="P123" s="13"/>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="12" t="n">
         <v>76</v>
       </c>
@@ -57895,7 +57883,7 @@
       <c r="O124" s="13"/>
       <c r="P124" s="13"/>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="12" t="n">
         <v>77</v>
       </c>
@@ -57938,7 +57926,7 @@
       <c r="O125" s="13"/>
       <c r="P125" s="13"/>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="12" t="n">
         <v>78</v>
       </c>
@@ -57983,7 +57971,7 @@
       <c r="O126" s="13"/>
       <c r="P126" s="13"/>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="12" t="n">
         <v>79</v>
       </c>
@@ -58028,7 +58016,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="12" t="n">
         <v>79</v>
       </c>
@@ -58075,7 +58063,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="12" t="n">
         <v>80</v>
       </c>
@@ -58122,7 +58110,7 @@
       </c>
       <c r="P129" s="13"/>
     </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="12" t="n">
         <v>81</v>
       </c>
@@ -58165,7 +58153,7 @@
       <c r="O130" s="13"/>
       <c r="P130" s="13"/>
     </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="12" t="n">
         <v>82</v>
       </c>
@@ -58210,7 +58198,7 @@
       <c r="O131" s="13"/>
       <c r="P131" s="13"/>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="12" t="n">
         <v>83</v>
       </c>
@@ -58253,7 +58241,7 @@
       <c r="O132" s="13"/>
       <c r="P132" s="13"/>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="12" t="n">
         <v>85</v>
       </c>
@@ -58300,7 +58288,7 @@
       </c>
       <c r="P133" s="13"/>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="12" t="n">
         <v>87</v>
       </c>
@@ -58347,7 +58335,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="12" t="n">
         <v>87</v>
       </c>
@@ -58394,7 +58382,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="12" t="n">
         <v>87</v>
       </c>
@@ -58441,7 +58429,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="12" t="n">
         <v>87</v>
       </c>
@@ -58488,7 +58476,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="12" t="n">
         <v>89</v>
       </c>
@@ -58531,7 +58519,7 @@
       <c r="O138" s="13"/>
       <c r="P138" s="13"/>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="12" t="n">
         <v>91</v>
       </c>
@@ -58576,7 +58564,7 @@
       <c r="O139" s="13"/>
       <c r="P139" s="13"/>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="12" t="n">
         <v>91</v>
       </c>
@@ -58619,7 +58607,7 @@
       <c r="O140" s="13"/>
       <c r="P140" s="13"/>
     </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="12" t="n">
         <v>92</v>
       </c>
@@ -58666,7 +58654,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="12" t="n">
         <v>95</v>
       </c>
@@ -58713,7 +58701,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="12" t="n">
         <v>95</v>
       </c>
@@ -58758,7 +58746,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="12" t="n">
         <v>95</v>
       </c>
@@ -58805,7 +58793,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="12" t="n">
         <v>95</v>
       </c>
@@ -58852,7 +58840,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="12" t="n">
         <v>96</v>
       </c>
@@ -58897,7 +58885,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="12" t="n">
         <v>96</v>
       </c>
@@ -58942,7 +58930,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="12" t="n">
         <v>97</v>
       </c>
@@ -58985,7 +58973,7 @@
       <c r="O148" s="13"/>
       <c r="P148" s="13"/>
     </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="12" t="n">
         <v>98</v>
       </c>
@@ -59028,7 +59016,7 @@
       <c r="O149" s="13"/>
       <c r="P149" s="13"/>
     </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="12" t="n">
         <v>99</v>
       </c>
@@ -59100,2221 +59088,2221 @@
   <dimension ref="A1:G90"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="8"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
         <v>2267</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="4" t="s">
         <v>2268</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="4" t="s">
         <v>2130</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="4" t="s">
         <v>2269</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="4" t="s">
         <v>2270</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="4" t="s">
         <v>2271</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="4" t="s">
         <v>2272</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="n">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="5" t="s">
         <v>2273</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="5" t="s">
         <v>2274</v>
       </c>
-      <c r="D2" s="18" t="n">
+      <c r="D2" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E2" s="18" t="n">
+      <c r="E2" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F2" s="18" t="n">
+      <c r="F2" s="5" t="n">
         <f aca="false">D2-E2</f>
         <v>0</v>
       </c>
-      <c r="G2" s="18" t="str">
+      <c r="G2" s="5" t="str">
         <f aca="false">IF(E2&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="n">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="5" t="s">
         <v>2051</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="5" t="s">
         <v>2275</v>
       </c>
-      <c r="D3" s="18" t="n">
+      <c r="D3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="18" t="n">
+      <c r="E3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="18" t="n">
+      <c r="F3" s="5" t="n">
         <f aca="false">D3-E3</f>
         <v>0</v>
       </c>
-      <c r="G3" s="18" t="str">
+      <c r="G3" s="5" t="str">
         <f aca="false">IF(E3&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="n">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="5" t="s">
         <v>2276</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="5" t="s">
         <v>2277</v>
       </c>
-      <c r="D4" s="18" t="n">
+      <c r="D4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="18" t="n">
+      <c r="E4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="18" t="n">
+      <c r="F4" s="5" t="n">
         <f aca="false">D4-E4</f>
         <v>0</v>
       </c>
-      <c r="G4" s="18" t="str">
+      <c r="G4" s="5" t="str">
         <f aca="false">IF(E4&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="5" t="s">
         <v>2278</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="5" t="s">
         <v>2279</v>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="D5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F5" s="18" t="n">
+      <c r="F5" s="5" t="n">
         <f aca="false">D5-E5</f>
         <v>0</v>
       </c>
-      <c r="G5" s="18" t="str">
+      <c r="G5" s="5" t="str">
         <f aca="false">IF(E5&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="5" t="s">
         <v>2280</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="5" t="s">
         <v>2281</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F6" s="18" t="n">
+      <c r="F6" s="5" t="n">
         <f aca="false">D6-E6</f>
         <v>4</v>
       </c>
-      <c r="G6" s="18" t="str">
+      <c r="G6" s="5" t="str">
         <f aca="false">IF(E6&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="5" t="s">
         <v>2282</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="5" t="s">
         <v>2283</v>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="18" t="n">
+      <c r="F7" s="5" t="n">
         <f aca="false">D7-E7</f>
         <v>2</v>
       </c>
-      <c r="G7" s="18" t="str">
+      <c r="G7" s="5" t="str">
         <f aca="false">IF(E7&gt;=5,"Check","")</f>
         <v>Check</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="5" t="s">
         <v>2024</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="5" t="s">
         <v>2284</v>
       </c>
-      <c r="D8" s="18" t="n">
+      <c r="D8" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="18" t="n">
+      <c r="F8" s="5" t="n">
         <f aca="false">D8-E8</f>
         <v>1</v>
       </c>
-      <c r="G8" s="18" t="str">
+      <c r="G8" s="5" t="str">
         <f aca="false">IF(E8&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="5" t="s">
         <v>2276</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="5" t="s">
         <v>2285</v>
       </c>
-      <c r="D9" s="18" t="n">
+      <c r="D9" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="18" t="n">
+      <c r="F9" s="5" t="n">
         <f aca="false">D9-E9</f>
         <v>2</v>
       </c>
-      <c r="G9" s="18" t="str">
+      <c r="G9" s="5" t="str">
         <f aca="false">IF(E9&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="5" t="s">
         <v>2102</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="5" t="s">
         <v>2286</v>
       </c>
-      <c r="D10" s="18" t="n">
+      <c r="D10" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="18" t="n">
+      <c r="F10" s="5" t="n">
         <f aca="false">D10-E10</f>
         <v>0</v>
       </c>
-      <c r="G10" s="18" t="str">
+      <c r="G10" s="5" t="str">
         <f aca="false">IF(E10&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="5" t="s">
         <v>2273</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="5" t="s">
         <v>2287</v>
       </c>
-      <c r="D11" s="18" t="n">
+      <c r="D11" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F11" s="18" t="n">
+      <c r="F11" s="5" t="n">
         <f aca="false">D11-E11</f>
         <v>3</v>
       </c>
-      <c r="G11" s="18" t="str">
+      <c r="G11" s="5" t="str">
         <f aca="false">IF(E11&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="5" t="s">
         <v>2038</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="5" t="s">
         <v>2288</v>
       </c>
-      <c r="D12" s="18" t="n">
+      <c r="D12" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="18" t="n">
+      <c r="F12" s="5" t="n">
         <f aca="false">D12-E12</f>
         <v>2</v>
       </c>
-      <c r="G12" s="18" t="str">
+      <c r="G12" s="5" t="str">
         <f aca="false">IF(E12&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="5" t="s">
         <v>2280</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="5" t="s">
         <v>2289</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="D13" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="18" t="n">
+      <c r="F13" s="5" t="n">
         <f aca="false">D13-E13</f>
         <v>3</v>
       </c>
-      <c r="G13" s="18" t="str">
+      <c r="G13" s="5" t="str">
         <f aca="false">IF(E13&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="5" t="s">
         <v>2282</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="5" t="s">
         <v>2290</v>
       </c>
-      <c r="D14" s="18" t="n">
+      <c r="D14" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="18" t="n">
+      <c r="F14" s="5" t="n">
         <f aca="false">D14-E14</f>
         <v>3</v>
       </c>
-      <c r="G14" s="18" t="str">
+      <c r="G14" s="5" t="str">
         <f aca="false">IF(E14&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="5" t="s">
         <v>2038</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="5" t="s">
         <v>2291</v>
       </c>
-      <c r="D15" s="18" t="n">
+      <c r="D15" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="E15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="18" t="n">
+      <c r="F15" s="5" t="n">
         <f aca="false">D15-E15</f>
         <v>2</v>
       </c>
-      <c r="G15" s="18" t="str">
+      <c r="G15" s="5" t="str">
         <f aca="false">IF(E15&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="5" t="s">
         <v>2278</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="5" t="s">
         <v>2292</v>
       </c>
-      <c r="D16" s="18" t="n">
+      <c r="D16" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E16" s="18" t="n">
+      <c r="E16" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F16" s="18" t="n">
+      <c r="F16" s="5" t="n">
         <f aca="false">D16-E16</f>
         <v>4</v>
       </c>
-      <c r="G16" s="18" t="str">
+      <c r="G16" s="5" t="str">
         <f aca="false">IF(E16&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="18" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="5" t="s">
         <v>2024</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="5" t="s">
         <v>2293</v>
       </c>
-      <c r="D17" s="18" t="n">
+      <c r="D17" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E17" s="18" t="n">
+      <c r="E17" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="18" t="n">
+      <c r="F17" s="5" t="n">
         <f aca="false">D17-E17</f>
         <v>2</v>
       </c>
-      <c r="G17" s="18" t="str">
+      <c r="G17" s="5" t="str">
         <f aca="false">IF(E17&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="18" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="5" t="s">
         <v>2051</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="5" t="s">
         <v>2294</v>
       </c>
-      <c r="D18" s="18" t="n">
+      <c r="D18" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E18" s="18" t="n">
+      <c r="E18" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F18" s="18" t="n">
+      <c r="F18" s="5" t="n">
         <f aca="false">D18-E18</f>
         <v>0</v>
       </c>
-      <c r="G18" s="18" t="str">
+      <c r="G18" s="5" t="str">
         <f aca="false">IF(E18&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="18" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="5" t="s">
         <v>2280</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="C19" s="5" t="s">
         <v>2295</v>
       </c>
-      <c r="D19" s="18" t="n">
+      <c r="D19" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E19" s="18" t="n">
+      <c r="E19" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F19" s="18" t="n">
+      <c r="F19" s="5" t="n">
         <f aca="false">D19-E19</f>
         <v>0</v>
       </c>
-      <c r="G19" s="18" t="str">
+      <c r="G19" s="5" t="str">
         <f aca="false">IF(E19&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="18" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="5" t="s">
         <v>2038</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="5" t="s">
         <v>2296</v>
       </c>
-      <c r="D20" s="18" t="n">
+      <c r="D20" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="18" t="n">
+      <c r="E20" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="18" t="n">
+      <c r="F20" s="5" t="n">
         <f aca="false">D20-E20</f>
         <v>0</v>
       </c>
-      <c r="G20" s="18" t="str">
+      <c r="G20" s="5" t="str">
         <f aca="false">IF(E20&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="18" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="5" t="s">
         <v>2078</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="5" t="s">
         <v>2297</v>
       </c>
-      <c r="D21" s="18" t="n">
+      <c r="D21" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="18" t="n">
+      <c r="E21" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F21" s="18" t="n">
+      <c r="F21" s="5" t="n">
         <f aca="false">D21-E21</f>
         <v>1</v>
       </c>
-      <c r="G21" s="18" t="str">
+      <c r="G21" s="5" t="str">
         <f aca="false">IF(E21&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="18" t="n">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="5" t="s">
         <v>2273</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="5" t="s">
         <v>2298</v>
       </c>
-      <c r="D22" s="18" t="n">
+      <c r="D22" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E22" s="18" t="n">
+      <c r="E22" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="18" t="n">
+      <c r="F22" s="5" t="n">
         <f aca="false">D22-E22</f>
         <v>4</v>
       </c>
-      <c r="G22" s="18" t="str">
+      <c r="G22" s="5" t="str">
         <f aca="false">IF(E22&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="18" t="n">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="5" t="s">
         <v>2276</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="5" t="s">
         <v>2299</v>
       </c>
-      <c r="D23" s="18" t="n">
+      <c r="D23" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E23" s="18" t="n">
+      <c r="E23" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F23" s="18" t="n">
+      <c r="F23" s="5" t="n">
         <f aca="false">D23-E23</f>
         <v>1</v>
       </c>
-      <c r="G23" s="18" t="str">
+      <c r="G23" s="5" t="str">
         <f aca="false">IF(E23&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="18" t="n">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="5" t="s">
         <v>2102</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="5" t="s">
         <v>2300</v>
       </c>
-      <c r="D24" s="18" t="n">
+      <c r="D24" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E24" s="18" t="n">
+      <c r="E24" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="18" t="n">
+      <c r="F24" s="5" t="n">
         <f aca="false">D24-E24</f>
         <v>3</v>
       </c>
-      <c r="G24" s="18" t="str">
+      <c r="G24" s="5" t="str">
         <f aca="false">IF(E24&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="18" t="n">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="5" t="s">
         <v>2278</v>
       </c>
-      <c r="C25" s="18" t="s">
+      <c r="C25" s="5" t="s">
         <v>2301</v>
       </c>
-      <c r="D25" s="18" t="n">
+      <c r="D25" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E25" s="18" t="n">
+      <c r="E25" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F25" s="18" t="n">
+      <c r="F25" s="5" t="n">
         <f aca="false">D25-E25</f>
         <v>2</v>
       </c>
-      <c r="G25" s="18" t="str">
+      <c r="G25" s="5" t="str">
         <f aca="false">IF(E25&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="18" t="n">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="5" t="s">
         <v>2282</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="5" t="s">
         <v>2302</v>
       </c>
-      <c r="D26" s="18" t="n">
+      <c r="D26" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E26" s="18" t="n">
+      <c r="E26" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F26" s="18" t="n">
+      <c r="F26" s="5" t="n">
         <f aca="false">D26-E26</f>
         <v>2</v>
       </c>
-      <c r="G26" s="18" t="str">
+      <c r="G26" s="5" t="str">
         <f aca="false">IF(E26&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="18" t="n">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="5" t="s">
         <v>2280</v>
       </c>
-      <c r="C27" s="18" t="s">
+      <c r="C27" s="5" t="s">
         <v>2303</v>
       </c>
-      <c r="D27" s="18" t="n">
+      <c r="D27" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E27" s="18" t="n">
+      <c r="E27" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F27" s="18" t="n">
+      <c r="F27" s="5" t="n">
         <f aca="false">D27-E27</f>
         <v>4</v>
       </c>
-      <c r="G27" s="18" t="str">
+      <c r="G27" s="5" t="str">
         <f aca="false">IF(E27&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18" t="n">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="5" t="s">
         <v>2051</v>
       </c>
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="5" t="s">
         <v>2304</v>
       </c>
-      <c r="D28" s="18" t="n">
+      <c r="D28" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E28" s="18" t="n">
+      <c r="E28" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F28" s="18" t="n">
+      <c r="F28" s="5" t="n">
         <f aca="false">D28-E28</f>
         <v>4</v>
       </c>
-      <c r="G28" s="18" t="str">
+      <c r="G28" s="5" t="str">
         <f aca="false">IF(E28&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="18" t="n">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="B29" s="18" t="s">
+      <c r="B29" s="5" t="s">
         <v>2276</v>
       </c>
-      <c r="C29" s="18" t="s">
+      <c r="C29" s="5" t="s">
         <v>2305</v>
       </c>
-      <c r="D29" s="18" t="n">
+      <c r="D29" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E29" s="18" t="n">
+      <c r="E29" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="18" t="n">
+      <c r="F29" s="5" t="n">
         <f aca="false">D29-E29</f>
         <v>0</v>
       </c>
-      <c r="G29" s="18" t="str">
+      <c r="G29" s="5" t="str">
         <f aca="false">IF(E29&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="18" t="n">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="B30" s="18" t="s">
+      <c r="B30" s="5" t="s">
         <v>2038</v>
       </c>
-      <c r="C30" s="18" t="s">
+      <c r="C30" s="5" t="s">
         <v>2306</v>
       </c>
-      <c r="D30" s="18" t="n">
+      <c r="D30" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E30" s="18" t="n">
+      <c r="E30" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F30" s="18" t="n">
+      <c r="F30" s="5" t="n">
         <f aca="false">D30-E30</f>
         <v>0</v>
       </c>
-      <c r="G30" s="18" t="str">
+      <c r="G30" s="5" t="str">
         <f aca="false">IF(E30&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="18" t="n">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="B31" s="18" t="s">
+      <c r="B31" s="5" t="s">
         <v>2051</v>
       </c>
-      <c r="C31" s="18" t="s">
+      <c r="C31" s="5" t="s">
         <v>2307</v>
       </c>
-      <c r="D31" s="18" t="n">
+      <c r="D31" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E31" s="18" t="n">
+      <c r="E31" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F31" s="18" t="n">
+      <c r="F31" s="5" t="n">
         <f aca="false">D31-E31</f>
         <v>5</v>
       </c>
-      <c r="G31" s="18" t="str">
+      <c r="G31" s="5" t="str">
         <f aca="false">IF(E31&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18" t="n">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="B32" s="18" t="s">
+      <c r="B32" s="5" t="s">
         <v>2078</v>
       </c>
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="5" t="s">
         <v>2308</v>
       </c>
-      <c r="D32" s="18" t="n">
+      <c r="D32" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E32" s="18" t="n">
+      <c r="E32" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F32" s="18" t="n">
+      <c r="F32" s="5" t="n">
         <f aca="false">D32-E32</f>
         <v>1</v>
       </c>
-      <c r="G32" s="18" t="str">
+      <c r="G32" s="5" t="str">
         <f aca="false">IF(E32&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="18" t="n">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="B33" s="18" t="s">
+      <c r="B33" s="5" t="s">
         <v>2273</v>
       </c>
-      <c r="C33" s="18" t="s">
+      <c r="C33" s="5" t="s">
         <v>2309</v>
       </c>
-      <c r="D33" s="18" t="n">
+      <c r="D33" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E33" s="18" t="n">
+      <c r="E33" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F33" s="18" t="n">
+      <c r="F33" s="5" t="n">
         <f aca="false">D33-E33</f>
         <v>3</v>
       </c>
-      <c r="G33" s="18" t="str">
+      <c r="G33" s="5" t="str">
         <f aca="false">IF(E33&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="18" t="n">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="B34" s="18" t="s">
+      <c r="B34" s="5" t="s">
         <v>2102</v>
       </c>
-      <c r="C34" s="18" t="s">
+      <c r="C34" s="5" t="s">
         <v>2310</v>
       </c>
-      <c r="D34" s="18" t="n">
+      <c r="D34" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E34" s="18" t="n">
+      <c r="E34" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="18" t="n">
+      <c r="F34" s="5" t="n">
         <f aca="false">D34-E34</f>
         <v>1</v>
       </c>
-      <c r="G34" s="18" t="str">
+      <c r="G34" s="5" t="str">
         <f aca="false">IF(E34&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="18" t="n">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="B35" s="18" t="s">
+      <c r="B35" s="5" t="s">
         <v>2024</v>
       </c>
-      <c r="C35" s="18" t="s">
+      <c r="C35" s="5" t="s">
         <v>2311</v>
       </c>
-      <c r="D35" s="18" t="n">
+      <c r="D35" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E35" s="18" t="n">
+      <c r="E35" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F35" s="18" t="n">
+      <c r="F35" s="5" t="n">
         <f aca="false">D35-E35</f>
         <v>2</v>
       </c>
-      <c r="G35" s="18" t="str">
+      <c r="G35" s="5" t="str">
         <f aca="false">IF(E35&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="18" t="n">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="B36" s="18" t="s">
+      <c r="B36" s="5" t="s">
         <v>2280</v>
       </c>
-      <c r="C36" s="18" t="s">
+      <c r="C36" s="5" t="s">
         <v>2312</v>
       </c>
-      <c r="D36" s="18" t="n">
+      <c r="D36" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E36" s="18" t="n">
+      <c r="E36" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F36" s="18" t="n">
+      <c r="F36" s="5" t="n">
         <f aca="false">D36-E36</f>
         <v>1</v>
       </c>
-      <c r="G36" s="18" t="str">
+      <c r="G36" s="5" t="str">
         <f aca="false">IF(E36&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="18" t="n">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="B37" s="18" t="s">
+      <c r="B37" s="5" t="s">
         <v>2282</v>
       </c>
-      <c r="C37" s="18" t="s">
+      <c r="C37" s="5" t="s">
         <v>2313</v>
       </c>
-      <c r="D37" s="18" t="n">
+      <c r="D37" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E37" s="18" t="n">
+      <c r="E37" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F37" s="18" t="n">
+      <c r="F37" s="5" t="n">
         <f aca="false">D37-E37</f>
         <v>0</v>
       </c>
-      <c r="G37" s="18" t="str">
+      <c r="G37" s="5" t="str">
         <f aca="false">IF(E37&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="18" t="n">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="B38" s="18" t="s">
+      <c r="B38" s="5" t="s">
         <v>2038</v>
       </c>
-      <c r="C38" s="18" t="s">
+      <c r="C38" s="5" t="s">
         <v>2314</v>
       </c>
-      <c r="D38" s="18" t="n">
+      <c r="D38" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E38" s="18" t="n">
+      <c r="E38" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F38" s="18" t="n">
+      <c r="F38" s="5" t="n">
         <f aca="false">D38-E38</f>
         <v>2</v>
       </c>
-      <c r="G38" s="18" t="str">
+      <c r="G38" s="5" t="str">
         <f aca="false">IF(E38&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="18" t="n">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="B39" s="18" t="s">
+      <c r="B39" s="5" t="s">
         <v>2276</v>
       </c>
-      <c r="C39" s="18" t="s">
+      <c r="C39" s="5" t="s">
         <v>2315</v>
       </c>
-      <c r="D39" s="18" t="n">
+      <c r="D39" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E39" s="18" t="n">
+      <c r="E39" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F39" s="18" t="n">
+      <c r="F39" s="5" t="n">
         <f aca="false">D39-E39</f>
         <v>1</v>
       </c>
-      <c r="G39" s="18" t="str">
+      <c r="G39" s="5" t="str">
         <f aca="false">IF(E39&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="18" t="n">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="B40" s="18" t="s">
+      <c r="B40" s="5" t="s">
         <v>2051</v>
       </c>
-      <c r="C40" s="18" t="s">
+      <c r="C40" s="5" t="s">
         <v>2316</v>
       </c>
-      <c r="D40" s="18" t="n">
+      <c r="D40" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E40" s="18" t="n">
+      <c r="E40" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F40" s="18" t="n">
+      <c r="F40" s="5" t="n">
         <f aca="false">D40-E40</f>
         <v>0</v>
       </c>
-      <c r="G40" s="18" t="str">
+      <c r="G40" s="5" t="str">
         <f aca="false">IF(E40&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="18" t="n">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="B41" s="18" t="s">
+      <c r="B41" s="5" t="s">
         <v>2280</v>
       </c>
-      <c r="C41" s="18" t="s">
+      <c r="C41" s="5" t="s">
         <v>2317</v>
       </c>
-      <c r="D41" s="18" t="n">
+      <c r="D41" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E41" s="18" t="n">
+      <c r="E41" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F41" s="18" t="n">
+      <c r="F41" s="5" t="n">
         <f aca="false">D41-E41</f>
         <v>2</v>
       </c>
-      <c r="G41" s="18" t="str">
+      <c r="G41" s="5" t="str">
         <f aca="false">IF(E41&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="18" t="n">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="5" t="n">
         <v>49</v>
       </c>
-      <c r="B42" s="18" t="s">
+      <c r="B42" s="5" t="s">
         <v>2278</v>
       </c>
-      <c r="C42" s="18" t="s">
+      <c r="C42" s="5" t="s">
         <v>2318</v>
       </c>
-      <c r="D42" s="18" t="n">
+      <c r="D42" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E42" s="18" t="n">
+      <c r="E42" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F42" s="18" t="n">
+      <c r="F42" s="5" t="n">
         <f aca="false">D42-E42</f>
         <v>1</v>
       </c>
-      <c r="G42" s="18" t="str">
+      <c r="G42" s="5" t="str">
         <f aca="false">IF(E42&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="18" t="n">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="B43" s="18" t="s">
+      <c r="B43" s="5" t="s">
         <v>2273</v>
       </c>
-      <c r="C43" s="18" t="s">
+      <c r="C43" s="5" t="s">
         <v>2319</v>
       </c>
-      <c r="D43" s="18" t="n">
+      <c r="D43" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E43" s="18" t="n">
+      <c r="E43" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="18" t="n">
+      <c r="F43" s="5" t="n">
         <f aca="false">D43-E43</f>
         <v>4</v>
       </c>
-      <c r="G43" s="18" t="str">
+      <c r="G43" s="5" t="str">
         <f aca="false">IF(E43&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="18" t="n">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="B44" s="18" t="s">
+      <c r="B44" s="5" t="s">
         <v>2024</v>
       </c>
-      <c r="C44" s="18" t="s">
+      <c r="C44" s="5" t="s">
         <v>2320</v>
       </c>
-      <c r="D44" s="18" t="n">
+      <c r="D44" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E44" s="18" t="n">
+      <c r="E44" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F44" s="18" t="n">
+      <c r="F44" s="5" t="n">
         <f aca="false">D44-E44</f>
         <v>2</v>
       </c>
-      <c r="G44" s="18" t="str">
+      <c r="G44" s="5" t="str">
         <f aca="false">IF(E44&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="18" t="n">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="B45" s="18" t="s">
+      <c r="B45" s="5" t="s">
         <v>2276</v>
       </c>
-      <c r="C45" s="18" t="s">
+      <c r="C45" s="5" t="s">
         <v>2321</v>
       </c>
-      <c r="D45" s="18" t="n">
+      <c r="D45" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E45" s="18" t="n">
+      <c r="E45" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F45" s="18" t="n">
+      <c r="F45" s="5" t="n">
         <f aca="false">D45-E45</f>
         <v>3</v>
       </c>
-      <c r="G45" s="18" t="str">
+      <c r="G45" s="5" t="str">
         <f aca="false">IF(E45&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="18" t="n">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="B46" s="18" t="s">
+      <c r="B46" s="5" t="s">
         <v>2038</v>
       </c>
-      <c r="C46" s="18" t="s">
+      <c r="C46" s="5" t="s">
         <v>2322</v>
       </c>
-      <c r="D46" s="18" t="n">
+      <c r="D46" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E46" s="18" t="n">
+      <c r="E46" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F46" s="18" t="n">
+      <c r="F46" s="5" t="n">
         <f aca="false">D46-E46</f>
         <v>0</v>
       </c>
-      <c r="G46" s="18" t="str">
+      <c r="G46" s="5" t="str">
         <f aca="false">IF(E46&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="18" t="n">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="5" t="n">
         <v>61</v>
       </c>
-      <c r="B47" s="18" t="s">
+      <c r="B47" s="5" t="s">
         <v>2078</v>
       </c>
-      <c r="C47" s="18" t="s">
+      <c r="C47" s="5" t="s">
         <v>2323</v>
       </c>
-      <c r="D47" s="18" t="n">
+      <c r="D47" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E47" s="18" t="n">
+      <c r="E47" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F47" s="18" t="n">
+      <c r="F47" s="5" t="n">
         <f aca="false">D47-E47</f>
         <v>0</v>
       </c>
-      <c r="G47" s="18" t="str">
+      <c r="G47" s="5" t="str">
         <f aca="false">IF(E47&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="18" t="n">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="B48" s="18" t="s">
+      <c r="B48" s="5" t="s">
         <v>2280</v>
       </c>
-      <c r="C48" s="18" t="s">
+      <c r="C48" s="5" t="s">
         <v>2324</v>
       </c>
-      <c r="D48" s="18" t="n">
+      <c r="D48" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E48" s="18" t="n">
+      <c r="E48" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F48" s="18" t="n">
+      <c r="F48" s="5" t="n">
         <f aca="false">D48-E48</f>
         <v>0</v>
       </c>
-      <c r="G48" s="18" t="str">
+      <c r="G48" s="5" t="str">
         <f aca="false">IF(E48&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="18" t="n">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="5" t="n">
         <v>63</v>
       </c>
-      <c r="B49" s="18" t="s">
+      <c r="B49" s="5" t="s">
         <v>2278</v>
       </c>
-      <c r="C49" s="18" t="s">
+      <c r="C49" s="5" t="s">
         <v>2325</v>
       </c>
-      <c r="D49" s="18" t="n">
+      <c r="D49" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E49" s="18" t="n">
+      <c r="E49" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F49" s="18" t="n">
+      <c r="F49" s="5" t="n">
         <f aca="false">D49-E49</f>
         <v>2</v>
       </c>
-      <c r="G49" s="18" t="str">
+      <c r="G49" s="5" t="str">
         <f aca="false">IF(E49&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="18" t="n">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="5" t="n">
         <v>63</v>
       </c>
-      <c r="B50" s="18" t="s">
+      <c r="B50" s="5" t="s">
         <v>2102</v>
       </c>
-      <c r="C50" s="18" t="s">
+      <c r="C50" s="5" t="s">
         <v>2326</v>
       </c>
-      <c r="D50" s="18" t="n">
+      <c r="D50" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E50" s="18" t="n">
+      <c r="E50" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F50" s="18" t="n">
+      <c r="F50" s="5" t="n">
         <f aca="false">D50-E50</f>
         <v>1</v>
       </c>
-      <c r="G50" s="18" t="str">
+      <c r="G50" s="5" t="str">
         <f aca="false">IF(E50&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="18" t="n">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="5" t="n">
         <v>67</v>
       </c>
-      <c r="B51" s="18" t="s">
+      <c r="B51" s="5" t="s">
         <v>2282</v>
       </c>
-      <c r="C51" s="18" t="s">
+      <c r="C51" s="5" t="s">
         <v>2327</v>
       </c>
-      <c r="D51" s="18" t="n">
+      <c r="D51" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E51" s="18" t="n">
+      <c r="E51" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F51" s="18" t="n">
+      <c r="F51" s="5" t="n">
         <f aca="false">D51-E51</f>
         <v>0</v>
       </c>
-      <c r="G51" s="18" t="str">
+      <c r="G51" s="5" t="str">
         <f aca="false">IF(E51&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="18" t="n">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="B52" s="18" t="s">
+      <c r="B52" s="5" t="s">
         <v>2078</v>
       </c>
-      <c r="C52" s="18" t="s">
+      <c r="C52" s="5" t="s">
         <v>2328</v>
       </c>
-      <c r="D52" s="18" t="n">
+      <c r="D52" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E52" s="18" t="n">
+      <c r="E52" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F52" s="18" t="n">
+      <c r="F52" s="5" t="n">
         <f aca="false">D52-E52</f>
         <v>0</v>
       </c>
-      <c r="G52" s="18" t="str">
+      <c r="G52" s="5" t="str">
         <f aca="false">IF(E52&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="18" t="n">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="5" t="n">
         <v>63</v>
       </c>
-      <c r="B53" s="18" t="s">
+      <c r="B53" s="5" t="s">
         <v>2278</v>
       </c>
-      <c r="C53" s="18" t="s">
+      <c r="C53" s="5" t="s">
         <v>2329</v>
       </c>
-      <c r="D53" s="18" t="n">
+      <c r="D53" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E53" s="18" t="n">
+      <c r="E53" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F53" s="18" t="n">
+      <c r="F53" s="5" t="n">
         <f aca="false">D53-E53</f>
         <v>0</v>
       </c>
-      <c r="G53" s="18" t="str">
+      <c r="G53" s="5" t="str">
         <f aca="false">IF(E53&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="18" t="n">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="5" t="n">
         <v>61</v>
       </c>
-      <c r="B54" s="18" t="s">
+      <c r="B54" s="5" t="s">
         <v>2276</v>
       </c>
-      <c r="C54" s="18" t="s">
+      <c r="C54" s="5" t="s">
         <v>2330</v>
       </c>
-      <c r="D54" s="18" t="n">
+      <c r="D54" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E54" s="18" t="n">
+      <c r="E54" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F54" s="18" t="n">
+      <c r="F54" s="5" t="n">
         <f aca="false">D54-E54</f>
         <v>0</v>
       </c>
-      <c r="G54" s="18" t="str">
+      <c r="G54" s="5" t="str">
         <f aca="false">IF(E54&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="18" t="n">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="5" t="n">
         <v>63</v>
       </c>
-      <c r="B55" s="18" t="s">
+      <c r="B55" s="5" t="s">
         <v>2273</v>
       </c>
-      <c r="C55" s="18" t="s">
+      <c r="C55" s="5" t="s">
         <v>2331</v>
       </c>
-      <c r="D55" s="18" t="n">
+      <c r="D55" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E55" s="18" t="n">
+      <c r="E55" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F55" s="18" t="n">
+      <c r="F55" s="5" t="n">
         <f aca="false">D55-E55</f>
         <v>3</v>
       </c>
-      <c r="G55" s="18" t="str">
+      <c r="G55" s="5" t="str">
         <f aca="false">IF(E55&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="18" t="n">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="5" t="n">
         <v>63</v>
       </c>
-      <c r="B56" s="18" t="s">
+      <c r="B56" s="5" t="s">
         <v>2280</v>
       </c>
-      <c r="C56" s="18" t="s">
+      <c r="C56" s="5" t="s">
         <v>2332</v>
       </c>
-      <c r="D56" s="18" t="n">
+      <c r="D56" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E56" s="18" t="n">
+      <c r="E56" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F56" s="18" t="n">
+      <c r="F56" s="5" t="n">
         <f aca="false">D56-E56</f>
         <v>5</v>
       </c>
-      <c r="G56" s="18" t="str">
+      <c r="G56" s="5" t="str">
         <f aca="false">IF(E56&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="18" t="n">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="5" t="n">
         <v>67</v>
       </c>
-      <c r="B57" s="18" t="s">
+      <c r="B57" s="5" t="s">
         <v>2282</v>
       </c>
-      <c r="C57" s="18" t="s">
+      <c r="C57" s="5" t="s">
         <v>2333</v>
       </c>
-      <c r="D57" s="18" t="n">
+      <c r="D57" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E57" s="18" t="n">
+      <c r="E57" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F57" s="18" t="n">
+      <c r="F57" s="5" t="n">
         <f aca="false">D57-E57</f>
         <v>1</v>
       </c>
-      <c r="G57" s="18" t="str">
+      <c r="G57" s="5" t="str">
         <f aca="false">IF(E57&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="18" t="n">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="B58" s="18" t="s">
+      <c r="B58" s="5" t="s">
         <v>2038</v>
       </c>
-      <c r="C58" s="18" t="s">
+      <c r="C58" s="5" t="s">
         <v>2334</v>
       </c>
-      <c r="D58" s="18" t="n">
+      <c r="D58" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E58" s="18" t="n">
+      <c r="E58" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F58" s="18" t="n">
+      <c r="F58" s="5" t="n">
         <f aca="false">D58-E58</f>
         <v>0</v>
       </c>
-      <c r="G58" s="18" t="str">
+      <c r="G58" s="5" t="str">
         <f aca="false">IF(E58&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="18" t="n">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="5" t="n">
         <v>66</v>
       </c>
-      <c r="B59" s="18" t="s">
+      <c r="B59" s="5" t="s">
         <v>2051</v>
       </c>
-      <c r="C59" s="18" t="s">
+      <c r="C59" s="5" t="s">
         <v>2335</v>
       </c>
-      <c r="D59" s="18" t="n">
+      <c r="D59" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E59" s="18" t="n">
+      <c r="E59" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F59" s="18" t="n">
+      <c r="F59" s="5" t="n">
         <f aca="false">D59-E59</f>
         <v>0</v>
       </c>
-      <c r="G59" s="18" t="str">
+      <c r="G59" s="5" t="str">
         <f aca="false">IF(E59&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="18" t="n">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="5" t="n">
         <v>72</v>
       </c>
-      <c r="B60" s="18" t="s">
+      <c r="B60" s="5" t="s">
         <v>2102</v>
       </c>
-      <c r="C60" s="18" t="s">
+      <c r="C60" s="5" t="s">
         <v>2336</v>
       </c>
-      <c r="D60" s="18" t="n">
+      <c r="D60" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E60" s="18" t="n">
+      <c r="E60" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F60" s="18" t="n">
+      <c r="F60" s="5" t="n">
         <f aca="false">D60-E60</f>
         <v>1</v>
       </c>
-      <c r="G60" s="18" t="str">
+      <c r="G60" s="5" t="str">
         <f aca="false">IF(E60&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="18" t="n">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="5" t="n">
         <v>68</v>
       </c>
-      <c r="B61" s="18" t="s">
+      <c r="B61" s="5" t="s">
         <v>2276</v>
       </c>
-      <c r="C61" s="18" t="s">
+      <c r="C61" s="5" t="s">
         <v>2337</v>
       </c>
-      <c r="D61" s="18" t="n">
+      <c r="D61" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E61" s="18" t="n">
+      <c r="E61" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F61" s="18" t="n">
+      <c r="F61" s="5" t="n">
         <f aca="false">D61-E61</f>
         <v>2</v>
       </c>
-      <c r="G61" s="18" t="str">
+      <c r="G61" s="5" t="str">
         <f aca="false">IF(E61&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="18" t="n">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="B62" s="18" t="s">
+      <c r="B62" s="5" t="s">
         <v>2078</v>
       </c>
-      <c r="C62" s="18" t="s">
+      <c r="C62" s="5" t="s">
         <v>2338</v>
       </c>
-      <c r="D62" s="18" t="n">
+      <c r="D62" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E62" s="18" t="n">
+      <c r="E62" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F62" s="18" t="n">
+      <c r="F62" s="5" t="n">
         <f aca="false">D62-E62</f>
         <v>1</v>
       </c>
-      <c r="G62" s="18" t="str">
+      <c r="G62" s="5" t="str">
         <f aca="false">IF(E62&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="18" t="n">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="B63" s="18" t="s">
+      <c r="B63" s="5" t="s">
         <v>2278</v>
       </c>
-      <c r="C63" s="18" t="s">
+      <c r="C63" s="5" t="s">
         <v>2339</v>
       </c>
-      <c r="D63" s="18" t="n">
+      <c r="D63" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E63" s="18" t="n">
+      <c r="E63" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F63" s="18" t="n">
+      <c r="F63" s="5" t="n">
         <f aca="false">D63-E63</f>
         <v>0</v>
       </c>
-      <c r="G63" s="18" t="str">
+      <c r="G63" s="5" t="str">
         <f aca="false">IF(E63&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="18" t="n">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="5" t="n">
         <v>71</v>
       </c>
-      <c r="B64" s="18" t="s">
+      <c r="B64" s="5" t="s">
         <v>2280</v>
       </c>
-      <c r="C64" s="18" t="s">
+      <c r="C64" s="5" t="s">
         <v>2340</v>
       </c>
-      <c r="D64" s="18" t="n">
+      <c r="D64" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E64" s="18" t="n">
+      <c r="E64" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F64" s="18" t="n">
+      <c r="F64" s="5" t="n">
         <f aca="false">D64-E64</f>
         <v>0</v>
       </c>
-      <c r="G64" s="18" t="str">
+      <c r="G64" s="5" t="str">
         <f aca="false">IF(E64&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="18" t="n">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="5" t="n">
         <v>72</v>
       </c>
-      <c r="B65" s="18" t="s">
+      <c r="B65" s="5" t="s">
         <v>2024</v>
       </c>
-      <c r="C65" s="18" t="s">
+      <c r="C65" s="5" t="s">
         <v>2341</v>
       </c>
-      <c r="D65" s="18" t="n">
+      <c r="D65" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E65" s="18" t="n">
+      <c r="E65" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F65" s="18" t="n">
+      <c r="F65" s="5" t="n">
         <f aca="false">D65-E65</f>
         <v>1</v>
       </c>
-      <c r="G65" s="18" t="str">
+      <c r="G65" s="5" t="str">
         <f aca="false">IF(E65&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="18" t="n">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="5" t="n">
         <v>73</v>
       </c>
-      <c r="B66" s="18" t="s">
+      <c r="B66" s="5" t="s">
         <v>2273</v>
       </c>
-      <c r="C66" s="18" t="s">
+      <c r="C66" s="5" t="s">
         <v>2342</v>
       </c>
-      <c r="D66" s="18" t="n">
+      <c r="D66" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E66" s="18" t="n">
+      <c r="E66" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F66" s="18" t="n">
+      <c r="F66" s="5" t="n">
         <f aca="false">D66-E66</f>
         <v>4</v>
       </c>
-      <c r="G66" s="18" t="str">
+      <c r="G66" s="5" t="str">
         <f aca="false">IF(E66&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="18" t="n">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="5" t="n">
         <v>73</v>
       </c>
-      <c r="B67" s="18" t="s">
+      <c r="B67" s="5" t="s">
         <v>2102</v>
       </c>
-      <c r="C67" s="18" t="s">
+      <c r="C67" s="5" t="s">
         <v>2343</v>
       </c>
-      <c r="D67" s="18" t="n">
+      <c r="D67" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E67" s="18" t="n">
+      <c r="E67" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F67" s="18" t="n">
+      <c r="F67" s="5" t="n">
         <f aca="false">D67-E67</f>
         <v>1</v>
       </c>
-      <c r="G67" s="18" t="str">
+      <c r="G67" s="5" t="str">
         <f aca="false">IF(E67&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="18" t="n">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="5" t="n">
         <v>76</v>
       </c>
-      <c r="B68" s="18" t="s">
+      <c r="B68" s="5" t="s">
         <v>2282</v>
       </c>
-      <c r="C68" s="18" t="s">
+      <c r="C68" s="5" t="s">
         <v>2344</v>
       </c>
-      <c r="D68" s="18" t="n">
+      <c r="D68" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E68" s="18" t="n">
+      <c r="E68" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F68" s="18" t="n">
+      <c r="F68" s="5" t="n">
         <f aca="false">D68-E68</f>
         <v>2</v>
       </c>
-      <c r="G68" s="18" t="str">
+      <c r="G68" s="5" t="str">
         <f aca="false">IF(E68&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="18" t="n">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="5" t="n">
         <v>84</v>
       </c>
-      <c r="B69" s="18" t="s">
+      <c r="B69" s="5" t="s">
         <v>2278</v>
       </c>
-      <c r="C69" s="18" t="s">
+      <c r="C69" s="5" t="s">
         <v>2345</v>
       </c>
-      <c r="D69" s="18" t="n">
+      <c r="D69" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E69" s="18" t="n">
+      <c r="E69" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F69" s="18" t="n">
+      <c r="F69" s="5" t="n">
         <f aca="false">D69-E69</f>
         <v>2</v>
       </c>
-      <c r="G69" s="18" t="str">
+      <c r="G69" s="5" t="str">
         <f aca="false">IF(E69&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="18" t="n">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="5" t="n">
         <v>79</v>
       </c>
-      <c r="B70" s="18" t="s">
+      <c r="B70" s="5" t="s">
         <v>2276</v>
       </c>
-      <c r="C70" s="18" t="s">
+      <c r="C70" s="5" t="s">
         <v>2346</v>
       </c>
-      <c r="D70" s="18" t="n">
+      <c r="D70" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E70" s="18" t="n">
+      <c r="E70" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F70" s="18" t="n">
+      <c r="F70" s="5" t="n">
         <f aca="false">D70-E70</f>
         <v>3</v>
       </c>
-      <c r="G70" s="18" t="str">
+      <c r="G70" s="5" t="str">
         <f aca="false">IF(E70&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="18" t="n">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="5" t="n">
         <v>85</v>
       </c>
-      <c r="B71" s="18" t="s">
+      <c r="B71" s="5" t="s">
         <v>2051</v>
       </c>
-      <c r="C71" s="18" t="s">
+      <c r="C71" s="5" t="s">
         <v>2347</v>
       </c>
-      <c r="D71" s="18" t="n">
+      <c r="D71" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E71" s="18" t="n">
+      <c r="E71" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F71" s="18" t="n">
+      <c r="F71" s="5" t="n">
         <f aca="false">D71-E71</f>
         <v>3</v>
       </c>
-      <c r="G71" s="18" t="str">
+      <c r="G71" s="5" t="str">
         <f aca="false">IF(E71&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="18" t="n">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="5" t="n">
         <v>79</v>
       </c>
-      <c r="B72" s="18" t="s">
+      <c r="B72" s="5" t="s">
         <v>2102</v>
       </c>
-      <c r="C72" s="18" t="s">
+      <c r="C72" s="5" t="s">
         <v>2348</v>
       </c>
-      <c r="D72" s="18" t="n">
+      <c r="D72" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E72" s="18" t="n">
+      <c r="E72" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F72" s="18" t="n">
+      <c r="F72" s="5" t="n">
         <f aca="false">D72-E72</f>
         <v>2</v>
       </c>
-      <c r="G72" s="18" t="str">
+      <c r="G72" s="5" t="str">
         <f aca="false">IF(E72&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="18" t="n">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="B73" s="18" t="s">
+      <c r="B73" s="5" t="s">
         <v>2280</v>
       </c>
-      <c r="C73" s="18" t="s">
+      <c r="C73" s="5" t="s">
         <v>2349</v>
       </c>
-      <c r="D73" s="18" t="n">
+      <c r="D73" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E73" s="18" t="n">
+      <c r="E73" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F73" s="18" t="n">
+      <c r="F73" s="5" t="n">
         <f aca="false">D73-E73</f>
         <v>1</v>
       </c>
-      <c r="G73" s="18" t="str">
+      <c r="G73" s="5" t="str">
         <f aca="false">IF(E73&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="18" t="n">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="5" t="n">
         <v>81</v>
       </c>
-      <c r="B74" s="18" t="s">
+      <c r="B74" s="5" t="s">
         <v>2038</v>
       </c>
-      <c r="C74" s="18" t="s">
+      <c r="C74" s="5" t="s">
         <v>2350</v>
       </c>
-      <c r="D74" s="18" t="n">
+      <c r="D74" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E74" s="18" t="n">
+      <c r="E74" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F74" s="18" t="n">
+      <c r="F74" s="5" t="n">
         <f aca="false">D74-E74</f>
         <v>0</v>
       </c>
-      <c r="G74" s="18" t="str">
+      <c r="G74" s="5" t="str">
         <f aca="false">IF(E74&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="18" t="n">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="5" t="n">
         <v>87</v>
       </c>
-      <c r="B75" s="18" t="s">
+      <c r="B75" s="5" t="s">
         <v>2278</v>
       </c>
-      <c r="C75" s="18" t="s">
+      <c r="C75" s="5" t="s">
         <v>2351</v>
       </c>
-      <c r="D75" s="18" t="n">
+      <c r="D75" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E75" s="18" t="n">
+      <c r="E75" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F75" s="18" t="n">
+      <c r="F75" s="5" t="n">
         <f aca="false">D75-E75</f>
         <v>3</v>
       </c>
-      <c r="G75" s="18" t="str">
+      <c r="G75" s="5" t="str">
         <f aca="false">IF(E75&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="18" t="n">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="B76" s="18" t="s">
+      <c r="B76" s="5" t="s">
         <v>2078</v>
       </c>
-      <c r="C76" s="18" t="s">
+      <c r="C76" s="5" t="s">
         <v>2352</v>
       </c>
-      <c r="D76" s="18" t="n">
+      <c r="D76" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E76" s="18" t="n">
+      <c r="E76" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F76" s="18" t="n">
+      <c r="F76" s="5" t="n">
         <f aca="false">D76-E76</f>
         <v>1</v>
       </c>
-      <c r="G76" s="18" t="str">
+      <c r="G76" s="5" t="str">
         <f aca="false">IF(E76&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="18" t="n">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="5" t="n">
         <v>85</v>
       </c>
-      <c r="B77" s="18" t="s">
+      <c r="B77" s="5" t="s">
         <v>2276</v>
       </c>
-      <c r="C77" s="18" t="s">
+      <c r="C77" s="5" t="s">
         <v>2353</v>
       </c>
-      <c r="D77" s="18" t="n">
+      <c r="D77" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E77" s="18" t="n">
+      <c r="E77" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F77" s="18" t="n">
+      <c r="F77" s="5" t="n">
         <f aca="false">D77-E77</f>
         <v>1</v>
       </c>
-      <c r="G77" s="18" t="str">
+      <c r="G77" s="5" t="str">
         <f aca="false">IF(E77&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="18" t="n">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="B78" s="18" t="s">
+      <c r="B78" s="5" t="s">
         <v>2273</v>
       </c>
-      <c r="C78" s="18" t="s">
+      <c r="C78" s="5" t="s">
         <v>2354</v>
       </c>
-      <c r="D78" s="18" t="n">
+      <c r="D78" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E78" s="18" t="n">
+      <c r="E78" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F78" s="18" t="n">
+      <c r="F78" s="5" t="n">
         <f aca="false">D78-E78</f>
         <v>2</v>
       </c>
-      <c r="G78" s="18" t="str">
+      <c r="G78" s="5" t="str">
         <f aca="false">IF(E78&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="18" t="n">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="5" t="n">
         <v>87</v>
       </c>
-      <c r="B79" s="18" t="s">
+      <c r="B79" s="5" t="s">
         <v>2280</v>
       </c>
-      <c r="C79" s="18" t="s">
+      <c r="C79" s="5" t="s">
         <v>2355</v>
       </c>
-      <c r="D79" s="18" t="n">
+      <c r="D79" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E79" s="18" t="n">
+      <c r="E79" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F79" s="18" t="n">
+      <c r="F79" s="5" t="n">
         <f aca="false">D79-E79</f>
         <v>1</v>
       </c>
-      <c r="G79" s="18" t="str">
+      <c r="G79" s="5" t="str">
         <f aca="false">IF(E79&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="18" t="n">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="5" t="n">
         <v>93</v>
       </c>
-      <c r="B80" s="18" t="s">
+      <c r="B80" s="5" t="s">
         <v>2282</v>
       </c>
-      <c r="C80" s="18" t="s">
+      <c r="C80" s="5" t="s">
         <v>2356</v>
       </c>
-      <c r="D80" s="18" t="n">
+      <c r="D80" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E80" s="18" t="n">
+      <c r="E80" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F80" s="18" t="n">
+      <c r="F80" s="5" t="n">
         <f aca="false">D80-E80</f>
         <v>0</v>
       </c>
-      <c r="G80" s="18" t="str">
+      <c r="G80" s="5" t="str">
         <f aca="false">IF(E80&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="18" t="n">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="5" t="n">
         <v>93</v>
       </c>
-      <c r="B81" s="18" t="s">
+      <c r="B81" s="5" t="s">
         <v>2024</v>
       </c>
-      <c r="C81" s="18" t="s">
+      <c r="C81" s="5" t="s">
         <v>2357</v>
       </c>
-      <c r="D81" s="18" t="n">
+      <c r="D81" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E81" s="18" t="n">
+      <c r="E81" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F81" s="18" t="n">
+      <c r="F81" s="5" t="n">
         <f aca="false">D81-E81</f>
         <v>0</v>
       </c>
-      <c r="G81" s="18" t="str">
+      <c r="G81" s="5" t="str">
         <f aca="false">IF(E81&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="18" t="n">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="5" t="n">
         <v>91</v>
       </c>
-      <c r="B82" s="18" t="s">
+      <c r="B82" s="5" t="s">
         <v>2038</v>
       </c>
-      <c r="C82" s="18" t="s">
+      <c r="C82" s="5" t="s">
         <v>2358</v>
       </c>
-      <c r="D82" s="18" t="n">
+      <c r="D82" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E82" s="18" t="n">
+      <c r="E82" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F82" s="18" t="n">
+      <c r="F82" s="5" t="n">
         <f aca="false">D82-E82</f>
         <v>0</v>
       </c>
-      <c r="G82" s="18" t="str">
+      <c r="G82" s="5" t="str">
         <f aca="false">IF(E82&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="18" t="n">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="5" t="n">
         <v>93</v>
       </c>
-      <c r="B83" s="18" t="s">
+      <c r="B83" s="5" t="s">
         <v>2051</v>
       </c>
-      <c r="C83" s="18" t="s">
+      <c r="C83" s="5" t="s">
         <v>2359</v>
       </c>
-      <c r="D83" s="18" t="n">
+      <c r="D83" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E83" s="18" t="n">
+      <c r="E83" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F83" s="18" t="n">
+      <c r="F83" s="5" t="n">
         <f aca="false">D83-E83</f>
         <v>0</v>
       </c>
-      <c r="G83" s="18" t="str">
+      <c r="G83" s="5" t="str">
         <f aca="false">IF(E83&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="18" t="n">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="B84" s="18" t="s">
+      <c r="B84" s="5" t="s">
         <v>2276</v>
       </c>
-      <c r="C84" s="18" t="s">
+      <c r="C84" s="5" t="s">
         <v>2360</v>
       </c>
-      <c r="D84" s="18" t="n">
+      <c r="D84" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E84" s="18" t="n">
+      <c r="E84" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F84" s="18" t="n">
+      <c r="F84" s="5" t="n">
         <f aca="false">D84-E84</f>
         <v>0</v>
       </c>
-      <c r="G84" s="18" t="str">
+      <c r="G84" s="5" t="str">
         <f aca="false">IF(E84&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="18" t="n">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="5" t="n">
         <v>95</v>
       </c>
-      <c r="B85" s="18" t="s">
+      <c r="B85" s="5" t="s">
         <v>2280</v>
       </c>
-      <c r="C85" s="18" t="s">
+      <c r="C85" s="5" t="s">
         <v>2361</v>
       </c>
-      <c r="D85" s="18" t="n">
+      <c r="D85" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E85" s="18" t="n">
+      <c r="E85" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F85" s="18" t="n">
+      <c r="F85" s="5" t="n">
         <f aca="false">D85-E85</f>
         <v>1</v>
       </c>
-      <c r="G85" s="18" t="str">
+      <c r="G85" s="5" t="str">
         <f aca="false">IF(E85&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="18" t="n">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="5" t="n">
         <v>98</v>
       </c>
-      <c r="B86" s="18" t="s">
+      <c r="B86" s="5" t="s">
         <v>2278</v>
       </c>
-      <c r="C86" s="18" t="s">
+      <c r="C86" s="5" t="s">
         <v>2362</v>
       </c>
-      <c r="D86" s="18" t="n">
+      <c r="D86" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E86" s="18" t="n">
+      <c r="E86" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F86" s="18" t="n">
+      <c r="F86" s="5" t="n">
         <f aca="false">D86-E86</f>
         <v>0</v>
       </c>
-      <c r="G86" s="18" t="str">
+      <c r="G86" s="5" t="str">
         <f aca="false">IF(E86&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="18" t="n">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="5" t="n">
         <v>97</v>
       </c>
-      <c r="B87" s="18" t="s">
+      <c r="B87" s="5" t="s">
         <v>2282</v>
       </c>
-      <c r="C87" s="18" t="s">
+      <c r="C87" s="5" t="s">
         <v>2363</v>
       </c>
-      <c r="D87" s="18" t="n">
+      <c r="D87" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E87" s="18" t="n">
+      <c r="E87" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F87" s="18" t="n">
+      <c r="F87" s="5" t="n">
         <f aca="false">D87-E87</f>
         <v>0</v>
       </c>
-      <c r="G87" s="18" t="str">
+      <c r="G87" s="5" t="str">
         <f aca="false">IF(E87&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="18" t="n">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="5" t="n">
         <v>98</v>
       </c>
-      <c r="B88" s="18" t="s">
+      <c r="B88" s="5" t="s">
         <v>2273</v>
       </c>
-      <c r="C88" s="18" t="s">
+      <c r="C88" s="5" t="s">
         <v>2364</v>
       </c>
-      <c r="D88" s="18" t="n">
+      <c r="D88" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E88" s="18" t="n">
+      <c r="E88" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F88" s="18" t="n">
+      <c r="F88" s="5" t="n">
         <f aca="false">D88-E88</f>
         <v>1</v>
       </c>
-      <c r="G88" s="18" t="str">
+      <c r="G88" s="5" t="str">
         <f aca="false">IF(E88&gt;=5,"Check","")</f>
         <v/>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B90" s="19" t="s">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B90" s="7" t="s">
         <v>2365</v>
       </c>
-      <c r="D90" s="18" t="n">
+      <c r="D90" s="5" t="n">
         <f aca="false">COUNTIF(D2:D88,"&gt;=5")</f>
         <v>10</v>
       </c>
-      <c r="E90" s="18" t="n">
+      <c r="E90" s="5" t="n">
         <f aca="false">COUNTIF(E2:E88,"&gt;=5")</f>
         <v>1</v>
       </c>

--- a/ingredient_asset_tracker.xlsx
+++ b/ingredient_asset_tracker.xlsx
@@ -4413,7 +4413,7 @@
     <t xml:space="preserve">confidence,healing,joy</t>
   </si>
   <si>
-    <t xml:space="preserve">calm, sleep, comfort, healing</t>
+    <t xml:space="preserve">calm, comfort, sleep, healing</t>
   </si>
   <si>
     <t xml:space="preserve">For the child who lies awake worrying. Mild as warm milk.</t>
@@ -42183,7 +42183,7 @@
       </c>
       <c r="L24" s="5" t="str">
         <f aca="false">", "&amp;C24&amp;", "</f>
-        <v>, calm, sleep, comfort, healing, </v>
+        <v>, calm, comfort, sleep, healing, </v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/ingredient_asset_tracker.xlsx
+++ b/ingredient_asset_tracker.xlsx
@@ -4347,7 +4347,7 @@
     <t xml:space="preserve">rest, calm, cleansing</t>
   </si>
   <si>
-    <t xml:space="preserve">Hushes the body toward rest.</t>
+    <t xml:space="preserve">Hushes the body, like a house after snowfall.</t>
   </si>
   <si>
     <t xml:space="preserve">calm,cleansing,rest</t>
@@ -4425,7 +4425,7 @@
     <t xml:space="preserve">luck, friendship, joy</t>
   </si>
   <si>
-    <t xml:space="preserve">Small, everyday luck, shared between friends.</t>
+    <t xml:space="preserve">Small, everyday good fortune, shared between friends.</t>
   </si>
   <si>
     <t xml:space="preserve">friendship,joy,luck</t>
@@ -4512,7 +4512,7 @@
     <t xml:space="preserve">luck, opportunity, joy</t>
   </si>
   <si>
-    <t xml:space="preserve">Rare and potent luck. Opens doors that were shut.</t>
+    <t xml:space="preserve">Rare and potent fortune. Opens doors that were shut.</t>
   </si>
   <si>
     <t xml:space="preserve">joy,luck,opportunity</t>
@@ -4530,7 +4530,7 @@
     <t xml:space="preserve">passion, love, beauty</t>
   </si>
   <si>
-    <t xml:space="preserve">Hot-blooded. Passion you can feel in your cheeks.</t>
+    <t xml:space="preserve">Hot-blooded. A fire you can feel in your cheeks.</t>
   </si>
   <si>
     <t xml:space="preserve">beauty,love,passion</t>
@@ -4539,7 +4539,7 @@
     <t xml:space="preserve">sleep, rest, calm</t>
   </si>
   <si>
-    <t xml:space="preserve">Heavy-lidded and gentle. Brings the body down to sleep.</t>
+    <t xml:space="preserve">Heavy-lidded and gentle. Brings the body down for the night.</t>
   </si>
   <si>
     <t xml:space="preserve">calm,rest,sleep</t>
@@ -4617,7 +4617,7 @@
     <t xml:space="preserve">dreams, intuition, protection</t>
   </si>
   <si>
-    <t xml:space="preserve">Strong dreams, open sight, watchful sleep. Not for the faint-hearted.</t>
+    <t xml:space="preserve">Vivid nights, open sight, a watchful pillow. Not for the faint-hearted.</t>
   </si>
   <si>
     <t xml:space="preserve">dreams,intuition,protection</t>
@@ -4746,7 +4746,7 @@
     <t xml:space="preserve">courage, confidence</t>
   </si>
   <si>
-    <t xml:space="preserve">Courage for a fearful heart.</t>
+    <t xml:space="preserve">Nerve for a fearful heart.</t>
   </si>
   <si>
     <t xml:space="preserve">confidence,courage</t>
@@ -5046,7 +5046,7 @@
     <t xml:space="preserve">success, passion, abundance, energy, comfort</t>
   </si>
   <si>
-    <t xml:space="preserve">Quick success and warm plenty.</t>
+    <t xml:space="preserve">Quick wins and warm plenty.</t>
   </si>
   <si>
     <t xml:space="preserve">abundance,comfort,energy,passion,success</t>
@@ -5214,7 +5214,7 @@
     <t xml:space="preserve">comfort, rest, self-love</t>
   </si>
   <si>
-    <t xml:space="preserve">Nursery comfort for grown-ups who need tucking in.</t>
+    <t xml:space="preserve">Nursery softness for grown-ups who need tucking in.</t>
   </si>
   <si>
     <t xml:space="preserve">comfort,rest,self-love</t>
@@ -5241,7 +5241,7 @@
     <t xml:space="preserve">luck, joy</t>
   </si>
   <si>
-    <t xml:space="preserve">Birthday-cake luck for whoever blows out the candles.</t>
+    <t xml:space="preserve">Birthday-cake fortune for whoever blows out the candles.</t>
   </si>
   <si>
     <t xml:space="preserve">joy,luck</t>
@@ -5253,7 +5253,7 @@
     <t xml:space="preserve">beauty, self-love, comfort</t>
   </si>
   <si>
-    <t xml:space="preserve">Draws out and smooths the skin. A beauty mask.</t>
+    <t xml:space="preserve">Draws out and smooths the skin. A face mask for a glow.</t>
   </si>
   <si>
     <t xml:space="preserve">protection, cleansing, grounding, home</t>
@@ -5295,7 +5295,7 @@
     <t xml:space="preserve">protection, beginnings</t>
   </si>
   <si>
-    <t xml:space="preserve">Crushed shell for gentle protection of new things.</t>
+    <t xml:space="preserve">Crushed shell that gently guards new things.</t>
   </si>
   <si>
     <t xml:space="preserve">beginnings,protection</t>
@@ -5454,7 +5454,7 @@
     <t xml:space="preserve">courage, creativity, energy</t>
   </si>
   <si>
-    <t xml:space="preserve">Fire for action and courage.</t>
+    <t xml:space="preserve">Fire for action and nerve.</t>
   </si>
   <si>
     <t xml:space="preserve">courage,creativity,energy</t>
@@ -5499,7 +5499,7 @@
     <t xml:space="preserve">luck, opportunity, abundance</t>
   </si>
   <si>
-    <t xml:space="preserve">Gentle luck and new chances.</t>
+    <t xml:space="preserve">Gentle good fortune and new chances.</t>
   </si>
   <si>
     <t xml:space="preserve">abundance,luck,opportunity</t>
@@ -5508,7 +5508,7 @@
     <t xml:space="preserve">grounding, protection, focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Heavy grounding for the body.</t>
+    <t xml:space="preserve">Heavy iron weight that keeps the body steady.</t>
   </si>
   <si>
     <t xml:space="preserve">focus,grounding,protection</t>
@@ -5535,7 +5535,7 @@
     <t xml:space="preserve">transformation, intuition, creativity</t>
   </si>
   <si>
-    <t xml:space="preserve">Shifting light of transformation.</t>
+    <t xml:space="preserve">Shifting light, for becoming someone new.</t>
   </si>
   <si>
     <t xml:space="preserve">creativity,intuition,transformation</t>
@@ -5544,7 +5544,7 @@
     <t xml:space="preserve">truth, communication</t>
   </si>
   <si>
-    <t xml:space="preserve">The stone of truth-telling.</t>
+    <t xml:space="preserve">The stone for saying what is real.</t>
   </si>
   <si>
     <t xml:space="preserve">communication,truth</t>
@@ -5586,7 +5586,7 @@
     <t xml:space="preserve">beauty, self-love, calm</t>
   </si>
   <si>
-    <t xml:space="preserve">Lustrous and still. Beauty that doesn't need to try.</t>
+    <t xml:space="preserve">Lustrous and still. Loveliness that doesn't need to try.</t>
   </si>
   <si>
     <t xml:space="preserve">beauty,calm,self-love</t>
@@ -5691,7 +5691,7 @@
     <t xml:space="preserve">boundaries, protection</t>
   </si>
   <si>
-    <t xml:space="preserve">Prickly. Boundaries for someone too soft-hearted.</t>
+    <t xml:space="preserve">Prickly. A line drawn for someone too soft-hearted.</t>
   </si>
   <si>
     <t xml:space="preserve">abundance, home, friendship</t>
@@ -5706,7 +5706,7 @@
     <t xml:space="preserve">luck, opportunity, play</t>
   </si>
   <si>
-    <t xml:space="preserve">Snatches luck and chances.</t>
+    <t xml:space="preserve">Snatches fortune and chances.</t>
   </si>
   <si>
     <t xml:space="preserve">luck,opportunity,play</t>
@@ -5715,7 +5715,7 @@
     <t xml:space="preserve">dreams, transformation, intuition</t>
   </si>
   <si>
-    <t xml:space="preserve">Drawn to the moon. Uncanny dreams and change.</t>
+    <t xml:space="preserve">Drawn to the moon. Uncanny nights and change.</t>
   </si>
   <si>
     <t xml:space="preserve">dreams,intuition,transformation</t>
@@ -6024,7 +6024,7 @@
     <t xml:space="preserve">love, attraction</t>
   </si>
   <si>
-    <t xml:space="preserve">Deep, devoted love.</t>
+    <t xml:space="preserve">Deep, devoted affection.</t>
   </si>
   <si>
     <t xml:space="preserve">attraction,love</t>
@@ -6108,7 +6108,7 @@
     <t xml:space="preserve">play, opportunity, travel</t>
   </si>
   <si>
-    <t xml:space="preserve">Wandering play and small chances.</t>
+    <t xml:space="preserve">Wandering games and small chances.</t>
   </si>
   <si>
     <t xml:space="preserve">opportunity,play,travel</t>
@@ -6141,7 +6141,7 @@
     <t xml:space="preserve">luck, abundance</t>
   </si>
   <si>
-    <t xml:space="preserve">Hard luck you can hold.</t>
+    <t xml:space="preserve">Hard fortune you can hold.</t>
   </si>
   <si>
     <t xml:space="preserve">protection, play, wonder</t>
@@ -6243,7 +6243,7 @@
     <t xml:space="preserve">luck, play</t>
   </si>
   <si>
-    <t xml:space="preserve">A roll of chance. Bold luck.</t>
+    <t xml:space="preserve">A roll of chance. Bold fortune.</t>
   </si>
   <si>
     <t xml:space="preserve">Write a name in it, then burn the page.</t>

--- a/ingredient_asset_tracker.xlsx
+++ b/ingredient_asset_tracker.xlsx
@@ -4356,7 +4356,7 @@
     <t xml:space="preserve">energy, creativity</t>
   </si>
   <si>
-    <t xml:space="preserve">Raw, crackling energy for a stuck mind.</t>
+    <t xml:space="preserve">Raw, crackling force for a stuck mind.</t>
   </si>
   <si>
     <t xml:space="preserve">creativity,energy</t>
@@ -6102,7 +6102,7 @@
     <t xml:space="preserve">courage,grounding,protection</t>
   </si>
   <si>
-    <t xml:space="preserve">Hung over the door. Old, steady protection.</t>
+    <t xml:space="preserve">Hung over the door. Old, steady guard.</t>
   </si>
   <si>
     <t xml:space="preserve">play, opportunity, travel</t>

--- a/ingredient_asset_tracker.xlsx
+++ b/ingredient_asset_tracker.xlsx
@@ -972,7 +972,7 @@
     <row r="18">
       <c r="A18" s="22" t="inlineStr">
         <is>
-          <t>Letters lists the 17 letters that arrive in the post: sender, the one or two ingredients each describes, the keyword it names, and the first order that needs it. Letters are a side help; every order can be solved without them.</t>
+          <t>Letters lists the 17 letters that arrive in the post. Each points at a dead end: an ingredient whose needed keyword is hidden, so searching collected words won't find it. Columns give the keyword it names, the first order that needs it, and why that spot is hard. Letters are a side help; every order can be solved without them.</t>
         </is>
       </c>
     </row>
@@ -74005,22 +74005,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="18" min="1" max="1"/>
     <col width="10" customWidth="1" style="18" min="2" max="2"/>
-    <col width="34" customWidth="1" style="18" min="3" max="3"/>
-    <col width="12" customWidth="1" style="18" min="4" max="4"/>
-    <col width="40" customWidth="1" style="18" min="5" max="5"/>
-    <col width="9" customWidth="1" style="18" min="6" max="6"/>
-    <col width="18" customWidth="1" style="18" min="7" max="7"/>
-    <col width="13" customWidth="1" style="18" min="8" max="8"/>
-    <col width="34" customWidth="1" style="18" min="9" max="9"/>
+    <col width="32" customWidth="1" style="18" min="3" max="3"/>
+    <col width="36" customWidth="1" style="18" min="4" max="4"/>
+    <col width="9" customWidth="1" style="18" min="5" max="5"/>
+    <col width="18" customWidth="1" style="18" min="6" max="6"/>
+    <col width="13" customWidth="1" style="18" min="7" max="7"/>
+    <col width="32" customWidth="1" style="18" min="8" max="8"/>
+    <col width="40" customWidth="1" style="18" min="9" max="9"/>
     <col width="18" customWidth="1" style="18" min="10" max="10"/>
     <col width="13" customWidth="1" style="18" min="11" max="11"/>
-    <col width="34" customWidth="1" style="18" min="12" max="12"/>
-    <col width="90" customWidth="1" style="18" min="13" max="13"/>
+    <col width="32" customWidth="1" style="18" min="12" max="12"/>
+    <col width="40" customWidth="1" style="18" min="13" max="13"/>
+    <col width="90" customWidth="1" style="18" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -74041,32 +74042,32 @@
       </c>
       <c r="D1" s="33" t="inlineStr">
         <is>
-          <t>Place type</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="E1" s="33" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Hints (#)</t>
         </is>
       </c>
       <c r="F1" s="33" t="inlineStr">
         <is>
-          <t>Hints (#)</t>
+          <t>Ingredient 1</t>
         </is>
       </c>
       <c r="G1" s="33" t="inlineStr">
         <is>
-          <t>Ingredient 1</t>
+          <t>Keyword 1</t>
         </is>
       </c>
       <c r="H1" s="33" t="inlineStr">
         <is>
-          <t>Keyword 1</t>
+          <t>First needed 1</t>
         </is>
       </c>
       <c r="I1" s="33" t="inlineStr">
         <is>
-          <t>First needed 1</t>
+          <t>Why it is hard 1</t>
         </is>
       </c>
       <c r="J1" s="33" t="inlineStr">
@@ -74085,6 +74086,11 @@
         </is>
       </c>
       <c r="M1" s="33" t="inlineStr">
+        <is>
+          <t>Why it is hard 2</t>
+        </is>
+      </c>
+      <c r="N1" s="33" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
@@ -74106,36 +74112,37 @@
       </c>
       <c r="D2" s="34" t="inlineStr">
         <is>
-          <t>Market town</t>
-        </is>
-      </c>
-      <c r="E2" s="34" t="inlineStr">
-        <is>
           <t>From the apothecary on Mill Lane</t>
         </is>
       </c>
-      <c r="F2" s="34" t="n">
+      <c r="E2" s="34" t="n">
         <v>1</v>
       </c>
+      <c r="F2" s="34" t="inlineStr">
+        <is>
+          <t>Nettle</t>
+        </is>
+      </c>
       <c r="G2" s="34" t="inlineStr">
         <is>
-          <t>Nettle</t>
+          <t>healing</t>
         </is>
       </c>
       <c r="H2" s="34" t="inlineStr">
         <is>
-          <t>healing</t>
+          <t>Day 1 · #194 The Inner Housekeeper</t>
         </is>
       </c>
       <c r="I2" s="34" t="inlineStr">
         <is>
-          <t>Day 1 · #194 The Inner Housekeeper</t>
+          <t>its entry shows no keyword; searching healing finds 3 other herbs &amp; flowers entries instead</t>
         </is>
       </c>
       <c r="J2" s="34" t="inlineStr"/>
       <c r="K2" s="34" t="inlineStr"/>
       <c r="L2" s="34" t="inlineStr"/>
-      <c r="M2" s="34" t="inlineStr">
+      <c r="M2" s="34" t="inlineStr"/>
+      <c r="N2" s="34" t="inlineStr">
         <is>
           <t>To whoever keeps the Emporium now,
 Our shelves are bare of the one herb we can't do without. You'll know the one: it stings your fingers when you pick it, and then it builds a worn-out body back up. Nothing does more for healing after a long sickness.
@@ -74146,73 +74153,78 @@
     </row>
     <row r="3">
       <c r="A3" s="34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B3" s="34" t="inlineStr">
         <is>
-          <t>Sunrise</t>
+          <t>Twilight</t>
         </is>
       </c>
       <c r="C3" s="34" t="inlineStr">
         <is>
-          <t>The Stanbridge Library of Old Craft</t>
+          <t>The Halloway Baths</t>
         </is>
       </c>
       <c r="D3" s="34" t="inlineStr">
         <is>
-          <t>University city</t>
-        </is>
-      </c>
-      <c r="E3" s="34" t="inlineStr">
-        <is>
-          <t>From the Stanbridge Library of Old Craft</t>
-        </is>
-      </c>
-      <c r="F3" s="34" t="n">
+          <t>From the bathhouse at Halloway</t>
+        </is>
+      </c>
+      <c r="E3" s="34" t="n">
         <v>2</v>
       </c>
+      <c r="F3" s="34" t="inlineStr">
+        <is>
+          <t>Epsom salt</t>
+        </is>
+      </c>
       <c r="G3" s="34" t="inlineStr">
         <is>
-          <t>Licorice root</t>
+          <t>cleansing</t>
         </is>
       </c>
       <c r="H3" s="34" t="inlineStr">
         <is>
-          <t>confidence</t>
+          <t>Day 10 · #161 The Fresh Linen Familiar</t>
         </is>
       </c>
       <c r="I3" s="34" t="inlineStr">
         <is>
-          <t>Day 4 · #49 The Unmasked Self</t>
+          <t>its entry shows no keyword; searching cleansing finds 2 other pantry: salts, sugars &amp; baking entries instead</t>
         </is>
       </c>
       <c r="J3" s="34" t="inlineStr">
         <is>
-          <t>Lapis lazuli</t>
+          <t>Rose clay</t>
         </is>
       </c>
       <c r="K3" s="34" t="inlineStr">
         <is>
-          <t>truth</t>
+          <t>comfort</t>
         </is>
       </c>
       <c r="L3" s="34" t="inlineStr">
         <is>
-          <t>Day 10 · #88 The Guiding Thread</t>
+          <t>Day 45 · #98 The Soft Return</t>
         </is>
       </c>
       <c r="M3" s="34" t="inlineStr">
         <is>
-          <t>To the keeper of the Emporium,
-Your shop still holds our copy of Herbs for the Lecture Hall (overdue since 1987). Chapter four is on the sweet black root that speakers chew before a big crowd; the author claims it lends the timid confidence. Chapter nine is on the blue stone flecked with gold that old scholars ground into their ink, so that whatever they wrote would be the truth.
-Kindly return the book, or failing that, a box of the root.
-The Librarian, Stanbridge Library of Old Craft</t>
+          <t>its entry shows only self-love; searching comfort finds 3 other pantry: salts, sugars &amp; baking entries instead</t>
+        </is>
+      </c>
+      <c r="N3" s="34" t="inlineStr">
+        <is>
+          <t>To the Emporium,
+Two orders, if you would. The bitter white crystals our guests tip into the hot pool after a long walk: they draw the ache out of the legs, and my mother called a soak in them a proper cleansing. And the soft pink mud for the face masks. The old ladies say nothing gives them more comfort of an evening.
+We have been buying poor stuff from Marrowgate and the guests can tell.
+Mr Hugo Fairweather, Manager, the Halloway Baths</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" s="34" t="inlineStr">
         <is>
@@ -74221,95 +74233,42 @@
       </c>
       <c r="C4" s="34" t="inlineStr">
         <is>
-          <t>Thistle &amp; Sons Wandwrights, Elderhollow</t>
+          <t>The Honeywell Beekeepers</t>
         </is>
       </c>
       <c r="D4" s="34" t="inlineStr">
         <is>
-          <t>Forest village</t>
-        </is>
-      </c>
-      <c r="E4" s="34" t="inlineStr">
-        <is>
-          <t>From the wandwrights in Elderhollow</t>
-        </is>
-      </c>
-      <c r="F4" s="34" t="n">
+          <t>From the beekeepers of Honeywell</t>
+        </is>
+      </c>
+      <c r="E4" s="34" t="n">
         <v>1</v>
       </c>
+      <c r="F4" s="34" t="inlineStr">
+        <is>
+          <t>Sweet pea</t>
+        </is>
+      </c>
       <c r="G4" s="34" t="inlineStr">
         <is>
-          <t>Ash wood</t>
+          <t>friendship</t>
         </is>
       </c>
       <c r="H4" s="34" t="inlineStr">
         <is>
-          <t>intuition</t>
+          <t>Day 12 · #65 Words Like Honey</t>
         </is>
       </c>
       <c r="I4" s="34" t="inlineStr">
         <is>
-          <t>Day 1 · #111 The Language of Ravens</t>
+          <t>its entry shows no keyword; searching friendship finds 1 other herbs &amp; flowers entry instead</t>
         </is>
       </c>
       <c r="J4" s="34" t="inlineStr"/>
       <c r="K4" s="34" t="inlineStr"/>
       <c r="L4" s="34" t="inlineStr"/>
-      <c r="M4" s="34" t="inlineStr">
-        <is>
-          <t>Madam,
-We are short of the pale, straight-grained wood the old carvers cut their staves of sight from. A wand of it points true. My grandfather swore it sharpened a witch's intuition better than any crystal.
-If you have offcuts in the back, we would pay well for them.
-Silas Thistle, Thistle &amp; Sons Wandwrights, Elderhollow</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="B5" s="34" t="inlineStr">
-        <is>
-          <t>Twilight</t>
-        </is>
-      </c>
-      <c r="C5" s="34" t="inlineStr">
-        <is>
-          <t>The Honeywell Beekeepers</t>
-        </is>
-      </c>
-      <c r="D5" s="34" t="inlineStr">
-        <is>
-          <t>Village</t>
-        </is>
-      </c>
-      <c r="E5" s="34" t="inlineStr">
-        <is>
-          <t>From the beekeepers of Honeywell</t>
-        </is>
-      </c>
-      <c r="F5" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="34" t="inlineStr">
-        <is>
-          <t>Sweet pea</t>
-        </is>
-      </c>
-      <c r="H5" s="34" t="inlineStr">
-        <is>
-          <t>friendship</t>
-        </is>
-      </c>
-      <c r="I5" s="34" t="inlineStr">
-        <is>
-          <t>Day 12 · #65 Words Like Honey</t>
-        </is>
-      </c>
-      <c r="J5" s="34" t="inlineStr"/>
-      <c r="K5" s="34" t="inlineStr"/>
-      <c r="L5" s="34" t="inlineStr"/>
-      <c r="M5" s="34" t="inlineStr">
+      <c r="M4" s="34" t="inlineStr"/>
+      <c r="N4" s="34" t="inlineStr">
         <is>
           <t>Dear Emporium,
 We grow a ruffled, sweet-smelling climber along the hive fence, the flower everyone sends when they mean thank you. The bees adore it and so do the neighbours. A jar of honey and a posy of it on the doorstep has kept friendship sweet on our lane for forty years.
@@ -74318,195 +74277,277 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="B5" s="34" t="inlineStr">
+        <is>
+          <t>Noon</t>
+        </is>
+      </c>
+      <c r="C5" s="34" t="inlineStr">
+        <is>
+          <t>Cloverdale Village School</t>
+        </is>
+      </c>
+      <c r="D5" s="34" t="inlineStr">
+        <is>
+          <t>From the village school in Cloverdale</t>
+        </is>
+      </c>
+      <c r="E5" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="34" t="inlineStr">
+        <is>
+          <t>Daisy</t>
+        </is>
+      </c>
+      <c r="G5" s="34" t="inlineStr">
+        <is>
+          <t>friendship</t>
+        </is>
+      </c>
+      <c r="H5" s="34" t="inlineStr">
+        <is>
+          <t>Day 13 · #68 A Thousand Little Lights</t>
+        </is>
+      </c>
+      <c r="I5" s="34" t="inlineStr">
+        <is>
+          <t>its entry shows only beginnings; searching friendship finds 7 other herbs &amp; flowers entries instead</t>
+        </is>
+      </c>
+      <c r="J5" s="34" t="inlineStr">
+        <is>
+          <t>Clover</t>
+        </is>
+      </c>
+      <c r="K5" s="34" t="inlineStr">
+        <is>
+          <t>luck</t>
+        </is>
+      </c>
+      <c r="L5" s="34" t="inlineStr">
+        <is>
+          <t>Day 20 · #31 Cloverkiss</t>
+        </is>
+      </c>
+      <c r="M5" s="34" t="inlineStr">
+        <is>
+          <t>its entry shows only friendship; searching luck finds 7 other herbs &amp; flowers entries instead</t>
+        </is>
+      </c>
+      <c r="N5" s="34" t="inlineStr">
+        <is>
+          <t>Dear Emporium,
+A new girl starts with us next week, and I want her first day to go well. Here the children make a chain of the little white-and-yellow field flowers for anyone new; it is how friendship starts in Cloverdale. The older ones go hunting in the fields for the plain three-leaved kind to tuck in her pocket, for luck.
+The frost has spoilt both. Have you any dried?
+Miss Primrose Dell, Cloverdale Village School</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" s="34" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="34" t="inlineStr">
         <is>
-          <t>Sunrise</t>
+          <t>Noon</t>
         </is>
       </c>
       <c r="C6" s="34" t="inlineStr">
         <is>
-          <t>The Copper Kettle, Teacup Lane, Marrowgate</t>
+          <t>Lavinia's Bridal Rooms, Kingsmere</t>
         </is>
       </c>
       <c r="D6" s="34" t="inlineStr">
         <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="E6" s="34" t="inlineStr">
-        <is>
-          <t>From a tea room on Teacup Lane</t>
-        </is>
-      </c>
-      <c r="F6" s="34" t="n">
+          <t>From a bridal boutique in Kingsmere</t>
+        </is>
+      </c>
+      <c r="E6" s="34" t="n">
         <v>2</v>
       </c>
+      <c r="F6" s="34" t="inlineStr">
+        <is>
+          <t>Orange blossom</t>
+        </is>
+      </c>
       <c r="G6" s="34" t="inlineStr">
         <is>
-          <t>Bergamot</t>
+          <t>joy</t>
         </is>
       </c>
       <c r="H6" s="34" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>Day 16 · #55 Celestial Spotlight</t>
         </is>
       </c>
       <c r="I6" s="34" t="inlineStr">
         <is>
-          <t>Day 15 · #165 The Solitude Sweetspot</t>
+          <t>its entry shows no keyword; searching joy finds 7 other herbs &amp; flowers entries instead</t>
         </is>
       </c>
       <c r="J6" s="34" t="inlineStr">
         <is>
-          <t>Black tea</t>
+          <t>White lily</t>
         </is>
       </c>
       <c r="K6" s="34" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>beauty</t>
         </is>
       </c>
       <c r="L6" s="34" t="inlineStr">
         <is>
-          <t>Day 15 · #165 The Solitude Sweetspot</t>
+          <t>Day 24 · #52 Swanlight</t>
         </is>
       </c>
       <c r="M6" s="34" t="inlineStr">
         <is>
-          <t>Hello from Marrowgate!
-Two requests from a very tired city. First, the little citrus that perfumes a good grey tea: our four o'clock ladies say nothing keeps them calm through a quarrel like it. Second, the strong dark leaf itself, brewed thick. Our night porters need the energy.
-Could we order a tin of each?
-Bess, The Copper Kettle, Teacup Lane</t>
+          <t>its entry shows only truth; searching beauty finds 5 other herbs &amp; flowers entries instead</t>
+        </is>
+      </c>
+      <c r="N6" s="34" t="inlineStr">
+        <is>
+          <t>Darling shop,
+Wedding season is upon us. My brides want the small white flowers from the citrus tree woven into their hair, as their grandmothers wore them: they say a bride crowned with them glows with joy. The tall still white flower goes in the bouquet. Nothing gives a quiet bride beauty like it.
+Send whatever you can. Kingsmere does not do things by halves.
+Lavinia, Lavinia's Bridal Rooms, Kingsmere</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="34" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>Noon</t>
+          <t>Twilight</t>
         </is>
       </c>
       <c r="C7" s="34" t="inlineStr">
         <is>
-          <t>St Aldric's Church, Thornbury</t>
+          <t>The Coastguard Station, Caldwell-on-Sea</t>
         </is>
       </c>
       <c r="D7" s="34" t="inlineStr">
         <is>
-          <t>Walled town</t>
-        </is>
-      </c>
-      <c r="E7" s="34" t="inlineStr">
-        <is>
-          <t>From the churchwarden at Thornbury</t>
-        </is>
-      </c>
-      <c r="F7" s="34" t="n">
+          <t>From the coastguard at Caldwell-on-Sea</t>
+        </is>
+      </c>
+      <c r="E7" s="34" t="n">
         <v>1</v>
       </c>
+      <c r="F7" s="34" t="inlineStr">
+        <is>
+          <t>Black tourmaline</t>
+        </is>
+      </c>
       <c r="G7" s="34" t="inlineStr">
         <is>
-          <t>Black pepper</t>
+          <t>protection</t>
         </is>
       </c>
       <c r="H7" s="34" t="inlineStr">
         <is>
-          <t>courage</t>
+          <t>Day 15 · #16 The Iron Moon</t>
         </is>
       </c>
       <c r="I7" s="34" t="inlineStr">
         <is>
-          <t>Day 25 · #85 First Spark, First Flame</t>
+          <t>its entry shows no keyword; searching protection finds 3 other crystals entries instead</t>
         </is>
       </c>
       <c r="J7" s="34" t="inlineStr"/>
       <c r="K7" s="34" t="inlineStr"/>
       <c r="L7" s="34" t="inlineStr"/>
-      <c r="M7" s="34" t="inlineStr">
+      <c r="M7" s="34" t="inlineStr"/>
+      <c r="N7" s="34" t="inlineStr">
         <is>
           <t>To the Emporium,
-The vicar has asked me, against my better judgement, to write. Before every sermon he grinds the little hot black corns over his breakfast eggs. He says the heat in the belly gives him the courage to face the congregation.
-Our grocer has run out. I trust this stays between us.
-Mr Edgar Penhallow, Churchwarden, Thornbury</t>
+Every coastguard on this stretch keeps a black, ridged stone in his coat, the kind that looks like a bundle of burnt matches. The old men say it soaks up whatever is thrown at you. It is the only protection I trust on a night shift.
+Mine went over the side in the last storm. Could you send another?
+Officer Jory Penrose, Caldwell-on-Sea</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="34" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B8" s="34" t="inlineStr">
         <is>
-          <t>Twilight</t>
+          <t>Noon</t>
         </is>
       </c>
       <c r="C8" s="34" t="inlineStr">
         <is>
-          <t>Lavinia's Bridal Rooms, Kingsmere</t>
+          <t>St Aldric's Church, Thornbury</t>
         </is>
       </c>
       <c r="D8" s="34" t="inlineStr">
         <is>
-          <t>Lake town</t>
-        </is>
-      </c>
-      <c r="E8" s="34" t="inlineStr">
-        <is>
-          <t>From a bridal boutique in Kingsmere</t>
-        </is>
-      </c>
-      <c r="F8" s="34" t="n">
+          <t>From the churchwarden at Thornbury</t>
+        </is>
+      </c>
+      <c r="E8" s="34" t="n">
         <v>2</v>
       </c>
+      <c r="F8" s="34" t="inlineStr">
+        <is>
+          <t>Copal</t>
+        </is>
+      </c>
       <c r="G8" s="34" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>calm</t>
         </is>
       </c>
       <c r="H8" s="34" t="inlineStr">
         <is>
-          <t>passion</t>
+          <t>Day 21 · #96 The Last Candle</t>
         </is>
       </c>
       <c r="I8" s="34" t="inlineStr">
         <is>
-          <t>Day 39 · #4 Ember of Eden</t>
+          <t>its entry shows no keyword; searching calm finds 1 other resins &amp; incense entry instead</t>
         </is>
       </c>
       <c r="J8" s="34" t="inlineStr">
         <is>
-          <t>Peach</t>
+          <t>Black pepper</t>
         </is>
       </c>
       <c r="K8" s="34" t="inlineStr">
         <is>
-          <t>beauty</t>
+          <t>courage</t>
         </is>
       </c>
       <c r="L8" s="34" t="inlineStr">
         <is>
-          <t>Day 45 · #222 The Camera Loves You</t>
+          <t>Day 25 · #85 First Spark, First Flame</t>
         </is>
       </c>
       <c r="M8" s="34" t="inlineStr">
         <is>
-          <t>Darling shop,
-Wedding season is upon us and my brides want two things. A deep red flower steeped into a tea that brings a hot flush to the cheeks; one of my grooms called it pure passion. And the soft, fuzzy summer fruit for the skin. Nothing gives a bride beauty like it on the morning.
-Send whatever you can. Kingsmere does not do things by halves.
-Lavinia, Lavinia's Bridal Rooms, Kingsmere</t>
+          <t>its entry shows no keyword; searching courage finds 1 other spices entry instead</t>
+        </is>
+      </c>
+      <c r="N8" s="34" t="inlineStr">
+        <is>
+          <t>To the Emporium,
+The vicar has asked me, against my better judgement, to write. He wants the pale sweet resin from overseas for the censer. When it burns, he says, the whole parish sits together in calm, even the Hendersons. He also grinds the little hot black corns over his breakfast eggs before every sermon, for the courage to face us.
+Our grocer has run out of both. I trust this stays between us.
+Mr Edgar Penhallow, Churchwarden, Thornbury</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="34" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B9" s="34" t="inlineStr">
         <is>
@@ -74515,346 +74556,360 @@
       </c>
       <c r="C9" s="34" t="inlineStr">
         <is>
-          <t>The Wool Basket, Little Mitten</t>
+          <t>Damson Cottage Jams, Plumtree Hollow</t>
         </is>
       </c>
       <c r="D9" s="34" t="inlineStr">
         <is>
-          <t>Hill village</t>
-        </is>
-      </c>
-      <c r="E9" s="34" t="inlineStr">
-        <is>
-          <t>From a wool shop in Little Mitten</t>
-        </is>
-      </c>
-      <c r="F9" s="34" t="n">
+          <t>From a jam-maker in Plumtree Hollow</t>
+        </is>
+      </c>
+      <c r="E9" s="34" t="n">
         <v>1</v>
       </c>
+      <c r="F9" s="34" t="inlineStr">
+        <is>
+          <t>Peridot</t>
+        </is>
+      </c>
       <c r="G9" s="34" t="inlineStr">
         <is>
-          <t>Rainbow threads</t>
+          <t>growth</t>
         </is>
       </c>
       <c r="H9" s="34" t="inlineStr">
         <is>
-          <t>friendship</t>
+          <t>Day 25 · #135 The Green Comet</t>
         </is>
       </c>
       <c r="I9" s="34" t="inlineStr">
         <is>
-          <t>Day 36 · #61 The Wildflower Circle</t>
+          <t>its entry shows no keyword; searching growth finds 1 other crystals entry instead</t>
         </is>
       </c>
       <c r="J9" s="34" t="inlineStr"/>
       <c r="K9" s="34" t="inlineStr"/>
       <c r="L9" s="34" t="inlineStr"/>
-      <c r="M9" s="34" t="inlineStr">
-        <is>
-          <t>Hello there,
-Every summer the children here plait bracelets out of every colour we stock and swap them on the last day of camp. Our knitting circle swears those swaps are where friendship in this village starts.
-We're short of the bright mixed bundles. Have you any put by?
-Nell, The Wool Basket, Little Mitten</t>
+      <c r="M9" s="34" t="inlineStr"/>
+      <c r="N9" s="34" t="inlineStr">
+        <is>
+          <t>Hello from the Hollow,
+When the plum trees come back after a bad winter, my aunt used to hang a little pale green stone on a ribbon from the oldest branch. She said it was for the first good week after a hard season, and for growth. The trees never failed her.
+The ribbon snapped and the stone is lost in the long grass. Do you sell them?
+Bessie Damson, Plumtree Hollow</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="34" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="B10" s="34" t="inlineStr">
         <is>
-          <t>Noon</t>
+          <t>Twilight</t>
         </is>
       </c>
       <c r="C10" s="34" t="inlineStr">
         <is>
-          <t>The Cider Fair Committee, Pippin Green</t>
+          <t>Crumb &amp; Co. Bakery, Whitcombe</t>
         </is>
       </c>
       <c r="D10" s="34" t="inlineStr">
         <is>
-          <t>Orchard village</t>
-        </is>
-      </c>
-      <c r="E10" s="34" t="inlineStr">
-        <is>
-          <t>From the cider fair committee in Pippin Green</t>
-        </is>
-      </c>
-      <c r="F10" s="34" t="n">
+          <t>From the bakery in Whitcombe</t>
+        </is>
+      </c>
+      <c r="E10" s="34" t="n">
         <v>2</v>
       </c>
+      <c r="F10" s="34" t="inlineStr">
+        <is>
+          <t>Raisins</t>
+        </is>
+      </c>
       <c r="G10" s="34" t="inlineStr">
         <is>
-          <t>Apple peel</t>
+          <t>joy</t>
         </is>
       </c>
       <c r="H10" s="34" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>Day 29 · #90 The Pocket-Sized Triumph</t>
         </is>
       </c>
       <c r="I10" s="34" t="inlineStr">
         <is>
-          <t>Day 39 · #4 Ember of Eden</t>
+          <t>its entry shows no keyword; searching joy finds 2 other fruits entries instead</t>
         </is>
       </c>
       <c r="J10" s="34" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Cocoa</t>
         </is>
       </c>
       <c r="K10" s="34" t="inlineStr">
         <is>
-          <t>love</t>
+          <t>comfort</t>
         </is>
       </c>
       <c r="L10" s="34" t="inlineStr">
         <is>
-          <t>Day 87 · #3 Two Hearts, One Hearth</t>
+          <t>Day 32 · #235 The Sweetness Permission</t>
         </is>
       </c>
       <c r="M10" s="34" t="inlineStr">
         <is>
-          <t>Dear Emporium,
-Two traditions for this year's fair, and we'd like to do them properly. The long curl peeled in one go at the kitchen table, tossed over the shoulder, to make a house feel like home. And the whole fruit, shared bite for bite between two sweethearts, which our grandmothers called plain honest love.
-Could you advise? Or send a basket of anything that helps.
-Rhoda Bell, Cider Fair Committee, Pippin Green</t>
+          <t>its entry shows no keyword; searching comfort finds 3 other pantry: salts, sugars &amp; baking entries instead</t>
+        </is>
+      </c>
+      <c r="N10" s="34" t="inlineStr">
+        <is>
+          <t>Dear neighbour,
+Two things for the winter menu. The little shrivelled dark fruit we fold into lunch-box buns. The mothers say one bun is pure joy for a child at school. And the dark bitter powder for the mugs we serve when people come in from the cold. Nothing else is such a comfort in January.
+Our supplier in Greywater has gone bust. Could you help?
+Mrs Ada Crumb, Crumb &amp; Co., Whitcombe</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="34" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B11" s="34" t="inlineStr">
         <is>
-          <t>Twilight</t>
+          <t>Noon</t>
         </is>
       </c>
       <c r="C11" s="34" t="inlineStr">
         <is>
-          <t>Mrs Pennywhistle's Sweet Shop, Sugarbrook</t>
+          <t>Thistle &amp; Sons Wandwrights, Elderhollow</t>
         </is>
       </c>
       <c r="D11" s="34" t="inlineStr">
         <is>
-          <t>Village</t>
-        </is>
-      </c>
-      <c r="E11" s="34" t="inlineStr">
-        <is>
-          <t>From the sweet shop in Sugarbrook</t>
-        </is>
-      </c>
-      <c r="F11" s="34" t="n">
-        <v>1</v>
+          <t>From the wandwrights in Elderhollow</t>
+        </is>
+      </c>
+      <c r="E11" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="34" t="inlineStr">
+        <is>
+          <t>Willow bark</t>
+        </is>
       </c>
       <c r="G11" s="34" t="inlineStr">
         <is>
-          <t>Pink glitter</t>
+          <t>intuition</t>
         </is>
       </c>
       <c r="H11" s="34" t="inlineStr">
         <is>
-          <t>play</t>
+          <t>Day 38 · #106 The Dreaming Garden</t>
         </is>
       </c>
       <c r="I11" s="34" t="inlineStr">
         <is>
-          <t>Day 56 · #198 The Forgiving Tide</t>
-        </is>
-      </c>
-      <c r="J11" s="34" t="inlineStr"/>
-      <c r="K11" s="34" t="inlineStr"/>
-      <c r="L11" s="34" t="inlineStr"/>
+          <t>its entry shows no keyword; searching intuition finds 4 other herbs &amp; flowers entries instead</t>
+        </is>
+      </c>
+      <c r="J11" s="34" t="inlineStr">
+        <is>
+          <t>Wormwood</t>
+        </is>
+      </c>
+      <c r="K11" s="34" t="inlineStr">
+        <is>
+          <t>transformation</t>
+        </is>
+      </c>
+      <c r="L11" s="34" t="inlineStr">
+        <is>
+          <t>Day 36 · #116 The Phoenix's First Petal</t>
+        </is>
+      </c>
       <c r="M11" s="34" t="inlineStr">
         <is>
-          <t>Dear shop,
-The girls who come in after school have been told to tone it down, and it shows. I used to dust their cake pops with the shiny pink stuff, and the whole lot of them would go back to play in the street like little ones again.
-Have you a pot to spare? I'll send fudge.
-Mrs Pennywhistle, Sugarbrook</t>
+          <t>its entry shows no keyword; searching transformation finds 1 other herbs &amp; flowers entry instead</t>
+        </is>
+      </c>
+      <c r="N11" s="34" t="inlineStr">
+        <is>
+          <t>Madam,
+Two old remedies my grandfather kept, which no one else seems to stock. The bark of the weeping tree by the river, which every grandmother uses for a sore back; few know that the old witches chewed it for intuition. And the bitter silver-grey herb he steeped in his spirits once a year, for transformation. He said it was not for the faint-hearted.
+If you have either, we would pay well.
+Silas Thistle, Thistle &amp; Sons Wandwrights, Elderhollow</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="34" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="B12" s="34" t="inlineStr">
         <is>
-          <t>Sunrise</t>
+          <t>Twilight</t>
         </is>
       </c>
       <c r="C12" s="34" t="inlineStr">
         <is>
-          <t>The Halloway Baths</t>
+          <t>The Crossed Keys Inn, Ashby Cross</t>
         </is>
       </c>
       <c r="D12" s="34" t="inlineStr">
         <is>
-          <t>Spa town</t>
-        </is>
-      </c>
-      <c r="E12" s="34" t="inlineStr">
-        <is>
-          <t>From the bathhouse at Halloway</t>
-        </is>
-      </c>
-      <c r="F12" s="34" t="n">
-        <v>2</v>
+          <t>From the coaching inn at Ashby Cross</t>
+        </is>
+      </c>
+      <c r="E12" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="34" t="inlineStr">
+        <is>
+          <t>Wooden die</t>
+        </is>
       </c>
       <c r="G12" s="34" t="inlineStr">
         <is>
-          <t>River stone</t>
+          <t>luck</t>
         </is>
       </c>
       <c r="H12" s="34" t="inlineStr">
         <is>
-          <t>grounding</t>
+          <t>Day 39 · #232 The Critical-Hit Charm</t>
         </is>
       </c>
       <c r="I12" s="34" t="inlineStr">
         <is>
-          <t>Day 53 · #168 The Waiting Room Oracle</t>
-        </is>
-      </c>
-      <c r="J12" s="34" t="inlineStr">
-        <is>
-          <t>Seaweed</t>
-        </is>
-      </c>
-      <c r="K12" s="34" t="inlineStr">
-        <is>
-          <t>connection</t>
-        </is>
-      </c>
-      <c r="L12" s="34" t="inlineStr">
-        <is>
-          <t>Day 56 · #198 The Forgiving Tide</t>
-        </is>
-      </c>
-      <c r="M12" s="34" t="inlineStr">
+          <t>its entry shows no keyword; searching luck finds 1 other findings &amp; tools entry instead</t>
+        </is>
+      </c>
+      <c r="J12" s="34" t="inlineStr"/>
+      <c r="K12" s="34" t="inlineStr"/>
+      <c r="L12" s="34" t="inlineStr"/>
+      <c r="M12" s="34" t="inlineStr"/>
+      <c r="N12" s="34" t="inlineStr">
         <is>
           <t>To the Emporium,
-Our guests rush from the train straight into the hot pool, which is no good to anybody. My mother kept a bowl of smooth stones from the riverbed by the door for them to carry; she called it grounding. She also wrapped the old ones in sea greens fresh off the tide, and said it brought back the connection with friends far away.
-Would you supply us again?
-Mr Hugo Fairweather, Manager, the Halloway Baths</t>
+Travellers wait here for the coach, and the waiting turns to gambling by supper. One old carter swears by a little carved wooden cube with dots on its faces that he blessed at your shop years ago. He says it gives him luck every time he throws it.
+The other regulars now want one each. Do you still bless them?
+Harry Oakes, landlord, the Crossed Keys, Ashby Cross</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="34" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B13" s="34" t="inlineStr">
         <is>
-          <t>Noon</t>
+          <t>Sunrise</t>
         </is>
       </c>
       <c r="C13" s="34" t="inlineStr">
         <is>
-          <t>Marchbank Haberdashery, Ribbonmere</t>
+          <t>The Starfall Retreat</t>
         </is>
       </c>
       <c r="D13" s="34" t="inlineStr">
         <is>
-          <t>Lakeside town</t>
-        </is>
-      </c>
-      <c r="E13" s="34" t="inlineStr">
-        <is>
-          <t>From a haberdasher in Ribbonmere</t>
-        </is>
-      </c>
-      <c r="F13" s="34" t="n">
+          <t>From the retreat at Starfall</t>
+        </is>
+      </c>
+      <c r="E13" s="34" t="n">
         <v>1</v>
       </c>
+      <c r="F13" s="34" t="inlineStr">
+        <is>
+          <t>Lotus</t>
+        </is>
+      </c>
       <c r="G13" s="34" t="inlineStr">
         <is>
-          <t>Velvet ribbon (red)</t>
+          <t>calm</t>
         </is>
       </c>
       <c r="H13" s="34" t="inlineStr">
         <is>
-          <t>love</t>
+          <t>Day 44 · #102 The Slow-Blooming Rose</t>
         </is>
       </c>
       <c r="I13" s="34" t="inlineStr">
         <is>
-          <t>Day 63 · #14 The Golden Vow</t>
+          <t>its entry shows only intuition; searching calm finds 4 other herbs &amp; flowers entries instead</t>
         </is>
       </c>
       <c r="J13" s="34" t="inlineStr"/>
       <c r="K13" s="34" t="inlineStr"/>
       <c r="L13" s="34" t="inlineStr"/>
-      <c r="M13" s="34" t="inlineStr">
+      <c r="M13" s="34" t="inlineStr"/>
+      <c r="N13" s="34" t="inlineStr">
         <is>
           <t>Dear Emporium,
-A gentleman came in wanting a deep red ribbon, the soft heavy kind, to tie round a ring box. He said his grandmother told him it holds a love that lasts. I sold him my last yard.
-If you keep any, I would buy the roll.
-Miss Agatha Marchbank, Ribbonmere</t>
+Our guests come up the mountain to sit and look at the stars, and most of them can't sit still for a minute. Our founder floated the great pale water flower in a bowl at the centre of the room. She said the inner sight it brings is only half its use; mostly it brings calm.
+Have you any dried blooms?
+Sister Wren, the Starfall Retreat</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="34" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="B14" s="34" t="inlineStr">
         <is>
-          <t>Twilight</t>
+          <t>Noon</t>
         </is>
       </c>
       <c r="C14" s="34" t="inlineStr">
         <is>
-          <t>Dunmore Harvest Supper</t>
+          <t>Hedge End Farm, Bramblebee</t>
         </is>
       </c>
       <c r="D14" s="34" t="inlineStr">
         <is>
-          <t>Farming town</t>
-        </is>
-      </c>
-      <c r="E14" s="34" t="inlineStr">
-        <is>
-          <t>From the harvest supper at Dunmore</t>
-        </is>
-      </c>
-      <c r="F14" s="34" t="n">
+          <t>From a farm in Bramblebee</t>
+        </is>
+      </c>
+      <c r="E14" s="34" t="n">
         <v>1</v>
       </c>
+      <c r="F14" s="34" t="inlineStr">
+        <is>
+          <t>Rose thorns</t>
+        </is>
+      </c>
       <c r="G14" s="34" t="inlineStr">
         <is>
-          <t>Wheat</t>
+          <t>boundaries</t>
         </is>
       </c>
       <c r="H14" s="34" t="inlineStr">
         <is>
-          <t>gratitude</t>
+          <t>Day 50 · #9 The Unbinding Rose</t>
         </is>
       </c>
       <c r="I14" s="34" t="inlineStr">
         <is>
-          <t>Day 69 · #37 The Abundance Garden</t>
+          <t>its entry shows no keyword; searching boundaries finds 2 other herbs &amp; flowers entries instead</t>
         </is>
       </c>
       <c r="J14" s="34" t="inlineStr"/>
       <c r="K14" s="34" t="inlineStr"/>
       <c r="L14" s="34" t="inlineStr"/>
-      <c r="M14" s="34" t="inlineStr">
-        <is>
-          <t>Hello from Dunmore,
-The harvest supper is coming, and we've always hung a sheaf of the last golden stalks from the field over the door. Gran said it was for gratitude, and a farm that forgets to say thank you has a hard winter.
-The storm flattened ours. Could you send a bundle?
-Tom Furrow, Dunmore</t>
+      <c r="M14" s="34" t="inlineStr"/>
+      <c r="N14" s="34" t="inlineStr">
+        <is>
+          <t>Hello,
+My mother used to grow a hedge of the old pink climbing flowers along our lane, and she kept a jar of the sharp bits she clipped off the stems. One on the windowsill, she said, and people learn your boundaries without you saying a word.
+My sister-in-law visits every Sunday. Have you a jar?
+Dora Bramble, Hedge End Farm, Bramblebee</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="34" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="B15" s="34" t="inlineStr">
         <is>
@@ -74863,64 +74918,69 @@
       </c>
       <c r="C15" s="34" t="inlineStr">
         <is>
-          <t>Old Things, Buttonwick</t>
+          <t>Mrs Pennywhistle's Sweet Shop, Sugarbrook</t>
         </is>
       </c>
       <c r="D15" s="34" t="inlineStr">
         <is>
-          <t>Village</t>
-        </is>
-      </c>
-      <c r="E15" s="34" t="inlineStr">
-        <is>
-          <t>From an antique shop in Buttonwick</t>
-        </is>
-      </c>
-      <c r="F15" s="34" t="n">
+          <t>From the sweet shop in Sugarbrook</t>
+        </is>
+      </c>
+      <c r="E15" s="34" t="n">
         <v>2</v>
       </c>
+      <c r="F15" s="34" t="inlineStr">
+        <is>
+          <t>Pink glitter</t>
+        </is>
+      </c>
       <c r="G15" s="34" t="inlineStr">
         <is>
-          <t>Square button</t>
+          <t>self-love</t>
         </is>
       </c>
       <c r="H15" s="34" t="inlineStr">
         <is>
-          <t>play</t>
+          <t>Day 56 · #198 The Forgiving Tide</t>
         </is>
       </c>
       <c r="I15" s="34" t="inlineStr">
         <is>
-          <t>Day 76 · #215 The Lucky Pixel</t>
+          <t>its entry shows no keyword; searching self-love finds 2 other pantry: salts, sugars &amp; baking entries instead</t>
         </is>
       </c>
       <c r="J15" s="34" t="inlineStr">
         <is>
-          <t>Locket</t>
+          <t>Pink sprinkles</t>
         </is>
       </c>
       <c r="K15" s="34" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>love</t>
         </is>
       </c>
       <c r="L15" s="34" t="inlineStr">
         <is>
-          <t>Day 82 · #191 The Forgotten Room</t>
+          <t>Day 63 · #11 Strawberry Moon</t>
         </is>
       </c>
       <c r="M15" s="34" t="inlineStr">
         <is>
-          <t>Dear neighbour,
-Two things turned up in a house clearance that I'd rather you had. A square button that must be a lost counter from some old board game, which made the grandchildren want to play all afternoon. And a small hinged case on a chain with a faded face inside, the sort that keeps a memory close.
-I'll hold them for you. Come by.
-Mr Ambrose Tuck, Old Things, Buttonwick</t>
+          <t>its entry shows no keyword; searching love finds 1 other pantry: salts, sugars &amp; baking entry instead</t>
+        </is>
+      </c>
+      <c r="N15" s="34" t="inlineStr">
+        <is>
+          <t>Dear shop,
+The girls who come in after school have been told to tone it down, and it shows. I used to dust their cake pops with the shiny pink stuff, and they'd walk out with some self-love again. And the boys buy cupcakes with the little pink sugar strands on top to hand to a sweetheart. My grandmother called those love on a cake.
+I'm out of both. I'll send fudge.
+Mrs Pennywhistle, Sugarbrook</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="34" t="n">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="B16" s="34" t="inlineStr">
         <is>
@@ -74929,106 +74989,108 @@
       </c>
       <c r="C16" s="34" t="inlineStr">
         <is>
-          <t>The Reed Weavers, Fenwick</t>
+          <t>The Cider Fair Committee, Pippin Green</t>
         </is>
       </c>
       <c r="D16" s="34" t="inlineStr">
         <is>
-          <t>Marsh village</t>
-        </is>
-      </c>
-      <c r="E16" s="34" t="inlineStr">
-        <is>
-          <t>From the reed weavers of Fenwick</t>
-        </is>
-      </c>
-      <c r="F16" s="34" t="n">
+          <t>From the cider fair committee in Pippin Green</t>
+        </is>
+      </c>
+      <c r="E16" s="34" t="n">
         <v>1</v>
       </c>
+      <c r="F16" s="34" t="inlineStr">
+        <is>
+          <t>Bee pollen</t>
+        </is>
+      </c>
       <c r="G16" s="34" t="inlineStr">
         <is>
-          <t>Web Dew</t>
+          <t>friendship</t>
         </is>
       </c>
       <c r="H16" s="34" t="inlineStr">
         <is>
-          <t>connection</t>
+          <t>Day 61 · #75 The Honeybee Feast</t>
         </is>
       </c>
       <c r="I16" s="34" t="inlineStr">
         <is>
-          <t>Day 80 · #239 The Keepsake Minute</t>
+          <t>its entry shows no keyword</t>
         </is>
       </c>
       <c r="J16" s="34" t="inlineStr"/>
       <c r="K16" s="34" t="inlineStr"/>
       <c r="L16" s="34" t="inlineStr"/>
-      <c r="M16" s="34" t="inlineStr">
-        <is>
-          <t>Hello,
-On foggy mornings the reed beds are strung with spider silk heavy with water. My mother collected the drops in a thimble. She said they tie one person to another, and used them to keep the connection between our village and the boats.
-If you want some, come before the sun burns the fog off.
-Wenna, Fenwick Reed Weavers</t>
+      <c r="M16" s="34" t="inlineStr"/>
+      <c r="N16" s="34" t="inlineStr">
+        <is>
+          <t>Dear Emporium,
+Our orchard bees leave little golden grains on everything in May, and the old orchard keepers sprinkled them over the fair loaves. They said whoever shares that bread shares the friendship of the hive.
+Our hives had a bad year. Could you send a jar for the fair?
+Rhoda Bell, Cider Fair Committee, Pippin Green</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="34" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="B17" s="34" t="inlineStr">
         <is>
-          <t>Sunrise</t>
+          <t>Twilight</t>
         </is>
       </c>
       <c r="C17" s="34" t="inlineStr">
         <is>
-          <t>The Lantern Makers, Moonmellow</t>
+          <t>Old Things, Buttonwick</t>
         </is>
       </c>
       <c r="D17" s="34" t="inlineStr">
         <is>
-          <t>Hilltop village</t>
-        </is>
-      </c>
-      <c r="E17" s="34" t="inlineStr">
-        <is>
-          <t>From the lantern makers of Moonmellow</t>
-        </is>
-      </c>
-      <c r="F17" s="34" t="n">
+          <t>From an antique shop in Buttonwick</t>
+        </is>
+      </c>
+      <c r="E17" s="34" t="n">
         <v>1</v>
       </c>
+      <c r="F17" s="34" t="inlineStr">
+        <is>
+          <t>Square button</t>
+        </is>
+      </c>
       <c r="G17" s="34" t="inlineStr">
         <is>
-          <t>Quill</t>
+          <t>play</t>
         </is>
       </c>
       <c r="H17" s="34" t="inlineStr">
         <is>
-          <t>creativity</t>
+          <t>Day 76 · #215 The Lucky Pixel</t>
         </is>
       </c>
       <c r="I17" s="34" t="inlineStr">
         <is>
-          <t>Day 87 · #112 Ink Beneath the Moon</t>
+          <t>its entry shows no keyword; searching play finds 1 other buttons entry instead</t>
         </is>
       </c>
       <c r="J17" s="34" t="inlineStr"/>
       <c r="K17" s="34" t="inlineStr"/>
       <c r="L17" s="34" t="inlineStr"/>
-      <c r="M17" s="34" t="inlineStr">
-        <is>
-          <t>Dear Emporium,
-Every lantern at our festival carries a poem, and this year I can't write a single line. The old lantern maker wrote hers with a long feather cut to a nib, and said the creativity came up through it like ink.
-If you have one, please send it before the festival.
-Pip, Moonmellow Lantern Makers</t>
+      <c r="M17" s="34" t="inlineStr"/>
+      <c r="N17" s="34" t="inlineStr">
+        <is>
+          <t>Dear neighbour,
+A house clearance turned up a box of buttons, and among them one odd square one that must be a lost counter from some old board game. I left it on the counter and the grandchildren wanted to play all afternoon.
+I'll hold it for you. Come by.
+Mr Ambrose Tuck, Old Things, Buttonwick</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="34" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B18" s="34" t="inlineStr">
         <is>
@@ -75042,52 +75104,41 @@
       </c>
       <c r="D18" s="34" t="inlineStr">
         <is>
-          <t>River city</t>
-        </is>
-      </c>
-      <c r="E18" s="34" t="inlineStr">
-        <is>
           <t>From the mill at Greywater</t>
         </is>
       </c>
-      <c r="F18" s="34" t="n">
-        <v>2</v>
+      <c r="E18" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="34" t="inlineStr">
+        <is>
+          <t>Cedar chips</t>
+        </is>
       </c>
       <c r="G18" s="34" t="inlineStr">
         <is>
-          <t>Iron filings</t>
+          <t>home</t>
         </is>
       </c>
       <c r="H18" s="34" t="inlineStr">
         <is>
-          <t>protection</t>
+          <t>Day 87 · #3 Two Hearts, One Hearth</t>
         </is>
       </c>
       <c r="I18" s="34" t="inlineStr">
         <is>
-          <t>Day 92 · #24 Rooted in Iron</t>
-        </is>
-      </c>
-      <c r="J18" s="34" t="inlineStr">
-        <is>
-          <t>Cedar chips</t>
-        </is>
-      </c>
-      <c r="K18" s="34" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="L18" s="34" t="inlineStr">
-        <is>
-          <t>Day 87 · #3 Two Hearts, One Hearth</t>
-        </is>
-      </c>
-      <c r="M18" s="34" t="inlineStr">
+          <t>its entry shows no keyword; searching home finds 1 other herbs &amp; flowers entry instead</t>
+        </is>
+      </c>
+      <c r="J18" s="34" t="inlineStr"/>
+      <c r="K18" s="34" t="inlineStr"/>
+      <c r="L18" s="34" t="inlineStr"/>
+      <c r="M18" s="34" t="inlineStr"/>
+      <c r="N18" s="34" t="inlineStr">
         <is>
           <t>To the Emporium,
-Two old mill habits I'd like to keep up. My father sprinkled the heavy grey dust from the smithy along the sill when storms came down the river; he called it protection. And he scattered sweet wood shavings in the flour bins and drawers until the whole mill smelled like home.
-Could you send a bag of each?
+My father scattered sweet red wood shavings in the flour bins and the drawers of the mill house, until the whole place smelled like home. Since he passed, it smells of damp.
+Could you send a bag?
 Sam Wend, Wend Mill, Greywater</t>
         </is>
       </c>

--- a/ingredient_asset_tracker.xlsx
+++ b/ingredient_asset_tracker.xlsx
@@ -717,7 +717,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="18">
       <c r="A4" s="21" t="inlineStr">
         <is>
@@ -939,7 +938,6 @@
         <v/>
       </c>
     </row>
-    <row r="12"/>
     <row r="13" ht="15" customHeight="1" s="18">
       <c r="A13" s="25" t="inlineStr">
         <is>
@@ -947,7 +945,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="15" customHeight="1" s="18">
       <c r="A15" s="22" t="inlineStr">
         <is>
@@ -74146,6 +74143,7 @@
         <is>
           <t>To whoever keeps the Emporium now,
 Our shelves are bare of the one herb we can't do without. You'll know the one: it stings your fingers when you pick it, and then it builds a worn-out body back up. Nothing does more for healing after a long sickness.
+I drink it myself, steeped with a little milk, after a long shift behind the counter, on the days I've looked after everyone in Wrenmoor and forgotten to look after me.
 Could you spare us a bundle or two? We'll pay in honey, as we always did.
 Agnes, Mill Lane Apothecary, Wrenmoor</t>
         </is>
@@ -74216,7 +74214,8 @@
       <c r="N3" s="34" t="inlineStr">
         <is>
           <t>To the Emporium,
-Two orders, if you would. The bitter white crystals our guests tip into the hot pool after a long walk: they draw the ache out of the legs, and my mother called a soak in them a proper cleansing. And the soft pink mud for the face masks. The old ladies say nothing gives them more comfort of an evening.
+Two orders, if you would. The bitter white crystals that draw the ache out of tired legs. Our laundry maids grate them into the soap for the towels too; they say it makes washday a proper cleansing and the hours go quicker.
+And the soft pink mud. We press it into little cakes of soap for the old gentlemen who come in after a hard day. They say nothing gives them more comfort before bed.
 We have been buying poor stuff from Marrowgate and the guests can tell.
 Mr Hugo Fairweather, Manager, the Halloway Baths</t>
         </is>
@@ -74271,7 +74270,7 @@
       <c r="N4" s="34" t="inlineStr">
         <is>
           <t>Dear Emporium,
-We grow a ruffled, sweet-smelling climber along the hive fence, the flower everyone sends when they mean thank you. The bees adore it and so do the neighbours. A jar of honey and a posy of it on the doorstep has kept friendship sweet on our lane for forty years.
+We grow a ruffled, sweet-smelling climber along the hive fence, the flower everyone sends when they mean thank you. When two neighbours here fall out and can't find the words to make it up, one of us brews a pot of tea with it and sits them down. It has kept friendship sweet on our lane for forty years.
 This year the frost took it. If you have dried flowers to spare, we'll pay in comb.
 Martha Hale and the Honeywell Beekeepers</t>
         </is>
@@ -74342,7 +74341,8 @@
       <c r="N5" s="34" t="inlineStr">
         <is>
           <t>Dear Emporium,
-A new girl starts with us next week, and I want her first day to go well. Here the children make a chain of the little white-and-yellow field flowers for anyone new; it is how friendship starts in Cloverdale. The older ones go hunting in the fields for the plain three-leaved kind to tuck in her pocket, for luck.
+The playground has turned unkind this term, and a new girl starts next week. Here the children make a chain of the little white-and-yellow field flowers for anyone new; it is how friendship starts in Cloverdale. My predecessor even burned dried ones in the classroom when tempers ran high.
+The older ones also go hunting for the plain three-leaved kind. Our school cook steeps it into a cordial on sports day, for luck.
 The frost has spoilt both. Have you any dried?
 Miss Primrose Dell, Cloverdale Village School</t>
         </is>
@@ -74413,7 +74413,8 @@
       <c r="N6" s="34" t="inlineStr">
         <is>
           <t>Darling shop,
-Wedding season is upon us. My brides want the small white flowers from the citrus tree woven into their hair, as their grandmothers wore them: they say a bride crowned with them glows with joy. The tall still white flower goes in the bouquet. Nothing gives a quiet bride beauty like it.
+Wedding season is upon us. My brides want the small white flowers of the citrus tree, dried and ground to a powder for their shoulders, so they shine in every photograph. Their grandmothers said a bride wearing it glows with joy.
+And for the bride who wants to walk down the aisle like a swan, a soap of the tall, still white flower. Nothing gives a quiet bride beauty like it.
 Send whatever you can. Kingsmere does not do things by halves.
 Lavinia, Lavinia's Bridal Rooms, Kingsmere</t>
         </is>
@@ -74468,7 +74469,7 @@
       <c r="N7" s="34" t="inlineStr">
         <is>
           <t>To the Emporium,
-Every coastguard on this stretch keeps a black, ridged stone in his coat, the kind that looks like a bundle of burnt matches. The old men say it soaks up whatever is thrown at you. It is the only protection I trust on a night shift.
+Everyone on this stretch of coast who works nights wears a black, ridged stone on a cord, the kind that looks like a bundle of burnt matches. The lighthouse keeper has worn one for thirty years. They say it soaks up whatever is thrown at you, seen or unseen. It is the only protection I trust out there.
 Mine went over the side in the last storm. Could you send another?
 Officer Jory Penrose, Caldwell-on-Sea</t>
         </is>
@@ -74539,7 +74540,8 @@
       <c r="N8" s="34" t="inlineStr">
         <is>
           <t>To the Emporium,
-The vicar has asked me, against my better judgement, to write. He wants the pale sweet resin from overseas for the censer. When it burns, he says, the whole parish sits together in calm, even the Hendersons. He also grinds the little hot black corns over his breakfast eggs before every sermon, for the courage to face us.
+The vicar has asked me, against my better judgement, to write. He wants the pale sweet resin from overseas. One of our widowers burns a pinch of it every evening at the same hour, and says the house fills with calm, as it did when his wife was alive.
+The vicar himself grinds the little hot black corns over his eggs. He started the week he took up painting, at sixty-one, and says it gave him the courage to make the first stroke.
 Our grocer has run out of both. I trust this stays between us.
 Mr Edgar Penhallow, Churchwarden, Thornbury</t>
         </is>
@@ -74594,8 +74596,8 @@
       <c r="N9" s="34" t="inlineStr">
         <is>
           <t>Hello from the Hollow,
-When the plum trees come back after a bad winter, my aunt used to hang a little pale green stone on a ribbon from the oldest branch. She said it was for the first good week after a hard season, and for growth. The trees never failed her.
-The ribbon snapped and the stone is lost in the long grass. Do you sell them?
+When the first green shoots show after a hard winter, my aunt used to sew a little pale green stone into a cloth bag and hang it from the oldest plum tree. She said it was for the first good week of spring, and for growth. The trees never failed her.
+The bag rotted and the stone is lost in the long grass. Do you sell them?
 Bessie Damson, Plumtree Hollow</t>
         </is>
       </c>
@@ -74665,7 +74667,8 @@
       <c r="N10" s="34" t="inlineStr">
         <is>
           <t>Dear neighbour,
-Two things for the winter menu. The little shrivelled dark fruit we fold into lunch-box buns. The mothers say one bun is pure joy for a child at school. And the dark bitter powder for the mugs we serve when people come in from the cold. Nothing else is such a comfort in January.
+Two things for the winter menu. The little shrivelled dark fruit we bake into the biscuits we give children who finish their reading charts. Such a small win, but the mothers say it is pure joy to them.
+And the dark bitter powder, whipped into the spread for our Saturday buns. Ladies come in saying they really shouldn't, and then they do. Nothing is such a comfort in January.
 Our supplier in Greywater has gone bust. Could you help?
 Mrs Ada Crumb, Crumb &amp; Co., Whitcombe</t>
         </is>
@@ -74736,7 +74739,8 @@
       <c r="N11" s="34" t="inlineStr">
         <is>
           <t>Madam,
-Two old remedies my grandfather kept, which no one else seems to stock. The bark of the weeping tree by the river, which every grandmother uses for a sore back; few know that the old witches chewed it for intuition. And the bitter silver-grey herb he steeped in his spirits once a year, for transformation. He said it was not for the faint-hearted.
+Two old remedies my grandfather kept. The bark of the weeping tree by the river, which every grandmother uses for a sore back. Few know the old witches sewed strips of it into their pillows for intuition, and woke with the strangest pictures still in their heads.
+And the bitter silver-grey herb he steeped in a drink every New Year's Eve, to close one chapter and start the next. For transformation, he said, and not for the faint-hearted.
 If you have either, we would pay well.
 Silas Thistle, Thistle &amp; Sons Wandwrights, Elderhollow</t>
         </is>
@@ -74791,8 +74795,8 @@
       <c r="N12" s="34" t="inlineStr">
         <is>
           <t>To the Emporium,
-Travellers wait here for the coach, and the waiting turns to gambling by supper. One old carter swears by a little carved wooden cube with dots on its faces that he blessed at your shop years ago. He says it gives him luck every time he throws it.
-The other regulars now want one each. Do you still bless them?
+Travellers wait here for the coach, and the young ones fill the back room with their long games of dragons and dungeons. One old carter swears by a little carved wooden cube with dots on its faces that he had blessed at your shop. He says it gives him luck every time he throws it.
+The young ones now want one each, for their games night. Do you still bless them?
 Harry Oakes, landlord, the Crossed Keys, Ashby Cross</t>
         </is>
       </c>
@@ -74846,7 +74850,7 @@
       <c r="N13" s="34" t="inlineStr">
         <is>
           <t>Dear Emporium,
-Our guests come up the mountain to sit and look at the stars, and most of them can't sit still for a minute. Our founder floated the great pale water flower in a bowl at the centre of the room. She said the inner sight it brings is only half its use; mostly it brings calm.
+Our guests come up the mountain to wait for shooting stars, and most of them can't wait for anything. Our founder tucked dried petals of the great pale water flower into a little bag under each pillow. She said the inner sight it brings is only half its use; mostly it teaches calm, and the stars come when they come.
 Have you any dried blooms?
 Sister Wren, the Starfall Retreat</t>
         </is>
@@ -74901,8 +74905,8 @@
       <c r="N14" s="34" t="inlineStr">
         <is>
           <t>Hello,
-My mother used to grow a hedge of the old pink climbing flowers along our lane, and she kept a jar of the sharp bits she clipped off the stems. One on the windowsill, she said, and people learn your boundaries without you saying a word.
-My sister-in-law visits every Sunday. Have you a jar?
+My daughter can't let go of a lad who is no good for her. My mother would have braided the sharp bits clipped from her pink climbing flowers into a knotted cord and hung it by the girl's bed. She said it teaches a soft heart its boundaries.
+I have the cord but not the thorns. Have you a jar?
 Dora Bramble, Hedge End Farm, Bramblebee</t>
         </is>
       </c>
@@ -74972,7 +74976,8 @@
       <c r="N15" s="34" t="inlineStr">
         <is>
           <t>Dear shop,
-The girls who come in after school have been told to tone it down, and it shows. I used to dust their cake pops with the shiny pink stuff, and they'd walk out with some self-love again. And the boys buy cupcakes with the little pink sugar strands on top to hand to a sweetheart. My grandmother called those love on a cake.
+There's a girl who comes in after school who can't stop going over one silly mistake she made. Her gran used to stir the shiny pink stuff into her bath salts and say it washed in a bit of self-love.
+And the boys buy cupcakes with the little pink sugar strands on top to hand to someone they fancy, giggling all the way out. My grandmother called those love on a cake.
 I'm out of both. I'll send fudge.
 Mrs Pennywhistle, Sugarbrook</t>
         </is>
@@ -75027,7 +75032,7 @@
       <c r="N16" s="34" t="inlineStr">
         <is>
           <t>Dear Emporium,
-Our orchard bees leave little golden grains on everything in May, and the old orchard keepers sprinkled them over the fair loaves. They said whoever shares that bread shares the friendship of the hive.
+Our orchard bees leave little golden grains on everything in May. The old orchard keepers beat them into butter for the fair loaves, and said whoever shares that bread with old friends shares the friendship of the hive.
 Our hives had a bad year. Could you send a jar for the fair?
 Rhoda Bell, Cider Fair Committee, Pippin Green</t>
         </is>
@@ -75082,7 +75087,7 @@
       <c r="N17" s="34" t="inlineStr">
         <is>
           <t>Dear neighbour,
-A house clearance turned up a box of buttons, and among them one odd square one that must be a lost counter from some old board game. I left it on the counter and the grandchildren wanted to play all afternoon.
+A house clearance turned up a box of buttons, and among them one odd square one that must be a lost counter from some old board game. I left it on the counter, and the grandchildren wanted to play all afternoon. The little one swears he won every game while it sat by the board.
 I'll hold it for you. Come by.
 Mr Ambrose Tuck, Old Things, Buttonwick</t>
         </is>
@@ -75137,8 +75142,8 @@
       <c r="N18" s="34" t="inlineStr">
         <is>
           <t>To the Emporium,
-My father scattered sweet red wood shavings in the flour bins and the drawers of the mill house, until the whole place smelled like home. Since he passed, it smells of damp.
-Could you send a bag?
+My mum and dad were married fifty-two years. Dad kept a corked bottle of sweet red wood shavings on the mantel, and scattered more in the drawers, until the whole mill house smelled like home. He said it kept them fond of each other through every winter.
+My wife and I could use some. Could you send a bag?
 Sam Wend, Wend Mill, Greywater</t>
         </is>
       </c>

--- a/ingredient_asset_tracker.xlsx
+++ b/ingredient_asset_tracker.xlsx
@@ -166,7 +166,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -268,6 +268,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -41005,7 +41006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G259"/>
+  <dimension ref="A1:H259"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="28" customWidth="1" style="17" min="1" max="1"/>
@@ -41015,6 +41016,7 @@
     <col width="34" customWidth="1" style="17" min="5" max="5"/>
     <col width="12" customWidth="1" style="17" min="6" max="6"/>
     <col width="30" customWidth="1" style="17" min="7" max="7"/>
+    <col width="34" customWidth="1" style="18" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1" s="18">
@@ -41053,6 +41055,11 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="H1" s="35" t="inlineStr">
+        <is>
+          <t>Look (art brief)</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="18">
       <c r="A2" s="27" t="inlineStr">
@@ -41085,6 +41092,11 @@
         </is>
       </c>
       <c r="G2" s="27" t="n"/>
+      <c r="H2" s="34" t="inlineStr">
+        <is>
+          <t>clear, with a silvery sheen</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="18">
       <c r="A3" s="27" t="inlineStr">
@@ -41117,6 +41129,11 @@
         </is>
       </c>
       <c r="G3" s="27" t="n"/>
+      <c r="H3" s="34" t="inlineStr">
+        <is>
+          <t>clear, with a golden glint</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="18">
       <c r="A4" s="27" t="inlineStr">
@@ -41149,6 +41166,11 @@
         </is>
       </c>
       <c r="G4" s="27" t="n"/>
+      <c r="H4" s="34" t="inlineStr">
+        <is>
+          <t>clear and plain</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="18">
       <c r="A5" s="27" t="inlineStr">
@@ -41181,6 +41203,11 @@
         </is>
       </c>
       <c r="G5" s="27" t="n"/>
+      <c r="H5" s="34" t="inlineStr">
+        <is>
+          <t>a few clear drops, cool to the touch</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="18">
       <c r="A6" s="27" t="inlineStr">
@@ -41213,6 +41240,11 @@
         </is>
       </c>
       <c r="G6" s="27" t="n"/>
+      <c r="H6" s="34" t="inlineStr">
+        <is>
+          <t>cloudy and salty</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="18">
       <c r="A7" s="27" t="inlineStr">
@@ -41245,6 +41277,11 @@
         </is>
       </c>
       <c r="G7" s="27" t="n"/>
+      <c r="H7" s="34" t="inlineStr">
+        <is>
+          <t>clear and plain</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="18">
       <c r="A8" s="27" t="inlineStr">
@@ -41277,6 +41314,11 @@
         </is>
       </c>
       <c r="G8" s="27" t="n"/>
+      <c r="H8" s="34" t="inlineStr">
+        <is>
+          <t>clear, with a pink blush</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="18">
       <c r="A9" s="27" t="inlineStr">
@@ -41309,6 +41351,11 @@
         </is>
       </c>
       <c r="G9" s="27" t="n"/>
+      <c r="H9" s="34" t="inlineStr">
+        <is>
+          <t>clear, and darker than it should be</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="18">
       <c r="A10" s="27" t="inlineStr">
@@ -41341,6 +41388,11 @@
         </is>
       </c>
       <c r="G10" s="27" t="n"/>
+      <c r="H10" s="34" t="inlineStr">
+        <is>
+          <t>tiny bright beads on a thread</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="18">
       <c r="A11" s="27" t="inlineStr">
@@ -41373,6 +41425,11 @@
         </is>
       </c>
       <c r="G11" s="27" t="n"/>
+      <c r="H11" s="34" t="inlineStr">
+        <is>
+          <t>clear and icy</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="18">
       <c r="A12" s="27" t="inlineStr">
@@ -41405,6 +41462,11 @@
         </is>
       </c>
       <c r="G12" s="27" t="n"/>
+      <c r="H12" s="34" t="inlineStr">
+        <is>
+          <t>grey and restless</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="18">
       <c r="A13" s="27" t="inlineStr">
@@ -41437,6 +41499,11 @@
         </is>
       </c>
       <c r="G13" s="27" t="n"/>
+      <c r="H13" s="34" t="inlineStr">
+        <is>
+          <t>pale and golden</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="18">
       <c r="A14" s="27" t="inlineStr">
@@ -41469,6 +41536,11 @@
         </is>
       </c>
       <c r="G14" s="27" t="n"/>
+      <c r="H14" s="34" t="inlineStr">
+        <is>
+          <t>clear and golden</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="18">
       <c r="A15" s="27" t="inlineStr">
@@ -41501,6 +41573,11 @@
         </is>
       </c>
       <c r="G15" s="27" t="n"/>
+      <c r="H15" s="34" t="inlineStr">
+        <is>
+          <t>green-gold</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="18">
       <c r="A16" s="27" t="inlineStr">
@@ -41533,6 +41610,11 @@
         </is>
       </c>
       <c r="G16" s="27" t="n"/>
+      <c r="H16" s="34" t="inlineStr">
+        <is>
+          <t>pale yellow</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="18">
       <c r="A17" s="27" t="inlineStr">
@@ -41565,6 +41647,11 @@
         </is>
       </c>
       <c r="G17" s="27" t="n"/>
+      <c r="H17" s="34" t="inlineStr">
+        <is>
+          <t>creamy white and soft</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="18">
       <c r="A18" s="27" t="inlineStr">
@@ -41597,6 +41684,11 @@
         </is>
       </c>
       <c r="G18" s="27" t="n"/>
+      <c r="H18" s="34" t="inlineStr">
+        <is>
+          <t>golden yellow and waxy</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="18">
       <c r="A19" s="27" t="inlineStr">
@@ -41629,6 +41721,11 @@
         </is>
       </c>
       <c r="G19" s="27" t="n"/>
+      <c r="H19" s="34" t="inlineStr">
+        <is>
+          <t>pale yellow and soft</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="18">
       <c r="A20" s="27" t="inlineStr">
@@ -41661,6 +41758,11 @@
         </is>
       </c>
       <c r="G20" s="27" t="n"/>
+      <c r="H20" s="34" t="inlineStr">
+        <is>
+          <t>a pale, knobbly root</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="18">
       <c r="A21" s="27" t="inlineStr">
@@ -41693,6 +41795,11 @@
         </is>
       </c>
       <c r="G21" s="27" t="n"/>
+      <c r="H21" s="34" t="inlineStr">
+        <is>
+          <t>bright green leaves, sweet-smelling</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="18">
       <c r="A22" s="27" t="inlineStr">
@@ -41725,6 +41832,11 @@
         </is>
       </c>
       <c r="G22" s="27" t="n"/>
+      <c r="H22" s="34" t="inlineStr">
+        <is>
+          <t>a stiff, glossy green leaf</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="18">
       <c r="A23" s="27" t="inlineStr">
@@ -41757,6 +41869,11 @@
         </is>
       </c>
       <c r="G23" s="27" t="n"/>
+      <c r="H23" s="34" t="inlineStr">
+        <is>
+          <t>bright orange petals</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="18">
       <c r="A24" s="27" t="inlineStr">
@@ -41789,6 +41906,11 @@
         </is>
       </c>
       <c r="G24" s="27" t="n"/>
+      <c r="H24" s="34" t="inlineStr">
+        <is>
+          <t>small, white and yellow-eyed</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="18">
       <c r="A25" s="27" t="inlineStr">
@@ -41821,6 +41943,11 @@
         </is>
       </c>
       <c r="G25" s="27" t="n"/>
+      <c r="H25" s="34" t="inlineStr">
+        <is>
+          <t>green leaves in threes</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="18">
       <c r="A26" s="27" t="inlineStr">
@@ -41853,6 +41980,11 @@
         </is>
       </c>
       <c r="G26" s="27" t="n"/>
+      <c r="H26" s="34" t="inlineStr">
+        <is>
+          <t>a large, fuzzy green leaf</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="18">
       <c r="A27" s="27" t="inlineStr">
@@ -41885,6 +42017,11 @@
         </is>
       </c>
       <c r="G27" s="27" t="n"/>
+      <c r="H27" s="34" t="inlineStr">
+        <is>
+          <t>bright blue and frilly</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="18">
       <c r="A28" s="27" t="inlineStr">
@@ -41917,6 +42054,11 @@
         </is>
       </c>
       <c r="G28" s="27" t="n"/>
+      <c r="H28" s="34" t="inlineStr">
+        <is>
+          <t>small, white and yellow-eyed</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="18">
       <c r="A29" s="27" t="inlineStr">
@@ -41949,6 +42091,11 @@
         </is>
       </c>
       <c r="G29" s="27" t="n"/>
+      <c r="H29" s="34" t="inlineStr">
+        <is>
+          <t>yellow and fluffy</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="18">
       <c r="A30" s="27" t="inlineStr">
@@ -41981,6 +42128,11 @@
         </is>
       </c>
       <c r="G30" s="27" t="n"/>
+      <c r="H30" s="34" t="inlineStr">
+        <is>
+          <t>a long, brown, bitter root</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="18">
       <c r="A31" s="27" t="inlineStr">
@@ -42013,6 +42165,11 @@
         </is>
       </c>
       <c r="G31" s="27" t="n"/>
+      <c r="H31" s="34" t="inlineStr">
+        <is>
+          <t>a cloud of tiny cream flowers</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="18">
       <c r="A32" s="27" t="inlineStr">
@@ -42045,6 +42202,11 @@
         </is>
       </c>
       <c r="G32" s="27" t="n"/>
+      <c r="H32" s="34" t="inlineStr">
+        <is>
+          <t>grey-green, round leaves</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="18">
       <c r="A33" s="27" t="inlineStr">
@@ -42077,6 +42239,11 @@
         </is>
       </c>
       <c r="G33" s="27" t="n"/>
+      <c r="H33" s="34" t="inlineStr">
+        <is>
+          <t>feathery green fronds</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="18">
       <c r="A34" s="27" t="inlineStr">
@@ -42109,6 +42276,11 @@
         </is>
       </c>
       <c r="G34" s="27" t="n"/>
+      <c r="H34" s="34" t="inlineStr">
+        <is>
+          <t>green leaves in fours</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="18">
       <c r="A35" s="27" t="inlineStr">
@@ -42141,6 +42313,11 @@
         </is>
       </c>
       <c r="G35" s="27" t="n"/>
+      <c r="H35" s="34" t="inlineStr">
+        <is>
+          <t>soft, grey-green leaves</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="18">
       <c r="A36" s="27" t="inlineStr">
@@ -42173,6 +42350,11 @@
         </is>
       </c>
       <c r="G36" s="27" t="n"/>
+      <c r="H36" s="34" t="inlineStr">
+        <is>
+          <t>deep red petals</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="18">
       <c r="A37" s="27" t="inlineStr">
@@ -42205,6 +42387,11 @@
         </is>
       </c>
       <c r="G37" s="27" t="n"/>
+      <c r="H37" s="34" t="inlineStr">
+        <is>
+          <t>pale green cones</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="18">
       <c r="A38" s="27" t="inlineStr">
@@ -42237,6 +42424,11 @@
         </is>
       </c>
       <c r="G38" s="27" t="n"/>
+      <c r="H38" s="34" t="inlineStr">
+        <is>
+          <t>small, white and starry</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="18">
       <c r="A39" s="27" t="inlineStr">
@@ -42269,6 +42461,11 @@
         </is>
       </c>
       <c r="G39" s="27" t="n"/>
+      <c r="H39" s="34" t="inlineStr">
+        <is>
+          <t>purple and spiky</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="18">
       <c r="A40" s="27" t="inlineStr">
@@ -42301,6 +42498,11 @@
         </is>
       </c>
       <c r="G40" s="27" t="n"/>
+      <c r="H40" s="34" t="inlineStr">
+        <is>
+          <t>soft green leaves that smell of lemon</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="18">
       <c r="A41" s="27" t="inlineStr">
@@ -42333,6 +42535,11 @@
         </is>
       </c>
       <c r="G41" s="27" t="n"/>
+      <c r="H41" s="34" t="inlineStr">
+        <is>
+          <t>tall, pale green stalks</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="18">
       <c r="A42" s="27" t="inlineStr">
@@ -42365,6 +42572,11 @@
         </is>
       </c>
       <c r="G42" s="27" t="n"/>
+      <c r="H42" s="34" t="inlineStr">
+        <is>
+          <t>dark, woody sticks</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="18">
       <c r="A43" s="27" t="inlineStr">
@@ -42397,6 +42609,11 @@
         </is>
       </c>
       <c r="G43" s="27" t="n"/>
+      <c r="H43" s="34" t="inlineStr">
+        <is>
+          <t>small purple flowers in clusters</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="18">
       <c r="A44" s="27" t="inlineStr">
@@ -42429,6 +42646,11 @@
         </is>
       </c>
       <c r="G44" s="27" t="n"/>
+      <c r="H44" s="34" t="inlineStr">
+        <is>
+          <t>large, pale and many-petalled</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="18">
       <c r="A45" s="27" t="inlineStr">
@@ -42461,6 +42683,11 @@
         </is>
       </c>
       <c r="G45" s="27" t="n"/>
+      <c r="H45" s="34" t="inlineStr">
+        <is>
+          <t>bright green leaves</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="18">
       <c r="A46" s="27" t="inlineStr">
@@ -42493,6 +42720,11 @@
         </is>
       </c>
       <c r="G46" s="27" t="n"/>
+      <c r="H46" s="34" t="inlineStr">
+        <is>
+          <t>silvery-green leaves</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="18">
       <c r="A47" s="27" t="inlineStr">
@@ -42525,6 +42757,11 @@
         </is>
       </c>
       <c r="G47" s="27" t="n"/>
+      <c r="H47" s="34" t="inlineStr">
+        <is>
+          <t>green, jagged and a little hairy</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="18">
       <c r="A48" s="27" t="inlineStr">
@@ -42557,6 +42794,11 @@
         </is>
       </c>
       <c r="G48" s="27" t="n"/>
+      <c r="H48" s="34" t="inlineStr">
+        <is>
+          <t>grey-green and crinkled</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="18">
       <c r="A49" s="27" t="inlineStr">
@@ -42589,6 +42831,11 @@
         </is>
       </c>
       <c r="G49" s="27" t="n"/>
+      <c r="H49" s="34" t="inlineStr">
+        <is>
+          <t>small, white and waxy</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="18">
       <c r="A50" s="27" t="inlineStr">
@@ -42621,6 +42868,11 @@
         </is>
       </c>
       <c r="G50" s="27" t="n"/>
+      <c r="H50" s="34" t="inlineStr">
+        <is>
+          <t>a pale, powdery root</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="18">
       <c r="A51" s="27" t="inlineStr">
@@ -42653,6 +42905,11 @@
         </is>
       </c>
       <c r="G51" s="27" t="n"/>
+      <c r="H51" s="34" t="inlineStr">
+        <is>
+          <t>bright green leaves</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="18">
       <c r="A52" s="27" t="inlineStr">
@@ -42685,6 +42942,11 @@
         </is>
       </c>
       <c r="G52" s="27" t="n"/>
+      <c r="H52" s="34" t="inlineStr">
+        <is>
+          <t>a full red flower</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="15" customHeight="1" s="18">
       <c r="A53" s="27" t="inlineStr">
@@ -42717,6 +42979,11 @@
         </is>
       </c>
       <c r="G53" s="27" t="n"/>
+      <c r="H53" s="34" t="inlineStr">
+        <is>
+          <t>soft pink petals</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="18">
       <c r="A54" s="27" t="inlineStr">
@@ -42749,6 +43016,11 @@
         </is>
       </c>
       <c r="G54" s="27" t="n"/>
+      <c r="H54" s="34" t="inlineStr">
+        <is>
+          <t>a small, tight pink bud</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="18">
       <c r="A55" s="27" t="inlineStr">
@@ -42781,6 +43053,11 @@
         </is>
       </c>
       <c r="G55" s="27" t="n"/>
+      <c r="H55" s="34" t="inlineStr">
+        <is>
+          <t>small, sharp and curved</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="18">
       <c r="A56" s="27" t="inlineStr">
@@ -42813,6 +43090,11 @@
         </is>
       </c>
       <c r="G56" s="27" t="n"/>
+      <c r="H56" s="34" t="inlineStr">
+        <is>
+          <t>green needles on a woody stem</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="18">
       <c r="A57" s="27" t="inlineStr">
@@ -42845,6 +43127,11 @@
         </is>
       </c>
       <c r="G57" s="27" t="n"/>
+      <c r="H57" s="34" t="inlineStr">
+        <is>
+          <t>blue-green, lobed leaves</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="18">
       <c r="A58" s="27" t="inlineStr">
@@ -42877,6 +43164,11 @@
         </is>
       </c>
       <c r="G58" s="27" t="n"/>
+      <c r="H58" s="34" t="inlineStr">
+        <is>
+          <t>small, white and drooping</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="18">
       <c r="A59" s="27" t="inlineStr">
@@ -42909,6 +43201,11 @@
         </is>
       </c>
       <c r="G59" s="27" t="n"/>
+      <c r="H59" s="34" t="inlineStr">
+        <is>
+          <t>long yellow petals</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="15" customHeight="1" s="18">
       <c r="A60" s="27" t="inlineStr">
@@ -42941,6 +43238,11 @@
         </is>
       </c>
       <c r="G60" s="27" t="n"/>
+      <c r="H60" s="34" t="inlineStr">
+        <is>
+          <t>ruffled and pastel</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="18">
       <c r="A61" s="27" t="inlineStr">
@@ -42973,6 +43275,11 @@
         </is>
       </c>
       <c r="G61" s="27" t="n"/>
+      <c r="H61" s="34" t="inlineStr">
+        <is>
+          <t>tiny leaves on thin stems</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="18">
       <c r="A62" s="27" t="inlineStr">
@@ -43005,6 +43312,11 @@
         </is>
       </c>
       <c r="G62" s="27" t="n"/>
+      <c r="H62" s="34" t="inlineStr">
+        <is>
+          <t>small pink-white clusters</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="18">
       <c r="A63" s="27" t="inlineStr">
@@ -43037,6 +43349,11 @@
         </is>
       </c>
       <c r="G63" s="27" t="n"/>
+      <c r="H63" s="34" t="inlineStr">
+        <is>
+          <t>small and purple</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="18">
       <c r="A64" s="27" t="inlineStr">
@@ -43069,6 +43386,11 @@
         </is>
       </c>
       <c r="G64" s="27" t="n"/>
+      <c r="H64" s="34" t="inlineStr">
+        <is>
+          <t>tall, white and trumpet-shaped</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="15" customHeight="1" s="18">
       <c r="A65" s="27" t="inlineStr">
@@ -43101,6 +43423,11 @@
         </is>
       </c>
       <c r="G65" s="27" t="n"/>
+      <c r="H65" s="34" t="inlineStr">
+        <is>
+          <t>silver-grey and feathery</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="15" customHeight="1" s="18">
       <c r="A66" s="27" t="inlineStr">
@@ -43133,6 +43460,11 @@
         </is>
       </c>
       <c r="G66" s="27" t="n"/>
+      <c r="H66" s="34" t="inlineStr">
+        <is>
+          <t>golden stalks with full ears</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="15" customHeight="1" s="18">
       <c r="A67" s="27" t="inlineStr">
@@ -43165,6 +43497,11 @@
         </is>
       </c>
       <c r="G67" s="27" t="n"/>
+      <c r="H67" s="34" t="inlineStr">
+        <is>
+          <t>dark green and slippery</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="15" customHeight="1" s="18">
       <c r="A68" s="27" t="inlineStr">
@@ -43197,6 +43534,11 @@
         </is>
       </c>
       <c r="G68" s="27" t="n"/>
+      <c r="H68" s="34" t="inlineStr">
+        <is>
+          <t>flat, pale and papery</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="18">
       <c r="A69" s="27" t="inlineStr">
@@ -43229,6 +43571,11 @@
         </is>
       </c>
       <c r="G69" s="27" t="n"/>
+      <c r="H69" s="34" t="inlineStr">
+        <is>
+          <t>dark, curled leaves</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="18">
       <c r="A70" s="27" t="inlineStr">
@@ -43261,6 +43608,11 @@
         </is>
       </c>
       <c r="G70" s="27" t="n"/>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>reddish wood and flat green sprigs</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="18">
       <c r="A71" s="27" t="inlineStr">
@@ -43293,6 +43645,11 @@
         </is>
       </c>
       <c r="G71" s="27" t="n"/>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>reddish wood shavings</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="15" customHeight="1" s="18">
       <c r="A72" s="27" t="inlineStr">
@@ -43325,6 +43682,11 @@
         </is>
       </c>
       <c r="G72" s="27" t="n"/>
+      <c r="H72" s="34" t="inlineStr">
+        <is>
+          <t>dark green sprigs</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="18">
       <c r="A73" s="27" t="inlineStr">
@@ -43357,6 +43719,11 @@
         </is>
       </c>
       <c r="G73" s="27" t="n"/>
+      <c r="H73" s="34" t="inlineStr">
+        <is>
+          <t>blue berries on prickly sprigs</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="15" customHeight="1" s="18">
       <c r="A74" s="27" t="inlineStr">
@@ -43389,6 +43756,11 @@
         </is>
       </c>
       <c r="G74" s="27" t="n"/>
+      <c r="H74" s="34" t="inlineStr">
+        <is>
+          <t>green needles</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="15" customHeight="1" s="18">
       <c r="A75" s="27" t="inlineStr">
@@ -43421,6 +43793,11 @@
         </is>
       </c>
       <c r="G75" s="27" t="n"/>
+      <c r="H75" s="34" t="inlineStr">
+        <is>
+          <t>rough brown strips of bark</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="15" customHeight="1" s="18">
       <c r="A76" s="27" t="inlineStr">
@@ -43453,6 +43830,11 @@
         </is>
       </c>
       <c r="G76" s="27" t="n"/>
+      <c r="H76" s="34" t="inlineStr">
+        <is>
+          <t>a curled orange leaf</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="15" customHeight="1" s="18">
       <c r="A77" s="27" t="inlineStr">
@@ -43485,6 +43867,11 @@
         </is>
       </c>
       <c r="G77" s="27" t="n"/>
+      <c r="H77" s="34" t="inlineStr">
+        <is>
+          <t>round, red and shiny</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="18">
       <c r="A78" s="27" t="inlineStr">
@@ -43517,6 +43904,11 @@
         </is>
       </c>
       <c r="G78" s="27" t="n"/>
+      <c r="H78" s="34" t="inlineStr">
+        <is>
+          <t>a long red curl</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="18">
       <c r="A79" s="27" t="inlineStr">
@@ -43549,6 +43941,11 @@
         </is>
       </c>
       <c r="G79" s="27" t="n"/>
+      <c r="H79" s="34" t="inlineStr">
+        <is>
+          <t>small, red and on a stalk</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="18">
       <c r="A80" s="27" t="inlineStr">
@@ -43581,6 +43978,11 @@
         </is>
       </c>
       <c r="G80" s="27" t="n"/>
+      <c r="H80" s="34" t="inlineStr">
+        <is>
+          <t>small and round, in a bunch</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="18">
       <c r="A81" s="27" t="inlineStr">
@@ -43613,6 +44015,11 @@
         </is>
       </c>
       <c r="G81" s="27" t="n"/>
+      <c r="H81" s="34" t="inlineStr">
+        <is>
+          <t>bright yellow and sour-smelling</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="18">
       <c r="A82" s="27" t="inlineStr">
@@ -43645,6 +44052,11 @@
         </is>
       </c>
       <c r="G82" s="27" t="n"/>
+      <c r="H82" s="34" t="inlineStr">
+        <is>
+          <t>bright yellow zest</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="18">
       <c r="A83" s="27" t="inlineStr">
@@ -43677,6 +44089,11 @@
         </is>
       </c>
       <c r="G83" s="27" t="n"/>
+      <c r="H83" s="34" t="inlineStr">
+        <is>
+          <t>bright green zest</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="15" customHeight="1" s="18">
       <c r="A84" s="27" t="inlineStr">
@@ -43709,6 +44126,11 @@
         </is>
       </c>
       <c r="G84" s="27" t="n"/>
+      <c r="H84" s="34" t="inlineStr">
+        <is>
+          <t>round and orange</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="18">
       <c r="A85" s="27" t="inlineStr">
@@ -43741,6 +44163,11 @@
         </is>
       </c>
       <c r="G85" s="27" t="n"/>
+      <c r="H85" s="34" t="inlineStr">
+        <is>
+          <t>orange zest</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="18">
       <c r="A86" s="27" t="inlineStr">
@@ -43773,6 +44200,11 @@
         </is>
       </c>
       <c r="G86" s="27" t="n"/>
+      <c r="H86" s="34" t="inlineStr">
+        <is>
+          <t>soft, fuzzy and blushing</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="18">
       <c r="A87" s="27" t="inlineStr">
@@ -43805,6 +44237,11 @@
         </is>
       </c>
       <c r="G87" s="27" t="n"/>
+      <c r="H87" s="34" t="inlineStr">
+        <is>
+          <t>jewel-red seeds</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="18">
       <c r="A88" s="27" t="inlineStr">
@@ -43837,6 +44274,11 @@
         </is>
       </c>
       <c r="G88" s="27" t="n"/>
+      <c r="H88" s="34" t="inlineStr">
+        <is>
+          <t>small, oval and red</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="18">
       <c r="A89" s="27" t="inlineStr">
@@ -43869,6 +44311,11 @@
         </is>
       </c>
       <c r="G89" s="27" t="n"/>
+      <c r="H89" s="34" t="inlineStr">
+        <is>
+          <t>small, red and seedy</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="18">
       <c r="A90" s="27" t="inlineStr">
@@ -43901,6 +44348,11 @@
         </is>
       </c>
       <c r="G90" s="27" t="n"/>
+      <c r="H90" s="34" t="inlineStr">
+        <is>
+          <t>small, dark and shrivelled</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="18">
       <c r="A91" s="27" t="inlineStr">
@@ -43933,6 +44385,11 @@
         </is>
       </c>
       <c r="G91" s="27" t="n"/>
+      <c r="H91" s="34" t="inlineStr">
+        <is>
+          <t>deep magenta powder</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="15" customHeight="1" s="18">
       <c r="A92" s="27" t="inlineStr">
@@ -43965,6 +44422,11 @@
         </is>
       </c>
       <c r="G92" s="27" t="n"/>
+      <c r="H92" s="34" t="inlineStr">
+        <is>
+          <t>round brown berries</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="18">
       <c r="A93" s="27" t="inlineStr">
@@ -43997,6 +44459,11 @@
         </is>
       </c>
       <c r="G93" s="27" t="n"/>
+      <c r="H93" s="34" t="inlineStr">
+        <is>
+          <t>green-yellow citrus rind</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="18">
       <c r="A94" s="27" t="inlineStr">
@@ -44029,6 +44496,11 @@
         </is>
       </c>
       <c r="G94" s="27" t="n"/>
+      <c r="H94" s="34" t="inlineStr">
+        <is>
+          <t>small, hard black corns</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="18">
       <c r="A95" s="27" t="inlineStr">
@@ -44061,6 +44533,11 @@
         </is>
       </c>
       <c r="G95" s="27" t="n"/>
+      <c r="H95" s="34" t="inlineStr">
+        <is>
+          <t>small green pods</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="18">
       <c r="A96" s="27" t="inlineStr">
@@ -44093,6 +44570,11 @@
         </is>
       </c>
       <c r="G96" s="27" t="n"/>
+      <c r="H96" s="34" t="inlineStr">
+        <is>
+          <t>long, red and shiny</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="15" customHeight="1" s="18">
       <c r="A97" s="27" t="inlineStr">
@@ -44125,6 +44607,11 @@
         </is>
       </c>
       <c r="G97" s="27" t="n"/>
+      <c r="H97" s="34" t="inlineStr">
+        <is>
+          <t>warm brown powder</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="15" customHeight="1" s="18">
       <c r="A98" s="27" t="inlineStr">
@@ -44157,6 +44644,11 @@
         </is>
       </c>
       <c r="G98" s="27" t="n"/>
+      <c r="H98" s="34" t="inlineStr">
+        <is>
+          <t>a rolled brown curl of bark</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="18">
       <c r="A99" s="27" t="inlineStr">
@@ -44189,6 +44681,11 @@
         </is>
       </c>
       <c r="G99" s="27" t="n"/>
+      <c r="H99" s="34" t="inlineStr">
+        <is>
+          <t>small, dark and nail-shaped</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="18">
       <c r="A100" s="27" t="inlineStr">
@@ -44221,6 +44718,11 @@
         </is>
       </c>
       <c r="G100" s="27" t="n"/>
+      <c r="H100" s="34" t="inlineStr">
+        <is>
+          <t>small, pale green seeds</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="15" customHeight="1" s="18">
       <c r="A101" s="27" t="inlineStr">
@@ -44253,6 +44755,11 @@
         </is>
       </c>
       <c r="G101" s="27" t="n"/>
+      <c r="H101" s="34" t="inlineStr">
+        <is>
+          <t>a knobbly, pale brown root</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="15" customHeight="1" s="18">
       <c r="A102" s="27" t="inlineStr">
@@ -44285,6 +44792,11 @@
         </is>
       </c>
       <c r="G102" s="27" t="n"/>
+      <c r="H102" s="34" t="inlineStr">
+        <is>
+          <t>hard, brown and round</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="15" customHeight="1" s="18">
       <c r="A103" s="27" t="inlineStr">
@@ -44317,6 +44829,11 @@
         </is>
       </c>
       <c r="G103" s="27" t="n"/>
+      <c r="H103" s="34" t="inlineStr">
+        <is>
+          <t>tiny blue-black seeds</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="15" customHeight="1" s="18">
       <c r="A104" s="27" t="inlineStr">
@@ -44349,6 +44866,11 @@
         </is>
       </c>
       <c r="G104" s="27" t="n"/>
+      <c r="H104" s="34" t="inlineStr">
+        <is>
+          <t>thin red threads</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="15" customHeight="1" s="18">
       <c r="A105" s="27" t="inlineStr">
@@ -44381,6 +44903,11 @@
         </is>
       </c>
       <c r="G105" s="27" t="n"/>
+      <c r="H105" s="34" t="inlineStr">
+        <is>
+          <t>brown and star-shaped</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="18">
       <c r="A106" s="27" t="inlineStr">
@@ -44413,6 +44940,11 @@
         </is>
       </c>
       <c r="G106" s="27" t="n"/>
+      <c r="H106" s="34" t="inlineStr">
+        <is>
+          <t>a long, dark, wrinkled pod</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="18">
       <c r="A107" s="27" t="inlineStr">
@@ -44445,6 +44977,11 @@
         </is>
       </c>
       <c r="G107" s="27" t="n"/>
+      <c r="H107" s="34" t="inlineStr">
+        <is>
+          <t>fine white powder</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="15" customHeight="1" s="18">
       <c r="A108" s="27" t="inlineStr">
@@ -44477,6 +45014,11 @@
         </is>
       </c>
       <c r="G108" s="27" t="n"/>
+      <c r="H108" s="34" t="inlineStr">
+        <is>
+          <t>coarse black grains</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="15" customHeight="1" s="18">
       <c r="A109" s="27" t="inlineStr">
@@ -44509,6 +45051,11 @@
         </is>
       </c>
       <c r="G109" s="27" t="n"/>
+      <c r="H109" s="34" t="inlineStr">
+        <is>
+          <t>soft brown grains</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="15" customHeight="1" s="18">
       <c r="A110" s="27" t="inlineStr">
@@ -44541,6 +45088,11 @@
         </is>
       </c>
       <c r="G110" s="27" t="n"/>
+      <c r="H110" s="34" t="inlineStr">
+        <is>
+          <t>small brown drops</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="15" customHeight="1" s="18">
       <c r="A111" s="27" t="inlineStr">
@@ -44573,6 +45125,11 @@
         </is>
       </c>
       <c r="G111" s="27" t="n"/>
+      <c r="H111" s="34" t="inlineStr">
+        <is>
+          <t>dark brown powder</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="15" customHeight="1" s="18">
       <c r="A112" s="27" t="inlineStr">
@@ -44605,6 +45162,11 @@
         </is>
       </c>
       <c r="G112" s="27" t="n"/>
+      <c r="H112" s="34" t="inlineStr">
+        <is>
+          <t>fine white powder</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="15" customHeight="1" s="18">
       <c r="A113" s="27" t="inlineStr">
@@ -44637,6 +45199,11 @@
         </is>
       </c>
       <c r="G113" s="27" t="n"/>
+      <c r="H113" s="34" t="inlineStr">
+        <is>
+          <t>clear white crystals</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="15" customHeight="1" s="18">
       <c r="A114" s="27" t="inlineStr">
@@ -44669,6 +45236,11 @@
         </is>
       </c>
       <c r="G114" s="27" t="n"/>
+      <c r="H114" s="34" t="inlineStr">
+        <is>
+          <t>fine white powder</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="15" customHeight="1" s="18">
       <c r="A115" s="27" t="inlineStr">
@@ -44701,6 +45273,11 @@
         </is>
       </c>
       <c r="G115" s="27" t="n"/>
+      <c r="H115" s="34" t="inlineStr">
+        <is>
+          <t>tiny gold balls</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="15" customHeight="1" s="18">
       <c r="A116" s="27" t="inlineStr">
@@ -44733,6 +45310,11 @@
         </is>
       </c>
       <c r="G116" s="27" t="n"/>
+      <c r="H116" s="34" t="inlineStr">
+        <is>
+          <t>golden and runny</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="15" customHeight="1" s="18">
       <c r="A117" s="27" t="inlineStr">
@@ -44765,6 +45347,11 @@
         </is>
       </c>
       <c r="G117" s="27" t="n"/>
+      <c r="H117" s="34" t="inlineStr">
+        <is>
+          <t>white and creamy</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="15" customHeight="1" s="18">
       <c r="A118" s="27" t="inlineStr">
@@ -44797,6 +45384,11 @@
         </is>
       </c>
       <c r="G118" s="27" t="n"/>
+      <c r="H118" s="34" t="inlineStr">
+        <is>
+          <t>fine white powder</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="15" customHeight="1" s="18">
       <c r="A119" s="27" t="inlineStr">
@@ -44829,6 +45421,11 @@
         </is>
       </c>
       <c r="G119" s="27" t="n"/>
+      <c r="H119" s="34" t="inlineStr">
+        <is>
+          <t>pale, flat flakes</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="15" customHeight="1" s="18">
       <c r="A120" s="27" t="inlineStr">
@@ -44861,6 +45458,11 @@
         </is>
       </c>
       <c r="G120" s="27" t="n"/>
+      <c r="H120" s="34" t="inlineStr">
+        <is>
+          <t>pink crystals</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="15" customHeight="1" s="18">
       <c r="A121" s="27" t="inlineStr">
@@ -44893,6 +45495,11 @@
         </is>
       </c>
       <c r="G121" s="27" t="n"/>
+      <c r="H121" s="34" t="inlineStr">
+        <is>
+          <t>thin pink strands</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="15" customHeight="1" s="18">
       <c r="A122" s="27" t="inlineStr">
@@ -44925,6 +45532,11 @@
         </is>
       </c>
       <c r="G122" s="27" t="n"/>
+      <c r="H122" s="34" t="inlineStr">
+        <is>
+          <t>many-coloured strands</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="15" customHeight="1" s="18">
       <c r="A123" s="27" t="inlineStr">
@@ -44957,6 +45569,11 @@
         </is>
       </c>
       <c r="G123" s="27" t="n"/>
+      <c r="H123" s="34" t="inlineStr">
+        <is>
+          <t>fine white powder</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="15" customHeight="1" s="18">
       <c r="A124" s="27" t="inlineStr">
@@ -44989,6 +45606,11 @@
         </is>
       </c>
       <c r="G124" s="27" t="n"/>
+      <c r="H124" s="34" t="inlineStr">
+        <is>
+          <t>soft pink powder</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="15" customHeight="1" s="18">
       <c r="A125" s="27" t="inlineStr">
@@ -45021,6 +45643,11 @@
         </is>
       </c>
       <c r="G125" s="27" t="n"/>
+      <c r="H125" s="34" t="inlineStr">
+        <is>
+          <t>white crystals</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="15" customHeight="1" s="18">
       <c r="A126" s="27" t="inlineStr">
@@ -45053,6 +45680,11 @@
         </is>
       </c>
       <c r="G126" s="27" t="n"/>
+      <c r="H126" s="34" t="inlineStr">
+        <is>
+          <t>white grains</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="15" customHeight="1" s="18">
       <c r="A127" s="27" t="inlineStr">
@@ -45085,6 +45717,11 @@
         </is>
       </c>
       <c r="G127" s="27" t="n"/>
+      <c r="H127" s="34" t="inlineStr">
+        <is>
+          <t>dark, crumbly earth</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="15" customHeight="1" s="18">
       <c r="A128" s="27" t="inlineStr">
@@ -45117,6 +45754,11 @@
         </is>
       </c>
       <c r="G128" s="27" t="n"/>
+      <c r="H128" s="34" t="inlineStr">
+        <is>
+          <t>soft grey ash</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="15" customHeight="1" s="18">
       <c r="A129" s="27" t="inlineStr">
@@ -45149,6 +45791,11 @@
         </is>
       </c>
       <c r="G129" s="27" t="n"/>
+      <c r="H129" s="34" t="inlineStr">
+        <is>
+          <t>white, thin and crushed</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="15" customHeight="1" s="18">
       <c r="A130" s="27" t="inlineStr">
@@ -45181,6 +45828,11 @@
         </is>
       </c>
       <c r="G130" s="27" t="n"/>
+      <c r="H130" s="34" t="inlineStr">
+        <is>
+          <t>a plain white block</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="15" customHeight="1" s="18">
       <c r="A131" s="27" t="inlineStr">
@@ -45213,6 +45865,11 @@
         </is>
       </c>
       <c r="G131" s="27" t="n"/>
+      <c r="H131" s="34" t="inlineStr">
+        <is>
+          <t>a black block</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="15" customHeight="1" s="18">
       <c r="A132" s="27" t="inlineStr">
@@ -45245,6 +45902,11 @@
         </is>
       </c>
       <c r="G132" s="27" t="n"/>
+      <c r="H132" s="34" t="inlineStr">
+        <is>
+          <t>gold shimmer dust</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="15" customHeight="1" s="18">
       <c r="A133" s="27" t="inlineStr">
@@ -45277,6 +45939,11 @@
         </is>
       </c>
       <c r="G133" s="27" t="n"/>
+      <c r="H133" s="34" t="inlineStr">
+        <is>
+          <t>silver shimmer dust</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="15" customHeight="1" s="18">
       <c r="A134" s="27" t="inlineStr">
@@ -45309,6 +45976,11 @@
         </is>
       </c>
       <c r="G134" s="27" t="n"/>
+      <c r="H134" s="34" t="inlineStr">
+        <is>
+          <t>silver sparkle</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="15" customHeight="1" s="18">
       <c r="A135" s="27" t="inlineStr">
@@ -45341,6 +46013,11 @@
         </is>
       </c>
       <c r="G135" s="27" t="n"/>
+      <c r="H135" s="34" t="inlineStr">
+        <is>
+          <t>pink sparkle</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="15" customHeight="1" s="18">
       <c r="A136" s="27" t="inlineStr">
@@ -45373,6 +46050,11 @@
         </is>
       </c>
       <c r="G136" s="27" t="n"/>
+      <c r="H136" s="34" t="inlineStr">
+        <is>
+          <t>many-coloured sparkle</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="15" customHeight="1" s="18">
       <c r="A137" s="27" t="inlineStr">
@@ -45405,6 +46087,11 @@
         </is>
       </c>
       <c r="G137" s="27" t="n"/>
+      <c r="H137" s="34" t="inlineStr">
+        <is>
+          <t>golden, see-through lumps</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="15" customHeight="1" s="18">
       <c r="A138" s="27" t="inlineStr">
@@ -45437,6 +46124,11 @@
         </is>
       </c>
       <c r="G138" s="27" t="n"/>
+      <c r="H138" s="34" t="inlineStr">
+        <is>
+          <t>pale yellow, sticky lumps</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="15" customHeight="1" s="18">
       <c r="A139" s="27" t="inlineStr">
@@ -45469,6 +46161,11 @@
         </is>
       </c>
       <c r="G139" s="27" t="n"/>
+      <c r="H139" s="34" t="inlineStr">
+        <is>
+          <t>pale, milky tears of resin</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="15" customHeight="1" s="18">
       <c r="A140" s="27" t="inlineStr">
@@ -45501,6 +46198,11 @@
         </is>
       </c>
       <c r="G140" s="27" t="n"/>
+      <c r="H140" s="34" t="inlineStr">
+        <is>
+          <t>red-brown lumps of resin</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="15" customHeight="1" s="18">
       <c r="A141" s="27" t="inlineStr">
@@ -45533,6 +46235,11 @@
         </is>
       </c>
       <c r="G141" s="27" t="n"/>
+      <c r="H141" s="34" t="inlineStr">
+        <is>
+          <t>dark, crumbly leaves</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="15" customHeight="1" s="18">
       <c r="A142" s="27" t="inlineStr">
@@ -45565,6 +46272,11 @@
         </is>
       </c>
       <c r="G142" s="27" t="n"/>
+      <c r="H142" s="34" t="inlineStr">
+        <is>
+          <t>pale wood chips</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="15" customHeight="1" s="18">
       <c r="A143" s="27" t="inlineStr">
@@ -45597,6 +46309,11 @@
         </is>
       </c>
       <c r="G143" s="27" t="n"/>
+      <c r="H143" s="34" t="inlineStr">
+        <is>
+          <t>pale sea-green</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="15" customHeight="1" s="18">
       <c r="A144" s="27" t="inlineStr">
@@ -45629,6 +46346,11 @@
         </is>
       </c>
       <c r="G144" s="27" t="n"/>
+      <c r="H144" s="34" t="inlineStr">
+        <is>
+          <t>purple and pointed</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="15" customHeight="1" s="18">
       <c r="A145" s="27" t="inlineStr">
@@ -45661,6 +46383,11 @@
         </is>
       </c>
       <c r="G145" s="27" t="n"/>
+      <c r="H145" s="34" t="inlineStr">
+        <is>
+          <t>clear and sea-blue</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="15" customHeight="1" s="18">
       <c r="A146" s="27" t="inlineStr">
@@ -45693,6 +46420,11 @@
         </is>
       </c>
       <c r="G146" s="27" t="n"/>
+      <c r="H146" s="34" t="inlineStr">
+        <is>
+          <t>a stone that belongs to someone</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="15" customHeight="1" s="18">
       <c r="A147" s="27" t="inlineStr">
@@ -45725,6 +46457,11 @@
         </is>
       </c>
       <c r="G147" s="27" t="n"/>
+      <c r="H147" s="34" t="inlineStr">
+        <is>
+          <t>black and ridged</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="15" customHeight="1" s="18">
       <c r="A148" s="27" t="inlineStr">
@@ -45757,6 +46494,11 @@
         </is>
       </c>
       <c r="G148" s="27" t="n"/>
+      <c r="H148" s="34" t="inlineStr">
+        <is>
+          <t>pale blue with soft white bands</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="15" customHeight="1" s="18">
       <c r="A149" s="27" t="inlineStr">
@@ -45789,6 +46531,11 @@
         </is>
       </c>
       <c r="G149" s="27" t="n"/>
+      <c r="H149" s="34" t="inlineStr">
+        <is>
+          <t>orange-red and glowing</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="15" customHeight="1" s="18">
       <c r="A150" s="27" t="inlineStr">
@@ -45821,6 +46568,11 @@
         </is>
       </c>
       <c r="G150" s="27" t="n"/>
+      <c r="H150" s="34" t="inlineStr">
+        <is>
+          <t>clear and honey-yellow</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="15" customHeight="1" s="18">
       <c r="A151" s="27" t="inlineStr">
@@ -45853,6 +46605,11 @@
         </is>
       </c>
       <c r="G151" s="27" t="n"/>
+      <c r="H151" s="34" t="inlineStr">
+        <is>
+          <t>clear as ice and pointed</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="15" customHeight="1" s="18">
       <c r="A152" s="27" t="inlineStr">
@@ -45885,6 +46642,11 @@
         </is>
       </c>
       <c r="G152" s="27" t="n"/>
+      <c r="H152" s="34" t="inlineStr">
+        <is>
+          <t>striped green and purple</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="15" customHeight="1" s="18">
       <c r="A153" s="27" t="inlineStr">
@@ -45917,6 +46679,11 @@
         </is>
       </c>
       <c r="G153" s="27" t="n"/>
+      <c r="H153" s="34" t="inlineStr">
+        <is>
+          <t>deep red</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="15" customHeight="1" s="18">
       <c r="A154" s="27" t="inlineStr">
@@ -45949,6 +46716,11 @@
         </is>
       </c>
       <c r="G154" s="27" t="n"/>
+      <c r="H154" s="34" t="inlineStr">
+        <is>
+          <t>green, with a faint sparkle</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="15" customHeight="1" s="18">
       <c r="A155" s="27" t="inlineStr">
@@ -45981,6 +46753,11 @@
         </is>
       </c>
       <c r="G155" s="27" t="n"/>
+      <c r="H155" s="34" t="inlineStr">
+        <is>
+          <t>heavy, grey and mirror-bright</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="15" customHeight="1" s="18">
       <c r="A156" s="27" t="inlineStr">
@@ -46013,6 +46790,11 @@
         </is>
       </c>
       <c r="G156" s="27" t="n"/>
+      <c r="H156" s="34" t="inlineStr">
+        <is>
+          <t>white with grey veins</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="15" customHeight="1" s="18">
       <c r="A157" s="27" t="inlineStr">
@@ -46045,6 +46827,11 @@
         </is>
       </c>
       <c r="G157" s="27" t="n"/>
+      <c r="H157" s="34" t="inlineStr">
+        <is>
+          <t>smooth and milky green</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="15" customHeight="1" s="18">
       <c r="A158" s="27" t="inlineStr">
@@ -46077,6 +46864,11 @@
         </is>
       </c>
       <c r="G158" s="27" t="n"/>
+      <c r="H158" s="34" t="inlineStr">
+        <is>
+          <t>grey, with flashes of blue</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="15" customHeight="1" s="18">
       <c r="A159" s="27" t="inlineStr">
@@ -46109,6 +46901,11 @@
         </is>
       </c>
       <c r="G159" s="27" t="n"/>
+      <c r="H159" s="34" t="inlineStr">
+        <is>
+          <t>deep blue with gold flecks</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="15" customHeight="1" s="18">
       <c r="A160" s="27" t="inlineStr">
@@ -46141,6 +46938,11 @@
         </is>
       </c>
       <c r="G160" s="27" t="n"/>
+      <c r="H160" s="34" t="inlineStr">
+        <is>
+          <t>banded in dark and light green</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="15" customHeight="1" s="18">
       <c r="A161" s="27" t="inlineStr">
@@ -46173,6 +46975,11 @@
         </is>
       </c>
       <c r="G161" s="27" t="n"/>
+      <c r="H161" s="34" t="inlineStr">
+        <is>
+          <t>milky, with a blue glow</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="15" customHeight="1" s="18">
       <c r="A162" s="27" t="inlineStr">
@@ -46205,6 +47012,11 @@
         </is>
       </c>
       <c r="G162" s="27" t="n"/>
+      <c r="H162" s="34" t="inlineStr">
+        <is>
+          <t>clear, with green threads inside</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="15" customHeight="1" s="18">
       <c r="A163" s="27" t="inlineStr">
@@ -46237,6 +47049,11 @@
         </is>
       </c>
       <c r="G163" s="27" t="n"/>
+      <c r="H163" s="34" t="inlineStr">
+        <is>
+          <t>black and glassy</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="15" customHeight="1" s="18">
       <c r="A164" s="27" t="inlineStr">
@@ -46269,6 +47086,11 @@
         </is>
       </c>
       <c r="G164" s="27" t="n"/>
+      <c r="H164" s="34" t="inlineStr">
+        <is>
+          <t>round, creamy and lustrous</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="15" customHeight="1" s="18">
       <c r="A165" s="27" t="inlineStr">
@@ -46301,6 +47123,11 @@
         </is>
       </c>
       <c r="G165" s="27" t="n"/>
+      <c r="H165" s="34" t="inlineStr">
+        <is>
+          <t>pale bright green</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="15" customHeight="1" s="18">
       <c r="A166" s="27" t="inlineStr">
@@ -46333,6 +47160,11 @@
         </is>
       </c>
       <c r="G166" s="27" t="n"/>
+      <c r="H166" s="34" t="inlineStr">
+        <is>
+          <t>brassy gold and cube-shaped</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="15" customHeight="1" s="18">
       <c r="A167" s="27" t="inlineStr">
@@ -46365,6 +47197,11 @@
         </is>
       </c>
       <c r="G167" s="27" t="n"/>
+      <c r="H167" s="34" t="inlineStr">
+        <is>
+          <t>pink with black veins</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="15" customHeight="1" s="18">
       <c r="A168" s="27" t="inlineStr">
@@ -46397,6 +47234,11 @@
         </is>
       </c>
       <c r="G168" s="27" t="n"/>
+      <c r="H168" s="34" t="inlineStr">
+        <is>
+          <t>soft pink and cloudy</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="15" customHeight="1" s="18">
       <c r="A169" s="27" t="inlineStr">
@@ -46429,6 +47271,11 @@
         </is>
       </c>
       <c r="G169" s="27" t="n"/>
+      <c r="H169" s="34" t="inlineStr">
+        <is>
+          <t>white and silky-striped</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="15" customHeight="1" s="18">
       <c r="A170" s="27" t="inlineStr">
@@ -46461,6 +47308,11 @@
         </is>
       </c>
       <c r="G170" s="27" t="n"/>
+      <c r="H170" s="34" t="inlineStr">
+        <is>
+          <t>brown and see-through</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="15" customHeight="1" s="18">
       <c r="A171" s="27" t="inlineStr">
@@ -46493,6 +47345,11 @@
         </is>
       </c>
       <c r="G171" s="27" t="n"/>
+      <c r="H171" s="34" t="inlineStr">
+        <is>
+          <t>orange, with a glittering shimmer</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="15" customHeight="1" s="18">
       <c r="A172" s="27" t="inlineStr">
@@ -46525,6 +47382,11 @@
         </is>
       </c>
       <c r="G172" s="27" t="n"/>
+      <c r="H172" s="34" t="inlineStr">
+        <is>
+          <t>striped gold and brown</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="15" customHeight="1" s="18">
       <c r="A173" s="27" t="inlineStr">
@@ -46557,6 +47419,11 @@
         </is>
       </c>
       <c r="G173" s="27" t="n"/>
+      <c r="H173" s="34" t="inlineStr">
+        <is>
+          <t>grey, smooth and round</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="15" customHeight="1" s="18">
       <c r="A174" s="27" t="inlineStr">
@@ -46589,6 +47456,11 @@
         </is>
       </c>
       <c r="G174" s="27" t="n"/>
+      <c r="H174" s="34" t="inlineStr">
+        <is>
+          <t>tiny golden grains</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="15" customHeight="1" s="18">
       <c r="A175" s="27" t="inlineStr">
@@ -46621,6 +47493,11 @@
         </is>
       </c>
       <c r="G175" s="27" t="n"/>
+      <c r="H175" s="34" t="inlineStr">
+        <is>
+          <t>soft, white and feathery</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="15" customHeight="1" s="18">
       <c r="A176" s="27" t="inlineStr">
@@ -46653,6 +47530,11 @@
         </is>
       </c>
       <c r="G176" s="27" t="n"/>
+      <c r="H176" s="34" t="inlineStr">
+        <is>
+          <t>thin, stiff and spiky</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="15" customHeight="1" s="18">
       <c r="A177" s="27" t="inlineStr">
@@ -46685,6 +47567,11 @@
         </is>
       </c>
       <c r="G177" s="27" t="n"/>
+      <c r="H177" s="34" t="inlineStr">
+        <is>
+          <t>golden and waxy, full of little cells</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="15" customHeight="1" s="18">
       <c r="A178" s="27" t="inlineStr">
@@ -46717,6 +47604,11 @@
         </is>
       </c>
       <c r="G178" s="27" t="n"/>
+      <c r="H178" s="34" t="inlineStr">
+        <is>
+          <t>glossy black and white</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="15" customHeight="1" s="18">
       <c r="A179" s="27" t="inlineStr">
@@ -46749,6 +47641,11 @@
         </is>
       </c>
       <c r="G179" s="27" t="n"/>
+      <c r="H179" s="34" t="inlineStr">
+        <is>
+          <t>soft grey powder</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="15" customHeight="1" s="18">
       <c r="A180" s="27" t="inlineStr">
@@ -46781,6 +47678,11 @@
         </is>
       </c>
       <c r="G180" s="27" t="n"/>
+      <c r="H180" s="34" t="inlineStr">
+        <is>
+          <t>mottled brown and soft</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="15" customHeight="1" s="18">
       <c r="A181" s="27" t="inlineStr">
@@ -46813,6 +47715,11 @@
         </is>
       </c>
       <c r="G181" s="27" t="n"/>
+      <c r="H181" s="34" t="inlineStr">
+        <is>
+          <t>long, with a shimmering eye</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="15" customHeight="1" s="18">
       <c r="A182" s="27" t="inlineStr">
@@ -46845,6 +47752,11 @@
         </is>
       </c>
       <c r="G182" s="27" t="n"/>
+      <c r="H182" s="34" t="inlineStr">
+        <is>
+          <t>long, glossy and black</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="15" customHeight="1" s="18">
       <c r="A183" s="27" t="inlineStr">
@@ -46877,6 +47789,11 @@
         </is>
       </c>
       <c r="G183" s="27" t="n"/>
+      <c r="H183" s="34" t="inlineStr">
+        <is>
+          <t>pale, ridged and curled</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="15" customHeight="1" s="18">
       <c r="A184" s="27" t="inlineStr">
@@ -46909,6 +47826,11 @@
         </is>
       </c>
       <c r="G184" s="27" t="n"/>
+      <c r="H184" s="34" t="inlineStr">
+        <is>
+          <t>a single fine white hair</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="15" customHeight="1" s="18">
       <c r="A185" s="27" t="inlineStr">
@@ -46941,6 +47863,11 @@
         </is>
       </c>
       <c r="G185" s="27" t="n"/>
+      <c r="H185" s="34" t="inlineStr">
+        <is>
+          <t>papery, scaled and see-through</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="15" customHeight="1" s="18">
       <c r="A186" s="27" t="inlineStr">
@@ -46973,6 +47900,11 @@
         </is>
       </c>
       <c r="G186" s="27" t="n"/>
+      <c r="H186" s="34" t="inlineStr">
+        <is>
+          <t>small, brown and spiralled</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="15" customHeight="1" s="18">
       <c r="A187" s="27" t="inlineStr">
@@ -47005,6 +47937,11 @@
         </is>
       </c>
       <c r="G187" s="27" t="n"/>
+      <c r="H187" s="34" t="inlineStr">
+        <is>
+          <t>white and fluffy as a cloud</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="15" customHeight="1" s="18">
       <c r="A188" s="27" t="inlineStr">
@@ -47037,6 +47974,11 @@
         </is>
       </c>
       <c r="G188" s="27" t="n"/>
+      <c r="H188" s="34" t="inlineStr">
+        <is>
+          <t>small, white and feathery</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="15" customHeight="1" s="18">
       <c r="A189" s="27" t="inlineStr">
@@ -47069,6 +48011,11 @@
         </is>
       </c>
       <c r="G189" s="27" t="n"/>
+      <c r="H189" s="34" t="inlineStr">
+        <is>
+          <t>thin, brown and woven</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="15" customHeight="1" s="18">
       <c r="A190" s="27" t="inlineStr">
@@ -47101,6 +48048,11 @@
         </is>
       </c>
       <c r="G190" s="27" t="n"/>
+      <c r="H190" s="34" t="inlineStr">
+        <is>
+          <t>golden and polished</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="15" customHeight="1" s="18">
       <c r="A191" s="27" t="inlineStr">
@@ -47133,6 +48085,11 @@
         </is>
       </c>
       <c r="G191" s="27" t="n"/>
+      <c r="H191" s="34" t="inlineStr">
+        <is>
+          <t>bright and many-coloured</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="15" customHeight="1" s="18">
       <c r="A192" s="27" t="inlineStr">
@@ -47165,6 +48122,11 @@
         </is>
       </c>
       <c r="G192" s="27" t="n"/>
+      <c r="H192" s="34" t="inlineStr">
+        <is>
+          <t>small and golden</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="15" customHeight="1" s="18">
       <c r="A193" s="27" t="inlineStr">
@@ -47197,6 +48159,11 @@
         </is>
       </c>
       <c r="G193" s="27" t="n"/>
+      <c r="H193" s="34" t="inlineStr">
+        <is>
+          <t>shaped like a little heart</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="15" customHeight="1" s="18">
       <c r="A194" s="27" t="inlineStr">
@@ -47229,6 +48196,11 @@
         </is>
       </c>
       <c r="G194" s="27" t="n"/>
+      <c r="H194" s="34" t="inlineStr">
+        <is>
+          <t>odd and one of a kind</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="15" customHeight="1" s="18">
       <c r="A195" s="27" t="inlineStr">
@@ -47261,6 +48233,11 @@
         </is>
       </c>
       <c r="G195" s="27" t="n"/>
+      <c r="H195" s="34" t="inlineStr">
+        <is>
+          <t>creamy and lustrous</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="15" customHeight="1" s="18">
       <c r="A196" s="27" t="inlineStr">
@@ -47293,6 +48270,11 @@
         </is>
       </c>
       <c r="G196" s="27" t="n"/>
+      <c r="H196" s="34" t="inlineStr">
+        <is>
+          <t>small and square-cornered</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="15" customHeight="1" s="18">
       <c r="A197" s="27" t="inlineStr">
@@ -47325,6 +48307,11 @@
         </is>
       </c>
       <c r="G197" s="27" t="n"/>
+      <c r="H197" s="34" t="inlineStr">
+        <is>
+          <t>star-shaped</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="15" customHeight="1" s="18">
       <c r="A198" s="27" t="inlineStr">
@@ -47357,6 +48344,11 @@
         </is>
       </c>
       <c r="G198" s="27" t="n"/>
+      <c r="H198" s="34" t="inlineStr">
+        <is>
+          <t>old, carved and a little worn</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="15" customHeight="1" s="18">
       <c r="A199" s="27" t="inlineStr">
@@ -47389,6 +48381,11 @@
         </is>
       </c>
       <c r="G199" s="27" t="n"/>
+      <c r="H199" s="34" t="inlineStr">
+        <is>
+          <t>dark thread</t>
+        </is>
+      </c>
     </row>
     <row r="200" ht="15" customHeight="1" s="18">
       <c r="A200" s="27" t="inlineStr">
@@ -47421,6 +48418,11 @@
         </is>
       </c>
       <c r="G200" s="27" t="n"/>
+      <c r="H200" s="34" t="inlineStr">
+        <is>
+          <t>cool-coloured thread</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="15" customHeight="1" s="18">
       <c r="A201" s="27" t="inlineStr">
@@ -47453,6 +48455,11 @@
         </is>
       </c>
       <c r="G201" s="27" t="n"/>
+      <c r="H201" s="34" t="inlineStr">
+        <is>
+          <t>metallic thread</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="15" customHeight="1" s="18">
       <c r="A202" s="27" t="inlineStr">
@@ -47485,6 +48492,11 @@
         </is>
       </c>
       <c r="G202" s="27" t="n"/>
+      <c r="H202" s="34" t="inlineStr">
+        <is>
+          <t>cool-coloured thread</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="15" customHeight="1" s="18">
       <c r="A203" s="27" t="inlineStr">
@@ -47517,6 +48529,11 @@
         </is>
       </c>
       <c r="G203" s="27" t="n"/>
+      <c r="H203" s="34" t="inlineStr">
+        <is>
+          <t>dull, soft thread</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="15" customHeight="1" s="18">
       <c r="A204" s="27" t="inlineStr">
@@ -47549,6 +48566,11 @@
         </is>
       </c>
       <c r="G204" s="27" t="n"/>
+      <c r="H204" s="34" t="inlineStr">
+        <is>
+          <t>warm-coloured thread</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="15" customHeight="1" s="18">
       <c r="A205" s="27" t="inlineStr">
@@ -47581,6 +48603,11 @@
         </is>
       </c>
       <c r="G205" s="27" t="n"/>
+      <c r="H205" s="34" t="inlineStr">
+        <is>
+          <t>soft, warm-coloured thread</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="15" customHeight="1" s="18">
       <c r="A206" s="27" t="inlineStr">
@@ -47613,6 +48640,11 @@
         </is>
       </c>
       <c r="G206" s="27" t="n"/>
+      <c r="H206" s="34" t="inlineStr">
+        <is>
+          <t>deep-coloured thread</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="15" customHeight="1" s="18">
       <c r="A207" s="27" t="inlineStr">
@@ -47645,6 +48677,11 @@
         </is>
       </c>
       <c r="G207" s="27" t="n"/>
+      <c r="H207" s="34" t="inlineStr">
+        <is>
+          <t>many-coloured threads</t>
+        </is>
+      </c>
     </row>
     <row r="208" ht="15" customHeight="1" s="18">
       <c r="A208" s="27" t="inlineStr">
@@ -47677,6 +48714,11 @@
         </is>
       </c>
       <c r="G208" s="27" t="n"/>
+      <c r="H208" s="34" t="inlineStr">
+        <is>
+          <t>warm-coloured thread</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="15" customHeight="1" s="18">
       <c r="A209" s="27" t="inlineStr">
@@ -47709,6 +48751,11 @@
         </is>
       </c>
       <c r="G209" s="27" t="n"/>
+      <c r="H209" s="34" t="inlineStr">
+        <is>
+          <t>metallic thread</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="15" customHeight="1" s="18">
       <c r="A210" s="27" t="inlineStr">
@@ -47741,6 +48788,11 @@
         </is>
       </c>
       <c r="G210" s="27" t="n"/>
+      <c r="H210" s="34" t="inlineStr">
+        <is>
+          <t>pale thread</t>
+        </is>
+      </c>
     </row>
     <row r="211" ht="15" customHeight="1" s="18">
       <c r="A211" s="27" t="inlineStr">
@@ -47773,6 +48825,11 @@
         </is>
       </c>
       <c r="G211" s="27" t="n"/>
+      <c r="H211" s="34" t="inlineStr">
+        <is>
+          <t>warm-coloured thread</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="15" customHeight="1" s="18">
       <c r="A212" s="27" t="inlineStr">
@@ -47805,6 +48862,11 @@
         </is>
       </c>
       <c r="G212" s="27" t="n"/>
+      <c r="H212" s="34" t="inlineStr">
+        <is>
+          <t>smooth and glossy</t>
+        </is>
+      </c>
     </row>
     <row r="213" ht="15" customHeight="1" s="18">
       <c r="A213" s="27" t="inlineStr">
@@ -47837,6 +48899,11 @@
         </is>
       </c>
       <c r="G213" s="27" t="n"/>
+      <c r="H213" s="34" t="inlineStr">
+        <is>
+          <t>soft, heavy and deep red</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="15" customHeight="1" s="18">
       <c r="A214" s="27" t="inlineStr">
@@ -47869,6 +48936,11 @@
         </is>
       </c>
       <c r="G214" s="27" t="n"/>
+      <c r="H214" s="34" t="inlineStr">
+        <is>
+          <t>a wooden spool, wound tight</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="15" customHeight="1" s="18">
       <c r="A215" s="27" t="inlineStr">
@@ -47901,6 +48973,11 @@
         </is>
       </c>
       <c r="G215" s="27" t="n"/>
+      <c r="H215" s="34" t="inlineStr">
+        <is>
+          <t>a little cloth bag</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="15" customHeight="1" s="18">
       <c r="A216" s="27" t="inlineStr">
@@ -47933,6 +49010,11 @@
         </is>
       </c>
       <c r="G216" s="27" t="n"/>
+      <c r="H216" s="34" t="inlineStr">
+        <is>
+          <t>a little dark, glossy bag</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="15" customHeight="1" s="18">
       <c r="A217" s="27" t="inlineStr">
@@ -47965,6 +49047,11 @@
         </is>
       </c>
       <c r="G217" s="27" t="n"/>
+      <c r="H217" s="34" t="inlineStr">
+        <is>
+          <t>thin, white and gauzy</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="15" customHeight="1" s="18">
       <c r="A218" s="27" t="inlineStr">
@@ -47997,6 +49084,11 @@
         </is>
       </c>
       <c r="G218" s="27" t="n"/>
+      <c r="H218" s="34" t="inlineStr">
+        <is>
+          <t>many-coloured scraps of cloth</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="15" customHeight="1" s="18">
       <c r="A219" s="27" t="inlineStr">
@@ -48029,6 +49121,11 @@
         </is>
       </c>
       <c r="G219" s="27" t="n"/>
+      <c r="H219" s="34" t="inlineStr">
+        <is>
+          <t>pale and straight</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="15" customHeight="1" s="18">
       <c r="A220" s="27" t="inlineStr">
@@ -48061,6 +49158,11 @@
         </is>
       </c>
       <c r="G220" s="27" t="n"/>
+      <c r="H220" s="34" t="inlineStr">
+        <is>
+          <t>pale and straight-grained</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="15" customHeight="1" s="18">
       <c r="A221" s="27" t="inlineStr">
@@ -48093,6 +49195,11 @@
         </is>
       </c>
       <c r="G221" s="27" t="n"/>
+      <c r="H221" s="34" t="inlineStr">
+        <is>
+          <t>white-barked</t>
+        </is>
+      </c>
     </row>
     <row r="222" ht="15" customHeight="1" s="18">
       <c r="A222" s="27" t="inlineStr">
@@ -48125,6 +49232,11 @@
         </is>
       </c>
       <c r="G222" s="27" t="n"/>
+      <c r="H222" s="34" t="inlineStr">
+        <is>
+          <t>white-barked</t>
+        </is>
+      </c>
     </row>
     <row r="223" ht="15" customHeight="1" s="18">
       <c r="A223" s="27" t="inlineStr">
@@ -48157,6 +49269,11 @@
         </is>
       </c>
       <c r="G223" s="27" t="n"/>
+      <c r="H223" s="34" t="inlineStr">
+        <is>
+          <t>dark and thorny</t>
+        </is>
+      </c>
     </row>
     <row r="224" ht="15" customHeight="1" s="18">
       <c r="A224" s="27" t="inlineStr">
@@ -48189,6 +49306,11 @@
         </is>
       </c>
       <c r="G224" s="27" t="n"/>
+      <c r="H224" s="34" t="inlineStr">
+        <is>
+          <t>smooth, brown and supple</t>
+        </is>
+      </c>
     </row>
     <row r="225" ht="15" customHeight="1" s="18">
       <c r="A225" s="27" t="inlineStr">
@@ -48221,6 +49343,11 @@
         </is>
       </c>
       <c r="G225" s="27" t="n"/>
+      <c r="H225" s="34" t="inlineStr">
+        <is>
+          <t>dark, heavy and rough</t>
+        </is>
+      </c>
     </row>
     <row r="226" ht="15" customHeight="1" s="18">
       <c r="A226" s="27" t="inlineStr">
@@ -48253,6 +49380,11 @@
         </is>
       </c>
       <c r="G226" s="27" t="n"/>
+      <c r="H226" s="34" t="inlineStr">
+        <is>
+          <t>slim, with red berries</t>
+        </is>
+      </c>
     </row>
     <row r="227" ht="15" customHeight="1" s="18">
       <c r="A227" s="27" t="inlineStr">
@@ -48285,6 +49417,11 @@
         </is>
       </c>
       <c r="G227" s="27" t="n"/>
+      <c r="H227" s="34" t="inlineStr">
+        <is>
+          <t>small, thin and brown</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="15" customHeight="1" s="18">
       <c r="A228" s="27" t="inlineStr">
@@ -48317,6 +49454,11 @@
         </is>
       </c>
       <c r="G228" s="27" t="n"/>
+      <c r="H228" s="34" t="inlineStr">
+        <is>
+          <t>long, thin and bendy</t>
+        </is>
+      </c>
     </row>
     <row r="229" ht="15" customHeight="1" s="18">
       <c r="A229" s="27" t="inlineStr">
@@ -48349,6 +49491,11 @@
         </is>
       </c>
       <c r="G229" s="27" t="n"/>
+      <c r="H229" s="34" t="inlineStr">
+        <is>
+          <t>pale and bendy</t>
+        </is>
+      </c>
     </row>
     <row r="230" ht="15" customHeight="1" s="18">
       <c r="A230" s="27" t="inlineStr">
@@ -48381,6 +49528,11 @@
         </is>
       </c>
       <c r="G230" s="27" t="n"/>
+      <c r="H230" s="34" t="inlineStr">
+        <is>
+          <t>flat, round and wooden</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="15" customHeight="1" s="18">
       <c r="A231" s="27" t="inlineStr">
@@ -48413,6 +49565,11 @@
         </is>
       </c>
       <c r="G231" s="27" t="n"/>
+      <c r="H231" s="34" t="inlineStr">
+        <is>
+          <t>small, brown and capped</t>
+        </is>
+      </c>
     </row>
     <row r="232" ht="15" customHeight="1" s="18">
       <c r="A232" s="27" t="inlineStr">
@@ -48445,6 +49602,11 @@
         </is>
       </c>
       <c r="G232" s="27" t="n"/>
+      <c r="H232" s="34" t="inlineStr">
+        <is>
+          <t>small, round and hinged, with a mirror</t>
+        </is>
+      </c>
     </row>
     <row r="233" ht="15" customHeight="1" s="18">
       <c r="A233" s="27" t="inlineStr">
@@ -48477,6 +49639,11 @@
         </is>
       </c>
       <c r="G233" s="27" t="n"/>
+      <c r="H233" s="34" t="inlineStr">
+        <is>
+          <t>small and hinged, with a dark mirror</t>
+        </is>
+      </c>
     </row>
     <row r="234" ht="15" customHeight="1" s="18">
       <c r="A234" s="27" t="inlineStr">
@@ -48509,6 +49676,11 @@
         </is>
       </c>
       <c r="G234" s="27" t="n"/>
+      <c r="H234" s="34" t="inlineStr">
+        <is>
+          <t>soft, grey and earthy</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="15" customHeight="1" s="18">
       <c r="A235" s="27" t="inlineStr">
@@ -48541,6 +49713,11 @@
         </is>
       </c>
       <c r="G235" s="27" t="n"/>
+      <c r="H235" s="34" t="inlineStr">
+        <is>
+          <t>small, round and metal</t>
+        </is>
+      </c>
     </row>
     <row r="236" ht="15" customHeight="1" s="18">
       <c r="A236" s="27" t="inlineStr">
@@ -48573,6 +49750,11 @@
         </is>
       </c>
       <c r="G236" s="27" t="n"/>
+      <c r="H236" s="34" t="inlineStr">
+        <is>
+          <t>flat, round and coppery</t>
+        </is>
+      </c>
     </row>
     <row r="237" ht="15" customHeight="1" s="18">
       <c r="A237" s="27" t="inlineStr">
@@ -48605,6 +49787,11 @@
         </is>
       </c>
       <c r="G237" s="27" t="n"/>
+      <c r="H237" s="34" t="inlineStr">
+        <is>
+          <t>small, round and see-through</t>
+        </is>
+      </c>
     </row>
     <row r="238" ht="15" customHeight="1" s="18">
       <c r="A238" s="27" t="inlineStr">
@@ -48637,6 +49824,11 @@
         </is>
       </c>
       <c r="G238" s="27" t="n"/>
+      <c r="H238" s="34" t="inlineStr">
+        <is>
+          <t>small, clear and stoppered</t>
+        </is>
+      </c>
     </row>
     <row r="239" ht="15" customHeight="1" s="18">
       <c r="A239" s="27" t="inlineStr">
@@ -48669,6 +49861,11 @@
         </is>
       </c>
       <c r="G239" s="27" t="n"/>
+      <c r="H239" s="34" t="inlineStr">
+        <is>
+          <t>heavy grey dust</t>
+        </is>
+      </c>
     </row>
     <row r="240" ht="15" customHeight="1" s="18">
       <c r="A240" s="27" t="inlineStr">
@@ -48701,6 +49898,11 @@
         </is>
       </c>
       <c r="G240" s="27" t="n"/>
+      <c r="H240" s="34" t="inlineStr">
+        <is>
+          <t>long, dark and metal</t>
+        </is>
+      </c>
     </row>
     <row r="241" ht="15" customHeight="1" s="18">
       <c r="A241" s="27" t="inlineStr">
@@ -48733,6 +49935,11 @@
         </is>
       </c>
       <c r="G241" s="27" t="n"/>
+      <c r="H241" s="34" t="inlineStr">
+        <is>
+          <t>thin, dark and pointed</t>
+        </is>
+      </c>
     </row>
     <row r="242" ht="15" customHeight="1" s="18">
       <c r="A242" s="27" t="inlineStr">
@@ -48765,6 +49972,11 @@
         </is>
       </c>
       <c r="G242" s="27" t="n"/>
+      <c r="H242" s="34" t="inlineStr">
+        <is>
+          <t>small, hinged, on a chain</t>
+        </is>
+      </c>
     </row>
     <row r="243" ht="15" customHeight="1" s="18">
       <c r="A243" s="27" t="inlineStr">
@@ -48797,6 +50009,11 @@
         </is>
       </c>
       <c r="G243" s="27" t="n"/>
+      <c r="H243" s="34" t="inlineStr">
+        <is>
+          <t>a few fine bristles</t>
+        </is>
+      </c>
     </row>
     <row r="244" ht="15" customHeight="1" s="18">
       <c r="A244" s="27" t="inlineStr">
@@ -48829,6 +50046,11 @@
         </is>
       </c>
       <c r="G244" s="27" t="n"/>
+      <c r="H244" s="34" t="inlineStr">
+        <is>
+          <t>plain and flat</t>
+        </is>
+      </c>
     </row>
     <row r="245" ht="15" customHeight="1" s="18">
       <c r="A245" s="27" t="inlineStr">
@@ -48861,6 +50083,11 @@
         </is>
       </c>
       <c r="G245" s="27" t="n"/>
+      <c r="H245" s="34" t="inlineStr">
+        <is>
+          <t>a long feather cut to a nib</t>
+        </is>
+      </c>
     </row>
     <row r="246" ht="15" customHeight="1" s="18">
       <c r="A246" s="27" t="inlineStr">
@@ -48893,6 +50120,11 @@
         </is>
       </c>
       <c r="G246" s="27" t="n"/>
+      <c r="H246" s="34" t="inlineStr">
+        <is>
+          <t>small, round and silver</t>
+        </is>
+      </c>
     </row>
     <row r="247" ht="15" customHeight="1" s="18">
       <c r="A247" s="27" t="inlineStr">
@@ -48925,6 +50157,11 @@
         </is>
       </c>
       <c r="G247" s="27" t="n"/>
+      <c r="H247" s="34" t="inlineStr">
+        <is>
+          <t>small and metal, with teeth</t>
+        </is>
+      </c>
     </row>
     <row r="248" ht="15" customHeight="1" s="18">
       <c r="A248" s="27" t="inlineStr">
@@ -48957,6 +50194,11 @@
         </is>
       </c>
       <c r="G248" s="27" t="n"/>
+      <c r="H248" s="34" t="inlineStr">
+        <is>
+          <t>tiny and teacup-shaped</t>
+        </is>
+      </c>
     </row>
     <row r="249" ht="15" customHeight="1" s="18">
       <c r="A249" s="27" t="inlineStr">
@@ -48989,6 +50231,11 @@
         </is>
       </c>
       <c r="G249" s="27" t="n"/>
+      <c r="H249" s="34" t="inlineStr">
+        <is>
+          <t>tiny, metal and ringing</t>
+        </is>
+      </c>
     </row>
     <row r="250" ht="15" customHeight="1" s="18">
       <c r="A250" s="27" t="inlineStr">
@@ -49021,6 +50268,11 @@
         </is>
       </c>
       <c r="G250" s="27" t="n"/>
+      <c r="H250" s="34" t="inlineStr">
+        <is>
+          <t>a round, red blob of wax</t>
+        </is>
+      </c>
     </row>
     <row r="251" ht="15" customHeight="1" s="18">
       <c r="A251" s="27" t="inlineStr">
@@ -49053,6 +50305,11 @@
         </is>
       </c>
       <c r="G251" s="27" t="n"/>
+      <c r="H251" s="34" t="inlineStr">
+        <is>
+          <t>small, wooden and dotted</t>
+        </is>
+      </c>
     </row>
     <row r="252" ht="15" customHeight="1" s="18">
       <c r="A252" s="27" t="inlineStr">
@@ -49085,6 +50342,11 @@
         </is>
       </c>
       <c r="G252" s="27" t="n"/>
+      <c r="H252" s="34" t="inlineStr">
+        <is>
+          <t>black and wet</t>
+        </is>
+      </c>
     </row>
     <row r="253" ht="15" customHeight="1" s="18">
       <c r="A253" s="27" t="inlineStr">
@@ -49117,6 +50379,11 @@
         </is>
       </c>
       <c r="G253" s="27" t="n"/>
+      <c r="H253" s="34" t="inlineStr">
+        <is>
+          <t>shimmering gold and wet</t>
+        </is>
+      </c>
     </row>
     <row r="254" ht="15" customHeight="1" s="18">
       <c r="A254" s="27" t="inlineStr">
@@ -49149,6 +50416,11 @@
         </is>
       </c>
       <c r="G254" s="27" t="n"/>
+      <c r="H254" s="34" t="inlineStr">
+        <is>
+          <t>dark and wet</t>
+        </is>
+      </c>
     </row>
     <row r="255" ht="15" customHeight="1" s="18">
       <c r="A255" s="27" t="inlineStr">
@@ -49181,6 +50453,11 @@
         </is>
       </c>
       <c r="G255" s="27" t="n"/>
+      <c r="H255" s="34" t="inlineStr">
+        <is>
+          <t>red and wet</t>
+        </is>
+      </c>
     </row>
     <row r="256" ht="15" customHeight="1" s="18">
       <c r="A256" s="27" t="inlineStr">
@@ -49213,6 +50490,11 @@
         </is>
       </c>
       <c r="G256" s="27" t="n"/>
+      <c r="H256" s="34" t="inlineStr">
+        <is>
+          <t>shimmering silver and wet</t>
+        </is>
+      </c>
     </row>
     <row r="257" ht="15" customHeight="1" s="18">
       <c r="A257" s="27" t="inlineStr">
@@ -49245,6 +50527,11 @@
         </is>
       </c>
       <c r="G257" s="27" t="n"/>
+      <c r="H257" s="34" t="inlineStr">
+        <is>
+          <t>purple and wet</t>
+        </is>
+      </c>
     </row>
     <row r="258" ht="15" customHeight="1" s="18">
       <c r="A258" s="27" t="inlineStr">
@@ -49277,6 +50564,11 @@
         </is>
       </c>
       <c r="G258" s="27" t="n"/>
+      <c r="H258" s="34" t="inlineStr">
+        <is>
+          <t>thick and gold</t>
+        </is>
+      </c>
     </row>
     <row r="259" ht="15" customHeight="1" s="18">
       <c r="A259" s="27" t="inlineStr">
@@ -49309,6 +50601,11 @@
         </is>
       </c>
       <c r="G259" s="27" t="n"/>
+      <c r="H259" s="34" t="inlineStr">
+        <is>
+          <t>thick and red</t>
+        </is>
+      </c>
     </row>
     <row r="260" ht="15" customHeight="1" s="18"/>
     <row r="261" ht="15" customHeight="1" s="18"/>

--- a/ingredient_asset_tracker.xlsx
+++ b/ingredient_asset_tracker.xlsx
@@ -75439,7 +75439,7 @@
       <c r="N2" s="34" t="inlineStr">
         <is>
           <t>To whoever keeps the Emporium now,
-Our shelves are bare of the one herb we can't do without. You'll know the one: it stings your fingers when you pick it, and then it builds a worn-out body back up. Nothing does more for healing after a long sickness.
+Our shelves are bare of nettle, the one herb we can't do without. It stings your fingers when you pick it, and then it builds a worn-out body back up. Nothing does more for healing after a long sickness.
 I drink it myself, steeped with a little milk, after a long shift behind the counter, on the days I've looked after everyone in Wrenmoor and forgotten to look after me.
 Could you spare us a bundle or two? We'll pay in honey, as we always did.
 Agnes, Mill Lane Apothecary, Wrenmoor</t>
@@ -75511,8 +75511,8 @@
       <c r="N3" s="34" t="inlineStr">
         <is>
           <t>To the Emporium,
-Two orders, if you would. The bitter white crystals that draw the ache out of tired legs. Our laundry maids grate them into the soap for the towels too; they say it makes washday a proper cleansing and the hours go quicker.
-And the soft pink mud. We press it into little cakes of soap for the old gentlemen who come in after a hard day. They say nothing gives them more comfort before bed.
+Two orders, if you would. Epsom salt, the bitter white crystals that draw the ache out of tired legs. Our laundry maids grate them into the soap for the towels too; they say it makes washday a proper cleansing and the hours go quicker.
+And rose clay, the soft pink mud. We press it into little cakes of soap for the old gentlemen who come in after a hard day. They say nothing gives them more comfort before bed.
 We have been buying poor stuff from Marrowgate and the guests can tell.
 Mr Hugo Fairweather, Manager, the Halloway Baths</t>
         </is>
@@ -75567,7 +75567,7 @@
       <c r="N4" s="34" t="inlineStr">
         <is>
           <t>Dear Emporium,
-We grow a ruffled, sweet-smelling climber along the hive fence, the flower everyone sends when they mean thank you. When two neighbours here fall out and can't find the words to make it up, one of us brews a pot of tea with it and sits them down. It has kept friendship sweet on our lane for forty years.
+We grow sweet peas along the hive fence, the flower everyone sends when they mean thank you. When two neighbours here fall out and can't find the words to make it up, one of us brews a pot of tea with it and sits them down. It has kept friendship sweet on our lane for forty years.
 This year the frost took it. If you have dried flowers to spare, we'll pay in comb.
 Martha Hale and the Honeywell Beekeepers</t>
         </is>
@@ -75638,8 +75638,8 @@
       <c r="N5" s="34" t="inlineStr">
         <is>
           <t>Dear Emporium,
-The playground has turned unkind this term, and a new girl starts next week. Here the children make a chain of the little white-and-yellow field flowers for anyone new; it is how friendship starts in Cloverdale. My predecessor even burned dried ones in the classroom when tempers ran high.
-The older ones also go hunting for the plain three-leaved kind. Our school cook steeps it into a cordial on sports day, for luck.
+The playground has turned unkind this term, and a new girl starts next week. Here the children make a daisy chain for anyone new; it is how friendship starts in Cloverdale. My predecessor even burned dried ones in the classroom when tempers ran high.
+The older ones also go hunting for clover, the plain three-leaved kind. Our school cook steeps it into a cordial on sports day, for luck.
 The frost has spoilt both. Have you any dried?
 Miss Primrose Dell, Cloverdale Village School</t>
         </is>
@@ -75710,8 +75710,8 @@
       <c r="N6" s="34" t="inlineStr">
         <is>
           <t>Darling shop,
-Wedding season is upon us. My brides want the small white flowers of the citrus tree, dried and ground to a powder for their shoulders, so they shine in every photograph. Their grandmothers said a bride wearing it glows with joy.
-And for the bride who wants to walk down the aisle like a swan, a soap of the tall, still white flower. Nothing gives a quiet bride beauty like it.
+Wedding season is upon us. My brides want orange blossom, dried and ground to a powder for their shoulders, so they shine in every photograph. Their grandmothers said a bride wearing it glows with joy.
+And for the bride who wants to walk down the aisle like a swan, a soap of white lily. Nothing gives a quiet bride beauty like it.
 Send whatever you can. Kingsmere does not do things by halves.
 Lavinia, Lavinia's Bridal Rooms, Kingsmere</t>
         </is>
@@ -75766,7 +75766,7 @@
       <c r="N7" s="34" t="inlineStr">
         <is>
           <t>To the Emporium,
-Everyone on this stretch of coast who works nights wears a black, ridged stone on a cord, the kind that looks like a bundle of burnt matches. The lighthouse keeper has worn one for thirty years. They say it soaks up whatever is thrown at you, seen or unseen. It is the only protection I trust out there.
+Everyone on this stretch of coast who works nights wears a piece of black tourmaline on a cord. The lighthouse keeper has worn one for thirty years. They say it soaks up whatever is thrown at you, seen or unseen. It is the only protection I trust out there.
 Mine went over the side in the last storm. Could you send another?
 Officer Jory Penrose, Caldwell-on-Sea</t>
         </is>
@@ -75837,8 +75837,8 @@
       <c r="N8" s="34" t="inlineStr">
         <is>
           <t>To the Emporium,
-The vicar has asked me, against my better judgement, to write. He wants the pale sweet resin from overseas. One of our widowers burns a pinch of it every evening at the same hour, and says the house fills with calm, as it did when his wife was alive.
-The vicar himself grinds the little hot black corns over his eggs. He started the week he took up painting, at sixty-one, and says it gave him the courage to make the first stroke.
+The vicar has asked me, against my better judgement, to write. He wants copal, the pale sweet resin from overseas. One of our widowers burns a pinch of it every evening at the same hour, and says the house fills with calm, as it did when his wife was alive.
+The vicar himself grinds black pepper over his eggs. He started the week he took up painting, at sixty-one, and says it gave him the courage to make the first stroke.
 Our grocer has run out of both. I trust this stays between us.
 Mr Edgar Penhallow, Churchwarden, Thornbury</t>
         </is>
@@ -75893,7 +75893,7 @@
       <c r="N9" s="34" t="inlineStr">
         <is>
           <t>Hello from the Hollow,
-When the first green shoots show after a hard winter, my aunt used to sew a little pale green stone into a cloth bag and hang it from the oldest plum tree. She said it was for the first good week of spring, and for growth. The trees never failed her.
+When the first green shoots show after a hard winter, my aunt used to sew a peridot into a cloth bag and hang it from the oldest plum tree. She said it was for the first good week of spring, and for growth. The trees never failed her.
 The bag rotted and the stone is lost in the long grass. Do you sell them?
 Bessie Damson, Plumtree Hollow</t>
         </is>
@@ -75964,8 +75964,8 @@
       <c r="N10" s="34" t="inlineStr">
         <is>
           <t>Dear neighbour,
-Two things for the winter menu. The little shrivelled dark fruit we bake into the biscuits we give children who finish their reading charts. Such a small win, but the mothers say it is pure joy to them.
-And the dark bitter powder, whipped into the spread for our Saturday buns. Ladies come in saying they really shouldn't, and then they do. Nothing is such a comfort in January.
+Two things for the winter menu. The raisins we bake into the biscuits we give children who finish their reading charts. Such a small win, but the mothers say it is pure joy to them.
+And cocoa, whipped into the spread for our Saturday buns. Ladies come in saying they really shouldn't, and then they do. Nothing is such a comfort in January.
 Our supplier in Greywater has gone bust. Could you help?
 Mrs Ada Crumb, Crumb &amp; Co., Whitcombe</t>
         </is>
@@ -76036,8 +76036,8 @@
       <c r="N11" s="34" t="inlineStr">
         <is>
           <t>Madam,
-Two old remedies my grandfather kept. The bark of the weeping tree by the river, which every grandmother uses for a sore back. Few know the old witches sewed strips of it into their pillows for intuition, and woke with the strangest pictures still in their heads.
-And the bitter silver-grey herb he steeped in a drink every New Year's Eve, to close one chapter and start the next. For transformation, he said, and not for the faint-hearted.
+Two old remedies my grandfather kept. Willow bark, which every grandmother uses for a sore back. Few know the old witches sewed strips of it into their pillows for intuition, and woke with the strangest pictures still in their heads.
+And wormwood, which he steeped in a drink every New Year's Eve, to close one chapter and start the next. For transformation, he said, and not for the faint-hearted.
 If you have either, we would pay well.
 Silas Thistle, Thistle &amp; Sons Wandwrights, Elderhollow</t>
         </is>
@@ -76092,7 +76092,7 @@
       <c r="N12" s="34" t="inlineStr">
         <is>
           <t>To the Emporium,
-Travellers wait here for the coach, and the young ones fill the back room with their long games of dragons and dungeons. One old carter swears by a little carved wooden cube with dots on its faces that he had blessed at your shop. He says it gives him luck every time he throws it.
+Travellers wait here for the coach, and the young ones fill the back room with their long games of dragons and dungeons. One old carter swears by a little wooden die that he had blessed at your shop. He says it gives him luck every time he throws it.
 The young ones now want one each, for their games night. Do you still bless them?
 Harry Oakes, landlord, the Crossed Keys, Ashby Cross</t>
         </is>
@@ -76147,7 +76147,7 @@
       <c r="N13" s="34" t="inlineStr">
         <is>
           <t>Dear Emporium,
-Our guests come up the mountain to wait for shooting stars, and most of them can't wait for anything. Our founder tucked dried petals of the great pale water flower into a little bag under each pillow. She said the inner sight it brings is only half its use; mostly it teaches calm, and the stars come when they come.
+Our guests come up the mountain to wait for shooting stars, and most of them can't wait for anything. Our founder tucked dried lotus petals into a little bag under each pillow. She said the inner sight it brings is only half its use; mostly it teaches calm, and the stars come when they come.
 Have you any dried blooms?
 Sister Wren, the Starfall Retreat</t>
         </is>
@@ -76202,7 +76202,7 @@
       <c r="N14" s="34" t="inlineStr">
         <is>
           <t>Hello,
-My daughter can't let go of a lad who is no good for her. My mother would have braided the sharp bits clipped from her pink climbing flowers into a knotted cord and hung it by the girl's bed. She said it teaches a soft heart its boundaries.
+My daughter can't let go of a lad who is no good for her. My mother would have braided rose thorns into a knotted cord and hung it by the girl's bed. She said it teaches a soft heart its boundaries.
 I have the cord but not the thorns. Have you a jar?
 Dora Bramble, Hedge End Farm, Bramblebee</t>
         </is>
@@ -76273,8 +76273,8 @@
       <c r="N15" s="34" t="inlineStr">
         <is>
           <t>Dear shop,
-There's a girl who comes in after school who can't stop going over one silly mistake she made. Her gran used to stir the shiny pink stuff into her bath salts and say it washed in a bit of self-love.
-And the boys buy cupcakes with the little pink sugar strands on top to hand to someone they fancy, giggling all the way out. My grandmother called those love on a cake.
+There's a girl who comes in after school who can't stop going over one silly mistake she made. Her gran used to stir pink glitter into her bath salts and say it washed in a bit of self-love.
+And the boys buy cupcakes with pink sprinkles on top to hand to someone they fancy, giggling all the way out. My grandmother called those love on a cake.
 I'm out of both. I'll send fudge.
 Mrs Pennywhistle, Sugarbrook</t>
         </is>
@@ -76329,7 +76329,7 @@
       <c r="N16" s="34" t="inlineStr">
         <is>
           <t>Dear Emporium,
-Our orchard bees leave little golden grains on everything in May. The old orchard keepers beat them into butter for the fair loaves, and said whoever shares that bread with old friends shares the friendship of the hive.
+Our orchard bees leave bee pollen on everything in May. The old orchard keepers beat it into butter for the fair loaves, and said whoever shares that bread with old friends shares the friendship of the hive.
 Our hives had a bad year. Could you send a jar for the fair?
 Rhoda Bell, Cider Fair Committee, Pippin Green</t>
         </is>
@@ -76384,7 +76384,7 @@
       <c r="N17" s="34" t="inlineStr">
         <is>
           <t>Dear neighbour,
-A house clearance turned up a box of buttons, and among them one odd square one that must be a lost counter from some old board game. I left it on the counter, and the grandchildren wanted to play all afternoon. The little one swears he won every game while it sat by the board.
+A house clearance turned up a box of buttons, and among them one odd square button that must be a lost counter from some old board game. I left it on the counter, and the grandchildren wanted to play all afternoon. The little one swears he won every game while it sat by the board.
 I'll hold it for you. Come by.
 Mr Ambrose Tuck, Old Things, Buttonwick</t>
         </is>
@@ -76439,7 +76439,7 @@
       <c r="N18" s="34" t="inlineStr">
         <is>
           <t>To the Emporium,
-My mum and dad were married fifty-two years. Dad kept a corked bottle of sweet red wood shavings on the mantel, and scattered more in the drawers, until the whole mill house smelled like home. He said it kept them fond of each other through every winter.
+My mum and dad were married fifty-two years. Dad kept a corked bottle of cedar chips on the mantel, and scattered more in the drawers, until the whole mill house smelled like home. He said it kept them fond of each other through every winter.
 My wife and I could use some. Could you send a bag?
 Sam Wend, Wend Mill, Greywater</t>
         </is>

--- a/ingredient_asset_tracker.xlsx
+++ b/ingredient_asset_tracker.xlsx
@@ -75396,7 +75396,7 @@
       </c>
       <c r="B2" s="34" t="inlineStr">
         <is>
-          <t>Noon</t>
+          <t>Sunrise</t>
         </is>
       </c>
       <c r="C2" s="34" t="inlineStr">

--- a/ingredient_asset_tracker.xlsx
+++ b/ingredient_asset_tracker.xlsx
@@ -31,7 +31,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Walk-in Plan'!$A$1:$P$150</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Candles'!$A$1:$E$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Tarot'!$A$1:$E$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Condition Icons'!$A$1:$E$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Condition Icons'!$A$1:$E$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Spell Products'!$A$1:$E$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Altar, Tools &amp; Books'!$A$1:$E$33</definedName>
   </definedNames>
@@ -1921,7 +1921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="17" min="1" max="1"/>
@@ -1961,17 +1961,17 @@
     <row r="2" ht="15" customHeight="1" s="18">
       <c r="A2" s="27" t="inlineStr">
         <is>
-          <t>Dark Moon</t>
+          <t>Full Moon</t>
         </is>
       </c>
       <c r="B2" s="27" t="inlineStr">
         <is>
-          <t>Moon phase</t>
+          <t xml:space="preserve">Full moon</t>
         </is>
       </c>
       <c r="C2" s="27" t="inlineStr">
         <is>
-          <t>icon_moon_dark_moon.png</t>
+          <t>icon_moon_full_moon.png</t>
         </is>
       </c>
       <c r="D2" s="28" t="inlineStr">
@@ -1984,17 +1984,17 @@
     <row r="3" ht="15" customHeight="1" s="18">
       <c r="A3" s="27" t="inlineStr">
         <is>
-          <t>New Moon</t>
+          <t>Wolf Moon</t>
         </is>
       </c>
       <c r="B3" s="27" t="inlineStr">
         <is>
-          <t>Moon phase</t>
+          <t>Named moon</t>
         </is>
       </c>
       <c r="C3" s="27" t="inlineStr">
         <is>
-          <t>icon_moon_new_moon.png</t>
+          <t>icon_named_wolf_moon.png</t>
         </is>
       </c>
       <c r="D3" s="28" t="inlineStr">
@@ -2007,17 +2007,17 @@
     <row r="4" ht="15" customHeight="1" s="18">
       <c r="A4" s="27" t="inlineStr">
         <is>
-          <t>Waxing Crescent</t>
+          <t>Snow Moon</t>
         </is>
       </c>
       <c r="B4" s="27" t="inlineStr">
         <is>
-          <t>Moon phase</t>
+          <t>Named moon</t>
         </is>
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>icon_moon_waxing_crescent.png</t>
+          <t>icon_named_snow_moon.png</t>
         </is>
       </c>
       <c r="D4" s="28" t="inlineStr">
@@ -2030,17 +2030,17 @@
     <row r="5" ht="15" customHeight="1" s="18">
       <c r="A5" s="27" t="inlineStr">
         <is>
-          <t>First Quarter</t>
+          <t>Worm Moon</t>
         </is>
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>Moon phase</t>
+          <t>Named moon</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>icon_moon_first_quarter.png</t>
+          <t>icon_named_worm_moon.png</t>
         </is>
       </c>
       <c r="D5" s="28" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="6" ht="15" customHeight="1" s="18">
       <c r="A6" s="27" t="inlineStr">
         <is>
-          <t>Waxing Gibbous</t>
+          <t>Pink Moon</t>
         </is>
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>Moon phase</t>
+          <t>Named moon</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>icon_moon_waxing_gibbous.png</t>
+          <t>icon_named_pink_moon.png</t>
         </is>
       </c>
       <c r="D6" s="28" t="inlineStr">
@@ -2076,17 +2076,17 @@
     <row r="7" ht="15" customHeight="1" s="18">
       <c r="A7" s="27" t="inlineStr">
         <is>
-          <t>Full Moon</t>
+          <t>Flower Moon</t>
         </is>
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>Moon phase</t>
+          <t>Named moon</t>
         </is>
       </c>
       <c r="C7" s="27" t="inlineStr">
         <is>
-          <t>icon_moon_full_moon.png</t>
+          <t>icon_named_flower_moon.png</t>
         </is>
       </c>
       <c r="D7" s="28" t="inlineStr">
@@ -2099,17 +2099,17 @@
     <row r="8" ht="15" customHeight="1" s="18">
       <c r="A8" s="27" t="inlineStr">
         <is>
-          <t>Waning Gibbous</t>
+          <t>Strawberry Moon</t>
         </is>
       </c>
       <c r="B8" s="27" t="inlineStr">
         <is>
-          <t>Moon phase</t>
+          <t>Named moon</t>
         </is>
       </c>
       <c r="C8" s="27" t="inlineStr">
         <is>
-          <t>icon_moon_waning_gibbous.png</t>
+          <t>icon_named_strawberry_moon.png</t>
         </is>
       </c>
       <c r="D8" s="28" t="inlineStr">
@@ -2122,17 +2122,17 @@
     <row r="9" ht="15" customHeight="1" s="18">
       <c r="A9" s="27" t="inlineStr">
         <is>
-          <t>Last Quarter</t>
+          <t>Buck Moon</t>
         </is>
       </c>
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>Moon phase</t>
+          <t>Named moon</t>
         </is>
       </c>
       <c r="C9" s="27" t="inlineStr">
         <is>
-          <t>icon_moon_last_quarter.png</t>
+          <t>icon_named_buck_moon.png</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
@@ -2145,17 +2145,17 @@
     <row r="10" ht="15" customHeight="1" s="18">
       <c r="A10" s="27" t="inlineStr">
         <is>
-          <t>Waning Crescent</t>
+          <t>Sturgeon Moon</t>
         </is>
       </c>
       <c r="B10" s="27" t="inlineStr">
         <is>
-          <t>Moon phase</t>
+          <t>Named moon</t>
         </is>
       </c>
       <c r="C10" s="27" t="inlineStr">
         <is>
-          <t>icon_moon_waning_crescent.png</t>
+          <t>icon_named_sturgeon_moon.png</t>
         </is>
       </c>
       <c r="D10" s="28" t="inlineStr">
@@ -2168,7 +2168,7 @@
     <row r="11" ht="15" customHeight="1" s="18">
       <c r="A11" s="27" t="inlineStr">
         <is>
-          <t>Wolf Moon</t>
+          <t>Harvest Moon</t>
         </is>
       </c>
       <c r="B11" s="27" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="C11" s="27" t="inlineStr">
         <is>
-          <t>icon_named_wolf_moon.png</t>
+          <t>icon_named_harvest_moon.png</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
@@ -2191,7 +2191,7 @@
     <row r="12" ht="15" customHeight="1" s="18">
       <c r="A12" s="27" t="inlineStr">
         <is>
-          <t>Snow Moon</t>
+          <t>Hunter's Moon</t>
         </is>
       </c>
       <c r="B12" s="27" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="C12" s="27" t="inlineStr">
         <is>
-          <t>icon_named_snow_moon.png</t>
+          <t>icon_named_hunter_s_moon.png</t>
         </is>
       </c>
       <c r="D12" s="28" t="inlineStr">
@@ -2214,7 +2214,7 @@
     <row r="13" ht="15" customHeight="1" s="18">
       <c r="A13" s="27" t="inlineStr">
         <is>
-          <t>Worm Moon</t>
+          <t>Beaver Moon</t>
         </is>
       </c>
       <c r="B13" s="27" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="C13" s="27" t="inlineStr">
         <is>
-          <t>icon_named_worm_moon.png</t>
+          <t>icon_named_beaver_moon.png</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
@@ -2237,7 +2237,7 @@
     <row r="14" ht="15" customHeight="1" s="18">
       <c r="A14" s="27" t="inlineStr">
         <is>
-          <t>Pink Moon</t>
+          <t>Cold Moon</t>
         </is>
       </c>
       <c r="B14" s="27" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="C14" s="27" t="inlineStr">
         <is>
-          <t>icon_named_pink_moon.png</t>
+          <t>icon_named_cold_moon.png</t>
         </is>
       </c>
       <c r="D14" s="28" t="inlineStr">
@@ -2257,10 +2257,10 @@
       </c>
       <c r="E14" s="27" t="n"/>
     </row>
-    <row r="15" ht="15" customHeight="1" s="18">
+    <row r="15" ht="23.25" customHeight="1" s="18">
       <c r="A15" s="27" t="inlineStr">
         <is>
-          <t>Flower Moon</t>
+          <t>Blue Moon (special event, replaces the Sturgeon Moon on Day 79)</t>
         </is>
       </c>
       <c r="B15" s="27" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="C15" s="27" t="inlineStr">
         <is>
-          <t>icon_named_flower_moon.png</t>
+          <t>icon_named_blue_moon_special_event_replaces_the_sturgeon_moon_on_day_79.png</t>
         </is>
       </c>
       <c r="D15" s="28" t="inlineStr">
@@ -2283,7 +2283,7 @@
     <row r="16" ht="15" customHeight="1" s="18">
       <c r="A16" s="27" t="inlineStr">
         <is>
-          <t>Strawberry Moon</t>
+          <t>Lunar Eclipse (event, Day 31)</t>
         </is>
       </c>
       <c r="B16" s="27" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="C16" s="27" t="inlineStr">
         <is>
-          <t>icon_named_strawberry_moon.png</t>
+          <t>icon_named_lunar_eclipse_event_day_31.png</t>
         </is>
       </c>
       <c r="D16" s="28" t="inlineStr">
@@ -2306,17 +2306,17 @@
     <row r="17" ht="15" customHeight="1" s="18">
       <c r="A17" s="27" t="inlineStr">
         <is>
-          <t>Buck Moon</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="B17" s="27" t="inlineStr">
         <is>
-          <t>Named moon</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="C17" s="27" t="inlineStr">
         <is>
-          <t>icon_named_buck_moon.png</t>
+          <t>icon_day_monday.png</t>
         </is>
       </c>
       <c r="D17" s="28" t="inlineStr">
@@ -2329,17 +2329,17 @@
     <row r="18" ht="15" customHeight="1" s="18">
       <c r="A18" s="27" t="inlineStr">
         <is>
-          <t>Sturgeon Moon</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B18" s="27" t="inlineStr">
         <is>
-          <t>Named moon</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="C18" s="27" t="inlineStr">
         <is>
-          <t>icon_named_sturgeon_moon.png</t>
+          <t>icon_day_tuesday.png</t>
         </is>
       </c>
       <c r="D18" s="28" t="inlineStr">
@@ -2352,17 +2352,17 @@
     <row r="19" ht="15" customHeight="1" s="18">
       <c r="A19" s="27" t="inlineStr">
         <is>
-          <t>Harvest Moon</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B19" s="27" t="inlineStr">
         <is>
-          <t>Named moon</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="C19" s="27" t="inlineStr">
         <is>
-          <t>icon_named_harvest_moon.png</t>
+          <t>icon_day_wednesday.png</t>
         </is>
       </c>
       <c r="D19" s="28" t="inlineStr">
@@ -2375,17 +2375,17 @@
     <row r="20" ht="15" customHeight="1" s="18">
       <c r="A20" s="27" t="inlineStr">
         <is>
-          <t>Hunter's Moon</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B20" s="27" t="inlineStr">
         <is>
-          <t>Named moon</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="C20" s="27" t="inlineStr">
         <is>
-          <t>icon_named_hunter_s_moon.png</t>
+          <t>icon_day_thursday.png</t>
         </is>
       </c>
       <c r="D20" s="28" t="inlineStr">
@@ -2398,17 +2398,17 @@
     <row r="21" ht="15" customHeight="1" s="18">
       <c r="A21" s="27" t="inlineStr">
         <is>
-          <t>Beaver Moon</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B21" s="27" t="inlineStr">
         <is>
-          <t>Named moon</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="C21" s="27" t="inlineStr">
         <is>
-          <t>icon_named_beaver_moon.png</t>
+          <t>icon_day_friday.png</t>
         </is>
       </c>
       <c r="D21" s="28" t="inlineStr">
@@ -2421,17 +2421,17 @@
     <row r="22" ht="15" customHeight="1" s="18">
       <c r="A22" s="27" t="inlineStr">
         <is>
-          <t>Cold Moon</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B22" s="27" t="inlineStr">
         <is>
-          <t>Named moon</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="C22" s="27" t="inlineStr">
         <is>
-          <t>icon_named_cold_moon.png</t>
+          <t>icon_day_saturday.png</t>
         </is>
       </c>
       <c r="D22" s="28" t="inlineStr">
@@ -2441,20 +2441,20 @@
       </c>
       <c r="E22" s="27" t="n"/>
     </row>
-    <row r="23" ht="23.25" customHeight="1" s="18">
+    <row r="23" ht="15" customHeight="1" s="18">
       <c r="A23" s="27" t="inlineStr">
         <is>
-          <t>Blue Moon (special event, replaces the Sturgeon Moon on Day 79)</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B23" s="27" t="inlineStr">
         <is>
-          <t>Named moon</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="C23" s="27" t="inlineStr">
         <is>
-          <t>icon_named_blue_moon_special_event_replaces_the_sturgeon_moon_on_day_79.png</t>
+          <t>icon_day_sunday.png</t>
         </is>
       </c>
       <c r="D23" s="28" t="inlineStr">
@@ -2467,17 +2467,17 @@
     <row r="24" ht="15" customHeight="1" s="18">
       <c r="A24" s="27" t="inlineStr">
         <is>
-          <t>Lunar Eclipse (event, Day 31)</t>
+          <t>Sunrise</t>
         </is>
       </c>
       <c r="B24" s="27" t="inlineStr">
         <is>
-          <t>Named moon</t>
+          <t>Time of day</t>
         </is>
       </c>
       <c r="C24" s="27" t="inlineStr">
         <is>
-          <t>icon_named_lunar_eclipse_event_day_31.png</t>
+          <t>icon_time_sunrise.png</t>
         </is>
       </c>
       <c r="D24" s="28" t="inlineStr">
@@ -2490,17 +2490,17 @@
     <row r="25" ht="15" customHeight="1" s="18">
       <c r="A25" s="27" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Noon</t>
         </is>
       </c>
       <c r="B25" s="27" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Time of day</t>
         </is>
       </c>
       <c r="C25" s="27" t="inlineStr">
         <is>
-          <t>icon_day_monday.png</t>
+          <t>icon_time_noon.png</t>
         </is>
       </c>
       <c r="D25" s="28" t="inlineStr">
@@ -2513,17 +2513,17 @@
     <row r="26" ht="15" customHeight="1" s="18">
       <c r="A26" s="27" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Twilight</t>
         </is>
       </c>
       <c r="B26" s="27" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Time of day</t>
         </is>
       </c>
       <c r="C26" s="27" t="inlineStr">
         <is>
-          <t>icon_day_tuesday.png</t>
+          <t>icon_time_twilight.png</t>
         </is>
       </c>
       <c r="D26" s="28" t="inlineStr">
@@ -2536,17 +2536,17 @@
     <row r="27" ht="15" customHeight="1" s="18">
       <c r="A27" s="27" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Nightfall</t>
         </is>
       </c>
       <c r="B27" s="27" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Time of day</t>
         </is>
       </c>
       <c r="C27" s="27" t="inlineStr">
         <is>
-          <t>icon_day_wednesday.png</t>
+          <t>icon_time_nightfall.png</t>
         </is>
       </c>
       <c r="D27" s="28" t="inlineStr">
@@ -2559,17 +2559,17 @@
     <row r="28" ht="15" customHeight="1" s="18">
       <c r="A28" s="27" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Clear starry night</t>
         </is>
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t xml:space="preserve">Sky event</t>
         </is>
       </c>
       <c r="C28" s="27" t="inlineStr">
         <is>
-          <t>icon_day_thursday.png</t>
+          <t>icon_weather_clear_starry_night.png</t>
         </is>
       </c>
       <c r="D28" s="28" t="inlineStr">
@@ -2582,17 +2582,17 @@
     <row r="29" ht="15" customHeight="1" s="18">
       <c r="A29" s="27" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Rainbow (rare event)</t>
         </is>
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t xml:space="preserve">Sky event</t>
         </is>
       </c>
       <c r="C29" s="27" t="inlineStr">
         <is>
-          <t>icon_day_friday.png</t>
+          <t>icon_weather_rainbow_rare_event.png</t>
         </is>
       </c>
       <c r="D29" s="28" t="inlineStr">
@@ -2605,17 +2605,17 @@
     <row r="30" ht="15" customHeight="1" s="18">
       <c r="A30" s="27" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Shooting star (rare event)</t>
         </is>
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t xml:space="preserve">Sky event</t>
         </is>
       </c>
       <c r="C30" s="27" t="inlineStr">
         <is>
-          <t>icon_day_saturday.png</t>
+          <t>icon_weather_shooting_star_rare_event.png</t>
         </is>
       </c>
       <c r="D30" s="28" t="inlineStr">
@@ -2628,17 +2628,17 @@
     <row r="31" ht="15" customHeight="1" s="18">
       <c r="A31" s="27" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Samhain</t>
         </is>
       </c>
       <c r="B31" s="27" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Sabbat</t>
         </is>
       </c>
       <c r="C31" s="27" t="inlineStr">
         <is>
-          <t>icon_day_sunday.png</t>
+          <t>icon_sabbat_samhain.png</t>
         </is>
       </c>
       <c r="D31" s="28" t="inlineStr">
@@ -2651,17 +2651,17 @@
     <row r="32" ht="15" customHeight="1" s="18">
       <c r="A32" s="27" t="inlineStr">
         <is>
-          <t>Sunrise</t>
+          <t>Yule</t>
         </is>
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>Time of day</t>
+          <t>Sabbat</t>
         </is>
       </c>
       <c r="C32" s="27" t="inlineStr">
         <is>
-          <t>icon_time_sunrise.png</t>
+          <t>icon_sabbat_yule.png</t>
         </is>
       </c>
       <c r="D32" s="28" t="inlineStr">
@@ -2674,17 +2674,17 @@
     <row r="33" ht="15" customHeight="1" s="18">
       <c r="A33" s="27" t="inlineStr">
         <is>
-          <t>Noon</t>
+          <t>Imbolc</t>
         </is>
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>Time of day</t>
+          <t>Sabbat</t>
         </is>
       </c>
       <c r="C33" s="27" t="inlineStr">
         <is>
-          <t>icon_time_noon.png</t>
+          <t>icon_sabbat_imbolc.png</t>
         </is>
       </c>
       <c r="D33" s="28" t="inlineStr">
@@ -2697,17 +2697,17 @@
     <row r="34" ht="15" customHeight="1" s="18">
       <c r="A34" s="27" t="inlineStr">
         <is>
-          <t>Twilight</t>
+          <t>Ostara</t>
         </is>
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>Time of day</t>
+          <t>Sabbat</t>
         </is>
       </c>
       <c r="C34" s="27" t="inlineStr">
         <is>
-          <t>icon_time_twilight.png</t>
+          <t>icon_sabbat_ostara.png</t>
         </is>
       </c>
       <c r="D34" s="28" t="inlineStr">
@@ -2720,17 +2720,17 @@
     <row r="35" ht="15" customHeight="1" s="18">
       <c r="A35" s="27" t="inlineStr">
         <is>
-          <t>Nightfall</t>
+          <t>Beltane</t>
         </is>
       </c>
       <c r="B35" s="27" t="inlineStr">
         <is>
-          <t>Time of day</t>
+          <t>Sabbat</t>
         </is>
       </c>
       <c r="C35" s="27" t="inlineStr">
         <is>
-          <t>icon_time_nightfall.png</t>
+          <t>icon_sabbat_beltane.png</t>
         </is>
       </c>
       <c r="D35" s="28" t="inlineStr">
@@ -2743,17 +2743,17 @@
     <row r="36" ht="15" customHeight="1" s="18">
       <c r="A36" s="27" t="inlineStr">
         <is>
-          <t>Clear &amp; sunny</t>
+          <t>Litha</t>
         </is>
       </c>
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>Weather</t>
+          <t>Sabbat</t>
         </is>
       </c>
       <c r="C36" s="27" t="inlineStr">
         <is>
-          <t>icon_weather_clear_sunny.png</t>
+          <t>icon_sabbat_litha.png</t>
         </is>
       </c>
       <c r="D36" s="28" t="inlineStr">
@@ -2766,17 +2766,17 @@
     <row r="37" ht="15" customHeight="1" s="18">
       <c r="A37" s="27" t="inlineStr">
         <is>
-          <t>Cloudy</t>
+          <t>Lughnasadh</t>
         </is>
       </c>
       <c r="B37" s="27" t="inlineStr">
         <is>
-          <t>Weather</t>
+          <t>Sabbat</t>
         </is>
       </c>
       <c r="C37" s="27" t="inlineStr">
         <is>
-          <t>icon_weather_cloudy.png</t>
+          <t>icon_sabbat_lughnasadh.png</t>
         </is>
       </c>
       <c r="D37" s="28" t="inlineStr">
@@ -2789,17 +2789,17 @@
     <row r="38" ht="15" customHeight="1" s="18">
       <c r="A38" s="27" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Mabon</t>
         </is>
       </c>
       <c r="B38" s="27" t="inlineStr">
         <is>
-          <t>Weather</t>
+          <t>Sabbat</t>
         </is>
       </c>
       <c r="C38" s="27" t="inlineStr">
         <is>
-          <t>icon_weather_rain.png</t>
+          <t>icon_sabbat_mabon.png</t>
         </is>
       </c>
       <c r="D38" s="28" t="inlineStr">
@@ -2809,355 +2809,10 @@
       </c>
       <c r="E38" s="27" t="n"/>
     </row>
-    <row r="39" ht="15" customHeight="1" s="18">
-      <c r="A39" s="27" t="inlineStr">
-        <is>
-          <t>Thunderstorm</t>
-        </is>
-      </c>
-      <c r="B39" s="27" t="inlineStr">
-        <is>
-          <t>Weather</t>
-        </is>
-      </c>
-      <c r="C39" s="27" t="inlineStr">
-        <is>
-          <t>icon_weather_thunderstorm.png</t>
-        </is>
-      </c>
-      <c r="D39" s="28" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-      <c r="E39" s="27" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="18">
-      <c r="A40" s="27" t="inlineStr">
-        <is>
-          <t>Fog / Mist</t>
-        </is>
-      </c>
-      <c r="B40" s="27" t="inlineStr">
-        <is>
-          <t>Weather</t>
-        </is>
-      </c>
-      <c r="C40" s="27" t="inlineStr">
-        <is>
-          <t>icon_weather_fog_mist.png</t>
-        </is>
-      </c>
-      <c r="D40" s="28" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-      <c r="E40" s="27" t="n"/>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="18">
-      <c r="A41" s="27" t="inlineStr">
-        <is>
-          <t>Windy</t>
-        </is>
-      </c>
-      <c r="B41" s="27" t="inlineStr">
-        <is>
-          <t>Weather</t>
-        </is>
-      </c>
-      <c r="C41" s="27" t="inlineStr">
-        <is>
-          <t>icon_weather_windy.png</t>
-        </is>
-      </c>
-      <c r="D41" s="28" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-      <c r="E41" s="27" t="n"/>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="18">
-      <c r="A42" s="27" t="inlineStr">
-        <is>
-          <t>Snow</t>
-        </is>
-      </c>
-      <c r="B42" s="27" t="inlineStr">
-        <is>
-          <t>Weather</t>
-        </is>
-      </c>
-      <c r="C42" s="27" t="inlineStr">
-        <is>
-          <t>icon_weather_snow.png</t>
-        </is>
-      </c>
-      <c r="D42" s="28" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-      <c r="E42" s="27" t="n"/>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="18">
-      <c r="A43" s="27" t="inlineStr">
-        <is>
-          <t>Clear starry night</t>
-        </is>
-      </c>
-      <c r="B43" s="27" t="inlineStr">
-        <is>
-          <t>Weather</t>
-        </is>
-      </c>
-      <c r="C43" s="27" t="inlineStr">
-        <is>
-          <t>icon_weather_clear_starry_night.png</t>
-        </is>
-      </c>
-      <c r="D43" s="28" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-      <c r="E43" s="27" t="n"/>
-    </row>
-    <row r="44" ht="15" customHeight="1" s="18">
-      <c r="A44" s="27" t="inlineStr">
-        <is>
-          <t>Rainbow (rare event)</t>
-        </is>
-      </c>
-      <c r="B44" s="27" t="inlineStr">
-        <is>
-          <t>Weather</t>
-        </is>
-      </c>
-      <c r="C44" s="27" t="inlineStr">
-        <is>
-          <t>icon_weather_rainbow_rare_event.png</t>
-        </is>
-      </c>
-      <c r="D44" s="28" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-      <c r="E44" s="27" t="n"/>
-    </row>
-    <row r="45" ht="15" customHeight="1" s="18">
-      <c r="A45" s="27" t="inlineStr">
-        <is>
-          <t>Shooting star (rare event)</t>
-        </is>
-      </c>
-      <c r="B45" s="27" t="inlineStr">
-        <is>
-          <t>Weather</t>
-        </is>
-      </c>
-      <c r="C45" s="27" t="inlineStr">
-        <is>
-          <t>icon_weather_shooting_star_rare_event.png</t>
-        </is>
-      </c>
-      <c r="D45" s="28" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-      <c r="E45" s="27" t="n"/>
-    </row>
-    <row r="46" ht="15" customHeight="1" s="18">
-      <c r="A46" s="27" t="inlineStr">
-        <is>
-          <t>Samhain</t>
-        </is>
-      </c>
-      <c r="B46" s="27" t="inlineStr">
-        <is>
-          <t>Sabbat</t>
-        </is>
-      </c>
-      <c r="C46" s="27" t="inlineStr">
-        <is>
-          <t>icon_sabbat_samhain.png</t>
-        </is>
-      </c>
-      <c r="D46" s="28" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-      <c r="E46" s="27" t="n"/>
-    </row>
-    <row r="47" ht="15" customHeight="1" s="18">
-      <c r="A47" s="27" t="inlineStr">
-        <is>
-          <t>Yule</t>
-        </is>
-      </c>
-      <c r="B47" s="27" t="inlineStr">
-        <is>
-          <t>Sabbat</t>
-        </is>
-      </c>
-      <c r="C47" s="27" t="inlineStr">
-        <is>
-          <t>icon_sabbat_yule.png</t>
-        </is>
-      </c>
-      <c r="D47" s="28" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-      <c r="E47" s="27" t="n"/>
-    </row>
-    <row r="48" ht="15" customHeight="1" s="18">
-      <c r="A48" s="27" t="inlineStr">
-        <is>
-          <t>Imbolc</t>
-        </is>
-      </c>
-      <c r="B48" s="27" t="inlineStr">
-        <is>
-          <t>Sabbat</t>
-        </is>
-      </c>
-      <c r="C48" s="27" t="inlineStr">
-        <is>
-          <t>icon_sabbat_imbolc.png</t>
-        </is>
-      </c>
-      <c r="D48" s="28" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-      <c r="E48" s="27" t="n"/>
-    </row>
-    <row r="49" ht="15" customHeight="1" s="18">
-      <c r="A49" s="27" t="inlineStr">
-        <is>
-          <t>Ostara</t>
-        </is>
-      </c>
-      <c r="B49" s="27" t="inlineStr">
-        <is>
-          <t>Sabbat</t>
-        </is>
-      </c>
-      <c r="C49" s="27" t="inlineStr">
-        <is>
-          <t>icon_sabbat_ostara.png</t>
-        </is>
-      </c>
-      <c r="D49" s="28" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-      <c r="E49" s="27" t="n"/>
-    </row>
-    <row r="50" ht="15" customHeight="1" s="18">
-      <c r="A50" s="27" t="inlineStr">
-        <is>
-          <t>Beltane</t>
-        </is>
-      </c>
-      <c r="B50" s="27" t="inlineStr">
-        <is>
-          <t>Sabbat</t>
-        </is>
-      </c>
-      <c r="C50" s="27" t="inlineStr">
-        <is>
-          <t>icon_sabbat_beltane.png</t>
-        </is>
-      </c>
-      <c r="D50" s="28" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-      <c r="E50" s="27" t="n"/>
-    </row>
-    <row r="51" ht="15" customHeight="1" s="18">
-      <c r="A51" s="27" t="inlineStr">
-        <is>
-          <t>Litha</t>
-        </is>
-      </c>
-      <c r="B51" s="27" t="inlineStr">
-        <is>
-          <t>Sabbat</t>
-        </is>
-      </c>
-      <c r="C51" s="27" t="inlineStr">
-        <is>
-          <t>icon_sabbat_litha.png</t>
-        </is>
-      </c>
-      <c r="D51" s="28" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-      <c r="E51" s="27" t="n"/>
-    </row>
-    <row r="52" ht="15" customHeight="1" s="18">
-      <c r="A52" s="27" t="inlineStr">
-        <is>
-          <t>Lughnasadh</t>
-        </is>
-      </c>
-      <c r="B52" s="27" t="inlineStr">
-        <is>
-          <t>Sabbat</t>
-        </is>
-      </c>
-      <c r="C52" s="27" t="inlineStr">
-        <is>
-          <t>icon_sabbat_lughnasadh.png</t>
-        </is>
-      </c>
-      <c r="D52" s="28" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-      <c r="E52" s="27" t="n"/>
-    </row>
-    <row r="53" ht="15" customHeight="1" s="18">
-      <c r="A53" s="27" t="inlineStr">
-        <is>
-          <t>Mabon</t>
-        </is>
-      </c>
-      <c r="B53" s="27" t="inlineStr">
-        <is>
-          <t>Sabbat</t>
-        </is>
-      </c>
-      <c r="C53" s="27" t="inlineStr">
-        <is>
-          <t>icon_sabbat_mabon.png</t>
-        </is>
-      </c>
-      <c r="D53" s="28" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-      <c r="E53" s="27" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E53"/>
+  <autoFilter ref="A1:E38"/>
   <dataValidations count="1">
-    <dataValidation sqref="D2:D53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="D2:D38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"To do,Sketch,In progress,Done"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -32664,7 +32319,7 @@
       </c>
       <c r="G3" s="22" t="inlineStr">
         <is>
-          <t>Friday · Waxing Crescent</t>
+          <t xml:space="preserve">Friday</t>
         </is>
       </c>
     </row>
@@ -32839,7 +32494,7 @@
       </c>
       <c r="G8" s="22" t="inlineStr">
         <is>
-          <t>Friday · Waxing Crescent</t>
+          <t xml:space="preserve">Friday</t>
         </is>
       </c>
     </row>
@@ -32909,7 +32564,7 @@
       </c>
       <c r="G10" s="22" t="inlineStr">
         <is>
-          <t>Saturday · Waning Moon · Twilight</t>
+          <t xml:space="preserve">Saturday · Twilight</t>
         </is>
       </c>
     </row>
@@ -32944,7 +32599,7 @@
       </c>
       <c r="G11" s="22" t="inlineStr">
         <is>
-          <t>Rain · Waning Gibbous</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
     </row>
@@ -33224,7 +32879,7 @@
       </c>
       <c r="G19" s="22" t="inlineStr">
         <is>
-          <t>Saturday · Dark Moon · Nightfall</t>
+          <t xml:space="preserve">Saturday · Nightfall</t>
         </is>
       </c>
     </row>
@@ -33364,7 +33019,7 @@
       </c>
       <c r="G23" s="22" t="inlineStr">
         <is>
-          <t>Waning Moon · Rain</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
     </row>
@@ -33434,7 +33089,7 @@
       </c>
       <c r="G25" s="22" t="inlineStr">
         <is>
-          <t>Saturday · after Rain</t>
+          <t xml:space="preserve">Saturday</t>
         </is>
       </c>
     </row>
@@ -33574,7 +33229,7 @@
       </c>
       <c r="G29" s="22" t="inlineStr">
         <is>
-          <t>Sunrise · New Moon</t>
+          <t xml:space="preserve">Sunrise</t>
         </is>
       </c>
     </row>
@@ -33714,7 +33369,7 @@
       </c>
       <c r="G33" s="22" t="inlineStr">
         <is>
-          <t>Thursday · Waxing Gibbous · Noon</t>
+          <t xml:space="preserve">Thursday · Noon</t>
         </is>
       </c>
     </row>
@@ -33819,7 +33474,7 @@
       </c>
       <c r="G36" s="22" t="inlineStr">
         <is>
-          <t>Thursday · Waxing Gibbous</t>
+          <t xml:space="preserve">Thursday</t>
         </is>
       </c>
     </row>
@@ -33889,7 +33544,7 @@
       </c>
       <c r="G38" s="22" t="inlineStr">
         <is>
-          <t>Thursday · Waxing Moon</t>
+          <t xml:space="preserve">Thursday</t>
         </is>
       </c>
     </row>
@@ -33959,7 +33614,7 @@
       </c>
       <c r="G40" s="22" t="inlineStr">
         <is>
-          <t>Windy</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
     </row>
@@ -34029,7 +33684,7 @@
       </c>
       <c r="G42" s="22" t="inlineStr">
         <is>
-          <t>Sunday · Noon · Clear &amp; sunny</t>
+          <t xml:space="preserve">Sunday · Noon</t>
         </is>
       </c>
     </row>
@@ -34274,7 +33929,7 @@
       </c>
       <c r="G49" s="22" t="inlineStr">
         <is>
-          <t>Friday · Waxing Crescent · Noon</t>
+          <t xml:space="preserve">Friday · Noon</t>
         </is>
       </c>
     </row>
@@ -34344,7 +33999,7 @@
       </c>
       <c r="G51" s="22" t="inlineStr">
         <is>
-          <t>Tuesday · Waxing Moon</t>
+          <t xml:space="preserve">Tuesday</t>
         </is>
       </c>
     </row>
@@ -34414,7 +34069,7 @@
       </c>
       <c r="G53" s="22" t="inlineStr">
         <is>
-          <t>Monday · Snow</t>
+          <t xml:space="preserve">Monday</t>
         </is>
       </c>
     </row>
@@ -34484,7 +34139,7 @@
       </c>
       <c r="G55" s="22" t="inlineStr">
         <is>
-          <t>Monday · Waning Moon · Twilight</t>
+          <t xml:space="preserve">Monday · Twilight</t>
         </is>
       </c>
     </row>
@@ -34659,7 +34314,7 @@
       </c>
       <c r="G60" s="22" t="inlineStr">
         <is>
-          <t>Friday · Dark Moon · Nightfall</t>
+          <t xml:space="preserve">Friday · Nightfall</t>
         </is>
       </c>
     </row>
@@ -34904,7 +34559,7 @@
       </c>
       <c r="G67" s="22" t="inlineStr">
         <is>
-          <t>after Rain</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
     </row>
@@ -35044,7 +34699,7 @@
       </c>
       <c r="G71" s="22" t="inlineStr">
         <is>
-          <t>Saturday · Waning Moon</t>
+          <t xml:space="preserve">Saturday</t>
         </is>
       </c>
     </row>
@@ -35114,7 +34769,7 @@
       </c>
       <c r="G73" s="22" t="inlineStr">
         <is>
-          <t>Friday · Clear &amp; sunny</t>
+          <t xml:space="preserve">Friday</t>
         </is>
       </c>
     </row>
@@ -35149,7 +34804,7 @@
       </c>
       <c r="G74" s="22" t="inlineStr">
         <is>
-          <t>Saturday · Waning Moon</t>
+          <t xml:space="preserve">Saturday</t>
         </is>
       </c>
     </row>
@@ -35184,7 +34839,7 @@
       </c>
       <c r="G75" s="22" t="inlineStr">
         <is>
-          <t>Monday · New Moon</t>
+          <t xml:space="preserve">Monday</t>
         </is>
       </c>
     </row>
@@ -35254,7 +34909,7 @@
       </c>
       <c r="G77" s="22" t="inlineStr">
         <is>
-          <t>Waxing Crescent</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
     </row>
@@ -35289,7 +34944,7 @@
       </c>
       <c r="G78" s="22" t="inlineStr">
         <is>
-          <t>Thunderstorm</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
     </row>
@@ -35359,7 +35014,7 @@
       </c>
       <c r="G80" s="22" t="inlineStr">
         <is>
-          <t>New Moon · Nightfall</t>
+          <t xml:space="preserve">Nightfall</t>
         </is>
       </c>
     </row>
@@ -35464,7 +35119,7 @@
       </c>
       <c r="G83" s="22" t="inlineStr">
         <is>
-          <t>Wednesday · Noon · Clear &amp; sunny</t>
+          <t xml:space="preserve">Wednesday · Noon</t>
         </is>
       </c>
     </row>
@@ -35639,7 +35294,7 @@
       </c>
       <c r="G88" s="22" t="inlineStr">
         <is>
-          <t>New Moon · Sunrise</t>
+          <t xml:space="preserve">Sunrise</t>
         </is>
       </c>
     </row>
@@ -35709,7 +35364,7 @@
       </c>
       <c r="G90" s="22" t="inlineStr">
         <is>
-          <t>Saturday · Waning Moon</t>
+          <t xml:space="preserve">Saturday</t>
         </is>
       </c>
     </row>
@@ -35814,7 +35469,7 @@
       </c>
       <c r="G93" s="22" t="inlineStr">
         <is>
-          <t>Rain · Waning Moon</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
     </row>
@@ -35849,7 +35504,7 @@
       </c>
       <c r="G94" s="22" t="inlineStr">
         <is>
-          <t>Saturday · Waning Moon</t>
+          <t xml:space="preserve">Saturday</t>
         </is>
       </c>
     </row>
@@ -35884,7 +35539,7 @@
       </c>
       <c r="G95" s="22" t="inlineStr">
         <is>
-          <t>Saturday · Waning Gibbous</t>
+          <t xml:space="preserve">Saturday</t>
         </is>
       </c>
     </row>
@@ -35989,7 +35644,7 @@
       </c>
       <c r="G98" s="22" t="inlineStr">
         <is>
-          <t>Saturday · after Rain</t>
+          <t xml:space="preserve">Saturday</t>
         </is>
       </c>
     </row>
@@ -36059,7 +35714,7 @@
       </c>
       <c r="G100" s="22" t="inlineStr">
         <is>
-          <t>Saturday · Waning Moon</t>
+          <t xml:space="preserve">Saturday</t>
         </is>
       </c>
     </row>
@@ -36094,7 +35749,7 @@
       </c>
       <c r="G101" s="22" t="inlineStr">
         <is>
-          <t>Samhain · Waning Moon</t>
+          <t xml:space="preserve">Samhain</t>
         </is>
       </c>
     </row>
@@ -36164,7 +35819,7 @@
       </c>
       <c r="G103" s="22" t="inlineStr">
         <is>
-          <t>Waxing Crescent</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
     </row>
@@ -36199,7 +35854,7 @@
       </c>
       <c r="G104" s="22" t="inlineStr">
         <is>
-          <t>Fog / Mist · Nightfall</t>
+          <t xml:space="preserve">Nightfall</t>
         </is>
       </c>
     </row>
@@ -36234,7 +35889,7 @@
       </c>
       <c r="G105" s="22" t="inlineStr">
         <is>
-          <t>Sunrise · New Moon</t>
+          <t xml:space="preserve">Sunrise</t>
         </is>
       </c>
     </row>
@@ -36374,7 +36029,7 @@
       </c>
       <c r="G109" s="22" t="inlineStr">
         <is>
-          <t>Dark Moon · Nightfall</t>
+          <t xml:space="preserve">Nightfall</t>
         </is>
       </c>
     </row>
@@ -36409,7 +36064,7 @@
       </c>
       <c r="G110" s="22" t="inlineStr">
         <is>
-          <t>Clear starry night · New Moon</t>
+          <t xml:space="preserve">Clear starry night</t>
         </is>
       </c>
     </row>
@@ -36444,7 +36099,7 @@
       </c>
       <c r="G111" s="22" t="inlineStr">
         <is>
-          <t>Ostara · after Rain</t>
+          <t xml:space="preserve">Ostara</t>
         </is>
       </c>
     </row>
@@ -36689,7 +36344,7 @@
       </c>
       <c r="G118" s="22" t="inlineStr">
         <is>
-          <t>Samhain · Waning Moon</t>
+          <t xml:space="preserve">Samhain</t>
         </is>
       </c>
     </row>
@@ -36724,7 +36379,7 @@
       </c>
       <c r="G119" s="22" t="inlineStr">
         <is>
-          <t>Saturday · Waning Moon</t>
+          <t xml:space="preserve">Saturday</t>
         </is>
       </c>
     </row>
@@ -36759,7 +36414,7 @@
       </c>
       <c r="G120" s="22" t="inlineStr">
         <is>
-          <t>New Moon</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
     </row>
@@ -36794,7 +36449,7 @@
       </c>
       <c r="G121" s="22" t="inlineStr">
         <is>
-          <t>Dark Moon · Nightfall</t>
+          <t xml:space="preserve">Nightfall</t>
         </is>
       </c>
     </row>
@@ -36829,7 +36484,7 @@
       </c>
       <c r="G122" s="22" t="inlineStr">
         <is>
-          <t>New Moon</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
     </row>
@@ -36864,7 +36519,7 @@
       </c>
       <c r="G123" s="22" t="inlineStr">
         <is>
-          <t>Waning Gibbous</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
     </row>
@@ -36899,7 +36554,7 @@
       </c>
       <c r="G124" s="22" t="inlineStr">
         <is>
-          <t>Waning Gibbous</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
     </row>
@@ -37004,7 +36659,7 @@
       </c>
       <c r="G127" s="22" t="inlineStr">
         <is>
-          <t>New Moon</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
     </row>
@@ -37039,7 +36694,7 @@
       </c>
       <c r="G128" s="22" t="inlineStr">
         <is>
-          <t>Waxing Gibbous</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
     </row>
@@ -37074,7 +36729,7 @@
       </c>
       <c r="G129" s="22" t="inlineStr">
         <is>
-          <t>Waning Crescent</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
     </row>
@@ -37669,7 +37324,7 @@
       </c>
       <c r="G146" s="22" t="inlineStr">
         <is>
-          <t>Waning Gibbous</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
     </row>
@@ -37704,7 +37359,7 @@
       </c>
       <c r="G147" s="22" t="inlineStr">
         <is>
-          <t>Windy</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
     </row>
@@ -38019,7 +37674,7 @@
       </c>
       <c r="G156" s="22" t="inlineStr">
         <is>
-          <t>Clear &amp; sunny</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
     </row>
@@ -38124,7 +37779,7 @@
       </c>
       <c r="G159" s="22" t="inlineStr">
         <is>
-          <t>Sunrise · Clear &amp; sunny</t>
+          <t xml:space="preserve">Sunrise</t>
         </is>
       </c>
     </row>
@@ -38159,7 +37814,7 @@
       </c>
       <c r="G160" s="22" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
     </row>
@@ -38194,7 +37849,7 @@
       </c>
       <c r="G161" s="22" t="inlineStr">
         <is>
-          <t>Wednesday · Waxing Moon</t>
+          <t xml:space="preserve">Wednesday</t>
         </is>
       </c>
     </row>
@@ -38229,7 +37884,7 @@
       </c>
       <c r="G162" s="22" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
     </row>
@@ -38684,7 +38339,7 @@
       </c>
       <c r="G175" s="22" t="inlineStr">
         <is>
-          <t>Snow</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
     </row>
@@ -38824,7 +38479,7 @@
       </c>
       <c r="G179" s="22" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
     </row>
@@ -38929,7 +38584,7 @@
       </c>
       <c r="G182" s="22" t="inlineStr">
         <is>
-          <t>New Moon</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
     </row>
@@ -38964,7 +38619,7 @@
       </c>
       <c r="G183" s="22" t="inlineStr">
         <is>
-          <t>Tuesday · New Moon</t>
+          <t xml:space="preserve">Tuesday</t>
         </is>
       </c>
     </row>
@@ -39034,7 +38689,7 @@
       </c>
       <c r="G185" s="22" t="inlineStr">
         <is>
-          <t>after Rain</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
     </row>
@@ -39069,7 +38724,7 @@
       </c>
       <c r="G186" s="22" t="inlineStr">
         <is>
-          <t>Tuesday · Waning Moon</t>
+          <t xml:space="preserve">Tuesday</t>
         </is>
       </c>
     </row>
@@ -39139,7 +38794,7 @@
       </c>
       <c r="G188" s="22" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
     </row>
@@ -39174,7 +38829,7 @@
       </c>
       <c r="G189" s="22" t="inlineStr">
         <is>
-          <t>Waning Moon · Twilight</t>
+          <t xml:space="preserve">Twilight</t>
         </is>
       </c>
     </row>
@@ -39279,7 +38934,7 @@
       </c>
       <c r="G192" s="22" t="inlineStr">
         <is>
-          <t>Fog / Mist</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
     </row>
@@ -39419,7 +39074,7 @@
       </c>
       <c r="G196" s="22" t="inlineStr">
         <is>
-          <t>Waning Gibbous</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
     </row>
@@ -39454,7 +39109,7 @@
       </c>
       <c r="G197" s="22" t="inlineStr">
         <is>
-          <t>Waning Crescent</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
     </row>
@@ -39524,7 +39179,7 @@
       </c>
       <c r="G199" s="22" t="inlineStr">
         <is>
-          <t>Waning Gibbous</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
     </row>
@@ -39629,7 +39284,7 @@
       </c>
       <c r="G202" s="22" t="inlineStr">
         <is>
-          <t>Waning Moon</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
     </row>
@@ -39769,7 +39424,7 @@
       </c>
       <c r="G206" s="22" t="inlineStr">
         <is>
-          <t>Waning Moon</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
     </row>
@@ -39874,7 +39529,7 @@
       </c>
       <c r="G209" s="22" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
     </row>
@@ -40329,7 +39984,7 @@
       </c>
       <c r="G222" s="22" t="inlineStr">
         <is>
-          <t>Windy</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
     </row>
@@ -40994,7 +40649,7 @@
       </c>
       <c r="G241" s="22" t="inlineStr">
         <is>
-          <t>Thunderstorm</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
     </row>
@@ -65647,12 +65302,12 @@
       </c>
       <c r="D1" s="35" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t xml:space="preserve">Full moon</t>
         </is>
       </c>
       <c r="E1" s="35" t="inlineStr">
         <is>
-          <t>Weather</t>
+          <t xml:space="preserve">Sky event</t>
         </is>
       </c>
       <c r="F1" s="35" t="inlineStr">
@@ -65725,16 +65380,8 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D2" s="43" t="inlineStr">
-        <is>
-          <t>Waning Gibbous</t>
-        </is>
-      </c>
-      <c r="E2" s="43" t="inlineStr">
-        <is>
-          <t>Cloudy</t>
-        </is>
-      </c>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
       <c r="F2" s="43" t="inlineStr">
         <is>
           <t>Noon</t>
@@ -65756,7 +65403,7 @@
       </c>
       <c r="K2" s="37" t="inlineStr">
         <is>
-          <t>Any time</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L2" s="43">
@@ -65792,16 +65439,8 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D3" s="43" t="inlineStr">
-        <is>
-          <t>Waning Gibbous</t>
-        </is>
-      </c>
-      <c r="E3" s="43" t="inlineStr">
-        <is>
-          <t>Cloudy</t>
-        </is>
-      </c>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
       <c r="F3" s="43" t="inlineStr">
         <is>
           <t>Nightfall</t>
@@ -65823,7 +65462,7 @@
       </c>
       <c r="K3" s="37" t="inlineStr">
         <is>
-          <t>Any time</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L3" s="43">
@@ -65859,16 +65498,8 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D4" s="43" t="inlineStr">
-        <is>
-          <t>Waning Crescent</t>
-        </is>
-      </c>
-      <c r="E4" s="43" t="inlineStr">
-        <is>
-          <t>Rain</t>
-        </is>
-      </c>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
       <c r="F4" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -65890,7 +65521,7 @@
       </c>
       <c r="K4" s="37" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t xml:space="preserve">Sunday</t>
         </is>
       </c>
       <c r="L4" s="43">
@@ -65930,16 +65561,8 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="D5" s="43" t="inlineStr">
-        <is>
-          <t>New Moon</t>
-        </is>
-      </c>
-      <c r="E5" s="43" t="inlineStr">
-        <is>
-          <t>Windy</t>
-        </is>
-      </c>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
       <c r="F5" s="43" t="inlineStr">
         <is>
           <t>Twilight</t>
@@ -65961,7 +65584,7 @@
       </c>
       <c r="K5" s="37" t="inlineStr">
         <is>
-          <t>New Moon</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L5" s="43">
@@ -65997,16 +65620,8 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D6" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Crescent</t>
-        </is>
-      </c>
-      <c r="E6" s="43" t="inlineStr">
-        <is>
-          <t>Thunderstorm</t>
-        </is>
-      </c>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
       <c r="F6" s="43" t="inlineStr">
         <is>
           <t>Twilight</t>
@@ -66028,7 +65643,7 @@
       </c>
       <c r="K6" s="37" t="inlineStr">
         <is>
-          <t>Any time</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L6" s="43">
@@ -66068,16 +65683,8 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D7" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Gibbous</t>
-        </is>
-      </c>
-      <c r="E7" s="43" t="inlineStr">
-        <is>
-          <t>Fog / Mist</t>
-        </is>
-      </c>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
       <c r="F7" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -66099,7 +65706,7 @@
       </c>
       <c r="K7" s="37" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t xml:space="preserve">Wednesday</t>
         </is>
       </c>
       <c r="L7" s="43">
@@ -66137,12 +65744,12 @@
       </c>
       <c r="D8" s="43" t="inlineStr">
         <is>
-          <t>Full Moon</t>
+          <t xml:space="preserve">Beaver Moon</t>
         </is>
       </c>
       <c r="E8" s="43" t="inlineStr">
         <is>
-          <t>Clear &amp; sunny</t>
+          <t xml:space="preserve">Clear starry night</t>
         </is>
       </c>
       <c r="F8" s="43" t="inlineStr">
@@ -66166,7 +65773,7 @@
       </c>
       <c r="K8" s="37" t="inlineStr">
         <is>
-          <t>Beaver Moon (November full moon)</t>
+          <t xml:space="preserve">Beaver Moon (November full moon)</t>
         </is>
       </c>
       <c r="L8" s="43">
@@ -66208,12 +65815,12 @@
       </c>
       <c r="D9" s="43" t="inlineStr">
         <is>
-          <t>Full Moon</t>
+          <t xml:space="preserve">Beaver Moon</t>
         </is>
       </c>
       <c r="E9" s="43" t="inlineStr">
         <is>
-          <t>Clear &amp; sunny</t>
+          <t xml:space="preserve">Clear starry night</t>
         </is>
       </c>
       <c r="F9" s="43" t="inlineStr">
@@ -66237,7 +65844,7 @@
       </c>
       <c r="K9" s="37" t="inlineStr">
         <is>
-          <t>Any time</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L9" s="43">
@@ -66273,16 +65880,8 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D10" s="43" t="inlineStr">
-        <is>
-          <t>Waning Crescent</t>
-        </is>
-      </c>
-      <c r="E10" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
       <c r="F10" s="43" t="inlineStr">
         <is>
           <t>Noon</t>
@@ -66304,7 +65903,7 @@
       </c>
       <c r="K10" s="37" t="inlineStr">
         <is>
-          <t>Saturday · Waning Moon</t>
+          <t xml:space="preserve">Saturday</t>
         </is>
       </c>
       <c r="L10" s="43">
@@ -66340,16 +65939,8 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D11" s="43" t="inlineStr">
-        <is>
-          <t>New Moon</t>
-        </is>
-      </c>
-      <c r="E11" s="43" t="inlineStr">
-        <is>
-          <t>Rain</t>
-        </is>
-      </c>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
       <c r="F11" s="43" t="inlineStr">
         <is>
           <t>Noon</t>
@@ -66371,7 +65962,7 @@
       </c>
       <c r="K11" s="37" t="inlineStr">
         <is>
-          <t>Sunday · Noon</t>
+          <t xml:space="preserve">Sunday · Noon</t>
         </is>
       </c>
       <c r="L11" s="43">
@@ -66407,16 +65998,8 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D12" s="43" t="inlineStr">
-        <is>
-          <t>New Moon</t>
-        </is>
-      </c>
-      <c r="E12" s="43" t="inlineStr">
-        <is>
-          <t>Rain</t>
-        </is>
-      </c>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
       <c r="F12" s="43" t="inlineStr">
         <is>
           <t>Twilight</t>
@@ -66438,7 +66021,7 @@
       </c>
       <c r="K12" s="37" t="inlineStr">
         <is>
-          <t>Twilight</t>
+          <t xml:space="preserve">Twilight</t>
         </is>
       </c>
       <c r="L12" s="43">
@@ -66474,16 +66057,8 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="D13" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Crescent</t>
-        </is>
-      </c>
-      <c r="E13" s="43" t="inlineStr">
-        <is>
-          <t>Windy</t>
-        </is>
-      </c>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
       <c r="F13" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -66505,7 +66080,7 @@
       </c>
       <c r="K13" s="37" t="inlineStr">
         <is>
-          <t>Yule · Sunrise</t>
+          <t xml:space="preserve">Yule · Sunrise</t>
         </is>
       </c>
       <c r="L13" s="43">
@@ -66541,16 +66116,8 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="D14" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Crescent</t>
-        </is>
-      </c>
-      <c r="E14" s="43" t="inlineStr">
-        <is>
-          <t>Windy</t>
-        </is>
-      </c>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
       <c r="F14" s="43" t="inlineStr">
         <is>
           <t>Noon</t>
@@ -66572,7 +66139,7 @@
       </c>
       <c r="K14" s="37" t="inlineStr">
         <is>
-          <t>Yule</t>
+          <t xml:space="preserve">Yule</t>
         </is>
       </c>
       <c r="L14" s="43">
@@ -66604,16 +66171,8 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D15" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Gibbous</t>
-        </is>
-      </c>
-      <c r="E15" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
       <c r="F15" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -66635,7 +66194,7 @@
       </c>
       <c r="K15" s="37" t="inlineStr">
         <is>
-          <t>Sunrise</t>
+          <t xml:space="preserve">Sunrise</t>
         </is>
       </c>
       <c r="L15" s="43">
@@ -66667,16 +66226,8 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D16" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Gibbous</t>
-        </is>
-      </c>
-      <c r="E16" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
       <c r="F16" s="43" t="inlineStr">
         <is>
           <t>Noon</t>
@@ -66698,7 +66249,7 @@
       </c>
       <c r="K16" s="37" t="inlineStr">
         <is>
-          <t>Tuesday · Waxing Moon</t>
+          <t xml:space="preserve">Tuesday</t>
         </is>
       </c>
       <c r="L16" s="43">
@@ -66732,14 +66283,10 @@
       </c>
       <c r="D17" s="43" t="inlineStr">
         <is>
-          <t>Full Moon</t>
-        </is>
-      </c>
-      <c r="E17" s="43" t="inlineStr">
-        <is>
-          <t>Cloudy</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Cold Moon</t>
+        </is>
+      </c>
+      <c r="E17" s="43"/>
       <c r="F17" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -66761,7 +66308,7 @@
       </c>
       <c r="K17" s="37" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t xml:space="preserve">Wednesday</t>
         </is>
       </c>
       <c r="L17" s="43">
@@ -66799,14 +66346,10 @@
       </c>
       <c r="D18" s="43" t="inlineStr">
         <is>
-          <t>Full Moon</t>
-        </is>
-      </c>
-      <c r="E18" s="43" t="inlineStr">
-        <is>
-          <t>Cloudy</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Cold Moon</t>
+        </is>
+      </c>
+      <c r="E18" s="43"/>
       <c r="F18" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -66828,7 +66371,7 @@
       </c>
       <c r="K18" s="37" t="inlineStr">
         <is>
-          <t>Cold Moon (December full moon)</t>
+          <t xml:space="preserve">Cold Moon (December full moon)</t>
         </is>
       </c>
       <c r="L18" s="43">
@@ -66864,16 +66407,8 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D19" s="43" t="inlineStr">
-        <is>
-          <t>Waning Gibbous</t>
-        </is>
-      </c>
-      <c r="E19" s="43" t="inlineStr">
-        <is>
-          <t>Snow</t>
-        </is>
-      </c>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43"/>
       <c r="F19" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -66895,7 +66430,7 @@
       </c>
       <c r="K19" s="37" t="inlineStr">
         <is>
-          <t>Sunrise</t>
+          <t xml:space="preserve">Sunrise</t>
         </is>
       </c>
       <c r="L19" s="43">
@@ -66931,16 +66466,8 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D20" s="43" t="inlineStr">
-        <is>
-          <t>Waning Gibbous</t>
-        </is>
-      </c>
-      <c r="E20" s="43" t="inlineStr">
-        <is>
-          <t>Snow</t>
-        </is>
-      </c>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
       <c r="F20" s="43" t="inlineStr">
         <is>
           <t>Noon</t>
@@ -66962,7 +66489,7 @@
       </c>
       <c r="K20" s="37" t="inlineStr">
         <is>
-          <t>Any time</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L20" s="43">
@@ -66998,16 +66525,8 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="D21" s="43" t="inlineStr">
-        <is>
-          <t>Waning Crescent</t>
-        </is>
-      </c>
-      <c r="E21" s="43" t="inlineStr">
-        <is>
-          <t>Snow</t>
-        </is>
-      </c>
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
       <c r="F21" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -67029,7 +66548,7 @@
       </c>
       <c r="K21" s="37" t="inlineStr">
         <is>
-          <t>Waning Moon</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L21" s="43">
@@ -67057,16 +66576,8 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="D22" s="43" t="inlineStr">
-        <is>
-          <t>Waning Crescent</t>
-        </is>
-      </c>
-      <c r="E22" s="43" t="inlineStr">
-        <is>
-          <t>Snow</t>
-        </is>
-      </c>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
       <c r="F22" s="43" t="inlineStr">
         <is>
           <t>Noon</t>
@@ -67088,7 +66599,7 @@
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
-          <t>Any time</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L22" s="43">
@@ -67120,16 +66631,8 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D23" s="43" t="inlineStr">
-        <is>
-          <t>New Moon</t>
-        </is>
-      </c>
-      <c r="E23" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D23" s="43"/>
+      <c r="E23" s="43"/>
       <c r="F23" s="43" t="inlineStr">
         <is>
           <t>Twilight</t>
@@ -67151,7 +66654,7 @@
       </c>
       <c r="K23" s="37" t="inlineStr">
         <is>
-          <t>Twilight (golden hour)</t>
+          <t xml:space="preserve">Twilight (golden hour)</t>
         </is>
       </c>
       <c r="L23" s="43">
@@ -67183,16 +66686,8 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D24" s="43" t="inlineStr">
-        <is>
-          <t>New Moon</t>
-        </is>
-      </c>
-      <c r="E24" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D24" s="43"/>
+      <c r="E24" s="43"/>
       <c r="F24" s="43" t="inlineStr">
         <is>
           <t>Nightfall</t>
@@ -67214,7 +66709,7 @@
       </c>
       <c r="K24" s="37" t="inlineStr">
         <is>
-          <t>Saturday · Dark Moon · Nightfall</t>
+          <t xml:space="preserve">Saturday · Nightfall</t>
         </is>
       </c>
       <c r="L24" s="43">
@@ -67246,16 +66741,8 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D25" s="43" t="inlineStr">
-        <is>
-          <t>New Moon</t>
-        </is>
-      </c>
-      <c r="E25" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D25" s="43"/>
+      <c r="E25" s="43"/>
       <c r="F25" s="43" t="inlineStr">
         <is>
           <t>Nightfall</t>
@@ -67277,7 +66764,7 @@
       </c>
       <c r="K25" s="37" t="inlineStr">
         <is>
-          <t>Clear starry night · New Moon</t>
+          <t xml:space="preserve">Clear starry night</t>
         </is>
       </c>
       <c r="L25" s="43">
@@ -67313,16 +66800,8 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D26" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Crescent</t>
-        </is>
-      </c>
-      <c r="E26" s="43" t="inlineStr">
-        <is>
-          <t>Rain</t>
-        </is>
-      </c>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
       <c r="F26" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -67348,7 +66827,7 @@
       </c>
       <c r="K26" s="37" t="inlineStr">
         <is>
-          <t>Waxing Crescent</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L26" s="43">
@@ -67384,16 +66863,8 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D27" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Crescent</t>
-        </is>
-      </c>
-      <c r="E27" s="43" t="inlineStr">
-        <is>
-          <t>Rain</t>
-        </is>
-      </c>
+      <c r="D27" s="43"/>
+      <c r="E27" s="43"/>
       <c r="F27" s="43" t="inlineStr">
         <is>
           <t>Noon</t>
@@ -67415,7 +66886,7 @@
       </c>
       <c r="K27" s="37" t="inlineStr">
         <is>
-          <t>Sunday · Noon</t>
+          <t xml:space="preserve">Sunday · Noon</t>
         </is>
       </c>
       <c r="L27" s="43">
@@ -67447,16 +66918,8 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="D28" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Gibbous</t>
-        </is>
-      </c>
-      <c r="E28" s="43" t="inlineStr">
-        <is>
-          <t>Snow</t>
-        </is>
-      </c>
+      <c r="D28" s="43"/>
+      <c r="E28" s="43"/>
       <c r="F28" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -67478,7 +66941,7 @@
       </c>
       <c r="K28" s="37" t="inlineStr">
         <is>
-          <t>Snow</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L28" s="43">
@@ -67510,16 +66973,8 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="D29" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Gibbous</t>
-        </is>
-      </c>
-      <c r="E29" s="43" t="inlineStr">
-        <is>
-          <t>Snow</t>
-        </is>
-      </c>
+      <c r="D29" s="43"/>
+      <c r="E29" s="43"/>
       <c r="F29" s="43" t="inlineStr">
         <is>
           <t>Noon</t>
@@ -67541,7 +66996,7 @@
       </c>
       <c r="K29" s="37" t="inlineStr">
         <is>
-          <t>Monday · Snow</t>
+          <t xml:space="preserve">Monday</t>
         </is>
       </c>
       <c r="L29" s="43">
@@ -67575,14 +67030,10 @@
       </c>
       <c r="D30" s="43" t="inlineStr">
         <is>
-          <t>Full Moon</t>
-        </is>
-      </c>
-      <c r="E30" s="43" t="inlineStr">
-        <is>
-          <t>Cloudy</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Wolf Moon</t>
+        </is>
+      </c>
+      <c r="E30" s="43"/>
       <c r="F30" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -67608,7 +67059,7 @@
       </c>
       <c r="K30" s="37" t="inlineStr">
         <is>
-          <t>Tuesday · Full Moon · Sunrise</t>
+          <t xml:space="preserve">Tuesday · Full Moon · Sunrise</t>
         </is>
       </c>
       <c r="L30" s="43">
@@ -67642,14 +67093,10 @@
       </c>
       <c r="D31" s="43" t="inlineStr">
         <is>
-          <t>Full Moon</t>
-        </is>
-      </c>
-      <c r="E31" s="43" t="inlineStr">
-        <is>
-          <t>Cloudy</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Wolf Moon</t>
+        </is>
+      </c>
+      <c r="E31" s="43"/>
       <c r="F31" s="43" t="inlineStr">
         <is>
           <t>Noon</t>
@@ -67671,7 +67118,7 @@
       </c>
       <c r="K31" s="37" t="inlineStr">
         <is>
-          <t>Wolf Moon (January full moon)</t>
+          <t xml:space="preserve">Wolf Moon (January full moon)</t>
         </is>
       </c>
       <c r="L31" s="43">
@@ -67703,16 +67150,8 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D32" s="43" t="inlineStr">
-        <is>
-          <t>Waning Gibbous</t>
-        </is>
-      </c>
-      <c r="E32" s="43" t="inlineStr">
-        <is>
-          <t>Snow</t>
-        </is>
-      </c>
+      <c r="D32" s="43"/>
+      <c r="E32" s="43"/>
       <c r="F32" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -67734,7 +67173,7 @@
       </c>
       <c r="K32" s="37" t="inlineStr">
         <is>
-          <t>Imbolc · Sunrise</t>
+          <t xml:space="preserve">Imbolc · Sunrise</t>
         </is>
       </c>
       <c r="L32" s="43">
@@ -67770,16 +67209,8 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D33" s="43" t="inlineStr">
-        <is>
-          <t>Waning Gibbous</t>
-        </is>
-      </c>
-      <c r="E33" s="43" t="inlineStr">
-        <is>
-          <t>Snow</t>
-        </is>
-      </c>
+      <c r="D33" s="43"/>
+      <c r="E33" s="43"/>
       <c r="F33" s="43" t="inlineStr">
         <is>
           <t>Noon</t>
@@ -67801,7 +67232,7 @@
       </c>
       <c r="K33" s="37" t="inlineStr">
         <is>
-          <t>Imbolc</t>
+          <t xml:space="preserve">Imbolc</t>
         </is>
       </c>
       <c r="L33" s="43">
@@ -67829,16 +67260,8 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D34" s="43" t="inlineStr">
-        <is>
-          <t>Waning Crescent</t>
-        </is>
-      </c>
-      <c r="E34" s="43" t="inlineStr">
-        <is>
-          <t>Cloudy</t>
-        </is>
-      </c>
+      <c r="D34" s="43"/>
+      <c r="E34" s="43"/>
       <c r="F34" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -67860,7 +67283,7 @@
       </c>
       <c r="K34" s="37" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t xml:space="preserve">Thursday</t>
         </is>
       </c>
       <c r="L34" s="43">
@@ -67896,16 +67319,8 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D35" s="43" t="inlineStr">
-        <is>
-          <t>Waning Crescent</t>
-        </is>
-      </c>
-      <c r="E35" s="43" t="inlineStr">
-        <is>
-          <t>Cloudy</t>
-        </is>
-      </c>
+      <c r="D35" s="43"/>
+      <c r="E35" s="43"/>
       <c r="F35" s="43" t="inlineStr">
         <is>
           <t>Noon</t>
@@ -67927,7 +67342,7 @@
       </c>
       <c r="K35" s="37" t="inlineStr">
         <is>
-          <t>Any time</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L35" s="43">
@@ -67963,16 +67378,8 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="D36" s="43" t="inlineStr">
-        <is>
-          <t>New Moon</t>
-        </is>
-      </c>
-      <c r="E36" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D36" s="43"/>
+      <c r="E36" s="43"/>
       <c r="F36" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -67998,7 +67405,7 @@
       </c>
       <c r="K36" s="37" t="inlineStr">
         <is>
-          <t>Friday · Clear &amp; sunny</t>
+          <t xml:space="preserve">Friday</t>
         </is>
       </c>
       <c r="L36" s="43">
@@ -68034,16 +67441,8 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="D37" s="43" t="inlineStr">
-        <is>
-          <t>New Moon</t>
-        </is>
-      </c>
-      <c r="E37" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D37" s="43"/>
+      <c r="E37" s="43"/>
       <c r="F37" s="43" t="inlineStr">
         <is>
           <t>Nightfall</t>
@@ -68065,7 +67464,7 @@
       </c>
       <c r="K37" s="37" t="inlineStr">
         <is>
-          <t>Friday · Dark Moon · Nightfall</t>
+          <t xml:space="preserve">Friday · Nightfall</t>
         </is>
       </c>
       <c r="L37" s="43">
@@ -68097,16 +67496,8 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D38" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Crescent</t>
-        </is>
-      </c>
-      <c r="E38" s="43" t="inlineStr">
-        <is>
-          <t>Cloudy</t>
-        </is>
-      </c>
+      <c r="D38" s="43"/>
+      <c r="E38" s="43"/>
       <c r="F38" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -68128,7 +67519,7 @@
       </c>
       <c r="K38" s="37" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t xml:space="preserve">Saturday</t>
         </is>
       </c>
       <c r="L38" s="43">
@@ -68164,16 +67555,8 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D39" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Crescent</t>
-        </is>
-      </c>
-      <c r="E39" s="43" t="inlineStr">
-        <is>
-          <t>Cloudy</t>
-        </is>
-      </c>
+      <c r="D39" s="43"/>
+      <c r="E39" s="43"/>
       <c r="F39" s="43" t="inlineStr">
         <is>
           <t>Noon</t>
@@ -68195,7 +67578,7 @@
       </c>
       <c r="K39" s="37" t="inlineStr">
         <is>
-          <t>Any time</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L39" s="43">
@@ -68231,16 +67614,8 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D40" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Gibbous</t>
-        </is>
-      </c>
-      <c r="E40" s="43" t="inlineStr">
-        <is>
-          <t>Snow</t>
-        </is>
-      </c>
+      <c r="D40" s="43"/>
+      <c r="E40" s="43"/>
       <c r="F40" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -68262,7 +67637,7 @@
       </c>
       <c r="K40" s="37" t="inlineStr">
         <is>
-          <t>Any time</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L40" s="43">
@@ -68298,16 +67673,8 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D41" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Gibbous</t>
-        </is>
-      </c>
-      <c r="E41" s="43" t="inlineStr">
-        <is>
-          <t>Snow</t>
-        </is>
-      </c>
+      <c r="D41" s="43"/>
+      <c r="E41" s="43"/>
       <c r="F41" s="43" t="inlineStr">
         <is>
           <t>Noon</t>
@@ -68329,7 +67696,7 @@
       </c>
       <c r="K41" s="37" t="inlineStr">
         <is>
-          <t>Waxing Gibbous</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L41" s="43">
@@ -68367,12 +67734,12 @@
       </c>
       <c r="D42" s="43" t="inlineStr">
         <is>
-          <t>Full Moon</t>
+          <t xml:space="preserve">Snow Moon</t>
         </is>
       </c>
       <c r="E42" s="43" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t xml:space="preserve">Lunar Eclipse (Snow Moon)</t>
         </is>
       </c>
       <c r="F42" s="43" t="inlineStr">
@@ -68396,7 +67763,7 @@
       </c>
       <c r="K42" s="37" t="inlineStr">
         <is>
-          <t>Monday · Full Moon</t>
+          <t xml:space="preserve">Monday · Full Moon</t>
         </is>
       </c>
       <c r="L42" s="43">
@@ -68430,12 +67797,12 @@
       </c>
       <c r="D43" s="43" t="inlineStr">
         <is>
-          <t>Full Moon</t>
+          <t xml:space="preserve">Snow Moon</t>
         </is>
       </c>
       <c r="E43" s="43" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t xml:space="preserve">Lunar Eclipse (Snow Moon)</t>
         </is>
       </c>
       <c r="F43" s="43" t="inlineStr">
@@ -68459,7 +67826,7 @@
       </c>
       <c r="K43" s="37" t="inlineStr">
         <is>
-          <t>Snow Moon (February full moon)</t>
+          <t xml:space="preserve">Snow Moon (February full moon)</t>
         </is>
       </c>
       <c r="L43" s="43">
@@ -68491,16 +67858,8 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D44" s="43" t="inlineStr">
-        <is>
-          <t>Waning Gibbous</t>
-        </is>
-      </c>
-      <c r="E44" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D44" s="43"/>
+      <c r="E44" s="43"/>
       <c r="F44" s="43" t="inlineStr">
         <is>
           <t>Noon</t>
@@ -68522,7 +67881,7 @@
       </c>
       <c r="K44" s="37" t="inlineStr">
         <is>
-          <t>Waning Gibbous</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L44" s="43">
@@ -68558,16 +67917,8 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D45" s="43" t="inlineStr">
-        <is>
-          <t>Waning Crescent</t>
-        </is>
-      </c>
-      <c r="E45" s="43" t="inlineStr">
-        <is>
-          <t>Windy</t>
-        </is>
-      </c>
+      <c r="D45" s="43"/>
+      <c r="E45" s="43"/>
       <c r="F45" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -68593,7 +67944,7 @@
       </c>
       <c r="K45" s="37" t="inlineStr">
         <is>
-          <t>Waning Crescent</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L45" s="43">
@@ -68629,16 +67980,8 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D46" s="43" t="inlineStr">
-        <is>
-          <t>Waning Crescent</t>
-        </is>
-      </c>
-      <c r="E46" s="43" t="inlineStr">
-        <is>
-          <t>Windy</t>
-        </is>
-      </c>
+      <c r="D46" s="43"/>
+      <c r="E46" s="43"/>
       <c r="F46" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -68664,7 +68007,7 @@
       </c>
       <c r="K46" s="37" t="inlineStr">
         <is>
-          <t>Windy</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L46" s="43">
@@ -68700,16 +68043,8 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D47" s="43" t="inlineStr">
-        <is>
-          <t>New Moon</t>
-        </is>
-      </c>
-      <c r="E47" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D47" s="43"/>
+      <c r="E47" s="43"/>
       <c r="F47" s="43" t="inlineStr">
         <is>
           <t>Twilight</t>
@@ -68731,7 +68066,7 @@
       </c>
       <c r="K47" s="37" t="inlineStr">
         <is>
-          <t>Ostara</t>
+          <t xml:space="preserve">Ostara</t>
         </is>
       </c>
       <c r="L47" s="43">
@@ -68767,16 +68102,8 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="D48" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Crescent</t>
-        </is>
-      </c>
-      <c r="E48" s="43" t="inlineStr">
-        <is>
-          <t>Rain</t>
-        </is>
-      </c>
+      <c r="D48" s="43"/>
+      <c r="E48" s="43"/>
       <c r="F48" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -68802,7 +68129,7 @@
       </c>
       <c r="K48" s="37" t="inlineStr">
         <is>
-          <t>Ostara · Sunrise</t>
+          <t xml:space="preserve">Ostara · Sunrise</t>
         </is>
       </c>
       <c r="L48" s="43">
@@ -68834,16 +68161,8 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="D49" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Crescent</t>
-        </is>
-      </c>
-      <c r="E49" s="43" t="inlineStr">
-        <is>
-          <t>Rain</t>
-        </is>
-      </c>
+      <c r="D49" s="43"/>
+      <c r="E49" s="43"/>
       <c r="F49" s="43" t="inlineStr">
         <is>
           <t>Noon</t>
@@ -68869,7 +68188,7 @@
       </c>
       <c r="K49" s="37" t="inlineStr">
         <is>
-          <t>Friday · Waxing Crescent · Noon</t>
+          <t xml:space="preserve">Friday · Noon</t>
         </is>
       </c>
       <c r="L49" s="43">
@@ -68901,16 +68220,8 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D50" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Gibbous</t>
-        </is>
-      </c>
-      <c r="E50" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D50" s="43"/>
+      <c r="E50" s="43"/>
       <c r="F50" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -68932,7 +68243,7 @@
       </c>
       <c r="K50" s="37" t="inlineStr">
         <is>
-          <t>Saturday · after Rain</t>
+          <t xml:space="preserve">Saturday</t>
         </is>
       </c>
       <c r="L50" s="43">
@@ -68964,16 +68275,8 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D51" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Gibbous</t>
-        </is>
-      </c>
-      <c r="E51" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D51" s="43"/>
+      <c r="E51" s="43"/>
       <c r="F51" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -68995,7 +68298,7 @@
       </c>
       <c r="K51" s="37" t="inlineStr">
         <is>
-          <t>Ostara · Sunrise</t>
+          <t xml:space="preserve">Ostara · Sunrise</t>
         </is>
       </c>
       <c r="L51" s="43">
@@ -69027,16 +68330,8 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D52" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Gibbous</t>
-        </is>
-      </c>
-      <c r="E52" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D52" s="43"/>
+      <c r="E52" s="43"/>
       <c r="F52" s="43" t="inlineStr">
         <is>
           <t>Noon</t>
@@ -69058,7 +68353,7 @@
       </c>
       <c r="K52" s="37" t="inlineStr">
         <is>
-          <t>Saturday · after Rain</t>
+          <t xml:space="preserve">Saturday</t>
         </is>
       </c>
       <c r="L52" s="43">
@@ -69090,16 +68385,8 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D53" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Gibbous</t>
-        </is>
-      </c>
-      <c r="E53" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D53" s="43"/>
+      <c r="E53" s="43"/>
       <c r="F53" s="43" t="inlineStr">
         <is>
           <t>Noon</t>
@@ -69121,7 +68408,7 @@
       </c>
       <c r="K53" s="37" t="inlineStr">
         <is>
-          <t>Ostara · after Rain</t>
+          <t xml:space="preserve">Ostara</t>
         </is>
       </c>
       <c r="L53" s="43">
@@ -69155,12 +68442,12 @@
       </c>
       <c r="D54" s="43" t="inlineStr">
         <is>
-          <t>Full Moon</t>
+          <t xml:space="preserve">Worm Moon</t>
         </is>
       </c>
       <c r="E54" s="43" t="inlineStr">
         <is>
-          <t>Windy</t>
+          <t xml:space="preserve">Clear starry night</t>
         </is>
       </c>
       <c r="F54" s="43" t="inlineStr">
@@ -69184,7 +68471,7 @@
       </c>
       <c r="K54" s="37" t="inlineStr">
         <is>
-          <t>Sunday · Full Moon</t>
+          <t xml:space="preserve">Sunday · Full Moon</t>
         </is>
       </c>
       <c r="L54" s="43">
@@ -69218,12 +68505,12 @@
       </c>
       <c r="D55" s="43" t="inlineStr">
         <is>
-          <t>Full Moon</t>
+          <t xml:space="preserve">Worm Moon</t>
         </is>
       </c>
       <c r="E55" s="43" t="inlineStr">
         <is>
-          <t>Windy</t>
+          <t xml:space="preserve">Clear starry night</t>
         </is>
       </c>
       <c r="F55" s="43" t="inlineStr">
@@ -69247,7 +68534,7 @@
       </c>
       <c r="K55" s="37" t="inlineStr">
         <is>
-          <t>Worm Moon (March full moon)</t>
+          <t xml:space="preserve">Worm Moon (March full moon)</t>
         </is>
       </c>
       <c r="L55" s="43">
@@ -69279,16 +68566,8 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="D56" s="43" t="inlineStr">
-        <is>
-          <t>Waning Gibbous</t>
-        </is>
-      </c>
-      <c r="E56" s="43" t="inlineStr">
-        <is>
-          <t>Rain</t>
-        </is>
-      </c>
+      <c r="D56" s="43"/>
+      <c r="E56" s="43"/>
       <c r="F56" s="43" t="inlineStr">
         <is>
           <t>Noon</t>
@@ -69310,7 +68589,7 @@
       </c>
       <c r="K56" s="37" t="inlineStr">
         <is>
-          <t>Any time</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L56" s="43">
@@ -69346,16 +68625,8 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="D57" s="43" t="inlineStr">
-        <is>
-          <t>Waning Gibbous</t>
-        </is>
-      </c>
-      <c r="E57" s="43" t="inlineStr">
-        <is>
-          <t>Rain</t>
-        </is>
-      </c>
+      <c r="D57" s="43"/>
+      <c r="E57" s="43"/>
       <c r="F57" s="43" t="inlineStr">
         <is>
           <t>Twilight</t>
@@ -69377,7 +68648,7 @@
       </c>
       <c r="K57" s="37" t="inlineStr">
         <is>
-          <t>Rain · Waning Moon</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L57" s="43">
@@ -69413,16 +68684,8 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D58" s="43" t="inlineStr">
-        <is>
-          <t>Waning Crescent</t>
-        </is>
-      </c>
-      <c r="E58" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D58" s="43"/>
+      <c r="E58" s="43"/>
       <c r="F58" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -69448,7 +68711,7 @@
       </c>
       <c r="K58" s="37" t="inlineStr">
         <is>
-          <t>Tuesday · Sunrise</t>
+          <t xml:space="preserve">Tuesday · Sunrise</t>
         </is>
       </c>
       <c r="L58" s="43">
@@ -69480,16 +68743,8 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D59" s="43" t="inlineStr">
-        <is>
-          <t>Waning Crescent</t>
-        </is>
-      </c>
-      <c r="E59" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D59" s="43"/>
+      <c r="E59" s="43"/>
       <c r="F59" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -69515,7 +68770,7 @@
       </c>
       <c r="K59" s="37" t="inlineStr">
         <is>
-          <t>Tuesday · Waning Moon</t>
+          <t xml:space="preserve">Tuesday</t>
         </is>
       </c>
       <c r="L59" s="43">
@@ -69543,16 +68798,8 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D60" s="43" t="inlineStr">
-        <is>
-          <t>New Moon</t>
-        </is>
-      </c>
-      <c r="E60" s="43" t="inlineStr">
-        <is>
-          <t>Rain</t>
-        </is>
-      </c>
+      <c r="D60" s="43"/>
+      <c r="E60" s="43"/>
       <c r="F60" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -69574,7 +68821,7 @@
       </c>
       <c r="K60" s="37" t="inlineStr">
         <is>
-          <t>Sunrise · New Moon</t>
+          <t xml:space="preserve">Sunrise</t>
         </is>
       </c>
       <c r="L60" s="43">
@@ -69606,16 +68853,8 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D61" s="43" t="inlineStr">
-        <is>
-          <t>New Moon</t>
-        </is>
-      </c>
-      <c r="E61" s="43" t="inlineStr">
-        <is>
-          <t>Rain</t>
-        </is>
-      </c>
+      <c r="D61" s="43"/>
+      <c r="E61" s="43"/>
       <c r="F61" s="43" t="inlineStr">
         <is>
           <t>Twilight</t>
@@ -69637,7 +68876,7 @@
       </c>
       <c r="K61" s="37" t="inlineStr">
         <is>
-          <t>New Moon</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L61" s="43">
@@ -69673,16 +68912,8 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D62" s="43" t="inlineStr">
-        <is>
-          <t>New Moon</t>
-        </is>
-      </c>
-      <c r="E62" s="43" t="inlineStr">
-        <is>
-          <t>Rain</t>
-        </is>
-      </c>
+      <c r="D62" s="43"/>
+      <c r="E62" s="43"/>
       <c r="F62" s="43" t="inlineStr">
         <is>
           <t>Nightfall</t>
@@ -69704,7 +68935,7 @@
       </c>
       <c r="K62" s="37" t="inlineStr">
         <is>
-          <t>Wednesday · Nightfall</t>
+          <t xml:space="preserve">Wednesday · Nightfall</t>
         </is>
       </c>
       <c r="L62" s="43">
@@ -69740,14 +68971,10 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D63" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Crescent</t>
-        </is>
-      </c>
+      <c r="D63" s="43"/>
       <c r="E63" s="43" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t xml:space="preserve">Rainbow</t>
         </is>
       </c>
       <c r="F63" s="43" t="inlineStr">
@@ -69771,7 +68998,7 @@
       </c>
       <c r="K63" s="37" t="inlineStr">
         <is>
-          <t>Thursday · Waxing Moon</t>
+          <t xml:space="preserve">Thursday</t>
         </is>
       </c>
       <c r="L63" s="43">
@@ -69803,14 +69030,10 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D64" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Crescent</t>
-        </is>
-      </c>
+      <c r="D64" s="43"/>
       <c r="E64" s="43" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t xml:space="preserve">Rainbow</t>
         </is>
       </c>
       <c r="F64" s="43" t="inlineStr">
@@ -69834,7 +69057,7 @@
       </c>
       <c r="K64" s="37" t="inlineStr">
         <is>
-          <t>Rainbow (rare event) · Thursday</t>
+          <t xml:space="preserve">Rainbow (rare event) · Thursday</t>
         </is>
       </c>
       <c r="L64" s="43">
@@ -69866,16 +69089,8 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="D65" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Gibbous</t>
-        </is>
-      </c>
-      <c r="E65" s="43" t="inlineStr">
-        <is>
-          <t>Fog / Mist</t>
-        </is>
-      </c>
+      <c r="D65" s="43"/>
+      <c r="E65" s="43"/>
       <c r="F65" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -69897,7 +69112,7 @@
       </c>
       <c r="K65" s="37" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t xml:space="preserve">Friday</t>
         </is>
       </c>
       <c r="L65" s="43">
@@ -69931,12 +69146,12 @@
       </c>
       <c r="D66" s="43" t="inlineStr">
         <is>
-          <t>Full Moon</t>
+          <t xml:space="preserve">Pink Moon</t>
         </is>
       </c>
       <c r="E66" s="43" t="inlineStr">
         <is>
-          <t>Windy</t>
+          <t xml:space="preserve">Clear starry night</t>
         </is>
       </c>
       <c r="F66" s="43" t="inlineStr">
@@ -69960,7 +69175,7 @@
       </c>
       <c r="K66" s="37" t="inlineStr">
         <is>
-          <t>Saturday · Full Moon</t>
+          <t xml:space="preserve">Saturday · Full Moon</t>
         </is>
       </c>
       <c r="L66" s="43">
@@ -69994,12 +69209,12 @@
       </c>
       <c r="D67" s="43" t="inlineStr">
         <is>
-          <t>Full Moon</t>
+          <t xml:space="preserve">Pink Moon</t>
         </is>
       </c>
       <c r="E67" s="43" t="inlineStr">
         <is>
-          <t>Windy</t>
+          <t xml:space="preserve">Clear starry night</t>
         </is>
       </c>
       <c r="F67" s="43" t="inlineStr">
@@ -70023,7 +69238,7 @@
       </c>
       <c r="K67" s="37" t="inlineStr">
         <is>
-          <t>Saturday · Full Moon</t>
+          <t xml:space="preserve">Saturday · Full Moon</t>
         </is>
       </c>
       <c r="L67" s="43">
@@ -70057,12 +69272,12 @@
       </c>
       <c r="D68" s="43" t="inlineStr">
         <is>
-          <t>Full Moon</t>
+          <t xml:space="preserve">Pink Moon</t>
         </is>
       </c>
       <c r="E68" s="43" t="inlineStr">
         <is>
-          <t>Windy</t>
+          <t xml:space="preserve">Clear starry night</t>
         </is>
       </c>
       <c r="F68" s="43" t="inlineStr">
@@ -70086,7 +69301,7 @@
       </c>
       <c r="K68" s="37" t="inlineStr">
         <is>
-          <t>Pink Moon (April full moon)</t>
+          <t xml:space="preserve">Pink Moon (April full moon)</t>
         </is>
       </c>
       <c r="L68" s="43">
@@ -70118,16 +69333,8 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D69" s="43" t="inlineStr">
-        <is>
-          <t>Waning Gibbous</t>
-        </is>
-      </c>
-      <c r="E69" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D69" s="43"/>
+      <c r="E69" s="43"/>
       <c r="F69" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -70149,7 +69356,7 @@
       </c>
       <c r="K69" s="37" t="inlineStr">
         <is>
-          <t>Beltane</t>
+          <t xml:space="preserve">Beltane</t>
         </is>
       </c>
       <c r="L69" s="43">
@@ -70185,16 +69392,8 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D70" s="43" t="inlineStr">
-        <is>
-          <t>Waning Gibbous</t>
-        </is>
-      </c>
-      <c r="E70" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D70" s="43"/>
+      <c r="E70" s="43"/>
       <c r="F70" s="43" t="inlineStr">
         <is>
           <t>Noon</t>
@@ -70216,7 +69415,7 @@
       </c>
       <c r="K70" s="37" t="inlineStr">
         <is>
-          <t>Sunday · Noon · Clear &amp; sunny</t>
+          <t xml:space="preserve">Sunday · Noon</t>
         </is>
       </c>
       <c r="L70" s="43">
@@ -70248,16 +69447,8 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="D71" s="43" t="inlineStr">
-        <is>
-          <t>Waning Crescent</t>
-        </is>
-      </c>
-      <c r="E71" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D71" s="43"/>
+      <c r="E71" s="43"/>
       <c r="F71" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -70279,7 +69470,7 @@
       </c>
       <c r="K71" s="37" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t xml:space="preserve">Monday</t>
         </is>
       </c>
       <c r="L71" s="43">
@@ -70311,16 +69502,8 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="D72" s="43" t="inlineStr">
-        <is>
-          <t>Waning Crescent</t>
-        </is>
-      </c>
-      <c r="E72" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D72" s="43"/>
+      <c r="E72" s="43"/>
       <c r="F72" s="43" t="inlineStr">
         <is>
           <t>Nightfall</t>
@@ -70342,7 +69525,7 @@
       </c>
       <c r="K72" s="37" t="inlineStr">
         <is>
-          <t>Monday · Nightfall</t>
+          <t xml:space="preserve">Monday · Nightfall</t>
         </is>
       </c>
       <c r="L72" s="43">
@@ -70374,16 +69557,8 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D73" s="43" t="inlineStr">
-        <is>
-          <t>New Moon</t>
-        </is>
-      </c>
-      <c r="E73" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D73" s="43"/>
+      <c r="E73" s="43"/>
       <c r="F73" s="43" t="inlineStr">
         <is>
           <t>Twilight</t>
@@ -70405,7 +69580,7 @@
       </c>
       <c r="K73" s="37" t="inlineStr">
         <is>
-          <t>Twilight</t>
+          <t xml:space="preserve">Twilight</t>
         </is>
       </c>
       <c r="L73" s="43">
@@ -70437,16 +69612,8 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D74" s="43" t="inlineStr">
-        <is>
-          <t>New Moon</t>
-        </is>
-      </c>
-      <c r="E74" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D74" s="43"/>
+      <c r="E74" s="43"/>
       <c r="F74" s="43" t="inlineStr">
         <is>
           <t>Nightfall</t>
@@ -70468,7 +69635,7 @@
       </c>
       <c r="K74" s="37" t="inlineStr">
         <is>
-          <t>New Moon · Nightfall</t>
+          <t xml:space="preserve">Nightfall</t>
         </is>
       </c>
       <c r="L74" s="43">
@@ -70500,16 +69667,8 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D75" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Crescent</t>
-        </is>
-      </c>
-      <c r="E75" s="43" t="inlineStr">
-        <is>
-          <t>Fog / Mist</t>
-        </is>
-      </c>
+      <c r="D75" s="43"/>
+      <c r="E75" s="43"/>
       <c r="F75" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -70531,7 +69690,7 @@
       </c>
       <c r="K75" s="37" t="inlineStr">
         <is>
-          <t>Wednesday · Waxing Moon</t>
+          <t xml:space="preserve">Wednesday</t>
         </is>
       </c>
       <c r="L75" s="43">
@@ -70563,16 +69722,8 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D76" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Crescent</t>
-        </is>
-      </c>
-      <c r="E76" s="43" t="inlineStr">
-        <is>
-          <t>Fog / Mist</t>
-        </is>
-      </c>
+      <c r="D76" s="43"/>
+      <c r="E76" s="43"/>
       <c r="F76" s="43" t="inlineStr">
         <is>
           <t>Nightfall</t>
@@ -70594,7 +69745,7 @@
       </c>
       <c r="K76" s="37" t="inlineStr">
         <is>
-          <t>Fog / Mist · Nightfall</t>
+          <t xml:space="preserve">Nightfall</t>
         </is>
       </c>
       <c r="L76" s="43">
@@ -70626,16 +69777,8 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D77" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Gibbous</t>
-        </is>
-      </c>
-      <c r="E77" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D77" s="43"/>
+      <c r="E77" s="43"/>
       <c r="F77" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -70657,7 +69800,7 @@
       </c>
       <c r="K77" s="37" t="inlineStr">
         <is>
-          <t>Thursday · Waxing Gibbous</t>
+          <t xml:space="preserve">Thursday</t>
         </is>
       </c>
       <c r="L77" s="43">
@@ -70693,16 +69836,8 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D78" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Gibbous</t>
-        </is>
-      </c>
-      <c r="E78" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D78" s="43"/>
+      <c r="E78" s="43"/>
       <c r="F78" s="43" t="inlineStr">
         <is>
           <t>Noon</t>
@@ -70724,7 +69859,7 @@
       </c>
       <c r="K78" s="37" t="inlineStr">
         <is>
-          <t>Thursday · Waxing Gibbous · Noon</t>
+          <t xml:space="preserve">Thursday · Noon</t>
         </is>
       </c>
       <c r="L78" s="43">
@@ -70762,12 +69897,12 @@
       </c>
       <c r="D79" s="43" t="inlineStr">
         <is>
-          <t>Full Moon</t>
+          <t xml:space="preserve">Flower Moon</t>
         </is>
       </c>
       <c r="E79" s="43" t="inlineStr">
         <is>
-          <t>Clear &amp; sunny</t>
+          <t xml:space="preserve">Clear starry night</t>
         </is>
       </c>
       <c r="F79" s="43" t="inlineStr">
@@ -70791,7 +69926,7 @@
       </c>
       <c r="K79" s="37" t="inlineStr">
         <is>
-          <t>Friday · Full Moon</t>
+          <t xml:space="preserve">Friday · Full Moon</t>
         </is>
       </c>
       <c r="L79" s="43">
@@ -70825,12 +69960,12 @@
       </c>
       <c r="D80" s="43" t="inlineStr">
         <is>
-          <t>Full Moon</t>
+          <t xml:space="preserve">Flower Moon</t>
         </is>
       </c>
       <c r="E80" s="43" t="inlineStr">
         <is>
-          <t>Clear &amp; sunny</t>
+          <t xml:space="preserve">Clear starry night</t>
         </is>
       </c>
       <c r="F80" s="43" t="inlineStr">
@@ -70854,7 +69989,7 @@
       </c>
       <c r="K80" s="37" t="inlineStr">
         <is>
-          <t>Friday · Full Moon</t>
+          <t xml:space="preserve">Friday · Full Moon</t>
         </is>
       </c>
       <c r="L80" s="43">
@@ -70892,12 +70027,12 @@
       </c>
       <c r="D81" s="43" t="inlineStr">
         <is>
-          <t>Full Moon</t>
+          <t xml:space="preserve">Flower Moon</t>
         </is>
       </c>
       <c r="E81" s="43" t="inlineStr">
         <is>
-          <t>Clear &amp; sunny</t>
+          <t xml:space="preserve">Clear starry night</t>
         </is>
       </c>
       <c r="F81" s="43" t="inlineStr">
@@ -70921,7 +70056,7 @@
       </c>
       <c r="K81" s="37" t="inlineStr">
         <is>
-          <t>Friday · Full Moon</t>
+          <t xml:space="preserve">Friday · Full Moon</t>
         </is>
       </c>
       <c r="L81" s="43">
@@ -70955,12 +70090,12 @@
       </c>
       <c r="D82" s="43" t="inlineStr">
         <is>
-          <t>Full Moon</t>
+          <t xml:space="preserve">Flower Moon</t>
         </is>
       </c>
       <c r="E82" s="43" t="inlineStr">
         <is>
-          <t>Clear &amp; sunny</t>
+          <t xml:space="preserve">Clear starry night</t>
         </is>
       </c>
       <c r="F82" s="43" t="inlineStr">
@@ -70984,7 +70119,7 @@
       </c>
       <c r="K82" s="37" t="inlineStr">
         <is>
-          <t>Flower Moon (May full moon)</t>
+          <t xml:space="preserve">Flower Moon (May full moon)</t>
         </is>
       </c>
       <c r="L82" s="43">
@@ -71016,16 +70151,8 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D83" s="43" t="inlineStr">
-        <is>
-          <t>Waning Gibbous</t>
-        </is>
-      </c>
-      <c r="E83" s="43" t="inlineStr">
-        <is>
-          <t>Windy</t>
-        </is>
-      </c>
+      <c r="D83" s="43"/>
+      <c r="E83" s="43"/>
       <c r="F83" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -71047,7 +70174,7 @@
       </c>
       <c r="K83" s="37" t="inlineStr">
         <is>
-          <t>Saturday · Waning Moon</t>
+          <t xml:space="preserve">Saturday</t>
         </is>
       </c>
       <c r="L83" s="43">
@@ -71079,16 +70206,8 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D84" s="43" t="inlineStr">
-        <is>
-          <t>Waning Gibbous</t>
-        </is>
-      </c>
-      <c r="E84" s="43" t="inlineStr">
-        <is>
-          <t>Windy</t>
-        </is>
-      </c>
+      <c r="D84" s="43"/>
+      <c r="E84" s="43"/>
       <c r="F84" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -71110,7 +70229,7 @@
       </c>
       <c r="K84" s="37" t="inlineStr">
         <is>
-          <t>Saturday · Waning Moon</t>
+          <t xml:space="preserve">Saturday</t>
         </is>
       </c>
       <c r="L84" s="43">
@@ -71142,16 +70261,8 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D85" s="43" t="inlineStr">
-        <is>
-          <t>Waning Gibbous</t>
-        </is>
-      </c>
-      <c r="E85" s="43" t="inlineStr">
-        <is>
-          <t>Windy</t>
-        </is>
-      </c>
+      <c r="D85" s="43"/>
+      <c r="E85" s="43"/>
       <c r="F85" s="43" t="inlineStr">
         <is>
           <t>Noon</t>
@@ -71173,7 +70284,7 @@
       </c>
       <c r="K85" s="37" t="inlineStr">
         <is>
-          <t>Saturday · Waning Gibbous</t>
+          <t xml:space="preserve">Saturday</t>
         </is>
       </c>
       <c r="L85" s="43">
@@ -71201,16 +70312,8 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D86" s="43" t="inlineStr">
-        <is>
-          <t>Waning Crescent</t>
-        </is>
-      </c>
-      <c r="E86" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D86" s="43"/>
+      <c r="E86" s="43"/>
       <c r="F86" s="43" t="inlineStr">
         <is>
           <t>Noon</t>
@@ -71232,7 +70335,7 @@
       </c>
       <c r="K86" s="37" t="inlineStr">
         <is>
-          <t>Sunday · Noon</t>
+          <t xml:space="preserve">Sunday · Noon</t>
         </is>
       </c>
       <c r="L86" s="43">
@@ -71264,16 +70367,8 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D87" s="43" t="inlineStr">
-        <is>
-          <t>Waning Crescent</t>
-        </is>
-      </c>
-      <c r="E87" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D87" s="43"/>
+      <c r="E87" s="43"/>
       <c r="F87" s="43" t="inlineStr">
         <is>
           <t>Nightfall</t>
@@ -71295,7 +70390,7 @@
       </c>
       <c r="K87" s="37" t="inlineStr">
         <is>
-          <t>Clear starry night</t>
+          <t xml:space="preserve">Clear starry night</t>
         </is>
       </c>
       <c r="L87" s="43">
@@ -71323,16 +70418,8 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="D88" s="43" t="inlineStr">
-        <is>
-          <t>New Moon</t>
-        </is>
-      </c>
-      <c r="E88" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D88" s="43"/>
+      <c r="E88" s="43"/>
       <c r="F88" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -71354,7 +70441,7 @@
       </c>
       <c r="K88" s="37" t="inlineStr">
         <is>
-          <t>Sunrise · New Moon</t>
+          <t xml:space="preserve">Sunrise</t>
         </is>
       </c>
       <c r="L88" s="43">
@@ -71382,16 +70469,8 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="D89" s="43" t="inlineStr">
-        <is>
-          <t>New Moon</t>
-        </is>
-      </c>
-      <c r="E89" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D89" s="43"/>
+      <c r="E89" s="43"/>
       <c r="F89" s="43" t="inlineStr">
         <is>
           <t>Noon</t>
@@ -71413,7 +70492,7 @@
       </c>
       <c r="K89" s="37" t="inlineStr">
         <is>
-          <t>Monday · New Moon</t>
+          <t xml:space="preserve">Monday</t>
         </is>
       </c>
       <c r="L89" s="43">
@@ -71441,16 +70520,8 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D90" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Crescent</t>
-        </is>
-      </c>
-      <c r="E90" s="43" t="inlineStr">
-        <is>
-          <t>Thunderstorm</t>
-        </is>
-      </c>
+      <c r="D90" s="43"/>
+      <c r="E90" s="43"/>
       <c r="F90" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -71476,7 +70547,7 @@
       </c>
       <c r="K90" s="37" t="inlineStr">
         <is>
-          <t>Sunrise</t>
+          <t xml:space="preserve">Sunrise</t>
         </is>
       </c>
       <c r="L90" s="43">
@@ -71504,16 +70575,8 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D91" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Gibbous</t>
-        </is>
-      </c>
-      <c r="E91" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D91" s="43"/>
+      <c r="E91" s="43"/>
       <c r="F91" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -71535,7 +70598,7 @@
       </c>
       <c r="K91" s="37" t="inlineStr">
         <is>
-          <t>after Rain</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L91" s="43">
@@ -71567,16 +70630,8 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D92" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Gibbous</t>
-        </is>
-      </c>
-      <c r="E92" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D92" s="43"/>
+      <c r="E92" s="43"/>
       <c r="F92" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -71598,7 +70653,7 @@
       </c>
       <c r="K92" s="37" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t xml:space="preserve">Wednesday</t>
         </is>
       </c>
       <c r="L92" s="43">
@@ -71628,12 +70683,12 @@
       </c>
       <c r="D93" s="43" t="inlineStr">
         <is>
-          <t>Full Moon</t>
+          <t xml:space="preserve">Strawberry Moon</t>
         </is>
       </c>
       <c r="E93" s="43" t="inlineStr">
         <is>
-          <t>Clear &amp; sunny</t>
+          <t xml:space="preserve">Clear starry night</t>
         </is>
       </c>
       <c r="F93" s="43" t="inlineStr">
@@ -71657,7 +70712,7 @@
       </c>
       <c r="K93" s="37" t="inlineStr">
         <is>
-          <t>Any equinox or solstice (Ostara, Litha, Mabon, Yule)</t>
+          <t xml:space="preserve">Any equinox or solstice (Ostara, Litha, Mabon, Yule)</t>
         </is>
       </c>
       <c r="L93" s="43">
@@ -71691,12 +70746,12 @@
       </c>
       <c r="D94" s="43" t="inlineStr">
         <is>
-          <t>Full Moon</t>
+          <t xml:space="preserve">Strawberry Moon</t>
         </is>
       </c>
       <c r="E94" s="43" t="inlineStr">
         <is>
-          <t>Clear &amp; sunny</t>
+          <t xml:space="preserve">Clear starry night</t>
         </is>
       </c>
       <c r="F94" s="43" t="inlineStr">
@@ -71720,7 +70775,7 @@
       </c>
       <c r="K94" s="37" t="inlineStr">
         <is>
-          <t>Full Moon</t>
+          <t xml:space="preserve">Full Moon</t>
         </is>
       </c>
       <c r="L94" s="43">
@@ -71750,12 +70805,12 @@
       </c>
       <c r="D95" s="43" t="inlineStr">
         <is>
-          <t>Full Moon</t>
+          <t xml:space="preserve">Strawberry Moon</t>
         </is>
       </c>
       <c r="E95" s="43" t="inlineStr">
         <is>
-          <t>Clear &amp; sunny</t>
+          <t xml:space="preserve">Clear starry night</t>
         </is>
       </c>
       <c r="F95" s="43" t="inlineStr">
@@ -71783,7 +70838,7 @@
       </c>
       <c r="K95" s="37" t="inlineStr">
         <is>
-          <t>Clear starry night · Full Moon</t>
+          <t xml:space="preserve">Clear starry night · Full Moon</t>
         </is>
       </c>
       <c r="L95" s="43">
@@ -71815,16 +70870,8 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="D96" s="43" t="inlineStr">
-        <is>
-          <t>Waning Gibbous</t>
-        </is>
-      </c>
-      <c r="E96" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D96" s="43"/>
+      <c r="E96" s="43"/>
       <c r="F96" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -71846,7 +70893,7 @@
       </c>
       <c r="K96" s="37" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t xml:space="preserve">Friday</t>
         </is>
       </c>
       <c r="L96" s="43">
@@ -71878,16 +70925,8 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="D97" s="43" t="inlineStr">
-        <is>
-          <t>Waning Gibbous</t>
-        </is>
-      </c>
-      <c r="E97" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D97" s="43"/>
+      <c r="E97" s="43"/>
       <c r="F97" s="43" t="inlineStr">
         <is>
           <t>Twilight</t>
@@ -71909,7 +70948,7 @@
       </c>
       <c r="K97" s="37" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t xml:space="preserve">Friday</t>
         </is>
       </c>
       <c r="L97" s="43">
@@ -71941,16 +70980,8 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D98" s="43" t="inlineStr">
-        <is>
-          <t>Waning Crescent</t>
-        </is>
-      </c>
-      <c r="E98" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D98" s="43"/>
+      <c r="E98" s="43"/>
       <c r="F98" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -71972,7 +71003,7 @@
       </c>
       <c r="K98" s="37" t="inlineStr">
         <is>
-          <t>Saturday · Waning Moon</t>
+          <t xml:space="preserve">Saturday</t>
         </is>
       </c>
       <c r="L98" s="43">
@@ -72004,16 +71035,8 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D99" s="43" t="inlineStr">
-        <is>
-          <t>Waning Crescent</t>
-        </is>
-      </c>
-      <c r="E99" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D99" s="43"/>
+      <c r="E99" s="43"/>
       <c r="F99" s="43" t="inlineStr">
         <is>
           <t>Noon</t>
@@ -72035,7 +71058,7 @@
       </c>
       <c r="K99" s="37" t="inlineStr">
         <is>
-          <t>Saturday · Waning Moon</t>
+          <t xml:space="preserve">Saturday</t>
         </is>
       </c>
       <c r="L99" s="43">
@@ -72071,16 +71094,8 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D100" s="43" t="inlineStr">
-        <is>
-          <t>Waning Crescent</t>
-        </is>
-      </c>
-      <c r="E100" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D100" s="43"/>
+      <c r="E100" s="43"/>
       <c r="F100" s="43" t="inlineStr">
         <is>
           <t>Twilight</t>
@@ -72102,7 +71117,7 @@
       </c>
       <c r="K100" s="37" t="inlineStr">
         <is>
-          <t>Saturday · Waning Moon · Twilight</t>
+          <t xml:space="preserve">Saturday · Twilight</t>
         </is>
       </c>
       <c r="L100" s="43">
@@ -72134,16 +71149,8 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D101" s="43" t="inlineStr">
-        <is>
-          <t>New Moon</t>
-        </is>
-      </c>
-      <c r="E101" s="43" t="inlineStr">
-        <is>
-          <t>Windy</t>
-        </is>
-      </c>
+      <c r="D101" s="43"/>
+      <c r="E101" s="43"/>
       <c r="F101" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -72169,7 +71176,7 @@
       </c>
       <c r="K101" s="37" t="inlineStr">
         <is>
-          <t>Windy</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L101" s="43">
@@ -72201,16 +71208,8 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D102" s="43" t="inlineStr">
-        <is>
-          <t>New Moon</t>
-        </is>
-      </c>
-      <c r="E102" s="43" t="inlineStr">
-        <is>
-          <t>Windy</t>
-        </is>
-      </c>
+      <c r="D102" s="43"/>
+      <c r="E102" s="43"/>
       <c r="F102" s="43" t="inlineStr">
         <is>
           <t>Nightfall</t>
@@ -72232,7 +71231,7 @@
       </c>
       <c r="K102" s="37" t="inlineStr">
         <is>
-          <t>Dark Moon · Nightfall</t>
+          <t xml:space="preserve">Nightfall</t>
         </is>
       </c>
       <c r="L102" s="43">
@@ -72260,14 +71259,10 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="D103" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Crescent</t>
-        </is>
-      </c>
+      <c r="D103" s="43"/>
       <c r="E103" s="43" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t xml:space="preserve">Rainbow</t>
         </is>
       </c>
       <c r="F103" s="43" t="inlineStr">
@@ -72291,7 +71286,7 @@
       </c>
       <c r="K103" s="37" t="inlineStr">
         <is>
-          <t>Rainbow (rare event)</t>
+          <t xml:space="preserve">Rainbow (rare event)</t>
         </is>
       </c>
       <c r="L103" s="43">
@@ -72319,14 +71314,10 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="D104" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Crescent</t>
-        </is>
-      </c>
+      <c r="D104" s="43"/>
       <c r="E104" s="43" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t xml:space="preserve">Rainbow</t>
         </is>
       </c>
       <c r="F104" s="43" t="inlineStr">
@@ -72350,7 +71341,7 @@
       </c>
       <c r="K104" s="37" t="inlineStr">
         <is>
-          <t>Monday · Nightfall</t>
+          <t xml:space="preserve">Monday · Nightfall</t>
         </is>
       </c>
       <c r="L104" s="43">
@@ -72378,16 +71369,8 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D105" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Gibbous</t>
-        </is>
-      </c>
-      <c r="E105" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D105" s="43"/>
+      <c r="E105" s="43"/>
       <c r="F105" s="43" t="inlineStr">
         <is>
           <t>Nightfall</t>
@@ -72409,7 +71392,7 @@
       </c>
       <c r="K105" s="37" t="inlineStr">
         <is>
-          <t>Clear starry night</t>
+          <t xml:space="preserve">Clear starry night</t>
         </is>
       </c>
       <c r="L105" s="43">
@@ -72443,12 +71426,12 @@
       </c>
       <c r="D106" s="43" t="inlineStr">
         <is>
-          <t>Full Moon</t>
+          <t xml:space="preserve">Buck Moon</t>
         </is>
       </c>
       <c r="E106" s="43" t="inlineStr">
         <is>
-          <t>Clear &amp; sunny</t>
+          <t xml:space="preserve">Clear starry night</t>
         </is>
       </c>
       <c r="F106" s="43" t="inlineStr">
@@ -72472,7 +71455,7 @@
       </c>
       <c r="K106" s="37" t="inlineStr">
         <is>
-          <t>Buck Moon (July full moon)</t>
+          <t xml:space="preserve">Buck Moon (July full moon)</t>
         </is>
       </c>
       <c r="L106" s="43">
@@ -72506,12 +71489,12 @@
       </c>
       <c r="D107" s="43" t="inlineStr">
         <is>
-          <t>Full Moon</t>
+          <t xml:space="preserve">Buck Moon</t>
         </is>
       </c>
       <c r="E107" s="43" t="inlineStr">
         <is>
-          <t>Clear &amp; sunny</t>
+          <t xml:space="preserve">Clear starry night</t>
         </is>
       </c>
       <c r="F107" s="43" t="inlineStr">
@@ -72539,7 +71522,7 @@
       </c>
       <c r="K107" s="37" t="inlineStr">
         <is>
-          <t>Clear starry night · Full Moon</t>
+          <t xml:space="preserve">Clear starry night · Full Moon</t>
         </is>
       </c>
       <c r="L107" s="43">
@@ -72571,16 +71554,8 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D108" s="43" t="inlineStr">
-        <is>
-          <t>Waning Gibbous</t>
-        </is>
-      </c>
-      <c r="E108" s="43" t="inlineStr">
-        <is>
-          <t>Rain</t>
-        </is>
-      </c>
+      <c r="D108" s="43"/>
+      <c r="E108" s="43"/>
       <c r="F108" s="43" t="inlineStr">
         <is>
           <t>Noon</t>
@@ -72602,7 +71577,7 @@
       </c>
       <c r="K108" s="37" t="inlineStr">
         <is>
-          <t>Waning Moon · Rain</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L108" s="43">
@@ -72630,16 +71605,8 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D109" s="43" t="inlineStr">
-        <is>
-          <t>Waning Gibbous</t>
-        </is>
-      </c>
-      <c r="E109" s="43" t="inlineStr">
-        <is>
-          <t>Rain</t>
-        </is>
-      </c>
+      <c r="D109" s="43"/>
+      <c r="E109" s="43"/>
       <c r="F109" s="43" t="inlineStr">
         <is>
           <t>Nightfall</t>
@@ -72661,7 +71628,7 @@
       </c>
       <c r="K109" s="37" t="inlineStr">
         <is>
-          <t>Rain · Waning Gibbous</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L109" s="43">
@@ -72689,16 +71656,8 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="D110" s="43" t="inlineStr">
-        <is>
-          <t>Waning Crescent</t>
-        </is>
-      </c>
-      <c r="E110" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D110" s="43"/>
+      <c r="E110" s="43"/>
       <c r="F110" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -72720,7 +71679,7 @@
       </c>
       <c r="K110" s="37" t="inlineStr">
         <is>
-          <t>Friday · Sunrise</t>
+          <t xml:space="preserve">Friday · Sunrise</t>
         </is>
       </c>
       <c r="L110" s="43">
@@ -72748,16 +71707,8 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="D111" s="43" t="inlineStr">
-        <is>
-          <t>Waning Crescent</t>
-        </is>
-      </c>
-      <c r="E111" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D111" s="43"/>
+      <c r="E111" s="43"/>
       <c r="F111" s="43" t="inlineStr">
         <is>
           <t>Nightfall</t>
@@ -72779,7 +71730,7 @@
       </c>
       <c r="K111" s="37" t="inlineStr">
         <is>
-          <t>Clear starry night</t>
+          <t xml:space="preserve">Clear starry night</t>
         </is>
       </c>
       <c r="L111" s="43">
@@ -72807,14 +71758,10 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D112" s="43" t="inlineStr">
-        <is>
-          <t>New Moon</t>
-        </is>
-      </c>
+      <c r="D112" s="43"/>
       <c r="E112" s="43" t="inlineStr">
         <is>
-          <t>Clear &amp; sunny</t>
+          <t xml:space="preserve">Shooting stars; Clear starry night</t>
         </is>
       </c>
       <c r="F112" s="43" t="inlineStr">
@@ -72838,7 +71785,7 @@
       </c>
       <c r="K112" s="37" t="inlineStr">
         <is>
-          <t>Sunrise · Clear &amp; sunny</t>
+          <t xml:space="preserve">Sunrise</t>
         </is>
       </c>
       <c r="L112" s="43">
@@ -72866,14 +71813,10 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D113" s="43" t="inlineStr">
-        <is>
-          <t>New Moon</t>
-        </is>
-      </c>
+      <c r="D113" s="43"/>
       <c r="E113" s="43" t="inlineStr">
         <is>
-          <t>Clear &amp; sunny</t>
+          <t xml:space="preserve">Shooting stars; Clear starry night</t>
         </is>
       </c>
       <c r="F113" s="43" t="inlineStr">
@@ -72897,7 +71840,7 @@
       </c>
       <c r="K113" s="37" t="inlineStr">
         <is>
-          <t>Shooting star (rare event)</t>
+          <t xml:space="preserve">Shooting star (rare event)</t>
         </is>
       </c>
       <c r="L113" s="43">
@@ -72929,14 +71872,10 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D114" s="43" t="inlineStr">
-        <is>
-          <t>New Moon</t>
-        </is>
-      </c>
+      <c r="D114" s="43"/>
       <c r="E114" s="43" t="inlineStr">
         <is>
-          <t>Clear &amp; sunny</t>
+          <t xml:space="preserve">Shooting stars; Clear starry night</t>
         </is>
       </c>
       <c r="F114" s="43" t="inlineStr">
@@ -72960,7 +71899,7 @@
       </c>
       <c r="K114" s="37" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t xml:space="preserve">Saturday</t>
         </is>
       </c>
       <c r="L114" s="43">
@@ -72992,14 +71931,10 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D115" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Crescent</t>
-        </is>
-      </c>
+      <c r="D115" s="43"/>
       <c r="E115" s="43" t="inlineStr">
         <is>
-          <t>Clear &amp; sunny</t>
+          <t xml:space="preserve">Shooting stars; Clear starry night</t>
         </is>
       </c>
       <c r="F115" s="43" t="inlineStr">
@@ -73023,7 +71958,7 @@
       </c>
       <c r="K115" s="37" t="inlineStr">
         <is>
-          <t>Any time</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L115" s="43">
@@ -73051,14 +71986,10 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D116" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Crescent</t>
-        </is>
-      </c>
+      <c r="D116" s="43"/>
       <c r="E116" s="43" t="inlineStr">
         <is>
-          <t>Clear &amp; sunny</t>
+          <t xml:space="preserve">Shooting stars; Clear starry night</t>
         </is>
       </c>
       <c r="F116" s="43" t="inlineStr">
@@ -73082,7 +72013,7 @@
       </c>
       <c r="K116" s="37" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t xml:space="preserve">Sunday</t>
         </is>
       </c>
       <c r="L116" s="43">
@@ -73110,14 +72041,10 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="D117" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Gibbous</t>
-        </is>
-      </c>
+      <c r="D117" s="43"/>
       <c r="E117" s="43" t="inlineStr">
         <is>
-          <t>Thunderstorm</t>
+          <t xml:space="preserve">Shooting stars</t>
         </is>
       </c>
       <c r="F117" s="43" t="inlineStr">
@@ -73141,7 +72068,7 @@
       </c>
       <c r="K117" s="37" t="inlineStr">
         <is>
-          <t>Any time</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L117" s="43">
@@ -73169,14 +72096,10 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="D118" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Gibbous</t>
-        </is>
-      </c>
+      <c r="D118" s="43"/>
       <c r="E118" s="43" t="inlineStr">
         <is>
-          <t>Thunderstorm</t>
+          <t xml:space="preserve">Shooting stars</t>
         </is>
       </c>
       <c r="F118" s="43" t="inlineStr">
@@ -73200,7 +72123,7 @@
       </c>
       <c r="K118" s="37" t="inlineStr">
         <is>
-          <t>Any time</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L118" s="43">
@@ -73230,12 +72153,12 @@
       </c>
       <c r="D119" s="43" t="inlineStr">
         <is>
-          <t>Full Moon</t>
+          <t xml:space="preserve">Sturgeon Moon</t>
         </is>
       </c>
       <c r="E119" s="43" t="inlineStr">
         <is>
-          <t>Clear &amp; sunny</t>
+          <t xml:space="preserve">Blue Moon; Clear starry night</t>
         </is>
       </c>
       <c r="F119" s="43" t="inlineStr">
@@ -73263,7 +72186,7 @@
       </c>
       <c r="K119" s="37" t="inlineStr">
         <is>
-          <t>Sturgeon Moon (August full moon)</t>
+          <t xml:space="preserve">Sturgeon Moon (August full moon)</t>
         </is>
       </c>
       <c r="L119" s="43">
@@ -73297,12 +72220,12 @@
       </c>
       <c r="D120" s="43" t="inlineStr">
         <is>
-          <t>Full Moon</t>
+          <t xml:space="preserve">Sturgeon Moon</t>
         </is>
       </c>
       <c r="E120" s="43" t="inlineStr">
         <is>
-          <t>Clear &amp; sunny</t>
+          <t xml:space="preserve">Blue Moon; Clear starry night</t>
         </is>
       </c>
       <c r="F120" s="43" t="inlineStr">
@@ -73326,7 +72249,7 @@
       </c>
       <c r="K120" s="37" t="inlineStr">
         <is>
-          <t>Full Moon · Clear starry night</t>
+          <t xml:space="preserve">Full Moon · Clear starry night</t>
         </is>
       </c>
       <c r="L120" s="43">
@@ -73354,16 +72277,8 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D121" s="43" t="inlineStr">
-        <is>
-          <t>Waning Gibbous</t>
-        </is>
-      </c>
-      <c r="E121" s="43" t="inlineStr">
-        <is>
-          <t>Rain</t>
-        </is>
-      </c>
+      <c r="D121" s="43"/>
+      <c r="E121" s="43"/>
       <c r="F121" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -73389,7 +72304,7 @@
       </c>
       <c r="K121" s="37" t="inlineStr">
         <is>
-          <t>Sunrise the morning after a Full Moon</t>
+          <t xml:space="preserve">Sunrise the morning after a Full Moon</t>
         </is>
       </c>
       <c r="L121" s="43">
@@ -73417,16 +72332,8 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D122" s="43" t="inlineStr">
-        <is>
-          <t>Waning Gibbous</t>
-        </is>
-      </c>
-      <c r="E122" s="43" t="inlineStr">
-        <is>
-          <t>Rain</t>
-        </is>
-      </c>
+      <c r="D122" s="43"/>
+      <c r="E122" s="43"/>
       <c r="F122" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -73452,7 +72359,7 @@
       </c>
       <c r="K122" s="37" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t xml:space="preserve">Wednesday</t>
         </is>
       </c>
       <c r="L122" s="43">
@@ -73484,16 +72391,8 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D123" s="43" t="inlineStr">
-        <is>
-          <t>Waning Crescent</t>
-        </is>
-      </c>
-      <c r="E123" s="43" t="inlineStr">
-        <is>
-          <t>Fog / Mist</t>
-        </is>
-      </c>
+      <c r="D123" s="43"/>
+      <c r="E123" s="43"/>
       <c r="F123" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -73515,7 +72414,7 @@
       </c>
       <c r="K123" s="37" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t xml:space="preserve">Thursday</t>
         </is>
       </c>
       <c r="L123" s="43">
@@ -73543,16 +72442,8 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D124" s="43" t="inlineStr">
-        <is>
-          <t>Waning Crescent</t>
-        </is>
-      </c>
-      <c r="E124" s="43" t="inlineStr">
-        <is>
-          <t>Fog / Mist</t>
-        </is>
-      </c>
+      <c r="D124" s="43"/>
+      <c r="E124" s="43"/>
       <c r="F124" s="43" t="inlineStr">
         <is>
           <t>Nightfall</t>
@@ -73574,7 +72465,7 @@
       </c>
       <c r="K124" s="37" t="inlineStr">
         <is>
-          <t>Thursday · Nightfall</t>
+          <t xml:space="preserve">Thursday · Nightfall</t>
         </is>
       </c>
       <c r="L124" s="43">
@@ -73602,16 +72493,8 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="D125" s="43" t="inlineStr">
-        <is>
-          <t>New Moon</t>
-        </is>
-      </c>
-      <c r="E125" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D125" s="43"/>
+      <c r="E125" s="43"/>
       <c r="F125" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -73633,7 +72516,7 @@
       </c>
       <c r="K125" s="37" t="inlineStr">
         <is>
-          <t>Any time</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L125" s="43">
@@ -73661,16 +72544,8 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="D126" s="43" t="inlineStr">
-        <is>
-          <t>New Moon</t>
-        </is>
-      </c>
-      <c r="E126" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D126" s="43"/>
+      <c r="E126" s="43"/>
       <c r="F126" s="43" t="inlineStr">
         <is>
           <t>Noon</t>
@@ -73692,7 +72567,7 @@
       </c>
       <c r="K126" s="37" t="inlineStr">
         <is>
-          <t>New Moon</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L126" s="43">
@@ -73720,16 +72595,8 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="D127" s="43" t="inlineStr">
-        <is>
-          <t>New Moon</t>
-        </is>
-      </c>
-      <c r="E127" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D127" s="43"/>
+      <c r="E127" s="43"/>
       <c r="F127" s="43" t="inlineStr">
         <is>
           <t>Nightfall</t>
@@ -73751,7 +72618,7 @@
       </c>
       <c r="K127" s="37" t="inlineStr">
         <is>
-          <t>Dark Moon · Nightfall</t>
+          <t xml:space="preserve">Nightfall</t>
         </is>
       </c>
       <c r="L127" s="43">
@@ -73779,16 +72646,8 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D128" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Crescent</t>
-        </is>
-      </c>
-      <c r="E128" s="43" t="inlineStr">
-        <is>
-          <t>Windy</t>
-        </is>
-      </c>
+      <c r="D128" s="43"/>
+      <c r="E128" s="43"/>
       <c r="F128" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -73810,7 +72669,7 @@
       </c>
       <c r="K128" s="37" t="inlineStr">
         <is>
-          <t>Mabon</t>
+          <t xml:space="preserve">Mabon</t>
         </is>
       </c>
       <c r="L128" s="43">
@@ -73846,16 +72705,8 @@
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D129" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Crescent</t>
-        </is>
-      </c>
-      <c r="E129" s="43" t="inlineStr">
-        <is>
-          <t>Windy</t>
-        </is>
-      </c>
+      <c r="D129" s="43"/>
+      <c r="E129" s="43"/>
       <c r="F129" s="43" t="inlineStr">
         <is>
           <t>Nightfall</t>
@@ -73877,7 +72728,7 @@
       </c>
       <c r="K129" s="37" t="inlineStr">
         <is>
-          <t>Clear starry night</t>
+          <t xml:space="preserve">Clear starry night</t>
         </is>
       </c>
       <c r="L129" s="43">
@@ -73909,16 +72760,8 @@
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D130" s="43" t="inlineStr">
-        <is>
-          <t>Waxing Gibbous</t>
-        </is>
-      </c>
-      <c r="E130" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D130" s="43"/>
+      <c r="E130" s="43"/>
       <c r="F130" s="43" t="inlineStr">
         <is>
           <t>Noon</t>
@@ -73940,7 +72783,7 @@
       </c>
       <c r="K130" s="37" t="inlineStr">
         <is>
-          <t>Any time</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L130" s="43">
@@ -73970,12 +72813,12 @@
       </c>
       <c r="D131" s="43" t="inlineStr">
         <is>
-          <t>Full Moon</t>
+          <t xml:space="preserve">Harvest Moon</t>
         </is>
       </c>
       <c r="E131" s="43" t="inlineStr">
         <is>
-          <t>Clear &amp; sunny</t>
+          <t xml:space="preserve">Clear starry night</t>
         </is>
       </c>
       <c r="F131" s="43" t="inlineStr">
@@ -73999,7 +72842,7 @@
       </c>
       <c r="K131" s="37" t="inlineStr">
         <is>
-          <t>Harvest Moon (September full moon)</t>
+          <t xml:space="preserve">Harvest Moon (September full moon)</t>
         </is>
       </c>
       <c r="L131" s="43">
@@ -74033,12 +72876,12 @@
       </c>
       <c r="D132" s="43" t="inlineStr">
         <is>
-          <t>Full Moon</t>
+          <t xml:space="preserve">Harvest Moon</t>
         </is>
       </c>
       <c r="E132" s="43" t="inlineStr">
         <is>
-          <t>Clear &amp; sunny</t>
+          <t xml:space="preserve">Clear starry night</t>
         </is>
       </c>
       <c r="F132" s="43" t="inlineStr">
@@ -74062,7 +72905,7 @@
       </c>
       <c r="K132" s="37" t="inlineStr">
         <is>
-          <t>Monday · Full Moon</t>
+          <t xml:space="preserve">Monday · Full Moon</t>
         </is>
       </c>
       <c r="L132" s="43">
@@ -74096,12 +72939,12 @@
       </c>
       <c r="D133" s="43" t="inlineStr">
         <is>
-          <t>Full Moon</t>
+          <t xml:space="preserve">Harvest Moon</t>
         </is>
       </c>
       <c r="E133" s="43" t="inlineStr">
         <is>
-          <t>Clear &amp; sunny</t>
+          <t xml:space="preserve">Clear starry night</t>
         </is>
       </c>
       <c r="F133" s="43" t="inlineStr">
@@ -74125,7 +72968,7 @@
       </c>
       <c r="K133" s="37" t="inlineStr">
         <is>
-          <t>Monday · Full Moon</t>
+          <t xml:space="preserve">Monday · Full Moon</t>
         </is>
       </c>
       <c r="L133" s="43">
@@ -74159,12 +73002,12 @@
       </c>
       <c r="D134" s="43" t="inlineStr">
         <is>
-          <t>Full Moon</t>
+          <t xml:space="preserve">Harvest Moon</t>
         </is>
       </c>
       <c r="E134" s="43" t="inlineStr">
         <is>
-          <t>Clear &amp; sunny</t>
+          <t xml:space="preserve">Clear starry night</t>
         </is>
       </c>
       <c r="F134" s="43" t="inlineStr">
@@ -74192,7 +73035,7 @@
       </c>
       <c r="K134" s="37" t="inlineStr">
         <is>
-          <t>Monday · Full Moon · Nightfall</t>
+          <t xml:space="preserve">Monday · Full Moon · Nightfall</t>
         </is>
       </c>
       <c r="L134" s="43">
@@ -74220,16 +73063,8 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D135" s="43" t="inlineStr">
-        <is>
-          <t>Waning Gibbous</t>
-        </is>
-      </c>
-      <c r="E135" s="43" t="inlineStr">
-        <is>
-          <t>Rain</t>
-        </is>
-      </c>
+      <c r="D135" s="43"/>
+      <c r="E135" s="43"/>
       <c r="F135" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -74251,7 +73086,7 @@
       </c>
       <c r="K135" s="37" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L135" s="43">
@@ -74279,16 +73114,8 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D136" s="43" t="inlineStr">
-        <is>
-          <t>Waning Gibbous</t>
-        </is>
-      </c>
-      <c r="E136" s="43" t="inlineStr">
-        <is>
-          <t>Rain</t>
-        </is>
-      </c>
+      <c r="D136" s="43"/>
+      <c r="E136" s="43"/>
       <c r="F136" s="43" t="inlineStr">
         <is>
           <t>Noon</t>
@@ -74310,7 +73137,7 @@
       </c>
       <c r="K136" s="37" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L136" s="43">
@@ -74338,16 +73165,8 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D137" s="43" t="inlineStr">
-        <is>
-          <t>Waning Gibbous</t>
-        </is>
-      </c>
-      <c r="E137" s="43" t="inlineStr">
-        <is>
-          <t>Rain</t>
-        </is>
-      </c>
+      <c r="D137" s="43"/>
+      <c r="E137" s="43"/>
       <c r="F137" s="43" t="inlineStr">
         <is>
           <t>Nightfall</t>
@@ -74369,7 +73188,7 @@
       </c>
       <c r="K137" s="37" t="inlineStr">
         <is>
-          <t>Waning Gibbous</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L137" s="43">
@@ -74401,16 +73220,8 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D138" s="43" t="inlineStr">
-        <is>
-          <t>Waning Crescent</t>
-        </is>
-      </c>
-      <c r="E138" s="43" t="inlineStr">
-        <is>
-          <t>Cloudy</t>
-        </is>
-      </c>
+      <c r="D138" s="43"/>
+      <c r="E138" s="43"/>
       <c r="F138" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -74432,7 +73243,7 @@
       </c>
       <c r="K138" s="37" t="inlineStr">
         <is>
-          <t>Wednesday · Sunrise</t>
+          <t xml:space="preserve">Wednesday · Sunrise</t>
         </is>
       </c>
       <c r="L138" s="43">
@@ -74460,16 +73271,8 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D139" s="43" t="inlineStr">
-        <is>
-          <t>Waning Crescent</t>
-        </is>
-      </c>
-      <c r="E139" s="43" t="inlineStr">
-        <is>
-          <t>Cloudy</t>
-        </is>
-      </c>
+      <c r="D139" s="43"/>
+      <c r="E139" s="43"/>
       <c r="F139" s="43" t="inlineStr">
         <is>
           <t>Noon</t>
@@ -74491,7 +73294,7 @@
       </c>
       <c r="K139" s="37" t="inlineStr">
         <is>
-          <t>after Rain</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L139" s="43">
@@ -74519,16 +73322,8 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D140" s="43" t="inlineStr">
-        <is>
-          <t>New Moon</t>
-        </is>
-      </c>
-      <c r="E140" s="43" t="inlineStr">
-        <is>
-          <t>Rain</t>
-        </is>
-      </c>
+      <c r="D140" s="43"/>
+      <c r="E140" s="43"/>
       <c r="F140" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -74550,7 +73345,7 @@
       </c>
       <c r="K140" s="37" t="inlineStr">
         <is>
-          <t>New Moon</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L140" s="43">
@@ -74578,16 +73373,8 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D141" s="43" t="inlineStr">
-        <is>
-          <t>New Moon</t>
-        </is>
-      </c>
-      <c r="E141" s="43" t="inlineStr">
-        <is>
-          <t>Rain</t>
-        </is>
-      </c>
+      <c r="D141" s="43"/>
+      <c r="E141" s="43"/>
       <c r="F141" s="43" t="inlineStr">
         <is>
           <t>Noon</t>
@@ -74609,7 +73396,7 @@
       </c>
       <c r="K141" s="37" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t xml:space="preserve">Thursday</t>
         </is>
       </c>
       <c r="L141" s="43">
@@ -74643,12 +73430,12 @@
       </c>
       <c r="D142" s="43" t="inlineStr">
         <is>
-          <t>Full Moon</t>
+          <t xml:space="preserve">Hunter's Moon</t>
         </is>
       </c>
       <c r="E142" s="43" t="inlineStr">
         <is>
-          <t>Clear &amp; sunny</t>
+          <t xml:space="preserve">Clear starry night</t>
         </is>
       </c>
       <c r="F142" s="43" t="inlineStr">
@@ -74676,7 +73463,7 @@
       </c>
       <c r="K142" s="37" t="inlineStr">
         <is>
-          <t>Sunday · Full Moon</t>
+          <t xml:space="preserve">Sunday · Full Moon</t>
         </is>
       </c>
       <c r="L142" s="43">
@@ -74704,16 +73491,8 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="D143" s="43" t="inlineStr">
-        <is>
-          <t>Waning Gibbous</t>
-        </is>
-      </c>
-      <c r="E143" s="43" t="inlineStr">
-        <is>
-          <t>Fog / Mist</t>
-        </is>
-      </c>
+      <c r="D143" s="43"/>
+      <c r="E143" s="43"/>
       <c r="F143" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -74735,7 +73514,7 @@
       </c>
       <c r="K143" s="37" t="inlineStr">
         <is>
-          <t>Samhain · Waning Moon</t>
+          <t xml:space="preserve">Samhain</t>
         </is>
       </c>
       <c r="L143" s="43">
@@ -74763,16 +73542,8 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="D144" s="43" t="inlineStr">
-        <is>
-          <t>Waning Gibbous</t>
-        </is>
-      </c>
-      <c r="E144" s="43" t="inlineStr">
-        <is>
-          <t>Fog / Mist</t>
-        </is>
-      </c>
+      <c r="D144" s="43"/>
+      <c r="E144" s="43"/>
       <c r="F144" s="43" t="inlineStr">
         <is>
           <t>Noon</t>
@@ -74794,7 +73565,7 @@
       </c>
       <c r="K144" s="37" t="inlineStr">
         <is>
-          <t>Fog / Mist</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L144" s="43">
@@ -74826,16 +73597,8 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D145" s="43" t="inlineStr">
-        <is>
-          <t>Waning Crescent</t>
-        </is>
-      </c>
-      <c r="E145" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D145" s="43"/>
+      <c r="E145" s="43"/>
       <c r="F145" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -74857,7 +73620,7 @@
       </c>
       <c r="K145" s="37" t="inlineStr">
         <is>
-          <t>Waning Moon</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L145" s="43">
@@ -74885,16 +73648,8 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D146" s="43" t="inlineStr">
-        <is>
-          <t>Waning Crescent</t>
-        </is>
-      </c>
-      <c r="E146" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D146" s="43"/>
+      <c r="E146" s="43"/>
       <c r="F146" s="43" t="inlineStr">
         <is>
           <t>Noon</t>
@@ -74916,7 +73671,7 @@
       </c>
       <c r="K146" s="37" t="inlineStr">
         <is>
-          <t>Waning Crescent</t>
+          <t xml:space="preserve">Any time</t>
         </is>
       </c>
       <c r="L146" s="43">
@@ -74944,16 +73699,8 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D147" s="43" t="inlineStr">
-        <is>
-          <t>New Moon</t>
-        </is>
-      </c>
-      <c r="E147" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D147" s="43"/>
+      <c r="E147" s="43"/>
       <c r="F147" s="43" t="inlineStr">
         <is>
           <t>Sunrise</t>
@@ -74975,7 +73722,7 @@
       </c>
       <c r="K147" s="37" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t xml:space="preserve">Wednesday</t>
         </is>
       </c>
       <c r="L147" s="43">
@@ -75003,16 +73750,8 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D148" s="43" t="inlineStr">
-        <is>
-          <t>New Moon</t>
-        </is>
-      </c>
-      <c r="E148" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D148" s="43"/>
+      <c r="E148" s="43"/>
       <c r="F148" s="43" t="inlineStr">
         <is>
           <t>Noon</t>
@@ -75034,7 +73773,7 @@
       </c>
       <c r="K148" s="37" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t xml:space="preserve">Wednesday</t>
         </is>
       </c>
       <c r="L148" s="43">
@@ -75062,16 +73801,8 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D149" s="43" t="inlineStr">
-        <is>
-          <t>New Moon</t>
-        </is>
-      </c>
-      <c r="E149" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D149" s="43"/>
+      <c r="E149" s="43"/>
       <c r="F149" s="43" t="inlineStr">
         <is>
           <t>Twilight</t>
@@ -75093,7 +73824,7 @@
       </c>
       <c r="K149" s="37" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t xml:space="preserve">Wednesday</t>
         </is>
       </c>
       <c r="L149" s="43">
@@ -75121,16 +73852,8 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D150" s="43" t="inlineStr">
-        <is>
-          <t>New Moon</t>
-        </is>
-      </c>
-      <c r="E150" s="43" t="inlineStr">
-        <is>
-          <t>Clear &amp; sunny</t>
-        </is>
-      </c>
+      <c r="D150" s="43"/>
+      <c r="E150" s="43"/>
       <c r="F150" s="43" t="inlineStr">
         <is>
           <t>Nightfall</t>
@@ -75152,7 +73875,7 @@
       </c>
       <c r="K150" s="37" t="inlineStr">
         <is>
-          <t>Samhain</t>
+          <t xml:space="preserve">Samhain</t>
         </is>
       </c>
       <c r="L150" s="43">

--- a/ingredient_asset_tracker.xlsx
+++ b/ingredient_asset_tracker.xlsx
@@ -32984,7 +32984,7 @@
       </c>
       <c r="G22" s="22" t="inlineStr">
         <is>
-          <t>Wednesday · Twilight</t>
+          <t xml:space="preserve">Full Moon · Nightfall</t>
         </is>
       </c>
     </row>
@@ -74160,8 +74160,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="38" t="n">
-        <v>12</v>
+      <c r="A9" s="38">
+        <v>6</v>
       </c>
       <c r="B9" s="38" t="inlineStr">
         <is>
@@ -74173,11 +74173,11 @@
           <t>#21 Wayfarer's Ward</t>
         </is>
       </c>
-      <c r="D9" s="38" t="n">
+      <c r="D9" s="38">
+        <v>7</v>
+      </c>
+      <c r="E9" s="38">
         <v>6</v>
-      </c>
-      <c r="E9" s="38" t="n">
-        <v>4</v>
       </c>
       <c r="F9" s="38">
         <f>D9-E9</f>
